--- a/tanulókártyák/Tanulókártyák.xlsx
+++ b/tanulókártyák/Tanulókártyák.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atesz\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC34949-1D64-4A65-BA92-6733CCFAF3FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB57CD8-FA35-41B7-BCD1-48550486BBF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="233">
   <si>
     <r>
       <rPr>
@@ -4058,6 +4058,598 @@
   </si>
   <si>
     <t>Mit okoz a @JoinColumn annotáció használata?</t>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> JUnit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> egy népszerű Java tesztelési keretrendszer (testing framework), amelyet unit tesztek írására és futtatására használnak. Segít ellenőrizni, hogy az egyes metódusok vagy modulok megfelelően működnek-e, valamint támogatja a kódminőség fenntartását a hibák korai felismerésével.
+Támogat annotációkat, például @Test, @BeforeEach és @AfterEach
+Gyakran használják Maven/Gradle és Spring Boot projektekben</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a Junit?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>unit tesztelés</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> azért fontos, mert segít biztosítani, hogy az alkalmazás egyes kisebb részei (például egy metódus vagy osztály) helyesen működjenek, még mielőtt más komponensekkel integrálnánk őket. Csökkenti a hibák számát, javítja a kód minőségét, és biztonságosabbá teszi a későbbi módosításokat.
+Segít a hibák korai felismerésében a fejlesztés során.
+Könnyebbé teszi a kód karbantartását és refaktorálását.
+Növeli a magabiztosságot a deployment előtt.</t>
+    </r>
+  </si>
+  <si>
+    <t>Miért fontos a unit tesztelés?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@Test</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> annotáció arra szolgál, hogy egy metódust tesztesetként jelöljünk meg a JUnit-ban. Amikor a tesztkészlet fut, a JUnit automatikusan felismeri és végrehajtja az összes @Test annotációval ellátott metódust, hogy ellenőrizze a kód elvárt működését.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mire szolgál a @Test annotáció?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Az </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>assertion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-ök a JUnit-ban arra szolgálnak, hogy ellenőrizzék, a tényleges eredmény megegyezik-e a várt eredménnyel egy tesztesetben. Ha egy assertion sikertelen, a JUnit a tesztet hibásnak (FAILED) jelöli, így a fejlesztők gyorsan azonosíthatják a problémákat.
+Gyakori metódusok: assertEquals(), assertTrue(), assertFalse(), assertNotNull(), assertThrows()</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi az assertion?</t>
+  </si>
+  <si>
+    <t>Mit csinál a @BeforeEach annotáció?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A JUnit 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@BeforeEach</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> annotáció arra szolgál, hogy egy metódust minden teszt-eset előtt lefuttasson egy tesztosztályban. Főként közös tesztadatok előkészítésére vagy objektumok inicializálására használják, így minden teszt friss, tiszta állapotból indul.
+Minden @Test metódus előtt lefut.
+Felkészíti a tesztkörnyezetet (pl. objektumok inicializálása, adatok beállítása).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Test-Driven Development </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(TDD) egy szoftverfejlesztési módszertan, ahol a fejlesztő először a teszteseteket írja meg, és csak ezután írja meg a tényleges kódot. A cél, hogy kis lépésekben fejlesszünk: először a teszt elbukik, majd olyan kódot írunk, ami átmegy a teszten, végül pedig a kódot refaktoráljuk.
+Javítja a kód minőségét és csökkenti a hibák számát
+Segít tiszta, jól tesztelhető kódot tervezni
+Strukturáltabbá és megbízhatóbbá teszi a fejlesztést</t>
+    </r>
+  </si>
+  <si>
+    <t>Mit jelent a TDD?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Red–Green–Refactor </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ciklus a TDD (Test-Driven Development) alap folyamata:
+Red: írunk egy tesztet, ami először elbukik
+Green: megírjuk a minimális kódot, ami átmegy a teszten
+Refactor: átalakítjuk és tisztítjuk a kódot úgy, hogy a teszt továbbra is sikeres maradjon</t>
+    </r>
+  </si>
+  <si>
+    <t>Mit jelent a Red-Green-Refactor kifejezés?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Git</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> egy elosztott verziókezelő rendszer (distributed version control system), amelyet a forráskódban történt változások követésére használnak szoftverfejlesztés során. Lehetővé teszi, hogy több fejlesztő egyszerre dolgozzon egy projekten anélkül, hogy zavarnák egymás módosításait. A Git különösen népszerű a gyorsasága miatt és azért, mert hatékonyan kezeli mind a kis, mind a nagy projekteket.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a Git?</t>
+  </si>
+  <si>
+    <t>Mi a Git repository?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Git repository</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (repo) egy olyan struktúra, amely egy projekt összes fájlját és azok teljes változástörténetét (commit history) tárolja. Segítségével nyomon követhetők a módosítások, és lehetővé teszi a csapatok számára az együttműködést.
+A Git kezelhet:
+lokális repositoryt (a saját gépeden)
+remote repositoryt (pl. GitHub, GitLab, Bitbucket szervereken)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>commit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a Git-ben egy pillanatkép (snapshot) a repository fájljain végrehajtott változtatásokról. Rögzíti az adott időpontban történt módosításokat, például fájlok hozzáadását vagy törlését. Minden commit tartalmaz egy egyedi üzenetet is, amely leírja, mi változott. Ez segít nyomon követni a projekt történetét, visszavonni módosításokat, és együtt dolgozni más fejlesztőkkel.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a commit?</t>
+  </si>
+  <si>
+    <t>Mit csinál a git add parancs?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>git</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> parancs előkészíti a módosításokat a következő commit számára. Megmondja a Gitnek, hogy mely fájlok változásait szeretnénk belefoglalni a következő mentésbe (commitba), így azok bekerülnek a staging area-ba. Ez a verziókövetés első lépése a változtatások rögzítésében.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>git</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>push</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> parancs arra szolgál, hogy a helyi repository-ban lévő változtatásokat feltöltsük egy távoli repository-ba. A legfrissebb commitokat továbbítja a kiválasztott helyi branch-ről a remote repository megfelelő branchére, így az ott is frissül.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mit csinál a git push parancs?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>git clone</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> parancs egy távoli repository teljes másolatát hozza létre a helyi gépen. Letölti az összes fájlt, branch-et és a teljes verziótörténetet, így lehetővé teszi a projektben való azonnali munkát vagy hozzájárulást.
+A git clone -b opcióval egy adott branch-et is ki lehet választani, így közvetlenül azon a branche-en lehet dolgozni.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mit csinál a git clone parancs?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A Git használata több előnnyel jár:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Segíti a csapatmunkát, mivel több fejlesztő is dolgozhat ugyanazon a projekten egyszerre.
+Minden fejlesztő rendelkezik egy helyi repository-val, ami gyorsabb működést és offline munkát is lehetővé tesz.
+Ingyenes és széles körben támogatott.
+Különböző típusú projektekhez is használható.
+Minden repository csak egy Git könyvtárral rendelkezik (a verziókövetési adatok tárolására).</t>
+    </r>
+  </si>
+  <si>
+    <t>Mik a Git használatának előnyei?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Git conflict:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+A Git általában automatikusan kezeli az összeolvasztásokat (merge), de konfliktusok akkor keletkeznek, ha két branch ugyanazt a sort módosítja, vagy ha az egyik branch töröl egy fájlt, miközben a másik módosítja azt.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a conflict, mikor alakul ki?</t>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Gitben a branch-ek közötti váltáshoz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a git checkout &lt;branch&gt; parancsot használjuk egy meglévő branch-re való átlépéshez. Az újabb Git verziókban erre a célra a git switch parancs is használható. Ez lehetővé teszi, hogy a projekt különböző verzióin vagy funkcióin külön branch-eken dolgozzunk.</t>
+    </r>
+  </si>
+  <si>
+    <t>Hogyan vátunk branch-et a git-ben?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Git repo inicializálás:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Töltsd le a Git-et a rendszeredre, ha még nincs telepítve.
+Hozz létre egy projektmappát azon a helyen, ahol a repository-t szeretnéd.
+Nyisd meg a Terminált vagy a Parancssort, és navigálj a projektmappába.
+Futtasd a git init parancsot a projektmappában. Ez létrehoz egy .git mappát, ami jelzi, hogy a repository inicializálva lett.</t>
+    </r>
+  </si>
+  <si>
+    <t>Hogyan inicializálunk egy git repository-t?</t>
   </si>
 </sst>
 </file>
@@ -4450,13 +5042,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CB151"/>
+  <dimension ref="A1:CR151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="80" width="11" customWidth="1"/>
+    <col min="1" max="96" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -4577,8 +5169,32 @@
       <c r="BZ1" s="8"/>
       <c r="CA1" s="8"/>
       <c r="CB1" s="8"/>
+      <c r="CC1" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="CD1" s="8"/>
+      <c r="CE1" s="8"/>
+      <c r="CF1" s="8"/>
+      <c r="CG1" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="CH1" s="8"/>
+      <c r="CI1" s="8"/>
+      <c r="CJ1" s="8"/>
+      <c r="CK1" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="CL1" s="8"/>
+      <c r="CM1" s="8"/>
+      <c r="CN1" s="8"/>
+      <c r="CO1" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="CP1" s="8"/>
+      <c r="CQ1" s="8"/>
+      <c r="CR1" s="8"/>
     </row>
-    <row r="2" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4659,8 +5275,24 @@
       <c r="BZ2" s="8"/>
       <c r="CA2" s="8"/>
       <c r="CB2" s="8"/>
+      <c r="CC2" s="8"/>
+      <c r="CD2" s="8"/>
+      <c r="CE2" s="8"/>
+      <c r="CF2" s="8"/>
+      <c r="CG2" s="8"/>
+      <c r="CH2" s="8"/>
+      <c r="CI2" s="8"/>
+      <c r="CJ2" s="8"/>
+      <c r="CK2" s="8"/>
+      <c r="CL2" s="8"/>
+      <c r="CM2" s="8"/>
+      <c r="CN2" s="8"/>
+      <c r="CO2" s="8"/>
+      <c r="CP2" s="8"/>
+      <c r="CQ2" s="8"/>
+      <c r="CR2" s="8"/>
     </row>
-    <row r="3" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -4741,8 +5373,24 @@
       <c r="BZ3" s="8"/>
       <c r="CA3" s="8"/>
       <c r="CB3" s="8"/>
+      <c r="CC3" s="8"/>
+      <c r="CD3" s="8"/>
+      <c r="CE3" s="8"/>
+      <c r="CF3" s="8"/>
+      <c r="CG3" s="8"/>
+      <c r="CH3" s="8"/>
+      <c r="CI3" s="8"/>
+      <c r="CJ3" s="8"/>
+      <c r="CK3" s="8"/>
+      <c r="CL3" s="8"/>
+      <c r="CM3" s="8"/>
+      <c r="CN3" s="8"/>
+      <c r="CO3" s="8"/>
+      <c r="CP3" s="8"/>
+      <c r="CQ3" s="8"/>
+      <c r="CR3" s="8"/>
     </row>
-    <row r="4" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -4823,8 +5471,24 @@
       <c r="BZ4" s="8"/>
       <c r="CA4" s="8"/>
       <c r="CB4" s="8"/>
+      <c r="CC4" s="8"/>
+      <c r="CD4" s="8"/>
+      <c r="CE4" s="8"/>
+      <c r="CF4" s="8"/>
+      <c r="CG4" s="8"/>
+      <c r="CH4" s="8"/>
+      <c r="CI4" s="8"/>
+      <c r="CJ4" s="8"/>
+      <c r="CK4" s="8"/>
+      <c r="CL4" s="8"/>
+      <c r="CM4" s="8"/>
+      <c r="CN4" s="8"/>
+      <c r="CO4" s="8"/>
+      <c r="CP4" s="8"/>
+      <c r="CQ4" s="8"/>
+      <c r="CR4" s="8"/>
     </row>
-    <row r="5" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -4905,8 +5569,24 @@
       <c r="BZ5" s="8"/>
       <c r="CA5" s="8"/>
       <c r="CB5" s="8"/>
+      <c r="CC5" s="8"/>
+      <c r="CD5" s="8"/>
+      <c r="CE5" s="8"/>
+      <c r="CF5" s="8"/>
+      <c r="CG5" s="8"/>
+      <c r="CH5" s="8"/>
+      <c r="CI5" s="8"/>
+      <c r="CJ5" s="8"/>
+      <c r="CK5" s="8"/>
+      <c r="CL5" s="8"/>
+      <c r="CM5" s="8"/>
+      <c r="CN5" s="8"/>
+      <c r="CO5" s="8"/>
+      <c r="CP5" s="8"/>
+      <c r="CQ5" s="8"/>
+      <c r="CR5" s="8"/>
     </row>
-    <row r="6" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -4987,8 +5667,24 @@
       <c r="BZ6" s="8"/>
       <c r="CA6" s="8"/>
       <c r="CB6" s="8"/>
+      <c r="CC6" s="8"/>
+      <c r="CD6" s="8"/>
+      <c r="CE6" s="8"/>
+      <c r="CF6" s="8"/>
+      <c r="CG6" s="8"/>
+      <c r="CH6" s="8"/>
+      <c r="CI6" s="8"/>
+      <c r="CJ6" s="8"/>
+      <c r="CK6" s="8"/>
+      <c r="CL6" s="8"/>
+      <c r="CM6" s="8"/>
+      <c r="CN6" s="8"/>
+      <c r="CO6" s="8"/>
+      <c r="CP6" s="8"/>
+      <c r="CQ6" s="8"/>
+      <c r="CR6" s="8"/>
     </row>
-    <row r="7" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -5069,8 +5765,24 @@
       <c r="BZ7" s="8"/>
       <c r="CA7" s="8"/>
       <c r="CB7" s="8"/>
+      <c r="CC7" s="8"/>
+      <c r="CD7" s="8"/>
+      <c r="CE7" s="8"/>
+      <c r="CF7" s="8"/>
+      <c r="CG7" s="8"/>
+      <c r="CH7" s="8"/>
+      <c r="CI7" s="8"/>
+      <c r="CJ7" s="8"/>
+      <c r="CK7" s="8"/>
+      <c r="CL7" s="8"/>
+      <c r="CM7" s="8"/>
+      <c r="CN7" s="8"/>
+      <c r="CO7" s="8"/>
+      <c r="CP7" s="8"/>
+      <c r="CQ7" s="8"/>
+      <c r="CR7" s="8"/>
     </row>
-    <row r="8" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -5151,8 +5863,24 @@
       <c r="BZ8" s="8"/>
       <c r="CA8" s="8"/>
       <c r="CB8" s="8"/>
+      <c r="CC8" s="8"/>
+      <c r="CD8" s="8"/>
+      <c r="CE8" s="8"/>
+      <c r="CF8" s="8"/>
+      <c r="CG8" s="8"/>
+      <c r="CH8" s="8"/>
+      <c r="CI8" s="8"/>
+      <c r="CJ8" s="8"/>
+      <c r="CK8" s="8"/>
+      <c r="CL8" s="8"/>
+      <c r="CM8" s="8"/>
+      <c r="CN8" s="8"/>
+      <c r="CO8" s="8"/>
+      <c r="CP8" s="8"/>
+      <c r="CQ8" s="8"/>
+      <c r="CR8" s="8"/>
     </row>
-    <row r="9" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -5233,8 +5961,24 @@
       <c r="BZ9" s="8"/>
       <c r="CA9" s="8"/>
       <c r="CB9" s="8"/>
+      <c r="CC9" s="8"/>
+      <c r="CD9" s="8"/>
+      <c r="CE9" s="8"/>
+      <c r="CF9" s="8"/>
+      <c r="CG9" s="8"/>
+      <c r="CH9" s="8"/>
+      <c r="CI9" s="8"/>
+      <c r="CJ9" s="8"/>
+      <c r="CK9" s="8"/>
+      <c r="CL9" s="8"/>
+      <c r="CM9" s="8"/>
+      <c r="CN9" s="8"/>
+      <c r="CO9" s="8"/>
+      <c r="CP9" s="8"/>
+      <c r="CQ9" s="8"/>
+      <c r="CR9" s="8"/>
     </row>
-    <row r="10" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -5315,8 +6059,24 @@
       <c r="BZ10" s="8"/>
       <c r="CA10" s="8"/>
       <c r="CB10" s="8"/>
+      <c r="CC10" s="8"/>
+      <c r="CD10" s="8"/>
+      <c r="CE10" s="8"/>
+      <c r="CF10" s="8"/>
+      <c r="CG10" s="8"/>
+      <c r="CH10" s="8"/>
+      <c r="CI10" s="8"/>
+      <c r="CJ10" s="8"/>
+      <c r="CK10" s="8"/>
+      <c r="CL10" s="8"/>
+      <c r="CM10" s="8"/>
+      <c r="CN10" s="8"/>
+      <c r="CO10" s="8"/>
+      <c r="CP10" s="8"/>
+      <c r="CQ10" s="8"/>
+      <c r="CR10" s="8"/>
     </row>
-    <row r="11" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>2</v>
       </c>
@@ -5437,8 +6197,32 @@
       <c r="BZ11" s="8"/>
       <c r="CA11" s="8"/>
       <c r="CB11" s="8"/>
+      <c r="CC11" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="CD11" s="8"/>
+      <c r="CE11" s="8"/>
+      <c r="CF11" s="8"/>
+      <c r="CG11" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="CH11" s="8"/>
+      <c r="CI11" s="8"/>
+      <c r="CJ11" s="8"/>
+      <c r="CK11" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="CL11" s="8"/>
+      <c r="CM11" s="8"/>
+      <c r="CN11" s="8"/>
+      <c r="CO11" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="CP11" s="8"/>
+      <c r="CQ11" s="8"/>
+      <c r="CR11" s="8"/>
     </row>
-    <row r="12" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -5519,8 +6303,24 @@
       <c r="BZ12" s="8"/>
       <c r="CA12" s="8"/>
       <c r="CB12" s="8"/>
+      <c r="CC12" s="8"/>
+      <c r="CD12" s="8"/>
+      <c r="CE12" s="8"/>
+      <c r="CF12" s="8"/>
+      <c r="CG12" s="8"/>
+      <c r="CH12" s="8"/>
+      <c r="CI12" s="8"/>
+      <c r="CJ12" s="8"/>
+      <c r="CK12" s="8"/>
+      <c r="CL12" s="8"/>
+      <c r="CM12" s="8"/>
+      <c r="CN12" s="8"/>
+      <c r="CO12" s="8"/>
+      <c r="CP12" s="8"/>
+      <c r="CQ12" s="8"/>
+      <c r="CR12" s="8"/>
     </row>
-    <row r="13" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -5601,8 +6401,24 @@
       <c r="BZ13" s="8"/>
       <c r="CA13" s="8"/>
       <c r="CB13" s="8"/>
+      <c r="CC13" s="8"/>
+      <c r="CD13" s="8"/>
+      <c r="CE13" s="8"/>
+      <c r="CF13" s="8"/>
+      <c r="CG13" s="8"/>
+      <c r="CH13" s="8"/>
+      <c r="CI13" s="8"/>
+      <c r="CJ13" s="8"/>
+      <c r="CK13" s="8"/>
+      <c r="CL13" s="8"/>
+      <c r="CM13" s="8"/>
+      <c r="CN13" s="8"/>
+      <c r="CO13" s="8"/>
+      <c r="CP13" s="8"/>
+      <c r="CQ13" s="8"/>
+      <c r="CR13" s="8"/>
     </row>
-    <row r="14" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -5683,8 +6499,24 @@
       <c r="BZ14" s="8"/>
       <c r="CA14" s="8"/>
       <c r="CB14" s="8"/>
+      <c r="CC14" s="8"/>
+      <c r="CD14" s="8"/>
+      <c r="CE14" s="8"/>
+      <c r="CF14" s="8"/>
+      <c r="CG14" s="8"/>
+      <c r="CH14" s="8"/>
+      <c r="CI14" s="8"/>
+      <c r="CJ14" s="8"/>
+      <c r="CK14" s="8"/>
+      <c r="CL14" s="8"/>
+      <c r="CM14" s="8"/>
+      <c r="CN14" s="8"/>
+      <c r="CO14" s="8"/>
+      <c r="CP14" s="8"/>
+      <c r="CQ14" s="8"/>
+      <c r="CR14" s="8"/>
     </row>
-    <row r="15" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -5765,8 +6597,24 @@
       <c r="BZ15" s="8"/>
       <c r="CA15" s="8"/>
       <c r="CB15" s="8"/>
+      <c r="CC15" s="8"/>
+      <c r="CD15" s="8"/>
+      <c r="CE15" s="8"/>
+      <c r="CF15" s="8"/>
+      <c r="CG15" s="8"/>
+      <c r="CH15" s="8"/>
+      <c r="CI15" s="8"/>
+      <c r="CJ15" s="8"/>
+      <c r="CK15" s="8"/>
+      <c r="CL15" s="8"/>
+      <c r="CM15" s="8"/>
+      <c r="CN15" s="8"/>
+      <c r="CO15" s="8"/>
+      <c r="CP15" s="8"/>
+      <c r="CQ15" s="8"/>
+      <c r="CR15" s="8"/>
     </row>
-    <row r="16" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -5847,8 +6695,24 @@
       <c r="BZ16" s="8"/>
       <c r="CA16" s="8"/>
       <c r="CB16" s="8"/>
+      <c r="CC16" s="8"/>
+      <c r="CD16" s="8"/>
+      <c r="CE16" s="8"/>
+      <c r="CF16" s="8"/>
+      <c r="CG16" s="8"/>
+      <c r="CH16" s="8"/>
+      <c r="CI16" s="8"/>
+      <c r="CJ16" s="8"/>
+      <c r="CK16" s="8"/>
+      <c r="CL16" s="8"/>
+      <c r="CM16" s="8"/>
+      <c r="CN16" s="8"/>
+      <c r="CO16" s="8"/>
+      <c r="CP16" s="8"/>
+      <c r="CQ16" s="8"/>
+      <c r="CR16" s="8"/>
     </row>
-    <row r="17" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -5929,8 +6793,24 @@
       <c r="BZ17" s="8"/>
       <c r="CA17" s="8"/>
       <c r="CB17" s="8"/>
+      <c r="CC17" s="8"/>
+      <c r="CD17" s="8"/>
+      <c r="CE17" s="8"/>
+      <c r="CF17" s="8"/>
+      <c r="CG17" s="8"/>
+      <c r="CH17" s="8"/>
+      <c r="CI17" s="8"/>
+      <c r="CJ17" s="8"/>
+      <c r="CK17" s="8"/>
+      <c r="CL17" s="8"/>
+      <c r="CM17" s="8"/>
+      <c r="CN17" s="8"/>
+      <c r="CO17" s="8"/>
+      <c r="CP17" s="8"/>
+      <c r="CQ17" s="8"/>
+      <c r="CR17" s="8"/>
     </row>
-    <row r="18" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -6011,8 +6891,24 @@
       <c r="BZ18" s="8"/>
       <c r="CA18" s="8"/>
       <c r="CB18" s="8"/>
+      <c r="CC18" s="8"/>
+      <c r="CD18" s="8"/>
+      <c r="CE18" s="8"/>
+      <c r="CF18" s="8"/>
+      <c r="CG18" s="8"/>
+      <c r="CH18" s="8"/>
+      <c r="CI18" s="8"/>
+      <c r="CJ18" s="8"/>
+      <c r="CK18" s="8"/>
+      <c r="CL18" s="8"/>
+      <c r="CM18" s="8"/>
+      <c r="CN18" s="8"/>
+      <c r="CO18" s="8"/>
+      <c r="CP18" s="8"/>
+      <c r="CQ18" s="8"/>
+      <c r="CR18" s="8"/>
     </row>
-    <row r="19" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -6093,8 +6989,24 @@
       <c r="BZ19" s="8"/>
       <c r="CA19" s="8"/>
       <c r="CB19" s="8"/>
+      <c r="CC19" s="8"/>
+      <c r="CD19" s="8"/>
+      <c r="CE19" s="8"/>
+      <c r="CF19" s="8"/>
+      <c r="CG19" s="8"/>
+      <c r="CH19" s="8"/>
+      <c r="CI19" s="8"/>
+      <c r="CJ19" s="8"/>
+      <c r="CK19" s="8"/>
+      <c r="CL19" s="8"/>
+      <c r="CM19" s="8"/>
+      <c r="CN19" s="8"/>
+      <c r="CO19" s="8"/>
+      <c r="CP19" s="8"/>
+      <c r="CQ19" s="8"/>
+      <c r="CR19" s="8"/>
     </row>
-    <row r="20" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -6175,8 +7087,24 @@
       <c r="BZ20" s="8"/>
       <c r="CA20" s="8"/>
       <c r="CB20" s="8"/>
+      <c r="CC20" s="8"/>
+      <c r="CD20" s="8"/>
+      <c r="CE20" s="8"/>
+      <c r="CF20" s="8"/>
+      <c r="CG20" s="8"/>
+      <c r="CH20" s="8"/>
+      <c r="CI20" s="8"/>
+      <c r="CJ20" s="8"/>
+      <c r="CK20" s="8"/>
+      <c r="CL20" s="8"/>
+      <c r="CM20" s="8"/>
+      <c r="CN20" s="8"/>
+      <c r="CO20" s="8"/>
+      <c r="CP20" s="8"/>
+      <c r="CQ20" s="8"/>
+      <c r="CR20" s="8"/>
     </row>
-    <row r="21" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>4</v>
       </c>
@@ -6297,8 +7225,32 @@
       <c r="BZ21" s="8"/>
       <c r="CA21" s="8"/>
       <c r="CB21" s="8"/>
+      <c r="CC21" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="CD21" s="8"/>
+      <c r="CE21" s="8"/>
+      <c r="CF21" s="8"/>
+      <c r="CG21" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="CH21" s="8"/>
+      <c r="CI21" s="8"/>
+      <c r="CJ21" s="8"/>
+      <c r="CK21" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="CL21" s="8"/>
+      <c r="CM21" s="8"/>
+      <c r="CN21" s="8"/>
+      <c r="CO21" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="CP21" s="8"/>
+      <c r="CQ21" s="8"/>
+      <c r="CR21" s="8"/>
     </row>
-    <row r="22" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -6379,8 +7331,24 @@
       <c r="BZ22" s="8"/>
       <c r="CA22" s="8"/>
       <c r="CB22" s="8"/>
+      <c r="CC22" s="8"/>
+      <c r="CD22" s="8"/>
+      <c r="CE22" s="8"/>
+      <c r="CF22" s="8"/>
+      <c r="CG22" s="8"/>
+      <c r="CH22" s="8"/>
+      <c r="CI22" s="8"/>
+      <c r="CJ22" s="8"/>
+      <c r="CK22" s="8"/>
+      <c r="CL22" s="8"/>
+      <c r="CM22" s="8"/>
+      <c r="CN22" s="8"/>
+      <c r="CO22" s="8"/>
+      <c r="CP22" s="8"/>
+      <c r="CQ22" s="8"/>
+      <c r="CR22" s="8"/>
     </row>
-    <row r="23" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -6461,8 +7429,24 @@
       <c r="BZ23" s="8"/>
       <c r="CA23" s="8"/>
       <c r="CB23" s="8"/>
+      <c r="CC23" s="8"/>
+      <c r="CD23" s="8"/>
+      <c r="CE23" s="8"/>
+      <c r="CF23" s="8"/>
+      <c r="CG23" s="8"/>
+      <c r="CH23" s="8"/>
+      <c r="CI23" s="8"/>
+      <c r="CJ23" s="8"/>
+      <c r="CK23" s="8"/>
+      <c r="CL23" s="8"/>
+      <c r="CM23" s="8"/>
+      <c r="CN23" s="8"/>
+      <c r="CO23" s="8"/>
+      <c r="CP23" s="8"/>
+      <c r="CQ23" s="8"/>
+      <c r="CR23" s="8"/>
     </row>
-    <row r="24" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -6543,8 +7527,24 @@
       <c r="BZ24" s="8"/>
       <c r="CA24" s="8"/>
       <c r="CB24" s="8"/>
+      <c r="CC24" s="8"/>
+      <c r="CD24" s="8"/>
+      <c r="CE24" s="8"/>
+      <c r="CF24" s="8"/>
+      <c r="CG24" s="8"/>
+      <c r="CH24" s="8"/>
+      <c r="CI24" s="8"/>
+      <c r="CJ24" s="8"/>
+      <c r="CK24" s="8"/>
+      <c r="CL24" s="8"/>
+      <c r="CM24" s="8"/>
+      <c r="CN24" s="8"/>
+      <c r="CO24" s="8"/>
+      <c r="CP24" s="8"/>
+      <c r="CQ24" s="8"/>
+      <c r="CR24" s="8"/>
     </row>
-    <row r="25" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -6625,8 +7625,24 @@
       <c r="BZ25" s="8"/>
       <c r="CA25" s="8"/>
       <c r="CB25" s="8"/>
+      <c r="CC25" s="8"/>
+      <c r="CD25" s="8"/>
+      <c r="CE25" s="8"/>
+      <c r="CF25" s="8"/>
+      <c r="CG25" s="8"/>
+      <c r="CH25" s="8"/>
+      <c r="CI25" s="8"/>
+      <c r="CJ25" s="8"/>
+      <c r="CK25" s="8"/>
+      <c r="CL25" s="8"/>
+      <c r="CM25" s="8"/>
+      <c r="CN25" s="8"/>
+      <c r="CO25" s="8"/>
+      <c r="CP25" s="8"/>
+      <c r="CQ25" s="8"/>
+      <c r="CR25" s="8"/>
     </row>
-    <row r="26" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -6707,8 +7723,24 @@
       <c r="BZ26" s="8"/>
       <c r="CA26" s="8"/>
       <c r="CB26" s="8"/>
+      <c r="CC26" s="8"/>
+      <c r="CD26" s="8"/>
+      <c r="CE26" s="8"/>
+      <c r="CF26" s="8"/>
+      <c r="CG26" s="8"/>
+      <c r="CH26" s="8"/>
+      <c r="CI26" s="8"/>
+      <c r="CJ26" s="8"/>
+      <c r="CK26" s="8"/>
+      <c r="CL26" s="8"/>
+      <c r="CM26" s="8"/>
+      <c r="CN26" s="8"/>
+      <c r="CO26" s="8"/>
+      <c r="CP26" s="8"/>
+      <c r="CQ26" s="8"/>
+      <c r="CR26" s="8"/>
     </row>
-    <row r="27" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -6789,8 +7821,24 @@
       <c r="BZ27" s="8"/>
       <c r="CA27" s="8"/>
       <c r="CB27" s="8"/>
+      <c r="CC27" s="8"/>
+      <c r="CD27" s="8"/>
+      <c r="CE27" s="8"/>
+      <c r="CF27" s="8"/>
+      <c r="CG27" s="8"/>
+      <c r="CH27" s="8"/>
+      <c r="CI27" s="8"/>
+      <c r="CJ27" s="8"/>
+      <c r="CK27" s="8"/>
+      <c r="CL27" s="8"/>
+      <c r="CM27" s="8"/>
+      <c r="CN27" s="8"/>
+      <c r="CO27" s="8"/>
+      <c r="CP27" s="8"/>
+      <c r="CQ27" s="8"/>
+      <c r="CR27" s="8"/>
     </row>
-    <row r="28" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -6871,8 +7919,24 @@
       <c r="BZ28" s="8"/>
       <c r="CA28" s="8"/>
       <c r="CB28" s="8"/>
+      <c r="CC28" s="8"/>
+      <c r="CD28" s="8"/>
+      <c r="CE28" s="8"/>
+      <c r="CF28" s="8"/>
+      <c r="CG28" s="8"/>
+      <c r="CH28" s="8"/>
+      <c r="CI28" s="8"/>
+      <c r="CJ28" s="8"/>
+      <c r="CK28" s="8"/>
+      <c r="CL28" s="8"/>
+      <c r="CM28" s="8"/>
+      <c r="CN28" s="8"/>
+      <c r="CO28" s="8"/>
+      <c r="CP28" s="8"/>
+      <c r="CQ28" s="8"/>
+      <c r="CR28" s="8"/>
     </row>
-    <row r="29" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -6953,8 +8017,24 @@
       <c r="BZ29" s="8"/>
       <c r="CA29" s="8"/>
       <c r="CB29" s="8"/>
+      <c r="CC29" s="8"/>
+      <c r="CD29" s="8"/>
+      <c r="CE29" s="8"/>
+      <c r="CF29" s="8"/>
+      <c r="CG29" s="8"/>
+      <c r="CH29" s="8"/>
+      <c r="CI29" s="8"/>
+      <c r="CJ29" s="8"/>
+      <c r="CK29" s="8"/>
+      <c r="CL29" s="8"/>
+      <c r="CM29" s="8"/>
+      <c r="CN29" s="8"/>
+      <c r="CO29" s="8"/>
+      <c r="CP29" s="8"/>
+      <c r="CQ29" s="8"/>
+      <c r="CR29" s="8"/>
     </row>
-    <row r="30" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -7035,8 +8115,24 @@
       <c r="BZ30" s="8"/>
       <c r="CA30" s="8"/>
       <c r="CB30" s="8"/>
+      <c r="CC30" s="8"/>
+      <c r="CD30" s="8"/>
+      <c r="CE30" s="8"/>
+      <c r="CF30" s="8"/>
+      <c r="CG30" s="8"/>
+      <c r="CH30" s="8"/>
+      <c r="CI30" s="8"/>
+      <c r="CJ30" s="8"/>
+      <c r="CK30" s="8"/>
+      <c r="CL30" s="8"/>
+      <c r="CM30" s="8"/>
+      <c r="CN30" s="8"/>
+      <c r="CO30" s="8"/>
+      <c r="CP30" s="8"/>
+      <c r="CQ30" s="8"/>
+      <c r="CR30" s="8"/>
     </row>
-    <row r="31" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>13</v>
       </c>
@@ -7157,8 +8253,30 @@
       <c r="BZ31" s="8"/>
       <c r="CA31" s="8"/>
       <c r="CB31" s="8"/>
+      <c r="CC31" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="CD31" s="8"/>
+      <c r="CE31" s="8"/>
+      <c r="CF31" s="8"/>
+      <c r="CG31" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="CH31" s="8"/>
+      <c r="CI31" s="8"/>
+      <c r="CJ31" s="8"/>
+      <c r="CK31" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="CL31" s="8"/>
+      <c r="CM31" s="8"/>
+      <c r="CN31" s="8"/>
+      <c r="CO31" s="7"/>
+      <c r="CP31" s="8"/>
+      <c r="CQ31" s="8"/>
+      <c r="CR31" s="8"/>
     </row>
-    <row r="32" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -7239,8 +8357,24 @@
       <c r="BZ32" s="8"/>
       <c r="CA32" s="8"/>
       <c r="CB32" s="8"/>
+      <c r="CC32" s="8"/>
+      <c r="CD32" s="8"/>
+      <c r="CE32" s="8"/>
+      <c r="CF32" s="8"/>
+      <c r="CG32" s="8"/>
+      <c r="CH32" s="8"/>
+      <c r="CI32" s="8"/>
+      <c r="CJ32" s="8"/>
+      <c r="CK32" s="8"/>
+      <c r="CL32" s="8"/>
+      <c r="CM32" s="8"/>
+      <c r="CN32" s="8"/>
+      <c r="CO32" s="8"/>
+      <c r="CP32" s="8"/>
+      <c r="CQ32" s="8"/>
+      <c r="CR32" s="8"/>
     </row>
-    <row r="33" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -7321,8 +8455,24 @@
       <c r="BZ33" s="8"/>
       <c r="CA33" s="8"/>
       <c r="CB33" s="8"/>
+      <c r="CC33" s="8"/>
+      <c r="CD33" s="8"/>
+      <c r="CE33" s="8"/>
+      <c r="CF33" s="8"/>
+      <c r="CG33" s="8"/>
+      <c r="CH33" s="8"/>
+      <c r="CI33" s="8"/>
+      <c r="CJ33" s="8"/>
+      <c r="CK33" s="8"/>
+      <c r="CL33" s="8"/>
+      <c r="CM33" s="8"/>
+      <c r="CN33" s="8"/>
+      <c r="CO33" s="8"/>
+      <c r="CP33" s="8"/>
+      <c r="CQ33" s="8"/>
+      <c r="CR33" s="8"/>
     </row>
-    <row r="34" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -7403,8 +8553,24 @@
       <c r="BZ34" s="8"/>
       <c r="CA34" s="8"/>
       <c r="CB34" s="8"/>
+      <c r="CC34" s="8"/>
+      <c r="CD34" s="8"/>
+      <c r="CE34" s="8"/>
+      <c r="CF34" s="8"/>
+      <c r="CG34" s="8"/>
+      <c r="CH34" s="8"/>
+      <c r="CI34" s="8"/>
+      <c r="CJ34" s="8"/>
+      <c r="CK34" s="8"/>
+      <c r="CL34" s="8"/>
+      <c r="CM34" s="8"/>
+      <c r="CN34" s="8"/>
+      <c r="CO34" s="8"/>
+      <c r="CP34" s="8"/>
+      <c r="CQ34" s="8"/>
+      <c r="CR34" s="8"/>
     </row>
-    <row r="35" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -7485,8 +8651,24 @@
       <c r="BZ35" s="8"/>
       <c r="CA35" s="8"/>
       <c r="CB35" s="8"/>
+      <c r="CC35" s="8"/>
+      <c r="CD35" s="8"/>
+      <c r="CE35" s="8"/>
+      <c r="CF35" s="8"/>
+      <c r="CG35" s="8"/>
+      <c r="CH35" s="8"/>
+      <c r="CI35" s="8"/>
+      <c r="CJ35" s="8"/>
+      <c r="CK35" s="8"/>
+      <c r="CL35" s="8"/>
+      <c r="CM35" s="8"/>
+      <c r="CN35" s="8"/>
+      <c r="CO35" s="8"/>
+      <c r="CP35" s="8"/>
+      <c r="CQ35" s="8"/>
+      <c r="CR35" s="8"/>
     </row>
-    <row r="36" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -7567,8 +8749,24 @@
       <c r="BZ36" s="8"/>
       <c r="CA36" s="8"/>
       <c r="CB36" s="8"/>
+      <c r="CC36" s="8"/>
+      <c r="CD36" s="8"/>
+      <c r="CE36" s="8"/>
+      <c r="CF36" s="8"/>
+      <c r="CG36" s="8"/>
+      <c r="CH36" s="8"/>
+      <c r="CI36" s="8"/>
+      <c r="CJ36" s="8"/>
+      <c r="CK36" s="8"/>
+      <c r="CL36" s="8"/>
+      <c r="CM36" s="8"/>
+      <c r="CN36" s="8"/>
+      <c r="CO36" s="8"/>
+      <c r="CP36" s="8"/>
+      <c r="CQ36" s="8"/>
+      <c r="CR36" s="8"/>
     </row>
-    <row r="37" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -7649,8 +8847,24 @@
       <c r="BZ37" s="8"/>
       <c r="CA37" s="8"/>
       <c r="CB37" s="8"/>
+      <c r="CC37" s="8"/>
+      <c r="CD37" s="8"/>
+      <c r="CE37" s="8"/>
+      <c r="CF37" s="8"/>
+      <c r="CG37" s="8"/>
+      <c r="CH37" s="8"/>
+      <c r="CI37" s="8"/>
+      <c r="CJ37" s="8"/>
+      <c r="CK37" s="8"/>
+      <c r="CL37" s="8"/>
+      <c r="CM37" s="8"/>
+      <c r="CN37" s="8"/>
+      <c r="CO37" s="8"/>
+      <c r="CP37" s="8"/>
+      <c r="CQ37" s="8"/>
+      <c r="CR37" s="8"/>
     </row>
-    <row r="38" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -7731,8 +8945,24 @@
       <c r="BZ38" s="8"/>
       <c r="CA38" s="8"/>
       <c r="CB38" s="8"/>
+      <c r="CC38" s="8"/>
+      <c r="CD38" s="8"/>
+      <c r="CE38" s="8"/>
+      <c r="CF38" s="8"/>
+      <c r="CG38" s="8"/>
+      <c r="CH38" s="8"/>
+      <c r="CI38" s="8"/>
+      <c r="CJ38" s="8"/>
+      <c r="CK38" s="8"/>
+      <c r="CL38" s="8"/>
+      <c r="CM38" s="8"/>
+      <c r="CN38" s="8"/>
+      <c r="CO38" s="8"/>
+      <c r="CP38" s="8"/>
+      <c r="CQ38" s="8"/>
+      <c r="CR38" s="8"/>
     </row>
-    <row r="39" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -7813,8 +9043,24 @@
       <c r="BZ39" s="8"/>
       <c r="CA39" s="8"/>
       <c r="CB39" s="8"/>
+      <c r="CC39" s="8"/>
+      <c r="CD39" s="8"/>
+      <c r="CE39" s="8"/>
+      <c r="CF39" s="8"/>
+      <c r="CG39" s="8"/>
+      <c r="CH39" s="8"/>
+      <c r="CI39" s="8"/>
+      <c r="CJ39" s="8"/>
+      <c r="CK39" s="8"/>
+      <c r="CL39" s="8"/>
+      <c r="CM39" s="8"/>
+      <c r="CN39" s="8"/>
+      <c r="CO39" s="8"/>
+      <c r="CP39" s="8"/>
+      <c r="CQ39" s="8"/>
+      <c r="CR39" s="8"/>
     </row>
-    <row r="40" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -7895,8 +9141,24 @@
       <c r="BZ40" s="8"/>
       <c r="CA40" s="8"/>
       <c r="CB40" s="8"/>
+      <c r="CC40" s="8"/>
+      <c r="CD40" s="8"/>
+      <c r="CE40" s="8"/>
+      <c r="CF40" s="8"/>
+      <c r="CG40" s="8"/>
+      <c r="CH40" s="8"/>
+      <c r="CI40" s="8"/>
+      <c r="CJ40" s="8"/>
+      <c r="CK40" s="8"/>
+      <c r="CL40" s="8"/>
+      <c r="CM40" s="8"/>
+      <c r="CN40" s="8"/>
+      <c r="CO40" s="8"/>
+      <c r="CP40" s="8"/>
+      <c r="CQ40" s="8"/>
+      <c r="CR40" s="8"/>
     </row>
-    <row r="41" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>16</v>
       </c>
@@ -8017,8 +9279,28 @@
       <c r="BZ41" s="8"/>
       <c r="CA41" s="8"/>
       <c r="CB41" s="8"/>
+      <c r="CC41" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="CD41" s="8"/>
+      <c r="CE41" s="8"/>
+      <c r="CF41" s="8"/>
+      <c r="CG41" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="CH41" s="8"/>
+      <c r="CI41" s="8"/>
+      <c r="CJ41" s="8"/>
+      <c r="CK41" s="7"/>
+      <c r="CL41" s="8"/>
+      <c r="CM41" s="8"/>
+      <c r="CN41" s="8"/>
+      <c r="CO41" s="9"/>
+      <c r="CP41" s="8"/>
+      <c r="CQ41" s="8"/>
+      <c r="CR41" s="8"/>
     </row>
-    <row r="42" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -8099,8 +9381,24 @@
       <c r="BZ42" s="8"/>
       <c r="CA42" s="8"/>
       <c r="CB42" s="8"/>
+      <c r="CC42" s="8"/>
+      <c r="CD42" s="8"/>
+      <c r="CE42" s="8"/>
+      <c r="CF42" s="8"/>
+      <c r="CG42" s="8"/>
+      <c r="CH42" s="8"/>
+      <c r="CI42" s="8"/>
+      <c r="CJ42" s="8"/>
+      <c r="CK42" s="8"/>
+      <c r="CL42" s="8"/>
+      <c r="CM42" s="8"/>
+      <c r="CN42" s="8"/>
+      <c r="CO42" s="8"/>
+      <c r="CP42" s="8"/>
+      <c r="CQ42" s="8"/>
+      <c r="CR42" s="8"/>
     </row>
-    <row r="43" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -8181,8 +9479,24 @@
       <c r="BZ43" s="8"/>
       <c r="CA43" s="8"/>
       <c r="CB43" s="8"/>
+      <c r="CC43" s="8"/>
+      <c r="CD43" s="8"/>
+      <c r="CE43" s="8"/>
+      <c r="CF43" s="8"/>
+      <c r="CG43" s="8"/>
+      <c r="CH43" s="8"/>
+      <c r="CI43" s="8"/>
+      <c r="CJ43" s="8"/>
+      <c r="CK43" s="8"/>
+      <c r="CL43" s="8"/>
+      <c r="CM43" s="8"/>
+      <c r="CN43" s="8"/>
+      <c r="CO43" s="8"/>
+      <c r="CP43" s="8"/>
+      <c r="CQ43" s="8"/>
+      <c r="CR43" s="8"/>
     </row>
-    <row r="44" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -8263,8 +9577,24 @@
       <c r="BZ44" s="8"/>
       <c r="CA44" s="8"/>
       <c r="CB44" s="8"/>
+      <c r="CC44" s="8"/>
+      <c r="CD44" s="8"/>
+      <c r="CE44" s="8"/>
+      <c r="CF44" s="8"/>
+      <c r="CG44" s="8"/>
+      <c r="CH44" s="8"/>
+      <c r="CI44" s="8"/>
+      <c r="CJ44" s="8"/>
+      <c r="CK44" s="8"/>
+      <c r="CL44" s="8"/>
+      <c r="CM44" s="8"/>
+      <c r="CN44" s="8"/>
+      <c r="CO44" s="8"/>
+      <c r="CP44" s="8"/>
+      <c r="CQ44" s="8"/>
+      <c r="CR44" s="8"/>
     </row>
-    <row r="45" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -8345,8 +9675,24 @@
       <c r="BZ45" s="8"/>
       <c r="CA45" s="8"/>
       <c r="CB45" s="8"/>
+      <c r="CC45" s="8"/>
+      <c r="CD45" s="8"/>
+      <c r="CE45" s="8"/>
+      <c r="CF45" s="8"/>
+      <c r="CG45" s="8"/>
+      <c r="CH45" s="8"/>
+      <c r="CI45" s="8"/>
+      <c r="CJ45" s="8"/>
+      <c r="CK45" s="8"/>
+      <c r="CL45" s="8"/>
+      <c r="CM45" s="8"/>
+      <c r="CN45" s="8"/>
+      <c r="CO45" s="8"/>
+      <c r="CP45" s="8"/>
+      <c r="CQ45" s="8"/>
+      <c r="CR45" s="8"/>
     </row>
-    <row r="46" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -8427,8 +9773,24 @@
       <c r="BZ46" s="8"/>
       <c r="CA46" s="8"/>
       <c r="CB46" s="8"/>
+      <c r="CC46" s="8"/>
+      <c r="CD46" s="8"/>
+      <c r="CE46" s="8"/>
+      <c r="CF46" s="8"/>
+      <c r="CG46" s="8"/>
+      <c r="CH46" s="8"/>
+      <c r="CI46" s="8"/>
+      <c r="CJ46" s="8"/>
+      <c r="CK46" s="8"/>
+      <c r="CL46" s="8"/>
+      <c r="CM46" s="8"/>
+      <c r="CN46" s="8"/>
+      <c r="CO46" s="8"/>
+      <c r="CP46" s="8"/>
+      <c r="CQ46" s="8"/>
+      <c r="CR46" s="8"/>
     </row>
-    <row r="47" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -8509,8 +9871,24 @@
       <c r="BZ47" s="8"/>
       <c r="CA47" s="8"/>
       <c r="CB47" s="8"/>
+      <c r="CC47" s="8"/>
+      <c r="CD47" s="8"/>
+      <c r="CE47" s="8"/>
+      <c r="CF47" s="8"/>
+      <c r="CG47" s="8"/>
+      <c r="CH47" s="8"/>
+      <c r="CI47" s="8"/>
+      <c r="CJ47" s="8"/>
+      <c r="CK47" s="8"/>
+      <c r="CL47" s="8"/>
+      <c r="CM47" s="8"/>
+      <c r="CN47" s="8"/>
+      <c r="CO47" s="8"/>
+      <c r="CP47" s="8"/>
+      <c r="CQ47" s="8"/>
+      <c r="CR47" s="8"/>
     </row>
-    <row r="48" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -8591,8 +9969,24 @@
       <c r="BZ48" s="8"/>
       <c r="CA48" s="8"/>
       <c r="CB48" s="8"/>
+      <c r="CC48" s="8"/>
+      <c r="CD48" s="8"/>
+      <c r="CE48" s="8"/>
+      <c r="CF48" s="8"/>
+      <c r="CG48" s="8"/>
+      <c r="CH48" s="8"/>
+      <c r="CI48" s="8"/>
+      <c r="CJ48" s="8"/>
+      <c r="CK48" s="8"/>
+      <c r="CL48" s="8"/>
+      <c r="CM48" s="8"/>
+      <c r="CN48" s="8"/>
+      <c r="CO48" s="8"/>
+      <c r="CP48" s="8"/>
+      <c r="CQ48" s="8"/>
+      <c r="CR48" s="8"/>
     </row>
-    <row r="49" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -8673,8 +10067,24 @@
       <c r="BZ49" s="8"/>
       <c r="CA49" s="8"/>
       <c r="CB49" s="8"/>
+      <c r="CC49" s="8"/>
+      <c r="CD49" s="8"/>
+      <c r="CE49" s="8"/>
+      <c r="CF49" s="8"/>
+      <c r="CG49" s="8"/>
+      <c r="CH49" s="8"/>
+      <c r="CI49" s="8"/>
+      <c r="CJ49" s="8"/>
+      <c r="CK49" s="8"/>
+      <c r="CL49" s="8"/>
+      <c r="CM49" s="8"/>
+      <c r="CN49" s="8"/>
+      <c r="CO49" s="8"/>
+      <c r="CP49" s="8"/>
+      <c r="CQ49" s="8"/>
+      <c r="CR49" s="8"/>
     </row>
-    <row r="50" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -8755,8 +10165,24 @@
       <c r="BZ50" s="8"/>
       <c r="CA50" s="8"/>
       <c r="CB50" s="8"/>
+      <c r="CC50" s="8"/>
+      <c r="CD50" s="8"/>
+      <c r="CE50" s="8"/>
+      <c r="CF50" s="8"/>
+      <c r="CG50" s="8"/>
+      <c r="CH50" s="8"/>
+      <c r="CI50" s="8"/>
+      <c r="CJ50" s="8"/>
+      <c r="CK50" s="8"/>
+      <c r="CL50" s="8"/>
+      <c r="CM50" s="8"/>
+      <c r="CN50" s="8"/>
+      <c r="CO50" s="8"/>
+      <c r="CP50" s="8"/>
+      <c r="CQ50" s="8"/>
+      <c r="CR50" s="8"/>
     </row>
-    <row r="51" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>6</v>
       </c>
@@ -8877,8 +10303,32 @@
       <c r="BZ51" s="6"/>
       <c r="CA51" s="6"/>
       <c r="CB51" s="6"/>
+      <c r="CC51" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="CD51" s="6"/>
+      <c r="CE51" s="6"/>
+      <c r="CF51" s="6"/>
+      <c r="CG51" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="CH51" s="6"/>
+      <c r="CI51" s="6"/>
+      <c r="CJ51" s="6"/>
+      <c r="CK51" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="CL51" s="6"/>
+      <c r="CM51" s="6"/>
+      <c r="CN51" s="6"/>
+      <c r="CO51" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="CP51" s="6"/>
+      <c r="CQ51" s="6"/>
+      <c r="CR51" s="6"/>
     </row>
-    <row r="52" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -8959,8 +10409,24 @@
       <c r="BZ52" s="6"/>
       <c r="CA52" s="6"/>
       <c r="CB52" s="6"/>
+      <c r="CC52" s="6"/>
+      <c r="CD52" s="6"/>
+      <c r="CE52" s="6"/>
+      <c r="CF52" s="6"/>
+      <c r="CG52" s="6"/>
+      <c r="CH52" s="6"/>
+      <c r="CI52" s="6"/>
+      <c r="CJ52" s="6"/>
+      <c r="CK52" s="6"/>
+      <c r="CL52" s="6"/>
+      <c r="CM52" s="6"/>
+      <c r="CN52" s="6"/>
+      <c r="CO52" s="6"/>
+      <c r="CP52" s="6"/>
+      <c r="CQ52" s="6"/>
+      <c r="CR52" s="6"/>
     </row>
-    <row r="53" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -9041,8 +10507,24 @@
       <c r="BZ53" s="6"/>
       <c r="CA53" s="6"/>
       <c r="CB53" s="6"/>
+      <c r="CC53" s="6"/>
+      <c r="CD53" s="6"/>
+      <c r="CE53" s="6"/>
+      <c r="CF53" s="6"/>
+      <c r="CG53" s="6"/>
+      <c r="CH53" s="6"/>
+      <c r="CI53" s="6"/>
+      <c r="CJ53" s="6"/>
+      <c r="CK53" s="6"/>
+      <c r="CL53" s="6"/>
+      <c r="CM53" s="6"/>
+      <c r="CN53" s="6"/>
+      <c r="CO53" s="6"/>
+      <c r="CP53" s="6"/>
+      <c r="CQ53" s="6"/>
+      <c r="CR53" s="6"/>
     </row>
-    <row r="54" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -9123,8 +10605,24 @@
       <c r="BZ54" s="6"/>
       <c r="CA54" s="6"/>
       <c r="CB54" s="6"/>
+      <c r="CC54" s="6"/>
+      <c r="CD54" s="6"/>
+      <c r="CE54" s="6"/>
+      <c r="CF54" s="6"/>
+      <c r="CG54" s="6"/>
+      <c r="CH54" s="6"/>
+      <c r="CI54" s="6"/>
+      <c r="CJ54" s="6"/>
+      <c r="CK54" s="6"/>
+      <c r="CL54" s="6"/>
+      <c r="CM54" s="6"/>
+      <c r="CN54" s="6"/>
+      <c r="CO54" s="6"/>
+      <c r="CP54" s="6"/>
+      <c r="CQ54" s="6"/>
+      <c r="CR54" s="6"/>
     </row>
-    <row r="55" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -9205,8 +10703,24 @@
       <c r="BZ55" s="6"/>
       <c r="CA55" s="6"/>
       <c r="CB55" s="6"/>
+      <c r="CC55" s="6"/>
+      <c r="CD55" s="6"/>
+      <c r="CE55" s="6"/>
+      <c r="CF55" s="6"/>
+      <c r="CG55" s="6"/>
+      <c r="CH55" s="6"/>
+      <c r="CI55" s="6"/>
+      <c r="CJ55" s="6"/>
+      <c r="CK55" s="6"/>
+      <c r="CL55" s="6"/>
+      <c r="CM55" s="6"/>
+      <c r="CN55" s="6"/>
+      <c r="CO55" s="6"/>
+      <c r="CP55" s="6"/>
+      <c r="CQ55" s="6"/>
+      <c r="CR55" s="6"/>
     </row>
-    <row r="56" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -9287,8 +10801,24 @@
       <c r="BZ56" s="6"/>
       <c r="CA56" s="6"/>
       <c r="CB56" s="6"/>
+      <c r="CC56" s="6"/>
+      <c r="CD56" s="6"/>
+      <c r="CE56" s="6"/>
+      <c r="CF56" s="6"/>
+      <c r="CG56" s="6"/>
+      <c r="CH56" s="6"/>
+      <c r="CI56" s="6"/>
+      <c r="CJ56" s="6"/>
+      <c r="CK56" s="6"/>
+      <c r="CL56" s="6"/>
+      <c r="CM56" s="6"/>
+      <c r="CN56" s="6"/>
+      <c r="CO56" s="6"/>
+      <c r="CP56" s="6"/>
+      <c r="CQ56" s="6"/>
+      <c r="CR56" s="6"/>
     </row>
-    <row r="57" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -9369,8 +10899,24 @@
       <c r="BZ57" s="6"/>
       <c r="CA57" s="6"/>
       <c r="CB57" s="6"/>
+      <c r="CC57" s="6"/>
+      <c r="CD57" s="6"/>
+      <c r="CE57" s="6"/>
+      <c r="CF57" s="6"/>
+      <c r="CG57" s="6"/>
+      <c r="CH57" s="6"/>
+      <c r="CI57" s="6"/>
+      <c r="CJ57" s="6"/>
+      <c r="CK57" s="6"/>
+      <c r="CL57" s="6"/>
+      <c r="CM57" s="6"/>
+      <c r="CN57" s="6"/>
+      <c r="CO57" s="6"/>
+      <c r="CP57" s="6"/>
+      <c r="CQ57" s="6"/>
+      <c r="CR57" s="6"/>
     </row>
-    <row r="58" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -9451,8 +10997,24 @@
       <c r="BZ58" s="6"/>
       <c r="CA58" s="6"/>
       <c r="CB58" s="6"/>
+      <c r="CC58" s="6"/>
+      <c r="CD58" s="6"/>
+      <c r="CE58" s="6"/>
+      <c r="CF58" s="6"/>
+      <c r="CG58" s="6"/>
+      <c r="CH58" s="6"/>
+      <c r="CI58" s="6"/>
+      <c r="CJ58" s="6"/>
+      <c r="CK58" s="6"/>
+      <c r="CL58" s="6"/>
+      <c r="CM58" s="6"/>
+      <c r="CN58" s="6"/>
+      <c r="CO58" s="6"/>
+      <c r="CP58" s="6"/>
+      <c r="CQ58" s="6"/>
+      <c r="CR58" s="6"/>
     </row>
-    <row r="59" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -9533,8 +11095,24 @@
       <c r="BZ59" s="6"/>
       <c r="CA59" s="6"/>
       <c r="CB59" s="6"/>
+      <c r="CC59" s="6"/>
+      <c r="CD59" s="6"/>
+      <c r="CE59" s="6"/>
+      <c r="CF59" s="6"/>
+      <c r="CG59" s="6"/>
+      <c r="CH59" s="6"/>
+      <c r="CI59" s="6"/>
+      <c r="CJ59" s="6"/>
+      <c r="CK59" s="6"/>
+      <c r="CL59" s="6"/>
+      <c r="CM59" s="6"/>
+      <c r="CN59" s="6"/>
+      <c r="CO59" s="6"/>
+      <c r="CP59" s="6"/>
+      <c r="CQ59" s="6"/>
+      <c r="CR59" s="6"/>
     </row>
-    <row r="60" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -9615,8 +11193,24 @@
       <c r="BZ60" s="6"/>
       <c r="CA60" s="6"/>
       <c r="CB60" s="6"/>
+      <c r="CC60" s="6"/>
+      <c r="CD60" s="6"/>
+      <c r="CE60" s="6"/>
+      <c r="CF60" s="6"/>
+      <c r="CG60" s="6"/>
+      <c r="CH60" s="6"/>
+      <c r="CI60" s="6"/>
+      <c r="CJ60" s="6"/>
+      <c r="CK60" s="6"/>
+      <c r="CL60" s="6"/>
+      <c r="CM60" s="6"/>
+      <c r="CN60" s="6"/>
+      <c r="CO60" s="6"/>
+      <c r="CP60" s="6"/>
+      <c r="CQ60" s="6"/>
+      <c r="CR60" s="6"/>
     </row>
-    <row r="61" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>8</v>
       </c>
@@ -9737,8 +11331,32 @@
       <c r="BZ61" s="6"/>
       <c r="CA61" s="6"/>
       <c r="CB61" s="6"/>
+      <c r="CC61" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="CD61" s="6"/>
+      <c r="CE61" s="6"/>
+      <c r="CF61" s="6"/>
+      <c r="CG61" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="CH61" s="6"/>
+      <c r="CI61" s="6"/>
+      <c r="CJ61" s="6"/>
+      <c r="CK61" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="CL61" s="6"/>
+      <c r="CM61" s="6"/>
+      <c r="CN61" s="6"/>
+      <c r="CO61" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="CP61" s="6"/>
+      <c r="CQ61" s="6"/>
+      <c r="CR61" s="6"/>
     </row>
-    <row r="62" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -9819,8 +11437,24 @@
       <c r="BZ62" s="6"/>
       <c r="CA62" s="6"/>
       <c r="CB62" s="6"/>
+      <c r="CC62" s="6"/>
+      <c r="CD62" s="6"/>
+      <c r="CE62" s="6"/>
+      <c r="CF62" s="6"/>
+      <c r="CG62" s="6"/>
+      <c r="CH62" s="6"/>
+      <c r="CI62" s="6"/>
+      <c r="CJ62" s="6"/>
+      <c r="CK62" s="6"/>
+      <c r="CL62" s="6"/>
+      <c r="CM62" s="6"/>
+      <c r="CN62" s="6"/>
+      <c r="CO62" s="6"/>
+      <c r="CP62" s="6"/>
+      <c r="CQ62" s="6"/>
+      <c r="CR62" s="6"/>
     </row>
-    <row r="63" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -9901,8 +11535,24 @@
       <c r="BZ63" s="6"/>
       <c r="CA63" s="6"/>
       <c r="CB63" s="6"/>
+      <c r="CC63" s="6"/>
+      <c r="CD63" s="6"/>
+      <c r="CE63" s="6"/>
+      <c r="CF63" s="6"/>
+      <c r="CG63" s="6"/>
+      <c r="CH63" s="6"/>
+      <c r="CI63" s="6"/>
+      <c r="CJ63" s="6"/>
+      <c r="CK63" s="6"/>
+      <c r="CL63" s="6"/>
+      <c r="CM63" s="6"/>
+      <c r="CN63" s="6"/>
+      <c r="CO63" s="6"/>
+      <c r="CP63" s="6"/>
+      <c r="CQ63" s="6"/>
+      <c r="CR63" s="6"/>
     </row>
-    <row r="64" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -9983,8 +11633,24 @@
       <c r="BZ64" s="6"/>
       <c r="CA64" s="6"/>
       <c r="CB64" s="6"/>
+      <c r="CC64" s="6"/>
+      <c r="CD64" s="6"/>
+      <c r="CE64" s="6"/>
+      <c r="CF64" s="6"/>
+      <c r="CG64" s="6"/>
+      <c r="CH64" s="6"/>
+      <c r="CI64" s="6"/>
+      <c r="CJ64" s="6"/>
+      <c r="CK64" s="6"/>
+      <c r="CL64" s="6"/>
+      <c r="CM64" s="6"/>
+      <c r="CN64" s="6"/>
+      <c r="CO64" s="6"/>
+      <c r="CP64" s="6"/>
+      <c r="CQ64" s="6"/>
+      <c r="CR64" s="6"/>
     </row>
-    <row r="65" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -10065,8 +11731,24 @@
       <c r="BZ65" s="6"/>
       <c r="CA65" s="6"/>
       <c r="CB65" s="6"/>
+      <c r="CC65" s="6"/>
+      <c r="CD65" s="6"/>
+      <c r="CE65" s="6"/>
+      <c r="CF65" s="6"/>
+      <c r="CG65" s="6"/>
+      <c r="CH65" s="6"/>
+      <c r="CI65" s="6"/>
+      <c r="CJ65" s="6"/>
+      <c r="CK65" s="6"/>
+      <c r="CL65" s="6"/>
+      <c r="CM65" s="6"/>
+      <c r="CN65" s="6"/>
+      <c r="CO65" s="6"/>
+      <c r="CP65" s="6"/>
+      <c r="CQ65" s="6"/>
+      <c r="CR65" s="6"/>
     </row>
-    <row r="66" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -10147,8 +11829,24 @@
       <c r="BZ66" s="6"/>
       <c r="CA66" s="6"/>
       <c r="CB66" s="6"/>
+      <c r="CC66" s="6"/>
+      <c r="CD66" s="6"/>
+      <c r="CE66" s="6"/>
+      <c r="CF66" s="6"/>
+      <c r="CG66" s="6"/>
+      <c r="CH66" s="6"/>
+      <c r="CI66" s="6"/>
+      <c r="CJ66" s="6"/>
+      <c r="CK66" s="6"/>
+      <c r="CL66" s="6"/>
+      <c r="CM66" s="6"/>
+      <c r="CN66" s="6"/>
+      <c r="CO66" s="6"/>
+      <c r="CP66" s="6"/>
+      <c r="CQ66" s="6"/>
+      <c r="CR66" s="6"/>
     </row>
-    <row r="67" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -10229,8 +11927,24 @@
       <c r="BZ67" s="6"/>
       <c r="CA67" s="6"/>
       <c r="CB67" s="6"/>
+      <c r="CC67" s="6"/>
+      <c r="CD67" s="6"/>
+      <c r="CE67" s="6"/>
+      <c r="CF67" s="6"/>
+      <c r="CG67" s="6"/>
+      <c r="CH67" s="6"/>
+      <c r="CI67" s="6"/>
+      <c r="CJ67" s="6"/>
+      <c r="CK67" s="6"/>
+      <c r="CL67" s="6"/>
+      <c r="CM67" s="6"/>
+      <c r="CN67" s="6"/>
+      <c r="CO67" s="6"/>
+      <c r="CP67" s="6"/>
+      <c r="CQ67" s="6"/>
+      <c r="CR67" s="6"/>
     </row>
-    <row r="68" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -10311,8 +12025,24 @@
       <c r="BZ68" s="6"/>
       <c r="CA68" s="6"/>
       <c r="CB68" s="6"/>
+      <c r="CC68" s="6"/>
+      <c r="CD68" s="6"/>
+      <c r="CE68" s="6"/>
+      <c r="CF68" s="6"/>
+      <c r="CG68" s="6"/>
+      <c r="CH68" s="6"/>
+      <c r="CI68" s="6"/>
+      <c r="CJ68" s="6"/>
+      <c r="CK68" s="6"/>
+      <c r="CL68" s="6"/>
+      <c r="CM68" s="6"/>
+      <c r="CN68" s="6"/>
+      <c r="CO68" s="6"/>
+      <c r="CP68" s="6"/>
+      <c r="CQ68" s="6"/>
+      <c r="CR68" s="6"/>
     </row>
-    <row r="69" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -10393,8 +12123,24 @@
       <c r="BZ69" s="6"/>
       <c r="CA69" s="6"/>
       <c r="CB69" s="6"/>
+      <c r="CC69" s="6"/>
+      <c r="CD69" s="6"/>
+      <c r="CE69" s="6"/>
+      <c r="CF69" s="6"/>
+      <c r="CG69" s="6"/>
+      <c r="CH69" s="6"/>
+      <c r="CI69" s="6"/>
+      <c r="CJ69" s="6"/>
+      <c r="CK69" s="6"/>
+      <c r="CL69" s="6"/>
+      <c r="CM69" s="6"/>
+      <c r="CN69" s="6"/>
+      <c r="CO69" s="6"/>
+      <c r="CP69" s="6"/>
+      <c r="CQ69" s="6"/>
+      <c r="CR69" s="6"/>
     </row>
-    <row r="70" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -10475,8 +12221,24 @@
       <c r="BZ70" s="6"/>
       <c r="CA70" s="6"/>
       <c r="CB70" s="6"/>
+      <c r="CC70" s="6"/>
+      <c r="CD70" s="6"/>
+      <c r="CE70" s="6"/>
+      <c r="CF70" s="6"/>
+      <c r="CG70" s="6"/>
+      <c r="CH70" s="6"/>
+      <c r="CI70" s="6"/>
+      <c r="CJ70" s="6"/>
+      <c r="CK70" s="6"/>
+      <c r="CL70" s="6"/>
+      <c r="CM70" s="6"/>
+      <c r="CN70" s="6"/>
+      <c r="CO70" s="6"/>
+      <c r="CP70" s="6"/>
+      <c r="CQ70" s="6"/>
+      <c r="CR70" s="6"/>
     </row>
-    <row r="71" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:96" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>11</v>
       </c>
@@ -10597,8 +12359,32 @@
       <c r="BZ71" s="6"/>
       <c r="CA71" s="6"/>
       <c r="CB71" s="6"/>
+      <c r="CC71" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="CD71" s="6"/>
+      <c r="CE71" s="6"/>
+      <c r="CF71" s="6"/>
+      <c r="CG71" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="CH71" s="6"/>
+      <c r="CI71" s="6"/>
+      <c r="CJ71" s="6"/>
+      <c r="CK71" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="CL71" s="6"/>
+      <c r="CM71" s="6"/>
+      <c r="CN71" s="6"/>
+      <c r="CO71" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="CP71" s="6"/>
+      <c r="CQ71" s="6"/>
+      <c r="CR71" s="6"/>
     </row>
-    <row r="72" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -10679,8 +12465,24 @@
       <c r="BZ72" s="6"/>
       <c r="CA72" s="6"/>
       <c r="CB72" s="6"/>
+      <c r="CC72" s="6"/>
+      <c r="CD72" s="6"/>
+      <c r="CE72" s="6"/>
+      <c r="CF72" s="6"/>
+      <c r="CG72" s="6"/>
+      <c r="CH72" s="6"/>
+      <c r="CI72" s="6"/>
+      <c r="CJ72" s="6"/>
+      <c r="CK72" s="6"/>
+      <c r="CL72" s="6"/>
+      <c r="CM72" s="6"/>
+      <c r="CN72" s="6"/>
+      <c r="CO72" s="6"/>
+      <c r="CP72" s="6"/>
+      <c r="CQ72" s="6"/>
+      <c r="CR72" s="6"/>
     </row>
-    <row r="73" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -10761,8 +12563,24 @@
       <c r="BZ73" s="6"/>
       <c r="CA73" s="6"/>
       <c r="CB73" s="6"/>
+      <c r="CC73" s="6"/>
+      <c r="CD73" s="6"/>
+      <c r="CE73" s="6"/>
+      <c r="CF73" s="6"/>
+      <c r="CG73" s="6"/>
+      <c r="CH73" s="6"/>
+      <c r="CI73" s="6"/>
+      <c r="CJ73" s="6"/>
+      <c r="CK73" s="6"/>
+      <c r="CL73" s="6"/>
+      <c r="CM73" s="6"/>
+      <c r="CN73" s="6"/>
+      <c r="CO73" s="6"/>
+      <c r="CP73" s="6"/>
+      <c r="CQ73" s="6"/>
+      <c r="CR73" s="6"/>
     </row>
-    <row r="74" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -10843,8 +12661,24 @@
       <c r="BZ74" s="6"/>
       <c r="CA74" s="6"/>
       <c r="CB74" s="6"/>
+      <c r="CC74" s="6"/>
+      <c r="CD74" s="6"/>
+      <c r="CE74" s="6"/>
+      <c r="CF74" s="6"/>
+      <c r="CG74" s="6"/>
+      <c r="CH74" s="6"/>
+      <c r="CI74" s="6"/>
+      <c r="CJ74" s="6"/>
+      <c r="CK74" s="6"/>
+      <c r="CL74" s="6"/>
+      <c r="CM74" s="6"/>
+      <c r="CN74" s="6"/>
+      <c r="CO74" s="6"/>
+      <c r="CP74" s="6"/>
+      <c r="CQ74" s="6"/>
+      <c r="CR74" s="6"/>
     </row>
-    <row r="75" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -10925,8 +12759,24 @@
       <c r="BZ75" s="6"/>
       <c r="CA75" s="6"/>
       <c r="CB75" s="6"/>
+      <c r="CC75" s="6"/>
+      <c r="CD75" s="6"/>
+      <c r="CE75" s="6"/>
+      <c r="CF75" s="6"/>
+      <c r="CG75" s="6"/>
+      <c r="CH75" s="6"/>
+      <c r="CI75" s="6"/>
+      <c r="CJ75" s="6"/>
+      <c r="CK75" s="6"/>
+      <c r="CL75" s="6"/>
+      <c r="CM75" s="6"/>
+      <c r="CN75" s="6"/>
+      <c r="CO75" s="6"/>
+      <c r="CP75" s="6"/>
+      <c r="CQ75" s="6"/>
+      <c r="CR75" s="6"/>
     </row>
-    <row r="76" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -11007,8 +12857,24 @@
       <c r="BZ76" s="6"/>
       <c r="CA76" s="6"/>
       <c r="CB76" s="6"/>
+      <c r="CC76" s="6"/>
+      <c r="CD76" s="6"/>
+      <c r="CE76" s="6"/>
+      <c r="CF76" s="6"/>
+      <c r="CG76" s="6"/>
+      <c r="CH76" s="6"/>
+      <c r="CI76" s="6"/>
+      <c r="CJ76" s="6"/>
+      <c r="CK76" s="6"/>
+      <c r="CL76" s="6"/>
+      <c r="CM76" s="6"/>
+      <c r="CN76" s="6"/>
+      <c r="CO76" s="6"/>
+      <c r="CP76" s="6"/>
+      <c r="CQ76" s="6"/>
+      <c r="CR76" s="6"/>
     </row>
-    <row r="77" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -11089,8 +12955,24 @@
       <c r="BZ77" s="6"/>
       <c r="CA77" s="6"/>
       <c r="CB77" s="6"/>
+      <c r="CC77" s="6"/>
+      <c r="CD77" s="6"/>
+      <c r="CE77" s="6"/>
+      <c r="CF77" s="6"/>
+      <c r="CG77" s="6"/>
+      <c r="CH77" s="6"/>
+      <c r="CI77" s="6"/>
+      <c r="CJ77" s="6"/>
+      <c r="CK77" s="6"/>
+      <c r="CL77" s="6"/>
+      <c r="CM77" s="6"/>
+      <c r="CN77" s="6"/>
+      <c r="CO77" s="6"/>
+      <c r="CP77" s="6"/>
+      <c r="CQ77" s="6"/>
+      <c r="CR77" s="6"/>
     </row>
-    <row r="78" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -11171,8 +13053,24 @@
       <c r="BZ78" s="6"/>
       <c r="CA78" s="6"/>
       <c r="CB78" s="6"/>
+      <c r="CC78" s="6"/>
+      <c r="CD78" s="6"/>
+      <c r="CE78" s="6"/>
+      <c r="CF78" s="6"/>
+      <c r="CG78" s="6"/>
+      <c r="CH78" s="6"/>
+      <c r="CI78" s="6"/>
+      <c r="CJ78" s="6"/>
+      <c r="CK78" s="6"/>
+      <c r="CL78" s="6"/>
+      <c r="CM78" s="6"/>
+      <c r="CN78" s="6"/>
+      <c r="CO78" s="6"/>
+      <c r="CP78" s="6"/>
+      <c r="CQ78" s="6"/>
+      <c r="CR78" s="6"/>
     </row>
-    <row r="79" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -11253,8 +13151,24 @@
       <c r="BZ79" s="6"/>
       <c r="CA79" s="6"/>
       <c r="CB79" s="6"/>
+      <c r="CC79" s="6"/>
+      <c r="CD79" s="6"/>
+      <c r="CE79" s="6"/>
+      <c r="CF79" s="6"/>
+      <c r="CG79" s="6"/>
+      <c r="CH79" s="6"/>
+      <c r="CI79" s="6"/>
+      <c r="CJ79" s="6"/>
+      <c r="CK79" s="6"/>
+      <c r="CL79" s="6"/>
+      <c r="CM79" s="6"/>
+      <c r="CN79" s="6"/>
+      <c r="CO79" s="6"/>
+      <c r="CP79" s="6"/>
+      <c r="CQ79" s="6"/>
+      <c r="CR79" s="6"/>
     </row>
-    <row r="80" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -11335,8 +13249,24 @@
       <c r="BZ80" s="6"/>
       <c r="CA80" s="6"/>
       <c r="CB80" s="6"/>
+      <c r="CC80" s="6"/>
+      <c r="CD80" s="6"/>
+      <c r="CE80" s="6"/>
+      <c r="CF80" s="6"/>
+      <c r="CG80" s="6"/>
+      <c r="CH80" s="6"/>
+      <c r="CI80" s="6"/>
+      <c r="CJ80" s="6"/>
+      <c r="CK80" s="6"/>
+      <c r="CL80" s="6"/>
+      <c r="CM80" s="6"/>
+      <c r="CN80" s="6"/>
+      <c r="CO80" s="6"/>
+      <c r="CP80" s="6"/>
+      <c r="CQ80" s="6"/>
+      <c r="CR80" s="6"/>
     </row>
-    <row r="81" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>15</v>
       </c>
@@ -11457,8 +13387,30 @@
       <c r="BZ81" s="6"/>
       <c r="CA81" s="6"/>
       <c r="CB81" s="6"/>
+      <c r="CC81" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="CD81" s="6"/>
+      <c r="CE81" s="6"/>
+      <c r="CF81" s="6"/>
+      <c r="CG81" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="CH81" s="6"/>
+      <c r="CI81" s="6"/>
+      <c r="CJ81" s="6"/>
+      <c r="CK81" s="5"/>
+      <c r="CL81" s="6"/>
+      <c r="CM81" s="6"/>
+      <c r="CN81" s="6"/>
+      <c r="CO81" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="CP81" s="6"/>
+      <c r="CQ81" s="6"/>
+      <c r="CR81" s="6"/>
     </row>
-    <row r="82" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -11539,8 +13491,24 @@
       <c r="BZ82" s="6"/>
       <c r="CA82" s="6"/>
       <c r="CB82" s="6"/>
+      <c r="CC82" s="6"/>
+      <c r="CD82" s="6"/>
+      <c r="CE82" s="6"/>
+      <c r="CF82" s="6"/>
+      <c r="CG82" s="6"/>
+      <c r="CH82" s="6"/>
+      <c r="CI82" s="6"/>
+      <c r="CJ82" s="6"/>
+      <c r="CK82" s="6"/>
+      <c r="CL82" s="6"/>
+      <c r="CM82" s="6"/>
+      <c r="CN82" s="6"/>
+      <c r="CO82" s="6"/>
+      <c r="CP82" s="6"/>
+      <c r="CQ82" s="6"/>
+      <c r="CR82" s="6"/>
     </row>
-    <row r="83" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -11621,8 +13589,24 @@
       <c r="BZ83" s="6"/>
       <c r="CA83" s="6"/>
       <c r="CB83" s="6"/>
+      <c r="CC83" s="6"/>
+      <c r="CD83" s="6"/>
+      <c r="CE83" s="6"/>
+      <c r="CF83" s="6"/>
+      <c r="CG83" s="6"/>
+      <c r="CH83" s="6"/>
+      <c r="CI83" s="6"/>
+      <c r="CJ83" s="6"/>
+      <c r="CK83" s="6"/>
+      <c r="CL83" s="6"/>
+      <c r="CM83" s="6"/>
+      <c r="CN83" s="6"/>
+      <c r="CO83" s="6"/>
+      <c r="CP83" s="6"/>
+      <c r="CQ83" s="6"/>
+      <c r="CR83" s="6"/>
     </row>
-    <row r="84" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -11703,8 +13687,24 @@
       <c r="BZ84" s="6"/>
       <c r="CA84" s="6"/>
       <c r="CB84" s="6"/>
+      <c r="CC84" s="6"/>
+      <c r="CD84" s="6"/>
+      <c r="CE84" s="6"/>
+      <c r="CF84" s="6"/>
+      <c r="CG84" s="6"/>
+      <c r="CH84" s="6"/>
+      <c r="CI84" s="6"/>
+      <c r="CJ84" s="6"/>
+      <c r="CK84" s="6"/>
+      <c r="CL84" s="6"/>
+      <c r="CM84" s="6"/>
+      <c r="CN84" s="6"/>
+      <c r="CO84" s="6"/>
+      <c r="CP84" s="6"/>
+      <c r="CQ84" s="6"/>
+      <c r="CR84" s="6"/>
     </row>
-    <row r="85" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -11785,8 +13785,24 @@
       <c r="BZ85" s="6"/>
       <c r="CA85" s="6"/>
       <c r="CB85" s="6"/>
+      <c r="CC85" s="6"/>
+      <c r="CD85" s="6"/>
+      <c r="CE85" s="6"/>
+      <c r="CF85" s="6"/>
+      <c r="CG85" s="6"/>
+      <c r="CH85" s="6"/>
+      <c r="CI85" s="6"/>
+      <c r="CJ85" s="6"/>
+      <c r="CK85" s="6"/>
+      <c r="CL85" s="6"/>
+      <c r="CM85" s="6"/>
+      <c r="CN85" s="6"/>
+      <c r="CO85" s="6"/>
+      <c r="CP85" s="6"/>
+      <c r="CQ85" s="6"/>
+      <c r="CR85" s="6"/>
     </row>
-    <row r="86" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -11867,8 +13883,24 @@
       <c r="BZ86" s="6"/>
       <c r="CA86" s="6"/>
       <c r="CB86" s="6"/>
+      <c r="CC86" s="6"/>
+      <c r="CD86" s="6"/>
+      <c r="CE86" s="6"/>
+      <c r="CF86" s="6"/>
+      <c r="CG86" s="6"/>
+      <c r="CH86" s="6"/>
+      <c r="CI86" s="6"/>
+      <c r="CJ86" s="6"/>
+      <c r="CK86" s="6"/>
+      <c r="CL86" s="6"/>
+      <c r="CM86" s="6"/>
+      <c r="CN86" s="6"/>
+      <c r="CO86" s="6"/>
+      <c r="CP86" s="6"/>
+      <c r="CQ86" s="6"/>
+      <c r="CR86" s="6"/>
     </row>
-    <row r="87" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -11949,8 +13981,24 @@
       <c r="BZ87" s="6"/>
       <c r="CA87" s="6"/>
       <c r="CB87" s="6"/>
+      <c r="CC87" s="6"/>
+      <c r="CD87" s="6"/>
+      <c r="CE87" s="6"/>
+      <c r="CF87" s="6"/>
+      <c r="CG87" s="6"/>
+      <c r="CH87" s="6"/>
+      <c r="CI87" s="6"/>
+      <c r="CJ87" s="6"/>
+      <c r="CK87" s="6"/>
+      <c r="CL87" s="6"/>
+      <c r="CM87" s="6"/>
+      <c r="CN87" s="6"/>
+      <c r="CO87" s="6"/>
+      <c r="CP87" s="6"/>
+      <c r="CQ87" s="6"/>
+      <c r="CR87" s="6"/>
     </row>
-    <row r="88" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -12031,8 +14079,24 @@
       <c r="BZ88" s="6"/>
       <c r="CA88" s="6"/>
       <c r="CB88" s="6"/>
+      <c r="CC88" s="6"/>
+      <c r="CD88" s="6"/>
+      <c r="CE88" s="6"/>
+      <c r="CF88" s="6"/>
+      <c r="CG88" s="6"/>
+      <c r="CH88" s="6"/>
+      <c r="CI88" s="6"/>
+      <c r="CJ88" s="6"/>
+      <c r="CK88" s="6"/>
+      <c r="CL88" s="6"/>
+      <c r="CM88" s="6"/>
+      <c r="CN88" s="6"/>
+      <c r="CO88" s="6"/>
+      <c r="CP88" s="6"/>
+      <c r="CQ88" s="6"/>
+      <c r="CR88" s="6"/>
     </row>
-    <row r="89" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -12113,8 +14177,24 @@
       <c r="BZ89" s="6"/>
       <c r="CA89" s="6"/>
       <c r="CB89" s="6"/>
+      <c r="CC89" s="6"/>
+      <c r="CD89" s="6"/>
+      <c r="CE89" s="6"/>
+      <c r="CF89" s="6"/>
+      <c r="CG89" s="6"/>
+      <c r="CH89" s="6"/>
+      <c r="CI89" s="6"/>
+      <c r="CJ89" s="6"/>
+      <c r="CK89" s="6"/>
+      <c r="CL89" s="6"/>
+      <c r="CM89" s="6"/>
+      <c r="CN89" s="6"/>
+      <c r="CO89" s="6"/>
+      <c r="CP89" s="6"/>
+      <c r="CQ89" s="6"/>
+      <c r="CR89" s="6"/>
     </row>
-    <row r="90" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -12195,8 +14275,24 @@
       <c r="BZ90" s="6"/>
       <c r="CA90" s="6"/>
       <c r="CB90" s="6"/>
+      <c r="CC90" s="6"/>
+      <c r="CD90" s="6"/>
+      <c r="CE90" s="6"/>
+      <c r="CF90" s="6"/>
+      <c r="CG90" s="6"/>
+      <c r="CH90" s="6"/>
+      <c r="CI90" s="6"/>
+      <c r="CJ90" s="6"/>
+      <c r="CK90" s="6"/>
+      <c r="CL90" s="6"/>
+      <c r="CM90" s="6"/>
+      <c r="CN90" s="6"/>
+      <c r="CO90" s="6"/>
+      <c r="CP90" s="6"/>
+      <c r="CQ90" s="6"/>
+      <c r="CR90" s="6"/>
     </row>
-    <row r="91" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>19</v>
       </c>
@@ -12317,8 +14413,28 @@
       <c r="BZ91" s="6"/>
       <c r="CA91" s="6"/>
       <c r="CB91" s="6"/>
+      <c r="CC91" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD91" s="6"/>
+      <c r="CE91" s="6"/>
+      <c r="CF91" s="6"/>
+      <c r="CG91" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="CH91" s="6"/>
+      <c r="CI91" s="6"/>
+      <c r="CJ91" s="6"/>
+      <c r="CK91" s="5"/>
+      <c r="CL91" s="6"/>
+      <c r="CM91" s="6"/>
+      <c r="CN91" s="6"/>
+      <c r="CO91" s="5"/>
+      <c r="CP91" s="6"/>
+      <c r="CQ91" s="6"/>
+      <c r="CR91" s="6"/>
     </row>
-    <row r="92" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -12399,8 +14515,24 @@
       <c r="BZ92" s="6"/>
       <c r="CA92" s="6"/>
       <c r="CB92" s="6"/>
+      <c r="CC92" s="6"/>
+      <c r="CD92" s="6"/>
+      <c r="CE92" s="6"/>
+      <c r="CF92" s="6"/>
+      <c r="CG92" s="6"/>
+      <c r="CH92" s="6"/>
+      <c r="CI92" s="6"/>
+      <c r="CJ92" s="6"/>
+      <c r="CK92" s="6"/>
+      <c r="CL92" s="6"/>
+      <c r="CM92" s="6"/>
+      <c r="CN92" s="6"/>
+      <c r="CO92" s="6"/>
+      <c r="CP92" s="6"/>
+      <c r="CQ92" s="6"/>
+      <c r="CR92" s="6"/>
     </row>
-    <row r="93" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -12481,8 +14613,24 @@
       <c r="BZ93" s="6"/>
       <c r="CA93" s="6"/>
       <c r="CB93" s="6"/>
+      <c r="CC93" s="6"/>
+      <c r="CD93" s="6"/>
+      <c r="CE93" s="6"/>
+      <c r="CF93" s="6"/>
+      <c r="CG93" s="6"/>
+      <c r="CH93" s="6"/>
+      <c r="CI93" s="6"/>
+      <c r="CJ93" s="6"/>
+      <c r="CK93" s="6"/>
+      <c r="CL93" s="6"/>
+      <c r="CM93" s="6"/>
+      <c r="CN93" s="6"/>
+      <c r="CO93" s="6"/>
+      <c r="CP93" s="6"/>
+      <c r="CQ93" s="6"/>
+      <c r="CR93" s="6"/>
     </row>
-    <row r="94" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -12563,8 +14711,24 @@
       <c r="BZ94" s="6"/>
       <c r="CA94" s="6"/>
       <c r="CB94" s="6"/>
+      <c r="CC94" s="6"/>
+      <c r="CD94" s="6"/>
+      <c r="CE94" s="6"/>
+      <c r="CF94" s="6"/>
+      <c r="CG94" s="6"/>
+      <c r="CH94" s="6"/>
+      <c r="CI94" s="6"/>
+      <c r="CJ94" s="6"/>
+      <c r="CK94" s="6"/>
+      <c r="CL94" s="6"/>
+      <c r="CM94" s="6"/>
+      <c r="CN94" s="6"/>
+      <c r="CO94" s="6"/>
+      <c r="CP94" s="6"/>
+      <c r="CQ94" s="6"/>
+      <c r="CR94" s="6"/>
     </row>
-    <row r="95" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -12645,8 +14809,24 @@
       <c r="BZ95" s="6"/>
       <c r="CA95" s="6"/>
       <c r="CB95" s="6"/>
+      <c r="CC95" s="6"/>
+      <c r="CD95" s="6"/>
+      <c r="CE95" s="6"/>
+      <c r="CF95" s="6"/>
+      <c r="CG95" s="6"/>
+      <c r="CH95" s="6"/>
+      <c r="CI95" s="6"/>
+      <c r="CJ95" s="6"/>
+      <c r="CK95" s="6"/>
+      <c r="CL95" s="6"/>
+      <c r="CM95" s="6"/>
+      <c r="CN95" s="6"/>
+      <c r="CO95" s="6"/>
+      <c r="CP95" s="6"/>
+      <c r="CQ95" s="6"/>
+      <c r="CR95" s="6"/>
     </row>
-    <row r="96" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -12727,8 +14907,24 @@
       <c r="BZ96" s="6"/>
       <c r="CA96" s="6"/>
       <c r="CB96" s="6"/>
+      <c r="CC96" s="6"/>
+      <c r="CD96" s="6"/>
+      <c r="CE96" s="6"/>
+      <c r="CF96" s="6"/>
+      <c r="CG96" s="6"/>
+      <c r="CH96" s="6"/>
+      <c r="CI96" s="6"/>
+      <c r="CJ96" s="6"/>
+      <c r="CK96" s="6"/>
+      <c r="CL96" s="6"/>
+      <c r="CM96" s="6"/>
+      <c r="CN96" s="6"/>
+      <c r="CO96" s="6"/>
+      <c r="CP96" s="6"/>
+      <c r="CQ96" s="6"/>
+      <c r="CR96" s="6"/>
     </row>
-    <row r="97" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -12809,8 +15005,24 @@
       <c r="BZ97" s="6"/>
       <c r="CA97" s="6"/>
       <c r="CB97" s="6"/>
+      <c r="CC97" s="6"/>
+      <c r="CD97" s="6"/>
+      <c r="CE97" s="6"/>
+      <c r="CF97" s="6"/>
+      <c r="CG97" s="6"/>
+      <c r="CH97" s="6"/>
+      <c r="CI97" s="6"/>
+      <c r="CJ97" s="6"/>
+      <c r="CK97" s="6"/>
+      <c r="CL97" s="6"/>
+      <c r="CM97" s="6"/>
+      <c r="CN97" s="6"/>
+      <c r="CO97" s="6"/>
+      <c r="CP97" s="6"/>
+      <c r="CQ97" s="6"/>
+      <c r="CR97" s="6"/>
     </row>
-    <row r="98" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -12891,8 +15103,24 @@
       <c r="BZ98" s="6"/>
       <c r="CA98" s="6"/>
       <c r="CB98" s="6"/>
+      <c r="CC98" s="6"/>
+      <c r="CD98" s="6"/>
+      <c r="CE98" s="6"/>
+      <c r="CF98" s="6"/>
+      <c r="CG98" s="6"/>
+      <c r="CH98" s="6"/>
+      <c r="CI98" s="6"/>
+      <c r="CJ98" s="6"/>
+      <c r="CK98" s="6"/>
+      <c r="CL98" s="6"/>
+      <c r="CM98" s="6"/>
+      <c r="CN98" s="6"/>
+      <c r="CO98" s="6"/>
+      <c r="CP98" s="6"/>
+      <c r="CQ98" s="6"/>
+      <c r="CR98" s="6"/>
     </row>
-    <row r="99" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -12973,8 +15201,24 @@
       <c r="BZ99" s="6"/>
       <c r="CA99" s="6"/>
       <c r="CB99" s="6"/>
+      <c r="CC99" s="6"/>
+      <c r="CD99" s="6"/>
+      <c r="CE99" s="6"/>
+      <c r="CF99" s="6"/>
+      <c r="CG99" s="6"/>
+      <c r="CH99" s="6"/>
+      <c r="CI99" s="6"/>
+      <c r="CJ99" s="6"/>
+      <c r="CK99" s="6"/>
+      <c r="CL99" s="6"/>
+      <c r="CM99" s="6"/>
+      <c r="CN99" s="6"/>
+      <c r="CO99" s="6"/>
+      <c r="CP99" s="6"/>
+      <c r="CQ99" s="6"/>
+      <c r="CR99" s="6"/>
     </row>
-    <row r="100" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -13055,8 +15299,24 @@
       <c r="BZ100" s="6"/>
       <c r="CA100" s="6"/>
       <c r="CB100" s="6"/>
+      <c r="CC100" s="6"/>
+      <c r="CD100" s="6"/>
+      <c r="CE100" s="6"/>
+      <c r="CF100" s="6"/>
+      <c r="CG100" s="6"/>
+      <c r="CH100" s="6"/>
+      <c r="CI100" s="6"/>
+      <c r="CJ100" s="6"/>
+      <c r="CK100" s="6"/>
+      <c r="CL100" s="6"/>
+      <c r="CM100" s="6"/>
+      <c r="CN100" s="6"/>
+      <c r="CO100" s="6"/>
+      <c r="CP100" s="6"/>
+      <c r="CQ100" s="6"/>
+      <c r="CR100" s="6"/>
     </row>
-    <row r="101" spans="1:80" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:96" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -13070,7 +15330,7 @@
       <c r="K101" s="4"/>
       <c r="L101" s="4"/>
     </row>
-    <row r="102" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A102" s="2"/>
       <c r="B102" s="3"/>
       <c r="C102" s="4"/>
@@ -13084,7 +15344,7 @@
       <c r="K102" s="4"/>
       <c r="L102" s="4"/>
     </row>
-    <row r="103" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A103" s="2"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -13098,7 +15358,7 @@
       <c r="K103" s="4"/>
       <c r="L103" s="4"/>
     </row>
-    <row r="104" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A104" s="2"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -13112,7 +15372,7 @@
       <c r="K104" s="4"/>
       <c r="L104" s="4"/>
     </row>
-    <row r="105" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A105" s="2"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -13126,7 +15386,7 @@
       <c r="K105" s="4"/>
       <c r="L105" s="4"/>
     </row>
-    <row r="106" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A106" s="2"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -13140,7 +15400,7 @@
       <c r="K106" s="4"/>
       <c r="L106" s="4"/>
     </row>
-    <row r="107" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A107" s="2"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -13154,7 +15414,7 @@
       <c r="K107" s="4"/>
       <c r="L107" s="4"/>
     </row>
-    <row r="108" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A108" s="2"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -13168,7 +15428,7 @@
       <c r="K108" s="4"/>
       <c r="L108" s="4"/>
     </row>
-    <row r="109" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A109" s="2"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -13182,7 +15442,7 @@
       <c r="K109" s="4"/>
       <c r="L109" s="4"/>
     </row>
-    <row r="110" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A110" s="2"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -13196,7 +15456,7 @@
       <c r="K110" s="4"/>
       <c r="L110" s="4"/>
     </row>
-    <row r="111" spans="1:80" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:96" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -13210,7 +15470,7 @@
       <c r="K111" s="4"/>
       <c r="L111" s="4"/>
     </row>
-    <row r="112" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A112" s="2"/>
       <c r="B112" s="3"/>
       <c r="C112" s="4"/>
@@ -13763,67 +16023,163 @@
       <c r="E151" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="200">
-    <mergeCell ref="BU51:BX60"/>
-    <mergeCell ref="BY51:CB60"/>
-    <mergeCell ref="BU61:BX70"/>
-    <mergeCell ref="BY61:CB70"/>
-    <mergeCell ref="BU71:BX80"/>
-    <mergeCell ref="BY71:CB80"/>
-    <mergeCell ref="BU81:BX90"/>
-    <mergeCell ref="BY81:CB90"/>
-    <mergeCell ref="BU91:BX100"/>
-    <mergeCell ref="BY91:CB100"/>
-    <mergeCell ref="BU1:BX10"/>
-    <mergeCell ref="BY1:CB10"/>
-    <mergeCell ref="BU11:BX20"/>
-    <mergeCell ref="BY11:CB20"/>
-    <mergeCell ref="BU21:BX30"/>
-    <mergeCell ref="BY21:CB30"/>
-    <mergeCell ref="BU31:BX40"/>
-    <mergeCell ref="BY31:CB40"/>
-    <mergeCell ref="BU41:BX50"/>
-    <mergeCell ref="BY41:CB50"/>
-    <mergeCell ref="BM51:BP60"/>
-    <mergeCell ref="BQ51:BT60"/>
-    <mergeCell ref="BM61:BP70"/>
-    <mergeCell ref="BQ61:BT70"/>
-    <mergeCell ref="BM71:BP80"/>
-    <mergeCell ref="BQ71:BT80"/>
-    <mergeCell ref="BM81:BP90"/>
-    <mergeCell ref="BQ81:BT90"/>
-    <mergeCell ref="BM91:BP100"/>
-    <mergeCell ref="BQ91:BT100"/>
-    <mergeCell ref="BM1:BP10"/>
-    <mergeCell ref="BQ1:BT10"/>
-    <mergeCell ref="BM11:BP20"/>
-    <mergeCell ref="BQ11:BT20"/>
-    <mergeCell ref="BM21:BP30"/>
-    <mergeCell ref="BQ21:BT30"/>
-    <mergeCell ref="BM31:BP40"/>
-    <mergeCell ref="BQ31:BT40"/>
-    <mergeCell ref="BM41:BP50"/>
-    <mergeCell ref="BQ41:BT50"/>
-    <mergeCell ref="BE51:BH60"/>
-    <mergeCell ref="BI51:BL60"/>
-    <mergeCell ref="BE61:BH70"/>
-    <mergeCell ref="BI61:BL70"/>
-    <mergeCell ref="BE71:BH80"/>
-    <mergeCell ref="BI71:BL80"/>
-    <mergeCell ref="BE81:BH90"/>
-    <mergeCell ref="BI81:BL90"/>
-    <mergeCell ref="BE91:BH100"/>
-    <mergeCell ref="BI91:BL100"/>
-    <mergeCell ref="BE1:BH10"/>
-    <mergeCell ref="BI1:BL10"/>
-    <mergeCell ref="BE11:BH20"/>
-    <mergeCell ref="BI11:BL20"/>
-    <mergeCell ref="BE21:BH30"/>
-    <mergeCell ref="BI21:BL30"/>
-    <mergeCell ref="BE31:BH40"/>
-    <mergeCell ref="BI31:BL40"/>
-    <mergeCell ref="BE41:BH50"/>
-    <mergeCell ref="BI41:BL50"/>
+  <mergeCells count="240">
+    <mergeCell ref="CK51:CN60"/>
+    <mergeCell ref="CO51:CR60"/>
+    <mergeCell ref="CK61:CN70"/>
+    <mergeCell ref="CO61:CR70"/>
+    <mergeCell ref="CK71:CN80"/>
+    <mergeCell ref="CO71:CR80"/>
+    <mergeCell ref="CK81:CN90"/>
+    <mergeCell ref="CO81:CR90"/>
+    <mergeCell ref="CK91:CN100"/>
+    <mergeCell ref="CO91:CR100"/>
+    <mergeCell ref="CK1:CN10"/>
+    <mergeCell ref="CO1:CR10"/>
+    <mergeCell ref="CK11:CN20"/>
+    <mergeCell ref="CO11:CR20"/>
+    <mergeCell ref="CK21:CN30"/>
+    <mergeCell ref="CO21:CR30"/>
+    <mergeCell ref="CK31:CN40"/>
+    <mergeCell ref="CO31:CR40"/>
+    <mergeCell ref="CK41:CN50"/>
+    <mergeCell ref="CO41:CR50"/>
+    <mergeCell ref="CC51:CF60"/>
+    <mergeCell ref="CG51:CJ60"/>
+    <mergeCell ref="CC61:CF70"/>
+    <mergeCell ref="CG61:CJ70"/>
+    <mergeCell ref="CC71:CF80"/>
+    <mergeCell ref="CG71:CJ80"/>
+    <mergeCell ref="CC81:CF90"/>
+    <mergeCell ref="CG81:CJ90"/>
+    <mergeCell ref="CC91:CF100"/>
+    <mergeCell ref="CG91:CJ100"/>
+    <mergeCell ref="CC1:CF10"/>
+    <mergeCell ref="CG1:CJ10"/>
+    <mergeCell ref="CC11:CF20"/>
+    <mergeCell ref="CG11:CJ20"/>
+    <mergeCell ref="CC21:CF30"/>
+    <mergeCell ref="CG21:CJ30"/>
+    <mergeCell ref="CC31:CF40"/>
+    <mergeCell ref="CG31:CJ40"/>
+    <mergeCell ref="CC41:CF50"/>
+    <mergeCell ref="CG41:CJ50"/>
+    <mergeCell ref="AS91:AV100"/>
+    <mergeCell ref="AS61:AV70"/>
+    <mergeCell ref="AO71:AR80"/>
+    <mergeCell ref="AS71:AV80"/>
+    <mergeCell ref="AO81:AR90"/>
+    <mergeCell ref="AS81:AV90"/>
+    <mergeCell ref="AO31:AR40"/>
+    <mergeCell ref="AS31:AV40"/>
+    <mergeCell ref="AO41:AR50"/>
+    <mergeCell ref="AS41:AV50"/>
+    <mergeCell ref="AO51:AR60"/>
+    <mergeCell ref="AS51:AV60"/>
+    <mergeCell ref="AO1:AR10"/>
+    <mergeCell ref="AS1:AV10"/>
+    <mergeCell ref="AO11:AR20"/>
+    <mergeCell ref="AS11:AV20"/>
+    <mergeCell ref="AO21:AR30"/>
+    <mergeCell ref="AS21:AV30"/>
+    <mergeCell ref="AG81:AJ90"/>
+    <mergeCell ref="AK81:AN90"/>
+    <mergeCell ref="AG91:AJ100"/>
+    <mergeCell ref="AK91:AN100"/>
+    <mergeCell ref="AO91:AR100"/>
+    <mergeCell ref="AG51:AJ60"/>
+    <mergeCell ref="AK51:AN60"/>
+    <mergeCell ref="AG61:AJ70"/>
+    <mergeCell ref="AK61:AN70"/>
+    <mergeCell ref="AO61:AR70"/>
+    <mergeCell ref="AG1:AJ10"/>
+    <mergeCell ref="AK1:AN10"/>
+    <mergeCell ref="AG11:AJ20"/>
+    <mergeCell ref="AK11:AN20"/>
+    <mergeCell ref="AG21:AJ30"/>
+    <mergeCell ref="AK21:AN30"/>
+    <mergeCell ref="AG31:AJ40"/>
+    <mergeCell ref="AK31:AN40"/>
+    <mergeCell ref="AG41:AJ50"/>
+    <mergeCell ref="AK41:AN50"/>
+    <mergeCell ref="AG71:AJ80"/>
+    <mergeCell ref="AK71:AN80"/>
+    <mergeCell ref="A1:D10"/>
+    <mergeCell ref="E1:H10"/>
+    <mergeCell ref="A11:D20"/>
+    <mergeCell ref="E11:H20"/>
+    <mergeCell ref="A21:D30"/>
+    <mergeCell ref="E21:H30"/>
+    <mergeCell ref="M31:P40"/>
+    <mergeCell ref="I41:L50"/>
+    <mergeCell ref="M41:P50"/>
+    <mergeCell ref="A31:D40"/>
+    <mergeCell ref="E31:H40"/>
+    <mergeCell ref="A41:D50"/>
+    <mergeCell ref="E41:H50"/>
+    <mergeCell ref="I31:L40"/>
+    <mergeCell ref="I1:L10"/>
+    <mergeCell ref="M1:P10"/>
+    <mergeCell ref="I11:L20"/>
+    <mergeCell ref="M11:P20"/>
+    <mergeCell ref="I21:L30"/>
+    <mergeCell ref="M21:P30"/>
+    <mergeCell ref="A81:D90"/>
+    <mergeCell ref="E81:H90"/>
+    <mergeCell ref="A91:D100"/>
+    <mergeCell ref="E91:H100"/>
+    <mergeCell ref="A51:D60"/>
+    <mergeCell ref="E51:H60"/>
+    <mergeCell ref="A61:D70"/>
+    <mergeCell ref="E61:H70"/>
+    <mergeCell ref="A71:D80"/>
+    <mergeCell ref="E71:H80"/>
+    <mergeCell ref="I81:L90"/>
+    <mergeCell ref="M81:P90"/>
+    <mergeCell ref="I91:L100"/>
+    <mergeCell ref="M91:P100"/>
+    <mergeCell ref="I51:L60"/>
+    <mergeCell ref="M51:P60"/>
+    <mergeCell ref="I61:L70"/>
+    <mergeCell ref="M61:P70"/>
+    <mergeCell ref="I71:L80"/>
+    <mergeCell ref="M71:P80"/>
+    <mergeCell ref="Q1:T10"/>
+    <mergeCell ref="U1:X10"/>
+    <mergeCell ref="Y1:AB10"/>
+    <mergeCell ref="AC1:AF10"/>
+    <mergeCell ref="Q11:T20"/>
+    <mergeCell ref="U11:X20"/>
+    <mergeCell ref="Y11:AB20"/>
+    <mergeCell ref="AC11:AF20"/>
+    <mergeCell ref="Q21:T30"/>
+    <mergeCell ref="U21:X30"/>
+    <mergeCell ref="Y21:AB30"/>
+    <mergeCell ref="AC21:AF30"/>
+    <mergeCell ref="Q31:T40"/>
+    <mergeCell ref="U31:X40"/>
+    <mergeCell ref="Y31:AB40"/>
+    <mergeCell ref="AC31:AF40"/>
+    <mergeCell ref="Q41:T50"/>
+    <mergeCell ref="U41:X50"/>
+    <mergeCell ref="Y41:AB50"/>
+    <mergeCell ref="AC41:AF50"/>
+    <mergeCell ref="Q51:T60"/>
+    <mergeCell ref="U51:X60"/>
+    <mergeCell ref="Y51:AB60"/>
+    <mergeCell ref="AC51:AF60"/>
+    <mergeCell ref="Q61:T70"/>
+    <mergeCell ref="U61:X70"/>
+    <mergeCell ref="Y61:AB70"/>
+    <mergeCell ref="AC61:AF70"/>
+    <mergeCell ref="Q71:T80"/>
+    <mergeCell ref="U71:X80"/>
+    <mergeCell ref="Y71:AB80"/>
+    <mergeCell ref="AC71:AF80"/>
+    <mergeCell ref="Q81:T90"/>
+    <mergeCell ref="U81:X90"/>
+    <mergeCell ref="Y81:AB90"/>
+    <mergeCell ref="AC81:AF90"/>
     <mergeCell ref="Q91:T100"/>
     <mergeCell ref="U91:X100"/>
     <mergeCell ref="Y91:AB100"/>
@@ -13848,122 +16204,66 @@
     <mergeCell ref="BA81:BD90"/>
     <mergeCell ref="AW91:AZ100"/>
     <mergeCell ref="BA91:BD100"/>
-    <mergeCell ref="Q61:T70"/>
-    <mergeCell ref="U61:X70"/>
-    <mergeCell ref="Y61:AB70"/>
-    <mergeCell ref="AC61:AF70"/>
-    <mergeCell ref="Q71:T80"/>
-    <mergeCell ref="U71:X80"/>
-    <mergeCell ref="Y71:AB80"/>
-    <mergeCell ref="AC71:AF80"/>
-    <mergeCell ref="Q81:T90"/>
-    <mergeCell ref="U81:X90"/>
-    <mergeCell ref="Y81:AB90"/>
-    <mergeCell ref="AC81:AF90"/>
-    <mergeCell ref="Q31:T40"/>
-    <mergeCell ref="U31:X40"/>
-    <mergeCell ref="Y31:AB40"/>
-    <mergeCell ref="AC31:AF40"/>
-    <mergeCell ref="Q41:T50"/>
-    <mergeCell ref="U41:X50"/>
-    <mergeCell ref="Y41:AB50"/>
-    <mergeCell ref="AC41:AF50"/>
-    <mergeCell ref="Q51:T60"/>
-    <mergeCell ref="U51:X60"/>
-    <mergeCell ref="Y51:AB60"/>
-    <mergeCell ref="AC51:AF60"/>
-    <mergeCell ref="Q1:T10"/>
-    <mergeCell ref="U1:X10"/>
-    <mergeCell ref="Y1:AB10"/>
-    <mergeCell ref="AC1:AF10"/>
-    <mergeCell ref="Q11:T20"/>
-    <mergeCell ref="U11:X20"/>
-    <mergeCell ref="Y11:AB20"/>
-    <mergeCell ref="AC11:AF20"/>
-    <mergeCell ref="Q21:T30"/>
-    <mergeCell ref="U21:X30"/>
-    <mergeCell ref="Y21:AB30"/>
-    <mergeCell ref="AC21:AF30"/>
-    <mergeCell ref="I81:L90"/>
-    <mergeCell ref="M81:P90"/>
-    <mergeCell ref="I91:L100"/>
-    <mergeCell ref="M91:P100"/>
-    <mergeCell ref="I51:L60"/>
-    <mergeCell ref="M51:P60"/>
-    <mergeCell ref="I61:L70"/>
-    <mergeCell ref="M61:P70"/>
-    <mergeCell ref="I71:L80"/>
-    <mergeCell ref="M71:P80"/>
-    <mergeCell ref="A81:D90"/>
-    <mergeCell ref="E81:H90"/>
-    <mergeCell ref="A91:D100"/>
-    <mergeCell ref="E91:H100"/>
-    <mergeCell ref="A51:D60"/>
-    <mergeCell ref="E51:H60"/>
-    <mergeCell ref="A61:D70"/>
-    <mergeCell ref="E61:H70"/>
-    <mergeCell ref="A71:D80"/>
-    <mergeCell ref="E71:H80"/>
-    <mergeCell ref="AG41:AJ50"/>
-    <mergeCell ref="AK41:AN50"/>
-    <mergeCell ref="AG71:AJ80"/>
-    <mergeCell ref="AK71:AN80"/>
-    <mergeCell ref="A1:D10"/>
-    <mergeCell ref="E1:H10"/>
-    <mergeCell ref="A11:D20"/>
-    <mergeCell ref="E11:H20"/>
-    <mergeCell ref="A21:D30"/>
-    <mergeCell ref="E21:H30"/>
-    <mergeCell ref="M31:P40"/>
-    <mergeCell ref="I41:L50"/>
-    <mergeCell ref="M41:P50"/>
-    <mergeCell ref="A31:D40"/>
-    <mergeCell ref="E31:H40"/>
-    <mergeCell ref="A41:D50"/>
-    <mergeCell ref="E41:H50"/>
-    <mergeCell ref="I31:L40"/>
-    <mergeCell ref="I1:L10"/>
-    <mergeCell ref="M1:P10"/>
-    <mergeCell ref="I11:L20"/>
-    <mergeCell ref="M11:P20"/>
-    <mergeCell ref="I21:L30"/>
-    <mergeCell ref="M21:P30"/>
-    <mergeCell ref="AO1:AR10"/>
-    <mergeCell ref="AS1:AV10"/>
-    <mergeCell ref="AO11:AR20"/>
-    <mergeCell ref="AS11:AV20"/>
-    <mergeCell ref="AO21:AR30"/>
-    <mergeCell ref="AS21:AV30"/>
-    <mergeCell ref="AG81:AJ90"/>
-    <mergeCell ref="AK81:AN90"/>
-    <mergeCell ref="AG91:AJ100"/>
-    <mergeCell ref="AK91:AN100"/>
-    <mergeCell ref="AO91:AR100"/>
-    <mergeCell ref="AG51:AJ60"/>
-    <mergeCell ref="AK51:AN60"/>
-    <mergeCell ref="AG61:AJ70"/>
-    <mergeCell ref="AK61:AN70"/>
-    <mergeCell ref="AO61:AR70"/>
-    <mergeCell ref="AG1:AJ10"/>
-    <mergeCell ref="AK1:AN10"/>
-    <mergeCell ref="AG11:AJ20"/>
-    <mergeCell ref="AK11:AN20"/>
-    <mergeCell ref="AG21:AJ30"/>
-    <mergeCell ref="AK21:AN30"/>
-    <mergeCell ref="AG31:AJ40"/>
-    <mergeCell ref="AK31:AN40"/>
-    <mergeCell ref="AS91:AV100"/>
-    <mergeCell ref="AS61:AV70"/>
-    <mergeCell ref="AO71:AR80"/>
-    <mergeCell ref="AS71:AV80"/>
-    <mergeCell ref="AO81:AR90"/>
-    <mergeCell ref="AS81:AV90"/>
-    <mergeCell ref="AO31:AR40"/>
-    <mergeCell ref="AS31:AV40"/>
-    <mergeCell ref="AO41:AR50"/>
-    <mergeCell ref="AS41:AV50"/>
-    <mergeCell ref="AO51:AR60"/>
-    <mergeCell ref="AS51:AV60"/>
+    <mergeCell ref="BE1:BH10"/>
+    <mergeCell ref="BI1:BL10"/>
+    <mergeCell ref="BE11:BH20"/>
+    <mergeCell ref="BI11:BL20"/>
+    <mergeCell ref="BE21:BH30"/>
+    <mergeCell ref="BI21:BL30"/>
+    <mergeCell ref="BE31:BH40"/>
+    <mergeCell ref="BI31:BL40"/>
+    <mergeCell ref="BE41:BH50"/>
+    <mergeCell ref="BI41:BL50"/>
+    <mergeCell ref="BE51:BH60"/>
+    <mergeCell ref="BI51:BL60"/>
+    <mergeCell ref="BE61:BH70"/>
+    <mergeCell ref="BI61:BL70"/>
+    <mergeCell ref="BE71:BH80"/>
+    <mergeCell ref="BI71:BL80"/>
+    <mergeCell ref="BE81:BH90"/>
+    <mergeCell ref="BI81:BL90"/>
+    <mergeCell ref="BE91:BH100"/>
+    <mergeCell ref="BI91:BL100"/>
+    <mergeCell ref="BM1:BP10"/>
+    <mergeCell ref="BQ1:BT10"/>
+    <mergeCell ref="BM11:BP20"/>
+    <mergeCell ref="BQ11:BT20"/>
+    <mergeCell ref="BM21:BP30"/>
+    <mergeCell ref="BQ21:BT30"/>
+    <mergeCell ref="BM31:BP40"/>
+    <mergeCell ref="BQ31:BT40"/>
+    <mergeCell ref="BM41:BP50"/>
+    <mergeCell ref="BQ41:BT50"/>
+    <mergeCell ref="BM51:BP60"/>
+    <mergeCell ref="BQ51:BT60"/>
+    <mergeCell ref="BM61:BP70"/>
+    <mergeCell ref="BQ61:BT70"/>
+    <mergeCell ref="BM71:BP80"/>
+    <mergeCell ref="BQ71:BT80"/>
+    <mergeCell ref="BM81:BP90"/>
+    <mergeCell ref="BQ81:BT90"/>
+    <mergeCell ref="BM91:BP100"/>
+    <mergeCell ref="BQ91:BT100"/>
+    <mergeCell ref="BU1:BX10"/>
+    <mergeCell ref="BY1:CB10"/>
+    <mergeCell ref="BU11:BX20"/>
+    <mergeCell ref="BY11:CB20"/>
+    <mergeCell ref="BU21:BX30"/>
+    <mergeCell ref="BY21:CB30"/>
+    <mergeCell ref="BU31:BX40"/>
+    <mergeCell ref="BY31:CB40"/>
+    <mergeCell ref="BU41:BX50"/>
+    <mergeCell ref="BY41:CB50"/>
+    <mergeCell ref="BU51:BX60"/>
+    <mergeCell ref="BY51:CB60"/>
+    <mergeCell ref="BU61:BX70"/>
+    <mergeCell ref="BY61:CB70"/>
+    <mergeCell ref="BU71:BX80"/>
+    <mergeCell ref="BY71:CB80"/>
+    <mergeCell ref="BU81:BX90"/>
+    <mergeCell ref="BY81:CB90"/>
+    <mergeCell ref="BU91:BX100"/>
+    <mergeCell ref="BY91:CB100"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.6692913385826772" right="0.6692913385826772" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/tanulókártyák/Tanulókártyák.xlsx
+++ b/tanulókártyák/Tanulókártyák.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atesz\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB57CD8-FA35-41B7-BCD1-48550486BBF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA79994-669B-4107-B260-F61FFCDB1D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1441,9 +1441,6 @@
     <t>Mik a terminal operations a Stream-ekben?</t>
   </si>
   <si>
-    <t>What is JDBC?</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -4650,6 +4647,9 @@
   </si>
   <si>
     <t>Hogyan inicializálunk egy git repository-t?</t>
+  </si>
+  <si>
+    <t>Mi aJDBC?</t>
   </si>
 </sst>
 </file>
@@ -5110,85 +5110,85 @@
       <c r="AM1" s="8"/>
       <c r="AN1" s="8"/>
       <c r="AO1" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AP1" s="8"/>
       <c r="AQ1" s="8"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AT1" s="8"/>
       <c r="AU1" s="8"/>
       <c r="AV1" s="8"/>
       <c r="AW1" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AX1" s="8"/>
       <c r="AY1" s="8"/>
       <c r="AZ1" s="8"/>
       <c r="BA1" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="BB1" s="8"/>
       <c r="BC1" s="8"/>
       <c r="BD1" s="8"/>
       <c r="BE1" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BF1" s="8"/>
       <c r="BG1" s="8"/>
       <c r="BH1" s="8"/>
       <c r="BI1" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BJ1" s="8"/>
       <c r="BK1" s="8"/>
       <c r="BL1" s="8"/>
       <c r="BM1" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="BN1" s="8"/>
       <c r="BO1" s="8"/>
       <c r="BP1" s="8"/>
       <c r="BQ1" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="BR1" s="8"/>
       <c r="BS1" s="8"/>
       <c r="BT1" s="8"/>
       <c r="BU1" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="BV1" s="8"/>
       <c r="BW1" s="8"/>
       <c r="BX1" s="8"/>
       <c r="BY1" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="BZ1" s="8"/>
       <c r="CA1" s="8"/>
       <c r="CB1" s="8"/>
       <c r="CC1" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="CD1" s="8"/>
       <c r="CE1" s="8"/>
       <c r="CF1" s="8"/>
       <c r="CG1" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="CH1" s="8"/>
       <c r="CI1" s="8"/>
       <c r="CJ1" s="8"/>
       <c r="CK1" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="CL1" s="8"/>
       <c r="CM1" s="8"/>
       <c r="CN1" s="8"/>
       <c r="CO1" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="CP1" s="8"/>
       <c r="CQ1" s="8"/>
@@ -6132,91 +6132,91 @@
       <c r="AI11" s="8"/>
       <c r="AJ11" s="8"/>
       <c r="AK11" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL11" s="8"/>
       <c r="AM11" s="8"/>
       <c r="AN11" s="8"/>
       <c r="AO11" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AP11" s="8"/>
       <c r="AQ11" s="8"/>
       <c r="AR11" s="8"/>
       <c r="AS11" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AT11" s="8"/>
       <c r="AU11" s="8"/>
       <c r="AV11" s="8"/>
       <c r="AW11" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AX11" s="8"/>
       <c r="AY11" s="8"/>
       <c r="AZ11" s="8"/>
       <c r="BA11" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BB11" s="8"/>
       <c r="BC11" s="8"/>
       <c r="BD11" s="8"/>
       <c r="BE11" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BF11" s="8"/>
       <c r="BG11" s="8"/>
       <c r="BH11" s="8"/>
       <c r="BI11" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="BJ11" s="8"/>
       <c r="BK11" s="8"/>
       <c r="BL11" s="8"/>
       <c r="BM11" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="BN11" s="8"/>
       <c r="BO11" s="8"/>
       <c r="BP11" s="8"/>
       <c r="BQ11" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="BR11" s="8"/>
       <c r="BS11" s="8"/>
       <c r="BT11" s="8"/>
       <c r="BU11" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BV11" s="8"/>
       <c r="BW11" s="8"/>
       <c r="BX11" s="8"/>
       <c r="BY11" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BZ11" s="8"/>
       <c r="CA11" s="8"/>
       <c r="CB11" s="8"/>
       <c r="CC11" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="CD11" s="8"/>
       <c r="CE11" s="8"/>
       <c r="CF11" s="8"/>
       <c r="CG11" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="CH11" s="8"/>
       <c r="CI11" s="8"/>
       <c r="CJ11" s="8"/>
       <c r="CK11" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="CL11" s="8"/>
       <c r="CM11" s="8"/>
       <c r="CN11" s="8"/>
       <c r="CO11" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="CP11" s="8"/>
       <c r="CQ11" s="8"/>
@@ -7124,7 +7124,7 @@
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N21" s="8"/>
       <c r="O21" s="8"/>
@@ -7154,97 +7154,97 @@
       <c r="AE21" s="8"/>
       <c r="AF21" s="8"/>
       <c r="AG21" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH21" s="8"/>
       <c r="AI21" s="8"/>
       <c r="AJ21" s="8"/>
       <c r="AK21" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AL21" s="8"/>
       <c r="AM21" s="8"/>
       <c r="AN21" s="8"/>
       <c r="AO21" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AP21" s="8"/>
       <c r="AQ21" s="8"/>
       <c r="AR21" s="8"/>
       <c r="AS21" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AT21" s="8"/>
       <c r="AU21" s="8"/>
       <c r="AV21" s="8"/>
       <c r="AW21" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AX21" s="8"/>
       <c r="AY21" s="8"/>
       <c r="AZ21" s="8"/>
       <c r="BA21" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="BB21" s="8"/>
       <c r="BC21" s="8"/>
       <c r="BD21" s="8"/>
       <c r="BE21" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="BF21" s="8"/>
       <c r="BG21" s="8"/>
       <c r="BH21" s="8"/>
       <c r="BI21" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="BJ21" s="8"/>
       <c r="BK21" s="8"/>
       <c r="BL21" s="8"/>
       <c r="BM21" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="BN21" s="8"/>
       <c r="BO21" s="8"/>
       <c r="BP21" s="8"/>
       <c r="BQ21" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="BR21" s="8"/>
       <c r="BS21" s="8"/>
       <c r="BT21" s="8"/>
       <c r="BU21" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="BV21" s="8"/>
       <c r="BW21" s="8"/>
       <c r="BX21" s="8"/>
       <c r="BY21" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BZ21" s="8"/>
       <c r="CA21" s="8"/>
       <c r="CB21" s="8"/>
       <c r="CC21" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="CD21" s="8"/>
       <c r="CE21" s="8"/>
       <c r="CF21" s="8"/>
       <c r="CG21" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="CH21" s="8"/>
       <c r="CI21" s="8"/>
       <c r="CJ21" s="8"/>
       <c r="CK21" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="CL21" s="8"/>
       <c r="CM21" s="8"/>
       <c r="CN21" s="8"/>
       <c r="CO21" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="CP21" s="8"/>
       <c r="CQ21" s="8"/>
@@ -8182,91 +8182,91 @@
       <c r="AE31" s="8"/>
       <c r="AF31" s="8"/>
       <c r="AG31" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AH31" s="8"/>
       <c r="AI31" s="8"/>
       <c r="AJ31" s="8"/>
       <c r="AK31" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AL31" s="8"/>
       <c r="AM31" s="8"/>
       <c r="AN31" s="8"/>
       <c r="AO31" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP31" s="8"/>
       <c r="AQ31" s="8"/>
       <c r="AR31" s="8"/>
       <c r="AS31" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AT31" s="8"/>
       <c r="AU31" s="8"/>
       <c r="AV31" s="8"/>
       <c r="AW31" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AX31" s="8"/>
       <c r="AY31" s="8"/>
       <c r="AZ31" s="8"/>
       <c r="BA31" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="BB31" s="8"/>
       <c r="BC31" s="8"/>
       <c r="BD31" s="8"/>
       <c r="BE31" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="BF31" s="8"/>
       <c r="BG31" s="8"/>
       <c r="BH31" s="8"/>
       <c r="BI31" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="BJ31" s="8"/>
       <c r="BK31" s="8"/>
       <c r="BL31" s="8"/>
       <c r="BM31" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="BN31" s="8"/>
       <c r="BO31" s="8"/>
       <c r="BP31" s="8"/>
       <c r="BQ31" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="BR31" s="8"/>
       <c r="BS31" s="8"/>
       <c r="BT31" s="8"/>
       <c r="BU31" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BV31" s="8"/>
       <c r="BW31" s="8"/>
       <c r="BX31" s="8"/>
       <c r="BY31" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BZ31" s="8"/>
       <c r="CA31" s="8"/>
       <c r="CB31" s="8"/>
       <c r="CC31" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="CD31" s="8"/>
       <c r="CE31" s="8"/>
       <c r="CF31" s="8"/>
       <c r="CG31" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="CH31" s="8"/>
       <c r="CI31" s="8"/>
       <c r="CJ31" s="8"/>
       <c r="CK31" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="CL31" s="8"/>
       <c r="CM31" s="8"/>
@@ -9196,7 +9196,7 @@
       <c r="W41" s="8"/>
       <c r="X41" s="8"/>
       <c r="Y41" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Z41" s="8"/>
       <c r="AA41" s="8"/>
@@ -9208,85 +9208,85 @@
       <c r="AE41" s="8"/>
       <c r="AF41" s="8"/>
       <c r="AG41" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AH41" s="8"/>
       <c r="AI41" s="8"/>
       <c r="AJ41" s="8"/>
       <c r="AK41" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AL41" s="8"/>
       <c r="AM41" s="8"/>
       <c r="AN41" s="8"/>
       <c r="AO41" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AP41" s="8"/>
       <c r="AQ41" s="8"/>
       <c r="AR41" s="8"/>
       <c r="AS41" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AT41" s="8"/>
       <c r="AU41" s="8"/>
       <c r="AV41" s="8"/>
       <c r="AW41" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AX41" s="8"/>
       <c r="AY41" s="8"/>
       <c r="AZ41" s="8"/>
       <c r="BA41" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="BB41" s="8"/>
       <c r="BC41" s="8"/>
       <c r="BD41" s="8"/>
       <c r="BE41" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="BF41" s="8"/>
       <c r="BG41" s="8"/>
       <c r="BH41" s="8"/>
       <c r="BI41" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="BJ41" s="8"/>
       <c r="BK41" s="8"/>
       <c r="BL41" s="8"/>
       <c r="BM41" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="BN41" s="8"/>
       <c r="BO41" s="8"/>
       <c r="BP41" s="8"/>
       <c r="BQ41" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="BR41" s="8"/>
       <c r="BS41" s="8"/>
       <c r="BT41" s="8"/>
       <c r="BU41" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BV41" s="8"/>
       <c r="BW41" s="8"/>
       <c r="BX41" s="8"/>
       <c r="BY41" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BZ41" s="8"/>
       <c r="CA41" s="8"/>
       <c r="CB41" s="8"/>
       <c r="CC41" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="CD41" s="8"/>
       <c r="CE41" s="8"/>
       <c r="CF41" s="8"/>
       <c r="CG41" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="CH41" s="8"/>
       <c r="CI41" s="8"/>
@@ -10244,85 +10244,85 @@
       <c r="AM51" s="6"/>
       <c r="AN51" s="6"/>
       <c r="AO51" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AP51" s="6"/>
       <c r="AQ51" s="6"/>
       <c r="AR51" s="6"/>
       <c r="AS51" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AT51" s="6"/>
       <c r="AU51" s="6"/>
       <c r="AV51" s="6"/>
       <c r="AW51" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AX51" s="6"/>
       <c r="AY51" s="6"/>
       <c r="AZ51" s="6"/>
       <c r="BA51" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BB51" s="6"/>
       <c r="BC51" s="6"/>
       <c r="BD51" s="6"/>
       <c r="BE51" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BF51" s="6"/>
       <c r="BG51" s="6"/>
       <c r="BH51" s="6"/>
       <c r="BI51" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BJ51" s="6"/>
       <c r="BK51" s="6"/>
       <c r="BL51" s="6"/>
       <c r="BM51" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="BN51" s="6"/>
       <c r="BO51" s="6"/>
       <c r="BP51" s="6"/>
       <c r="BQ51" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="BR51" s="6"/>
       <c r="BS51" s="6"/>
       <c r="BT51" s="6"/>
       <c r="BU51" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BV51" s="6"/>
       <c r="BW51" s="6"/>
       <c r="BX51" s="6"/>
       <c r="BY51" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="BZ51" s="6"/>
       <c r="CA51" s="6"/>
       <c r="CB51" s="6"/>
       <c r="CC51" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="CD51" s="6"/>
       <c r="CE51" s="6"/>
       <c r="CF51" s="6"/>
       <c r="CG51" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="CH51" s="6"/>
       <c r="CI51" s="6"/>
       <c r="CJ51" s="6"/>
       <c r="CK51" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="CL51" s="6"/>
       <c r="CM51" s="6"/>
       <c r="CN51" s="6"/>
       <c r="CO51" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="CP51" s="6"/>
       <c r="CQ51" s="6"/>
@@ -11260,7 +11260,7 @@
       <c r="AE61" s="6"/>
       <c r="AF61" s="6"/>
       <c r="AG61" s="5" t="s">
-        <v>83</v>
+        <v>232</v>
       </c>
       <c r="AH61" s="6"/>
       <c r="AI61" s="6"/>
@@ -11272,85 +11272,85 @@
       <c r="AM61" s="6"/>
       <c r="AN61" s="6"/>
       <c r="AO61" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AP61" s="6"/>
       <c r="AQ61" s="6"/>
       <c r="AR61" s="6"/>
       <c r="AS61" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AT61" s="6"/>
       <c r="AU61" s="6"/>
       <c r="AV61" s="6"/>
       <c r="AW61" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AX61" s="6"/>
       <c r="AY61" s="6"/>
       <c r="AZ61" s="6"/>
       <c r="BA61" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="BB61" s="6"/>
       <c r="BC61" s="6"/>
       <c r="BD61" s="6"/>
       <c r="BE61" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="BF61" s="6"/>
       <c r="BG61" s="6"/>
       <c r="BH61" s="6"/>
       <c r="BI61" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="BJ61" s="6"/>
       <c r="BK61" s="6"/>
       <c r="BL61" s="6"/>
       <c r="BM61" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="BN61" s="6"/>
       <c r="BO61" s="6"/>
       <c r="BP61" s="6"/>
       <c r="BQ61" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BR61" s="6"/>
       <c r="BS61" s="6"/>
       <c r="BT61" s="6"/>
       <c r="BU61" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BV61" s="6"/>
       <c r="BW61" s="6"/>
       <c r="BX61" s="6"/>
       <c r="BY61" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BZ61" s="6"/>
       <c r="CA61" s="6"/>
       <c r="CB61" s="6"/>
       <c r="CC61" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="CD61" s="6"/>
       <c r="CE61" s="6"/>
       <c r="CF61" s="6"/>
       <c r="CG61" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="CH61" s="6"/>
       <c r="CI61" s="6"/>
       <c r="CJ61" s="6"/>
       <c r="CK61" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="CL61" s="6"/>
       <c r="CM61" s="6"/>
       <c r="CN61" s="6"/>
       <c r="CO61" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="CP61" s="6"/>
       <c r="CQ61" s="6"/>
@@ -12288,97 +12288,97 @@
       <c r="AE71" s="6"/>
       <c r="AF71" s="6"/>
       <c r="AG71" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH71" s="6"/>
       <c r="AI71" s="6"/>
       <c r="AJ71" s="6"/>
       <c r="AK71" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL71" s="6"/>
       <c r="AM71" s="6"/>
       <c r="AN71" s="6"/>
       <c r="AO71" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AP71" s="6"/>
       <c r="AQ71" s="6"/>
       <c r="AR71" s="6"/>
       <c r="AS71" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AT71" s="6"/>
       <c r="AU71" s="6"/>
       <c r="AV71" s="6"/>
       <c r="AW71" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AX71" s="6"/>
       <c r="AY71" s="6"/>
       <c r="AZ71" s="6"/>
       <c r="BA71" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BB71" s="6"/>
       <c r="BC71" s="6"/>
       <c r="BD71" s="6"/>
       <c r="BE71" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="BF71" s="6"/>
       <c r="BG71" s="6"/>
       <c r="BH71" s="6"/>
       <c r="BI71" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="BJ71" s="6"/>
       <c r="BK71" s="6"/>
       <c r="BL71" s="6"/>
       <c r="BM71" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BN71" s="6"/>
       <c r="BO71" s="6"/>
       <c r="BP71" s="6"/>
       <c r="BQ71" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="BR71" s="6"/>
       <c r="BS71" s="6"/>
       <c r="BT71" s="6"/>
       <c r="BU71" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BV71" s="6"/>
       <c r="BW71" s="6"/>
       <c r="BX71" s="6"/>
       <c r="BY71" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BZ71" s="6"/>
       <c r="CA71" s="6"/>
       <c r="CB71" s="6"/>
       <c r="CC71" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="CD71" s="6"/>
       <c r="CE71" s="6"/>
       <c r="CF71" s="6"/>
       <c r="CG71" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="CH71" s="6"/>
       <c r="CI71" s="6"/>
       <c r="CJ71" s="6"/>
       <c r="CK71" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="CL71" s="6"/>
       <c r="CM71" s="6"/>
       <c r="CN71" s="6"/>
       <c r="CO71" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="CP71" s="6"/>
       <c r="CQ71" s="6"/>
@@ -13316,85 +13316,85 @@
       <c r="AE81" s="6"/>
       <c r="AF81" s="6"/>
       <c r="AG81" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AH81" s="6"/>
       <c r="AI81" s="6"/>
       <c r="AJ81" s="6"/>
       <c r="AK81" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AL81" s="6"/>
       <c r="AM81" s="6"/>
       <c r="AN81" s="6"/>
       <c r="AO81" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AP81" s="6"/>
       <c r="AQ81" s="6"/>
       <c r="AR81" s="6"/>
       <c r="AS81" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AT81" s="6"/>
       <c r="AU81" s="6"/>
       <c r="AV81" s="6"/>
       <c r="AW81" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AX81" s="6"/>
       <c r="AY81" s="6"/>
       <c r="AZ81" s="6"/>
       <c r="BA81" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BB81" s="6"/>
       <c r="BC81" s="6"/>
       <c r="BD81" s="6"/>
       <c r="BE81" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="BF81" s="6"/>
       <c r="BG81" s="6"/>
       <c r="BH81" s="6"/>
       <c r="BI81" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="BJ81" s="6"/>
       <c r="BK81" s="6"/>
       <c r="BL81" s="6"/>
       <c r="BM81" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="BN81" s="6"/>
       <c r="BO81" s="6"/>
       <c r="BP81" s="6"/>
       <c r="BQ81" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="BR81" s="6"/>
       <c r="BS81" s="6"/>
       <c r="BT81" s="6"/>
       <c r="BU81" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="BV81" s="6"/>
       <c r="BW81" s="6"/>
       <c r="BX81" s="6"/>
       <c r="BY81" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="BZ81" s="6"/>
       <c r="CA81" s="6"/>
       <c r="CB81" s="6"/>
       <c r="CC81" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="CD81" s="6"/>
       <c r="CE81" s="6"/>
       <c r="CF81" s="6"/>
       <c r="CG81" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="CH81" s="6"/>
       <c r="CI81" s="6"/>
@@ -13404,7 +13404,7 @@
       <c r="CM81" s="6"/>
       <c r="CN81" s="6"/>
       <c r="CO81" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CP81" s="6"/>
       <c r="CQ81" s="6"/>
@@ -14342,85 +14342,85 @@
       <c r="AE91" s="6"/>
       <c r="AF91" s="6"/>
       <c r="AG91" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AH91" s="6"/>
       <c r="AI91" s="6"/>
       <c r="AJ91" s="6"/>
       <c r="AK91" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AL91" s="6"/>
       <c r="AM91" s="6"/>
       <c r="AN91" s="6"/>
       <c r="AO91" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AP91" s="6"/>
       <c r="AQ91" s="6"/>
       <c r="AR91" s="6"/>
       <c r="AS91" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AT91" s="6"/>
       <c r="AU91" s="6"/>
       <c r="AV91" s="6"/>
       <c r="AW91" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AX91" s="6"/>
       <c r="AY91" s="6"/>
       <c r="AZ91" s="6"/>
       <c r="BA91" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="BB91" s="6"/>
       <c r="BC91" s="6"/>
       <c r="BD91" s="6"/>
       <c r="BE91" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="BF91" s="6"/>
       <c r="BG91" s="6"/>
       <c r="BH91" s="6"/>
       <c r="BI91" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="BJ91" s="6"/>
       <c r="BK91" s="6"/>
       <c r="BL91" s="6"/>
       <c r="BM91" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="BN91" s="6"/>
       <c r="BO91" s="6"/>
       <c r="BP91" s="6"/>
       <c r="BQ91" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BR91" s="6"/>
       <c r="BS91" s="6"/>
       <c r="BT91" s="6"/>
       <c r="BU91" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BV91" s="6"/>
       <c r="BW91" s="6"/>
       <c r="BX91" s="6"/>
       <c r="BY91" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BZ91" s="6"/>
       <c r="CA91" s="6"/>
       <c r="CB91" s="6"/>
       <c r="CC91" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="CD91" s="6"/>
       <c r="CE91" s="6"/>
       <c r="CF91" s="6"/>
       <c r="CG91" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="CH91" s="6"/>
       <c r="CI91" s="6"/>
@@ -16024,58 +16024,170 @@
     </row>
   </sheetData>
   <mergeCells count="240">
-    <mergeCell ref="CK51:CN60"/>
-    <mergeCell ref="CO51:CR60"/>
-    <mergeCell ref="CK61:CN70"/>
-    <mergeCell ref="CO61:CR70"/>
-    <mergeCell ref="CK71:CN80"/>
-    <mergeCell ref="CO71:CR80"/>
-    <mergeCell ref="CK81:CN90"/>
-    <mergeCell ref="CO81:CR90"/>
-    <mergeCell ref="CK91:CN100"/>
-    <mergeCell ref="CO91:CR100"/>
-    <mergeCell ref="CK1:CN10"/>
-    <mergeCell ref="CO1:CR10"/>
-    <mergeCell ref="CK11:CN20"/>
-    <mergeCell ref="CO11:CR20"/>
-    <mergeCell ref="CK21:CN30"/>
-    <mergeCell ref="CO21:CR30"/>
-    <mergeCell ref="CK31:CN40"/>
-    <mergeCell ref="CO31:CR40"/>
-    <mergeCell ref="CK41:CN50"/>
-    <mergeCell ref="CO41:CR50"/>
-    <mergeCell ref="CC51:CF60"/>
-    <mergeCell ref="CG51:CJ60"/>
-    <mergeCell ref="CC61:CF70"/>
-    <mergeCell ref="CG61:CJ70"/>
-    <mergeCell ref="CC71:CF80"/>
-    <mergeCell ref="CG71:CJ80"/>
-    <mergeCell ref="CC81:CF90"/>
-    <mergeCell ref="CG81:CJ90"/>
-    <mergeCell ref="CC91:CF100"/>
-    <mergeCell ref="CG91:CJ100"/>
-    <mergeCell ref="CC1:CF10"/>
-    <mergeCell ref="CG1:CJ10"/>
-    <mergeCell ref="CC11:CF20"/>
-    <mergeCell ref="CG11:CJ20"/>
-    <mergeCell ref="CC21:CF30"/>
-    <mergeCell ref="CG21:CJ30"/>
-    <mergeCell ref="CC31:CF40"/>
-    <mergeCell ref="CG31:CJ40"/>
-    <mergeCell ref="CC41:CF50"/>
-    <mergeCell ref="CG41:CJ50"/>
-    <mergeCell ref="AS91:AV100"/>
-    <mergeCell ref="AS61:AV70"/>
-    <mergeCell ref="AO71:AR80"/>
-    <mergeCell ref="AS71:AV80"/>
-    <mergeCell ref="AO81:AR90"/>
-    <mergeCell ref="AS81:AV90"/>
-    <mergeCell ref="AO31:AR40"/>
-    <mergeCell ref="AS31:AV40"/>
-    <mergeCell ref="AO41:AR50"/>
-    <mergeCell ref="AS41:AV50"/>
-    <mergeCell ref="AO51:AR60"/>
-    <mergeCell ref="AS51:AV60"/>
+    <mergeCell ref="BU51:BX60"/>
+    <mergeCell ref="BY51:CB60"/>
+    <mergeCell ref="BU61:BX70"/>
+    <mergeCell ref="BY61:CB70"/>
+    <mergeCell ref="BU71:BX80"/>
+    <mergeCell ref="BY71:CB80"/>
+    <mergeCell ref="BU81:BX90"/>
+    <mergeCell ref="BY81:CB90"/>
+    <mergeCell ref="BU91:BX100"/>
+    <mergeCell ref="BY91:CB100"/>
+    <mergeCell ref="BU1:BX10"/>
+    <mergeCell ref="BY1:CB10"/>
+    <mergeCell ref="BU11:BX20"/>
+    <mergeCell ref="BY11:CB20"/>
+    <mergeCell ref="BU21:BX30"/>
+    <mergeCell ref="BY21:CB30"/>
+    <mergeCell ref="BU31:BX40"/>
+    <mergeCell ref="BY31:CB40"/>
+    <mergeCell ref="BU41:BX50"/>
+    <mergeCell ref="BY41:CB50"/>
+    <mergeCell ref="BM51:BP60"/>
+    <mergeCell ref="BQ51:BT60"/>
+    <mergeCell ref="BM61:BP70"/>
+    <mergeCell ref="BQ61:BT70"/>
+    <mergeCell ref="BM71:BP80"/>
+    <mergeCell ref="BQ71:BT80"/>
+    <mergeCell ref="BM81:BP90"/>
+    <mergeCell ref="BQ81:BT90"/>
+    <mergeCell ref="BM91:BP100"/>
+    <mergeCell ref="BQ91:BT100"/>
+    <mergeCell ref="BM1:BP10"/>
+    <mergeCell ref="BQ1:BT10"/>
+    <mergeCell ref="BM11:BP20"/>
+    <mergeCell ref="BQ11:BT20"/>
+    <mergeCell ref="BM21:BP30"/>
+    <mergeCell ref="BQ21:BT30"/>
+    <mergeCell ref="BM31:BP40"/>
+    <mergeCell ref="BQ31:BT40"/>
+    <mergeCell ref="BM41:BP50"/>
+    <mergeCell ref="BQ41:BT50"/>
+    <mergeCell ref="BE51:BH60"/>
+    <mergeCell ref="BI51:BL60"/>
+    <mergeCell ref="BE61:BH70"/>
+    <mergeCell ref="BI61:BL70"/>
+    <mergeCell ref="BE71:BH80"/>
+    <mergeCell ref="BI71:BL80"/>
+    <mergeCell ref="BE81:BH90"/>
+    <mergeCell ref="BI81:BL90"/>
+    <mergeCell ref="BE91:BH100"/>
+    <mergeCell ref="BI91:BL100"/>
+    <mergeCell ref="BE1:BH10"/>
+    <mergeCell ref="BI1:BL10"/>
+    <mergeCell ref="BE11:BH20"/>
+    <mergeCell ref="BI11:BL20"/>
+    <mergeCell ref="BE21:BH30"/>
+    <mergeCell ref="BI21:BL30"/>
+    <mergeCell ref="BE31:BH40"/>
+    <mergeCell ref="BI31:BL40"/>
+    <mergeCell ref="BE41:BH50"/>
+    <mergeCell ref="BI41:BL50"/>
+    <mergeCell ref="Q91:T100"/>
+    <mergeCell ref="U91:X100"/>
+    <mergeCell ref="Y91:AB100"/>
+    <mergeCell ref="AC91:AF100"/>
+    <mergeCell ref="AW1:AZ10"/>
+    <mergeCell ref="BA1:BD10"/>
+    <mergeCell ref="AW11:AZ20"/>
+    <mergeCell ref="BA11:BD20"/>
+    <mergeCell ref="AW21:AZ30"/>
+    <mergeCell ref="BA21:BD30"/>
+    <mergeCell ref="AW31:AZ40"/>
+    <mergeCell ref="BA31:BD40"/>
+    <mergeCell ref="AW41:AZ50"/>
+    <mergeCell ref="BA41:BD50"/>
+    <mergeCell ref="AW51:AZ60"/>
+    <mergeCell ref="BA51:BD60"/>
+    <mergeCell ref="AW61:AZ70"/>
+    <mergeCell ref="BA61:BD70"/>
+    <mergeCell ref="AW71:AZ80"/>
+    <mergeCell ref="BA71:BD80"/>
+    <mergeCell ref="AW81:AZ90"/>
+    <mergeCell ref="BA81:BD90"/>
+    <mergeCell ref="AW91:AZ100"/>
+    <mergeCell ref="BA91:BD100"/>
+    <mergeCell ref="Q61:T70"/>
+    <mergeCell ref="U61:X70"/>
+    <mergeCell ref="Y61:AB70"/>
+    <mergeCell ref="AC61:AF70"/>
+    <mergeCell ref="Q71:T80"/>
+    <mergeCell ref="U71:X80"/>
+    <mergeCell ref="Y71:AB80"/>
+    <mergeCell ref="AC71:AF80"/>
+    <mergeCell ref="Q81:T90"/>
+    <mergeCell ref="U81:X90"/>
+    <mergeCell ref="Y81:AB90"/>
+    <mergeCell ref="AC81:AF90"/>
+    <mergeCell ref="Q31:T40"/>
+    <mergeCell ref="U31:X40"/>
+    <mergeCell ref="Y31:AB40"/>
+    <mergeCell ref="AC31:AF40"/>
+    <mergeCell ref="Q41:T50"/>
+    <mergeCell ref="U41:X50"/>
+    <mergeCell ref="Y41:AB50"/>
+    <mergeCell ref="AC41:AF50"/>
+    <mergeCell ref="Q51:T60"/>
+    <mergeCell ref="U51:X60"/>
+    <mergeCell ref="Y51:AB60"/>
+    <mergeCell ref="AC51:AF60"/>
+    <mergeCell ref="Q1:T10"/>
+    <mergeCell ref="U1:X10"/>
+    <mergeCell ref="Y1:AB10"/>
+    <mergeCell ref="AC1:AF10"/>
+    <mergeCell ref="Q11:T20"/>
+    <mergeCell ref="U11:X20"/>
+    <mergeCell ref="Y11:AB20"/>
+    <mergeCell ref="AC11:AF20"/>
+    <mergeCell ref="Q21:T30"/>
+    <mergeCell ref="U21:X30"/>
+    <mergeCell ref="Y21:AB30"/>
+    <mergeCell ref="AC21:AF30"/>
+    <mergeCell ref="I81:L90"/>
+    <mergeCell ref="M81:P90"/>
+    <mergeCell ref="I91:L100"/>
+    <mergeCell ref="M91:P100"/>
+    <mergeCell ref="I51:L60"/>
+    <mergeCell ref="M51:P60"/>
+    <mergeCell ref="I61:L70"/>
+    <mergeCell ref="M61:P70"/>
+    <mergeCell ref="I71:L80"/>
+    <mergeCell ref="M71:P80"/>
+    <mergeCell ref="A81:D90"/>
+    <mergeCell ref="E81:H90"/>
+    <mergeCell ref="A91:D100"/>
+    <mergeCell ref="E91:H100"/>
+    <mergeCell ref="A51:D60"/>
+    <mergeCell ref="E51:H60"/>
+    <mergeCell ref="A61:D70"/>
+    <mergeCell ref="E61:H70"/>
+    <mergeCell ref="A71:D80"/>
+    <mergeCell ref="E71:H80"/>
+    <mergeCell ref="AG41:AJ50"/>
+    <mergeCell ref="AK41:AN50"/>
+    <mergeCell ref="AG71:AJ80"/>
+    <mergeCell ref="AK71:AN80"/>
+    <mergeCell ref="A1:D10"/>
+    <mergeCell ref="E1:H10"/>
+    <mergeCell ref="A11:D20"/>
+    <mergeCell ref="E11:H20"/>
+    <mergeCell ref="A21:D30"/>
+    <mergeCell ref="E21:H30"/>
+    <mergeCell ref="M31:P40"/>
+    <mergeCell ref="I41:L50"/>
+    <mergeCell ref="M41:P50"/>
+    <mergeCell ref="A31:D40"/>
+    <mergeCell ref="E31:H40"/>
+    <mergeCell ref="A41:D50"/>
+    <mergeCell ref="E41:H50"/>
+    <mergeCell ref="I31:L40"/>
+    <mergeCell ref="I1:L10"/>
+    <mergeCell ref="M1:P10"/>
+    <mergeCell ref="I11:L20"/>
+    <mergeCell ref="M11:P20"/>
+    <mergeCell ref="I21:L30"/>
+    <mergeCell ref="M21:P30"/>
     <mergeCell ref="AO1:AR10"/>
     <mergeCell ref="AS1:AV10"/>
     <mergeCell ref="AO11:AR20"/>
@@ -16100,170 +16212,58 @@
     <mergeCell ref="AK21:AN30"/>
     <mergeCell ref="AG31:AJ40"/>
     <mergeCell ref="AK31:AN40"/>
-    <mergeCell ref="AG41:AJ50"/>
-    <mergeCell ref="AK41:AN50"/>
-    <mergeCell ref="AG71:AJ80"/>
-    <mergeCell ref="AK71:AN80"/>
-    <mergeCell ref="A1:D10"/>
-    <mergeCell ref="E1:H10"/>
-    <mergeCell ref="A11:D20"/>
-    <mergeCell ref="E11:H20"/>
-    <mergeCell ref="A21:D30"/>
-    <mergeCell ref="E21:H30"/>
-    <mergeCell ref="M31:P40"/>
-    <mergeCell ref="I41:L50"/>
-    <mergeCell ref="M41:P50"/>
-    <mergeCell ref="A31:D40"/>
-    <mergeCell ref="E31:H40"/>
-    <mergeCell ref="A41:D50"/>
-    <mergeCell ref="E41:H50"/>
-    <mergeCell ref="I31:L40"/>
-    <mergeCell ref="I1:L10"/>
-    <mergeCell ref="M1:P10"/>
-    <mergeCell ref="I11:L20"/>
-    <mergeCell ref="M11:P20"/>
-    <mergeCell ref="I21:L30"/>
-    <mergeCell ref="M21:P30"/>
-    <mergeCell ref="A81:D90"/>
-    <mergeCell ref="E81:H90"/>
-    <mergeCell ref="A91:D100"/>
-    <mergeCell ref="E91:H100"/>
-    <mergeCell ref="A51:D60"/>
-    <mergeCell ref="E51:H60"/>
-    <mergeCell ref="A61:D70"/>
-    <mergeCell ref="E61:H70"/>
-    <mergeCell ref="A71:D80"/>
-    <mergeCell ref="E71:H80"/>
-    <mergeCell ref="I81:L90"/>
-    <mergeCell ref="M81:P90"/>
-    <mergeCell ref="I91:L100"/>
-    <mergeCell ref="M91:P100"/>
-    <mergeCell ref="I51:L60"/>
-    <mergeCell ref="M51:P60"/>
-    <mergeCell ref="I61:L70"/>
-    <mergeCell ref="M61:P70"/>
-    <mergeCell ref="I71:L80"/>
-    <mergeCell ref="M71:P80"/>
-    <mergeCell ref="Q1:T10"/>
-    <mergeCell ref="U1:X10"/>
-    <mergeCell ref="Y1:AB10"/>
-    <mergeCell ref="AC1:AF10"/>
-    <mergeCell ref="Q11:T20"/>
-    <mergeCell ref="U11:X20"/>
-    <mergeCell ref="Y11:AB20"/>
-    <mergeCell ref="AC11:AF20"/>
-    <mergeCell ref="Q21:T30"/>
-    <mergeCell ref="U21:X30"/>
-    <mergeCell ref="Y21:AB30"/>
-    <mergeCell ref="AC21:AF30"/>
-    <mergeCell ref="Q31:T40"/>
-    <mergeCell ref="U31:X40"/>
-    <mergeCell ref="Y31:AB40"/>
-    <mergeCell ref="AC31:AF40"/>
-    <mergeCell ref="Q41:T50"/>
-    <mergeCell ref="U41:X50"/>
-    <mergeCell ref="Y41:AB50"/>
-    <mergeCell ref="AC41:AF50"/>
-    <mergeCell ref="Q51:T60"/>
-    <mergeCell ref="U51:X60"/>
-    <mergeCell ref="Y51:AB60"/>
-    <mergeCell ref="AC51:AF60"/>
-    <mergeCell ref="Q61:T70"/>
-    <mergeCell ref="U61:X70"/>
-    <mergeCell ref="Y61:AB70"/>
-    <mergeCell ref="AC61:AF70"/>
-    <mergeCell ref="Q71:T80"/>
-    <mergeCell ref="U71:X80"/>
-    <mergeCell ref="Y71:AB80"/>
-    <mergeCell ref="AC71:AF80"/>
-    <mergeCell ref="Q81:T90"/>
-    <mergeCell ref="U81:X90"/>
-    <mergeCell ref="Y81:AB90"/>
-    <mergeCell ref="AC81:AF90"/>
-    <mergeCell ref="Q91:T100"/>
-    <mergeCell ref="U91:X100"/>
-    <mergeCell ref="Y91:AB100"/>
-    <mergeCell ref="AC91:AF100"/>
-    <mergeCell ref="AW1:AZ10"/>
-    <mergeCell ref="BA1:BD10"/>
-    <mergeCell ref="AW11:AZ20"/>
-    <mergeCell ref="BA11:BD20"/>
-    <mergeCell ref="AW21:AZ30"/>
-    <mergeCell ref="BA21:BD30"/>
-    <mergeCell ref="AW31:AZ40"/>
-    <mergeCell ref="BA31:BD40"/>
-    <mergeCell ref="AW41:AZ50"/>
-    <mergeCell ref="BA41:BD50"/>
-    <mergeCell ref="AW51:AZ60"/>
-    <mergeCell ref="BA51:BD60"/>
-    <mergeCell ref="AW61:AZ70"/>
-    <mergeCell ref="BA61:BD70"/>
-    <mergeCell ref="AW71:AZ80"/>
-    <mergeCell ref="BA71:BD80"/>
-    <mergeCell ref="AW81:AZ90"/>
-    <mergeCell ref="BA81:BD90"/>
-    <mergeCell ref="AW91:AZ100"/>
-    <mergeCell ref="BA91:BD100"/>
-    <mergeCell ref="BE1:BH10"/>
-    <mergeCell ref="BI1:BL10"/>
-    <mergeCell ref="BE11:BH20"/>
-    <mergeCell ref="BI11:BL20"/>
-    <mergeCell ref="BE21:BH30"/>
-    <mergeCell ref="BI21:BL30"/>
-    <mergeCell ref="BE31:BH40"/>
-    <mergeCell ref="BI31:BL40"/>
-    <mergeCell ref="BE41:BH50"/>
-    <mergeCell ref="BI41:BL50"/>
-    <mergeCell ref="BE51:BH60"/>
-    <mergeCell ref="BI51:BL60"/>
-    <mergeCell ref="BE61:BH70"/>
-    <mergeCell ref="BI61:BL70"/>
-    <mergeCell ref="BE71:BH80"/>
-    <mergeCell ref="BI71:BL80"/>
-    <mergeCell ref="BE81:BH90"/>
-    <mergeCell ref="BI81:BL90"/>
-    <mergeCell ref="BE91:BH100"/>
-    <mergeCell ref="BI91:BL100"/>
-    <mergeCell ref="BM1:BP10"/>
-    <mergeCell ref="BQ1:BT10"/>
-    <mergeCell ref="BM11:BP20"/>
-    <mergeCell ref="BQ11:BT20"/>
-    <mergeCell ref="BM21:BP30"/>
-    <mergeCell ref="BQ21:BT30"/>
-    <mergeCell ref="BM31:BP40"/>
-    <mergeCell ref="BQ31:BT40"/>
-    <mergeCell ref="BM41:BP50"/>
-    <mergeCell ref="BQ41:BT50"/>
-    <mergeCell ref="BM51:BP60"/>
-    <mergeCell ref="BQ51:BT60"/>
-    <mergeCell ref="BM61:BP70"/>
-    <mergeCell ref="BQ61:BT70"/>
-    <mergeCell ref="BM71:BP80"/>
-    <mergeCell ref="BQ71:BT80"/>
-    <mergeCell ref="BM81:BP90"/>
-    <mergeCell ref="BQ81:BT90"/>
-    <mergeCell ref="BM91:BP100"/>
-    <mergeCell ref="BQ91:BT100"/>
-    <mergeCell ref="BU1:BX10"/>
-    <mergeCell ref="BY1:CB10"/>
-    <mergeCell ref="BU11:BX20"/>
-    <mergeCell ref="BY11:CB20"/>
-    <mergeCell ref="BU21:BX30"/>
-    <mergeCell ref="BY21:CB30"/>
-    <mergeCell ref="BU31:BX40"/>
-    <mergeCell ref="BY31:CB40"/>
-    <mergeCell ref="BU41:BX50"/>
-    <mergeCell ref="BY41:CB50"/>
-    <mergeCell ref="BU51:BX60"/>
-    <mergeCell ref="BY51:CB60"/>
-    <mergeCell ref="BU61:BX70"/>
-    <mergeCell ref="BY61:CB70"/>
-    <mergeCell ref="BU71:BX80"/>
-    <mergeCell ref="BY71:CB80"/>
-    <mergeCell ref="BU81:BX90"/>
-    <mergeCell ref="BY81:CB90"/>
-    <mergeCell ref="BU91:BX100"/>
-    <mergeCell ref="BY91:CB100"/>
+    <mergeCell ref="AS91:AV100"/>
+    <mergeCell ref="AS61:AV70"/>
+    <mergeCell ref="AO71:AR80"/>
+    <mergeCell ref="AS71:AV80"/>
+    <mergeCell ref="AO81:AR90"/>
+    <mergeCell ref="AS81:AV90"/>
+    <mergeCell ref="AO31:AR40"/>
+    <mergeCell ref="AS31:AV40"/>
+    <mergeCell ref="AO41:AR50"/>
+    <mergeCell ref="AS41:AV50"/>
+    <mergeCell ref="AO51:AR60"/>
+    <mergeCell ref="AS51:AV60"/>
+    <mergeCell ref="CC1:CF10"/>
+    <mergeCell ref="CG1:CJ10"/>
+    <mergeCell ref="CC11:CF20"/>
+    <mergeCell ref="CG11:CJ20"/>
+    <mergeCell ref="CC21:CF30"/>
+    <mergeCell ref="CG21:CJ30"/>
+    <mergeCell ref="CC31:CF40"/>
+    <mergeCell ref="CG31:CJ40"/>
+    <mergeCell ref="CC41:CF50"/>
+    <mergeCell ref="CG41:CJ50"/>
+    <mergeCell ref="CC51:CF60"/>
+    <mergeCell ref="CG51:CJ60"/>
+    <mergeCell ref="CC61:CF70"/>
+    <mergeCell ref="CG61:CJ70"/>
+    <mergeCell ref="CC71:CF80"/>
+    <mergeCell ref="CG71:CJ80"/>
+    <mergeCell ref="CC81:CF90"/>
+    <mergeCell ref="CG81:CJ90"/>
+    <mergeCell ref="CC91:CF100"/>
+    <mergeCell ref="CG91:CJ100"/>
+    <mergeCell ref="CK1:CN10"/>
+    <mergeCell ref="CO1:CR10"/>
+    <mergeCell ref="CK11:CN20"/>
+    <mergeCell ref="CO11:CR20"/>
+    <mergeCell ref="CK21:CN30"/>
+    <mergeCell ref="CO21:CR30"/>
+    <mergeCell ref="CK31:CN40"/>
+    <mergeCell ref="CO31:CR40"/>
+    <mergeCell ref="CK41:CN50"/>
+    <mergeCell ref="CO41:CR50"/>
+    <mergeCell ref="CK51:CN60"/>
+    <mergeCell ref="CO51:CR60"/>
+    <mergeCell ref="CK61:CN70"/>
+    <mergeCell ref="CO61:CR70"/>
+    <mergeCell ref="CK71:CN80"/>
+    <mergeCell ref="CO71:CR80"/>
+    <mergeCell ref="CK81:CN90"/>
+    <mergeCell ref="CO81:CR90"/>
+    <mergeCell ref="CK91:CN100"/>
+    <mergeCell ref="CO91:CR100"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.6692913385826772" right="0.6692913385826772" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/tanulókártyák/Tanulókártyák.xlsx
+++ b/tanulókártyák/Tanulókártyák.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atesz\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA79994-669B-4107-B260-F61FFCDB1D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D087CB-FA50-495D-BA4A-83F5B00F82A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="269">
   <si>
     <r>
       <rPr>
@@ -4650,6 +4650,831 @@
   </si>
   <si>
     <t>Mi aJDBC?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">CRUD - HTTP methods:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">CREATE - POST
+READ - GET,
+UPDATE - PUT, 
+DELETE - DELETE
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Mit takar a CRUD betűszó
+és milyen HTTP metódusoknak
+ feleltethetőek meg az elemei?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">HTTP methods:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>POST - Adatküldés, mentés a szerveren
+GET - Adat/információ lekérés a szerverről
+PUT - Adat módosítás a szerveren
+DELETE - Adat törlés a szerveren
+PATCH - Adat módosítás a szerveren
+OPTION - Engedélyeztetések kommunikációs beállítások lekérése
+HEAD - Információ lekérdezés a szerverről (pl: letöltés elött ellenőrizni a fáj méretet)</t>
+    </r>
+  </si>
+  <si>
+    <t>Milyen HTTP netódusok vannak, mit csinálnak?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">HTTP Response status code:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>100 - általános információ a kliensnek. pl: ne vegye figyelembe a szerver választ
+200 - sikeres szerver művelet. pl: sikerült módosítani egy adatot a szerveren
+300 - átirányítás történt. pl: ideiglenesen más szerver szolgálja ki a választ
+400 - hibakód. pl: autentikációs hiba, vagy hibás "path", általában kliens oldali hibára utal.
+500 - hibakód. Szerver oldali hiba.</t>
+    </r>
+  </si>
+  <si>
+    <t>Milyen HTTP response code-okat ismersz?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">HTTP:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A HTTP protokoll egy adatküldési protokoll, egy olyan szabályrendszer, amely azon szabályokat írja le, amely mentén az interneten a kliensek és a szerverek szöveges adatokat küldenek egymásnak, kérések és válaszok formájában.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi az HTTP?</t>
+  </si>
+  <si>
+    <t>Mit jelent, hogy az HTTP állpotmentes protokoll?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Egy HTTP kérés tartalmazza: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+a kérés metódusát, egy elérési utat, az alkalmazott protokoll verzióját, egy header elemet, és a metódustól függően egy body elemet.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">A HTTP válasz kiegészül:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>egy státusz kóddal, és egy státusz üzenettel</t>
+    </r>
+  </si>
+  <si>
+    <t>Milyen elemeket tartalmaz
+ egy HTTP kérés és válasz?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">A HTTP állapotmentes (stateless) protokoll:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>azt jelenti, hogy minden kérés független, és nem tárol információt a korábbi kérésekről.
+Az állapotmentesség problémáit általában cookie-k és session-ök használatával kezelik, amelyek lehetővé teszik az állapotinformációk tárolását a kliens és a szerver között.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi az HTTPS?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Az </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HTTPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (HTTP Secure) egy kiegészítő protokoll, amely titkosítást használ a kliens és a szerver közötti adatátvitel biztonságának növelése érdekében. Az HTTPS SSL (Secure Sockets Layer) vagy TLS (Transport Layer Security) protokollokon keresztül biztosítja az adatok titkosítását.
+/A TLS az SSL modernizált változata és ma már szinte csak azt használják./</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Az </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IP-cím</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> egy hálózati eszköz egyedi azonosítója.
+Segítségével találják meg egymást az eszközök az interneten vagy egy helyi hálózaton. Olyan, mint egy postacím a digitális világban.
+Az </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IPv4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a legelterjedtebb IP-címzési rendszer.
+32 bites címeket használ, például: 192.168.1.1.
+Körülbelül 4,3 milliárd egyedi címet tud kezelni.
+Az</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> IPv6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> az IPv4 utódja. 128 bites címeket használ, például: 2001:db8::1. Gyakorlatilag kimeríthetetlen mennyiségű címet biztosít.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi az IP-cím, 
+mi a különbség az IPv4 és IPv6 között?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DNS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a Domain Name System rövidítése.
+A domainneveket (pl. google.com) IP-címekké alakítja.
+Olyan, mint az internet telefonkönyve.
+A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>domain név</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> egy könnyen megjegyezhető internetes cím.
+Például: google.com vagy openai.com.
+A DNS fordítja le IP-címre.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a DNS és a domain név?</t>
+  </si>
+  <si>
+    <t>Mi a TCP és az UDP?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TCP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> megbízható adatátviteli protokoll.
+Ellenőrzi, hogy minden csomag megérkezett-e és helyes sorrendben van-e.
+Weboldalak és e-mailek esetén gyakran használják.
+A</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> UDP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gyorsabb, mint a TCP.
+Nem ellenőrzi a csomagok megérkezését vagy sorrendjét.
+Gyakori online játékoknál és videóhívásoknál.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FTP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SCP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: (File Trasfer Protocol, Secure Copy protocol) - fájlok másolásására szolgáló kommunikációs protokoll számítógépek között</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi az FTP és SCP?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>REST</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Representational State Transfer) nem egy protokoll, hanem egy architekturális stílus a hálózati alkalmazások, különösen webes szolgáltatások fejlesztéséhez. A REST alapelvei segítségével a fejlesztők egyszerű, skálázható és könnyen karbantartható webes API-kat hozhatnak létre.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kliens–szerver elválasztás</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : A kliens (pl. böngésző vagy mobilapp) és a szerver külön felelősségi körrel rendelkezik. A kliens kéréseket küld, a szerver adatot és szolgáltatást nyújt.
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Stateless (állapotmentes)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: A szerver nem tárolja a kliens korábbi kéréseinek állapotát. Minden kérésnek önmagában tartalmaznia kell minden szükséges információt.
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Erőforrás-alapú működés</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Minden adat egy erőforrásként jelenik meg, amelyet URI-val érünk el.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>REST alapelvek (1/2)</t>
+  </si>
+  <si>
+    <t>Mi a REST?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Egységes interfész (Uniform Interface):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Az API következetesen használja a HTTP metódusokat.
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cache-elhetőség:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+A válaszok megjelölhetők gyorsítótárazhatónak.
+Ez csökkenti a szerver terhelését és gyorsítja a válaszidőt.
+6. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rétegzett architektúra:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+A kliensnek nem kell tudnia, hogy közvetlenül a szerverrel vagy köztes rendszereken (proxy, load balancer, gateway) keresztül kommunikál.</t>
+    </r>
+  </si>
+  <si>
+    <t>REST alapelvek (2/2)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>JSON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (JavaScript Object Notation) egy könnyű adatcsere-formátum, amely ember által olvasható szöveges formátumban tárol adatokat. Gyakran használják webes alkalmazásokban adatok küldésére és fogadására a szerver és a kliens között. Előnye, hogy könnyen értelmezhető és generálható a legtöbb programozási nyelven.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a JSON?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">A 4 rétegű TCP/IP modell </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">az internet működését leíró hálózati modell. Egyszerűbb, mint a 7 rétegű OSI modell, és a gyakorlatban ezt használják gyakrabban.
+Röviden:
+1. Alkalmazási réteg (HTTP/HTTPS, DNS, SMTP)
+2. Szállítási réteg (TCP, UDP)
+3. Internet réteg (IPv4, IPv6)
+4. Hálózati hozzáférési réteg (Ethernet kábel, Wi-Fi, optikai hálózat)
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi és miből áll a 4 rétegű TCP/IP modell?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HTTP három fő jellemzője:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Kapcsolat nélküli (connectionless): a kliens elküldi a kérést, a kapcsolat lezárul, majd megvárja a választ.
+Médiafüggetlen: bármilyen adattípust továbbíthat, ha a kliens és a szerver is támogatja.
+Állapotmentes (stateless): a kérések között nem tárol állapotot, minden kérés önálló.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a HTTP három fő jellemzője?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Cascade: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A szülő entitás műveleteit automatikusan továbbítja a kapcsolódó entitásokra.
+CascadeType.PERSIST: Mentéskor a kapcsolódó objektumokat is menti.
+.MERGE: A kapcsolódó objektumokat is frissíti.
+.REMOVE: Törléskor a kapcsolódó objektumokat is törli.
+.REFRESH: Újratölti az adatokat az adatbázisból.
+.DETACH: Leválasztja az entitásokat a persistence contextből.
+.ALL: Az összes cascade műveletet alkalmazza.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mit jelent a cascade, milyen formái vannak?</t>
   </si>
 </sst>
 </file>
@@ -5042,13 +5867,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CR151"/>
+  <dimension ref="A1:DH151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="96" width="11" customWidth="1"/>
+    <col min="1" max="112" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -5193,8 +6018,32 @@
       <c r="CP1" s="8"/>
       <c r="CQ1" s="8"/>
       <c r="CR1" s="8"/>
+      <c r="CS1" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="CT1" s="8"/>
+      <c r="CU1" s="8"/>
+      <c r="CV1" s="8"/>
+      <c r="CW1" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="CX1" s="8"/>
+      <c r="CY1" s="8"/>
+      <c r="CZ1" s="8"/>
+      <c r="DA1" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="DB1" s="8"/>
+      <c r="DC1" s="8"/>
+      <c r="DD1" s="8"/>
+      <c r="DE1" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="DF1" s="8"/>
+      <c r="DG1" s="8"/>
+      <c r="DH1" s="8"/>
     </row>
-    <row r="2" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -5291,8 +6140,24 @@
       <c r="CP2" s="8"/>
       <c r="CQ2" s="8"/>
       <c r="CR2" s="8"/>
+      <c r="CS2" s="8"/>
+      <c r="CT2" s="8"/>
+      <c r="CU2" s="8"/>
+      <c r="CV2" s="8"/>
+      <c r="CW2" s="8"/>
+      <c r="CX2" s="8"/>
+      <c r="CY2" s="8"/>
+      <c r="CZ2" s="8"/>
+      <c r="DA2" s="8"/>
+      <c r="DB2" s="8"/>
+      <c r="DC2" s="8"/>
+      <c r="DD2" s="8"/>
+      <c r="DE2" s="8"/>
+      <c r="DF2" s="8"/>
+      <c r="DG2" s="8"/>
+      <c r="DH2" s="8"/>
     </row>
-    <row r="3" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -5389,8 +6254,24 @@
       <c r="CP3" s="8"/>
       <c r="CQ3" s="8"/>
       <c r="CR3" s="8"/>
+      <c r="CS3" s="8"/>
+      <c r="CT3" s="8"/>
+      <c r="CU3" s="8"/>
+      <c r="CV3" s="8"/>
+      <c r="CW3" s="8"/>
+      <c r="CX3" s="8"/>
+      <c r="CY3" s="8"/>
+      <c r="CZ3" s="8"/>
+      <c r="DA3" s="8"/>
+      <c r="DB3" s="8"/>
+      <c r="DC3" s="8"/>
+      <c r="DD3" s="8"/>
+      <c r="DE3" s="8"/>
+      <c r="DF3" s="8"/>
+      <c r="DG3" s="8"/>
+      <c r="DH3" s="8"/>
     </row>
-    <row r="4" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -5487,8 +6368,24 @@
       <c r="CP4" s="8"/>
       <c r="CQ4" s="8"/>
       <c r="CR4" s="8"/>
+      <c r="CS4" s="8"/>
+      <c r="CT4" s="8"/>
+      <c r="CU4" s="8"/>
+      <c r="CV4" s="8"/>
+      <c r="CW4" s="8"/>
+      <c r="CX4" s="8"/>
+      <c r="CY4" s="8"/>
+      <c r="CZ4" s="8"/>
+      <c r="DA4" s="8"/>
+      <c r="DB4" s="8"/>
+      <c r="DC4" s="8"/>
+      <c r="DD4" s="8"/>
+      <c r="DE4" s="8"/>
+      <c r="DF4" s="8"/>
+      <c r="DG4" s="8"/>
+      <c r="DH4" s="8"/>
     </row>
-    <row r="5" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -5585,8 +6482,24 @@
       <c r="CP5" s="8"/>
       <c r="CQ5" s="8"/>
       <c r="CR5" s="8"/>
+      <c r="CS5" s="8"/>
+      <c r="CT5" s="8"/>
+      <c r="CU5" s="8"/>
+      <c r="CV5" s="8"/>
+      <c r="CW5" s="8"/>
+      <c r="CX5" s="8"/>
+      <c r="CY5" s="8"/>
+      <c r="CZ5" s="8"/>
+      <c r="DA5" s="8"/>
+      <c r="DB5" s="8"/>
+      <c r="DC5" s="8"/>
+      <c r="DD5" s="8"/>
+      <c r="DE5" s="8"/>
+      <c r="DF5" s="8"/>
+      <c r="DG5" s="8"/>
+      <c r="DH5" s="8"/>
     </row>
-    <row r="6" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -5683,8 +6596,24 @@
       <c r="CP6" s="8"/>
       <c r="CQ6" s="8"/>
       <c r="CR6" s="8"/>
+      <c r="CS6" s="8"/>
+      <c r="CT6" s="8"/>
+      <c r="CU6" s="8"/>
+      <c r="CV6" s="8"/>
+      <c r="CW6" s="8"/>
+      <c r="CX6" s="8"/>
+      <c r="CY6" s="8"/>
+      <c r="CZ6" s="8"/>
+      <c r="DA6" s="8"/>
+      <c r="DB6" s="8"/>
+      <c r="DC6" s="8"/>
+      <c r="DD6" s="8"/>
+      <c r="DE6" s="8"/>
+      <c r="DF6" s="8"/>
+      <c r="DG6" s="8"/>
+      <c r="DH6" s="8"/>
     </row>
-    <row r="7" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -5781,8 +6710,24 @@
       <c r="CP7" s="8"/>
       <c r="CQ7" s="8"/>
       <c r="CR7" s="8"/>
+      <c r="CS7" s="8"/>
+      <c r="CT7" s="8"/>
+      <c r="CU7" s="8"/>
+      <c r="CV7" s="8"/>
+      <c r="CW7" s="8"/>
+      <c r="CX7" s="8"/>
+      <c r="CY7" s="8"/>
+      <c r="CZ7" s="8"/>
+      <c r="DA7" s="8"/>
+      <c r="DB7" s="8"/>
+      <c r="DC7" s="8"/>
+      <c r="DD7" s="8"/>
+      <c r="DE7" s="8"/>
+      <c r="DF7" s="8"/>
+      <c r="DG7" s="8"/>
+      <c r="DH7" s="8"/>
     </row>
-    <row r="8" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -5879,8 +6824,24 @@
       <c r="CP8" s="8"/>
       <c r="CQ8" s="8"/>
       <c r="CR8" s="8"/>
+      <c r="CS8" s="8"/>
+      <c r="CT8" s="8"/>
+      <c r="CU8" s="8"/>
+      <c r="CV8" s="8"/>
+      <c r="CW8" s="8"/>
+      <c r="CX8" s="8"/>
+      <c r="CY8" s="8"/>
+      <c r="CZ8" s="8"/>
+      <c r="DA8" s="8"/>
+      <c r="DB8" s="8"/>
+      <c r="DC8" s="8"/>
+      <c r="DD8" s="8"/>
+      <c r="DE8" s="8"/>
+      <c r="DF8" s="8"/>
+      <c r="DG8" s="8"/>
+      <c r="DH8" s="8"/>
     </row>
-    <row r="9" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -5977,8 +6938,24 @@
       <c r="CP9" s="8"/>
       <c r="CQ9" s="8"/>
       <c r="CR9" s="8"/>
+      <c r="CS9" s="8"/>
+      <c r="CT9" s="8"/>
+      <c r="CU9" s="8"/>
+      <c r="CV9" s="8"/>
+      <c r="CW9" s="8"/>
+      <c r="CX9" s="8"/>
+      <c r="CY9" s="8"/>
+      <c r="CZ9" s="8"/>
+      <c r="DA9" s="8"/>
+      <c r="DB9" s="8"/>
+      <c r="DC9" s="8"/>
+      <c r="DD9" s="8"/>
+      <c r="DE9" s="8"/>
+      <c r="DF9" s="8"/>
+      <c r="DG9" s="8"/>
+      <c r="DH9" s="8"/>
     </row>
-    <row r="10" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -6075,8 +7052,24 @@
       <c r="CP10" s="8"/>
       <c r="CQ10" s="8"/>
       <c r="CR10" s="8"/>
+      <c r="CS10" s="8"/>
+      <c r="CT10" s="8"/>
+      <c r="CU10" s="8"/>
+      <c r="CV10" s="8"/>
+      <c r="CW10" s="8"/>
+      <c r="CX10" s="8"/>
+      <c r="CY10" s="8"/>
+      <c r="CZ10" s="8"/>
+      <c r="DA10" s="8"/>
+      <c r="DB10" s="8"/>
+      <c r="DC10" s="8"/>
+      <c r="DD10" s="8"/>
+      <c r="DE10" s="8"/>
+      <c r="DF10" s="8"/>
+      <c r="DG10" s="8"/>
+      <c r="DH10" s="8"/>
     </row>
-    <row r="11" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>2</v>
       </c>
@@ -6221,8 +7214,32 @@
       <c r="CP11" s="8"/>
       <c r="CQ11" s="8"/>
       <c r="CR11" s="8"/>
+      <c r="CS11" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="CT11" s="8"/>
+      <c r="CU11" s="8"/>
+      <c r="CV11" s="8"/>
+      <c r="CW11" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="CX11" s="8"/>
+      <c r="CY11" s="8"/>
+      <c r="CZ11" s="8"/>
+      <c r="DA11" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="DB11" s="8"/>
+      <c r="DC11" s="8"/>
+      <c r="DD11" s="8"/>
+      <c r="DE11" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="DF11" s="8"/>
+      <c r="DG11" s="8"/>
+      <c r="DH11" s="8"/>
     </row>
-    <row r="12" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -6319,8 +7336,24 @@
       <c r="CP12" s="8"/>
       <c r="CQ12" s="8"/>
       <c r="CR12" s="8"/>
+      <c r="CS12" s="8"/>
+      <c r="CT12" s="8"/>
+      <c r="CU12" s="8"/>
+      <c r="CV12" s="8"/>
+      <c r="CW12" s="8"/>
+      <c r="CX12" s="8"/>
+      <c r="CY12" s="8"/>
+      <c r="CZ12" s="8"/>
+      <c r="DA12" s="8"/>
+      <c r="DB12" s="8"/>
+      <c r="DC12" s="8"/>
+      <c r="DD12" s="8"/>
+      <c r="DE12" s="8"/>
+      <c r="DF12" s="8"/>
+      <c r="DG12" s="8"/>
+      <c r="DH12" s="8"/>
     </row>
-    <row r="13" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -6417,8 +7450,24 @@
       <c r="CP13" s="8"/>
       <c r="CQ13" s="8"/>
       <c r="CR13" s="8"/>
+      <c r="CS13" s="8"/>
+      <c r="CT13" s="8"/>
+      <c r="CU13" s="8"/>
+      <c r="CV13" s="8"/>
+      <c r="CW13" s="8"/>
+      <c r="CX13" s="8"/>
+      <c r="CY13" s="8"/>
+      <c r="CZ13" s="8"/>
+      <c r="DA13" s="8"/>
+      <c r="DB13" s="8"/>
+      <c r="DC13" s="8"/>
+      <c r="DD13" s="8"/>
+      <c r="DE13" s="8"/>
+      <c r="DF13" s="8"/>
+      <c r="DG13" s="8"/>
+      <c r="DH13" s="8"/>
     </row>
-    <row r="14" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -6515,8 +7564,24 @@
       <c r="CP14" s="8"/>
       <c r="CQ14" s="8"/>
       <c r="CR14" s="8"/>
+      <c r="CS14" s="8"/>
+      <c r="CT14" s="8"/>
+      <c r="CU14" s="8"/>
+      <c r="CV14" s="8"/>
+      <c r="CW14" s="8"/>
+      <c r="CX14" s="8"/>
+      <c r="CY14" s="8"/>
+      <c r="CZ14" s="8"/>
+      <c r="DA14" s="8"/>
+      <c r="DB14" s="8"/>
+      <c r="DC14" s="8"/>
+      <c r="DD14" s="8"/>
+      <c r="DE14" s="8"/>
+      <c r="DF14" s="8"/>
+      <c r="DG14" s="8"/>
+      <c r="DH14" s="8"/>
     </row>
-    <row r="15" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -6613,8 +7678,24 @@
       <c r="CP15" s="8"/>
       <c r="CQ15" s="8"/>
       <c r="CR15" s="8"/>
+      <c r="CS15" s="8"/>
+      <c r="CT15" s="8"/>
+      <c r="CU15" s="8"/>
+      <c r="CV15" s="8"/>
+      <c r="CW15" s="8"/>
+      <c r="CX15" s="8"/>
+      <c r="CY15" s="8"/>
+      <c r="CZ15" s="8"/>
+      <c r="DA15" s="8"/>
+      <c r="DB15" s="8"/>
+      <c r="DC15" s="8"/>
+      <c r="DD15" s="8"/>
+      <c r="DE15" s="8"/>
+      <c r="DF15" s="8"/>
+      <c r="DG15" s="8"/>
+      <c r="DH15" s="8"/>
     </row>
-    <row r="16" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -6711,8 +7792,24 @@
       <c r="CP16" s="8"/>
       <c r="CQ16" s="8"/>
       <c r="CR16" s="8"/>
+      <c r="CS16" s="8"/>
+      <c r="CT16" s="8"/>
+      <c r="CU16" s="8"/>
+      <c r="CV16" s="8"/>
+      <c r="CW16" s="8"/>
+      <c r="CX16" s="8"/>
+      <c r="CY16" s="8"/>
+      <c r="CZ16" s="8"/>
+      <c r="DA16" s="8"/>
+      <c r="DB16" s="8"/>
+      <c r="DC16" s="8"/>
+      <c r="DD16" s="8"/>
+      <c r="DE16" s="8"/>
+      <c r="DF16" s="8"/>
+      <c r="DG16" s="8"/>
+      <c r="DH16" s="8"/>
     </row>
-    <row r="17" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -6809,8 +7906,24 @@
       <c r="CP17" s="8"/>
       <c r="CQ17" s="8"/>
       <c r="CR17" s="8"/>
+      <c r="CS17" s="8"/>
+      <c r="CT17" s="8"/>
+      <c r="CU17" s="8"/>
+      <c r="CV17" s="8"/>
+      <c r="CW17" s="8"/>
+      <c r="CX17" s="8"/>
+      <c r="CY17" s="8"/>
+      <c r="CZ17" s="8"/>
+      <c r="DA17" s="8"/>
+      <c r="DB17" s="8"/>
+      <c r="DC17" s="8"/>
+      <c r="DD17" s="8"/>
+      <c r="DE17" s="8"/>
+      <c r="DF17" s="8"/>
+      <c r="DG17" s="8"/>
+      <c r="DH17" s="8"/>
     </row>
-    <row r="18" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -6907,8 +8020,24 @@
       <c r="CP18" s="8"/>
       <c r="CQ18" s="8"/>
       <c r="CR18" s="8"/>
+      <c r="CS18" s="8"/>
+      <c r="CT18" s="8"/>
+      <c r="CU18" s="8"/>
+      <c r="CV18" s="8"/>
+      <c r="CW18" s="8"/>
+      <c r="CX18" s="8"/>
+      <c r="CY18" s="8"/>
+      <c r="CZ18" s="8"/>
+      <c r="DA18" s="8"/>
+      <c r="DB18" s="8"/>
+      <c r="DC18" s="8"/>
+      <c r="DD18" s="8"/>
+      <c r="DE18" s="8"/>
+      <c r="DF18" s="8"/>
+      <c r="DG18" s="8"/>
+      <c r="DH18" s="8"/>
     </row>
-    <row r="19" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -7005,8 +8134,24 @@
       <c r="CP19" s="8"/>
       <c r="CQ19" s="8"/>
       <c r="CR19" s="8"/>
+      <c r="CS19" s="8"/>
+      <c r="CT19" s="8"/>
+      <c r="CU19" s="8"/>
+      <c r="CV19" s="8"/>
+      <c r="CW19" s="8"/>
+      <c r="CX19" s="8"/>
+      <c r="CY19" s="8"/>
+      <c r="CZ19" s="8"/>
+      <c r="DA19" s="8"/>
+      <c r="DB19" s="8"/>
+      <c r="DC19" s="8"/>
+      <c r="DD19" s="8"/>
+      <c r="DE19" s="8"/>
+      <c r="DF19" s="8"/>
+      <c r="DG19" s="8"/>
+      <c r="DH19" s="8"/>
     </row>
-    <row r="20" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -7103,8 +8248,24 @@
       <c r="CP20" s="8"/>
       <c r="CQ20" s="8"/>
       <c r="CR20" s="8"/>
+      <c r="CS20" s="8"/>
+      <c r="CT20" s="8"/>
+      <c r="CU20" s="8"/>
+      <c r="CV20" s="8"/>
+      <c r="CW20" s="8"/>
+      <c r="CX20" s="8"/>
+      <c r="CY20" s="8"/>
+      <c r="CZ20" s="8"/>
+      <c r="DA20" s="8"/>
+      <c r="DB20" s="8"/>
+      <c r="DC20" s="8"/>
+      <c r="DD20" s="8"/>
+      <c r="DE20" s="8"/>
+      <c r="DF20" s="8"/>
+      <c r="DG20" s="8"/>
+      <c r="DH20" s="8"/>
     </row>
-    <row r="21" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>4</v>
       </c>
@@ -7249,8 +8410,30 @@
       <c r="CP21" s="8"/>
       <c r="CQ21" s="8"/>
       <c r="CR21" s="8"/>
+      <c r="CS21" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="CT21" s="8"/>
+      <c r="CU21" s="8"/>
+      <c r="CV21" s="8"/>
+      <c r="CW21" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="CX21" s="8"/>
+      <c r="CY21" s="8"/>
+      <c r="CZ21" s="8"/>
+      <c r="DA21" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="DB21" s="8"/>
+      <c r="DC21" s="8"/>
+      <c r="DD21" s="8"/>
+      <c r="DE21" s="7"/>
+      <c r="DF21" s="8"/>
+      <c r="DG21" s="8"/>
+      <c r="DH21" s="8"/>
     </row>
-    <row r="22" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -7347,8 +8530,24 @@
       <c r="CP22" s="8"/>
       <c r="CQ22" s="8"/>
       <c r="CR22" s="8"/>
+      <c r="CS22" s="8"/>
+      <c r="CT22" s="8"/>
+      <c r="CU22" s="8"/>
+      <c r="CV22" s="8"/>
+      <c r="CW22" s="8"/>
+      <c r="CX22" s="8"/>
+      <c r="CY22" s="8"/>
+      <c r="CZ22" s="8"/>
+      <c r="DA22" s="8"/>
+      <c r="DB22" s="8"/>
+      <c r="DC22" s="8"/>
+      <c r="DD22" s="8"/>
+      <c r="DE22" s="8"/>
+      <c r="DF22" s="8"/>
+      <c r="DG22" s="8"/>
+      <c r="DH22" s="8"/>
     </row>
-    <row r="23" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -7445,8 +8644,24 @@
       <c r="CP23" s="8"/>
       <c r="CQ23" s="8"/>
       <c r="CR23" s="8"/>
+      <c r="CS23" s="8"/>
+      <c r="CT23" s="8"/>
+      <c r="CU23" s="8"/>
+      <c r="CV23" s="8"/>
+      <c r="CW23" s="8"/>
+      <c r="CX23" s="8"/>
+      <c r="CY23" s="8"/>
+      <c r="CZ23" s="8"/>
+      <c r="DA23" s="8"/>
+      <c r="DB23" s="8"/>
+      <c r="DC23" s="8"/>
+      <c r="DD23" s="8"/>
+      <c r="DE23" s="8"/>
+      <c r="DF23" s="8"/>
+      <c r="DG23" s="8"/>
+      <c r="DH23" s="8"/>
     </row>
-    <row r="24" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -7543,8 +8758,24 @@
       <c r="CP24" s="8"/>
       <c r="CQ24" s="8"/>
       <c r="CR24" s="8"/>
+      <c r="CS24" s="8"/>
+      <c r="CT24" s="8"/>
+      <c r="CU24" s="8"/>
+      <c r="CV24" s="8"/>
+      <c r="CW24" s="8"/>
+      <c r="CX24" s="8"/>
+      <c r="CY24" s="8"/>
+      <c r="CZ24" s="8"/>
+      <c r="DA24" s="8"/>
+      <c r="DB24" s="8"/>
+      <c r="DC24" s="8"/>
+      <c r="DD24" s="8"/>
+      <c r="DE24" s="8"/>
+      <c r="DF24" s="8"/>
+      <c r="DG24" s="8"/>
+      <c r="DH24" s="8"/>
     </row>
-    <row r="25" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -7641,8 +8872,24 @@
       <c r="CP25" s="8"/>
       <c r="CQ25" s="8"/>
       <c r="CR25" s="8"/>
+      <c r="CS25" s="8"/>
+      <c r="CT25" s="8"/>
+      <c r="CU25" s="8"/>
+      <c r="CV25" s="8"/>
+      <c r="CW25" s="8"/>
+      <c r="CX25" s="8"/>
+      <c r="CY25" s="8"/>
+      <c r="CZ25" s="8"/>
+      <c r="DA25" s="8"/>
+      <c r="DB25" s="8"/>
+      <c r="DC25" s="8"/>
+      <c r="DD25" s="8"/>
+      <c r="DE25" s="8"/>
+      <c r="DF25" s="8"/>
+      <c r="DG25" s="8"/>
+      <c r="DH25" s="8"/>
     </row>
-    <row r="26" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -7739,8 +8986,24 @@
       <c r="CP26" s="8"/>
       <c r="CQ26" s="8"/>
       <c r="CR26" s="8"/>
+      <c r="CS26" s="8"/>
+      <c r="CT26" s="8"/>
+      <c r="CU26" s="8"/>
+      <c r="CV26" s="8"/>
+      <c r="CW26" s="8"/>
+      <c r="CX26" s="8"/>
+      <c r="CY26" s="8"/>
+      <c r="CZ26" s="8"/>
+      <c r="DA26" s="8"/>
+      <c r="DB26" s="8"/>
+      <c r="DC26" s="8"/>
+      <c r="DD26" s="8"/>
+      <c r="DE26" s="8"/>
+      <c r="DF26" s="8"/>
+      <c r="DG26" s="8"/>
+      <c r="DH26" s="8"/>
     </row>
-    <row r="27" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -7837,8 +9100,24 @@
       <c r="CP27" s="8"/>
       <c r="CQ27" s="8"/>
       <c r="CR27" s="8"/>
+      <c r="CS27" s="8"/>
+      <c r="CT27" s="8"/>
+      <c r="CU27" s="8"/>
+      <c r="CV27" s="8"/>
+      <c r="CW27" s="8"/>
+      <c r="CX27" s="8"/>
+      <c r="CY27" s="8"/>
+      <c r="CZ27" s="8"/>
+      <c r="DA27" s="8"/>
+      <c r="DB27" s="8"/>
+      <c r="DC27" s="8"/>
+      <c r="DD27" s="8"/>
+      <c r="DE27" s="8"/>
+      <c r="DF27" s="8"/>
+      <c r="DG27" s="8"/>
+      <c r="DH27" s="8"/>
     </row>
-    <row r="28" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -7935,8 +9214,24 @@
       <c r="CP28" s="8"/>
       <c r="CQ28" s="8"/>
       <c r="CR28" s="8"/>
+      <c r="CS28" s="8"/>
+      <c r="CT28" s="8"/>
+      <c r="CU28" s="8"/>
+      <c r="CV28" s="8"/>
+      <c r="CW28" s="8"/>
+      <c r="CX28" s="8"/>
+      <c r="CY28" s="8"/>
+      <c r="CZ28" s="8"/>
+      <c r="DA28" s="8"/>
+      <c r="DB28" s="8"/>
+      <c r="DC28" s="8"/>
+      <c r="DD28" s="8"/>
+      <c r="DE28" s="8"/>
+      <c r="DF28" s="8"/>
+      <c r="DG28" s="8"/>
+      <c r="DH28" s="8"/>
     </row>
-    <row r="29" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -8033,8 +9328,24 @@
       <c r="CP29" s="8"/>
       <c r="CQ29" s="8"/>
       <c r="CR29" s="8"/>
+      <c r="CS29" s="8"/>
+      <c r="CT29" s="8"/>
+      <c r="CU29" s="8"/>
+      <c r="CV29" s="8"/>
+      <c r="CW29" s="8"/>
+      <c r="CX29" s="8"/>
+      <c r="CY29" s="8"/>
+      <c r="CZ29" s="8"/>
+      <c r="DA29" s="8"/>
+      <c r="DB29" s="8"/>
+      <c r="DC29" s="8"/>
+      <c r="DD29" s="8"/>
+      <c r="DE29" s="8"/>
+      <c r="DF29" s="8"/>
+      <c r="DG29" s="8"/>
+      <c r="DH29" s="8"/>
     </row>
-    <row r="30" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -8131,8 +9442,24 @@
       <c r="CP30" s="8"/>
       <c r="CQ30" s="8"/>
       <c r="CR30" s="8"/>
+      <c r="CS30" s="8"/>
+      <c r="CT30" s="8"/>
+      <c r="CU30" s="8"/>
+      <c r="CV30" s="8"/>
+      <c r="CW30" s="8"/>
+      <c r="CX30" s="8"/>
+      <c r="CY30" s="8"/>
+      <c r="CZ30" s="8"/>
+      <c r="DA30" s="8"/>
+      <c r="DB30" s="8"/>
+      <c r="DC30" s="8"/>
+      <c r="DD30" s="8"/>
+      <c r="DE30" s="8"/>
+      <c r="DF30" s="8"/>
+      <c r="DG30" s="8"/>
+      <c r="DH30" s="8"/>
     </row>
-    <row r="31" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>13</v>
       </c>
@@ -8271,12 +9598,34 @@
       <c r="CL31" s="8"/>
       <c r="CM31" s="8"/>
       <c r="CN31" s="8"/>
-      <c r="CO31" s="7"/>
+      <c r="CO31" s="7" t="s">
+        <v>233</v>
+      </c>
       <c r="CP31" s="8"/>
       <c r="CQ31" s="8"/>
       <c r="CR31" s="8"/>
+      <c r="CS31" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="CT31" s="8"/>
+      <c r="CU31" s="8"/>
+      <c r="CV31" s="8"/>
+      <c r="CW31" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="CX31" s="8"/>
+      <c r="CY31" s="8"/>
+      <c r="CZ31" s="8"/>
+      <c r="DA31" s="7"/>
+      <c r="DB31" s="8"/>
+      <c r="DC31" s="8"/>
+      <c r="DD31" s="8"/>
+      <c r="DE31" s="7"/>
+      <c r="DF31" s="8"/>
+      <c r="DG31" s="8"/>
+      <c r="DH31" s="8"/>
     </row>
-    <row r="32" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -8373,8 +9722,24 @@
       <c r="CP32" s="8"/>
       <c r="CQ32" s="8"/>
       <c r="CR32" s="8"/>
+      <c r="CS32" s="8"/>
+      <c r="CT32" s="8"/>
+      <c r="CU32" s="8"/>
+      <c r="CV32" s="8"/>
+      <c r="CW32" s="8"/>
+      <c r="CX32" s="8"/>
+      <c r="CY32" s="8"/>
+      <c r="CZ32" s="8"/>
+      <c r="DA32" s="8"/>
+      <c r="DB32" s="8"/>
+      <c r="DC32" s="8"/>
+      <c r="DD32" s="8"/>
+      <c r="DE32" s="8"/>
+      <c r="DF32" s="8"/>
+      <c r="DG32" s="8"/>
+      <c r="DH32" s="8"/>
     </row>
-    <row r="33" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -8471,8 +9836,24 @@
       <c r="CP33" s="8"/>
       <c r="CQ33" s="8"/>
       <c r="CR33" s="8"/>
+      <c r="CS33" s="8"/>
+      <c r="CT33" s="8"/>
+      <c r="CU33" s="8"/>
+      <c r="CV33" s="8"/>
+      <c r="CW33" s="8"/>
+      <c r="CX33" s="8"/>
+      <c r="CY33" s="8"/>
+      <c r="CZ33" s="8"/>
+      <c r="DA33" s="8"/>
+      <c r="DB33" s="8"/>
+      <c r="DC33" s="8"/>
+      <c r="DD33" s="8"/>
+      <c r="DE33" s="8"/>
+      <c r="DF33" s="8"/>
+      <c r="DG33" s="8"/>
+      <c r="DH33" s="8"/>
     </row>
-    <row r="34" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -8569,8 +9950,24 @@
       <c r="CP34" s="8"/>
       <c r="CQ34" s="8"/>
       <c r="CR34" s="8"/>
+      <c r="CS34" s="8"/>
+      <c r="CT34" s="8"/>
+      <c r="CU34" s="8"/>
+      <c r="CV34" s="8"/>
+      <c r="CW34" s="8"/>
+      <c r="CX34" s="8"/>
+      <c r="CY34" s="8"/>
+      <c r="CZ34" s="8"/>
+      <c r="DA34" s="8"/>
+      <c r="DB34" s="8"/>
+      <c r="DC34" s="8"/>
+      <c r="DD34" s="8"/>
+      <c r="DE34" s="8"/>
+      <c r="DF34" s="8"/>
+      <c r="DG34" s="8"/>
+      <c r="DH34" s="8"/>
     </row>
-    <row r="35" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -8667,8 +10064,24 @@
       <c r="CP35" s="8"/>
       <c r="CQ35" s="8"/>
       <c r="CR35" s="8"/>
+      <c r="CS35" s="8"/>
+      <c r="CT35" s="8"/>
+      <c r="CU35" s="8"/>
+      <c r="CV35" s="8"/>
+      <c r="CW35" s="8"/>
+      <c r="CX35" s="8"/>
+      <c r="CY35" s="8"/>
+      <c r="CZ35" s="8"/>
+      <c r="DA35" s="8"/>
+      <c r="DB35" s="8"/>
+      <c r="DC35" s="8"/>
+      <c r="DD35" s="8"/>
+      <c r="DE35" s="8"/>
+      <c r="DF35" s="8"/>
+      <c r="DG35" s="8"/>
+      <c r="DH35" s="8"/>
     </row>
-    <row r="36" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -8765,8 +10178,24 @@
       <c r="CP36" s="8"/>
       <c r="CQ36" s="8"/>
       <c r="CR36" s="8"/>
+      <c r="CS36" s="8"/>
+      <c r="CT36" s="8"/>
+      <c r="CU36" s="8"/>
+      <c r="CV36" s="8"/>
+      <c r="CW36" s="8"/>
+      <c r="CX36" s="8"/>
+      <c r="CY36" s="8"/>
+      <c r="CZ36" s="8"/>
+      <c r="DA36" s="8"/>
+      <c r="DB36" s="8"/>
+      <c r="DC36" s="8"/>
+      <c r="DD36" s="8"/>
+      <c r="DE36" s="8"/>
+      <c r="DF36" s="8"/>
+      <c r="DG36" s="8"/>
+      <c r="DH36" s="8"/>
     </row>
-    <row r="37" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -8863,8 +10292,24 @@
       <c r="CP37" s="8"/>
       <c r="CQ37" s="8"/>
       <c r="CR37" s="8"/>
+      <c r="CS37" s="8"/>
+      <c r="CT37" s="8"/>
+      <c r="CU37" s="8"/>
+      <c r="CV37" s="8"/>
+      <c r="CW37" s="8"/>
+      <c r="CX37" s="8"/>
+      <c r="CY37" s="8"/>
+      <c r="CZ37" s="8"/>
+      <c r="DA37" s="8"/>
+      <c r="DB37" s="8"/>
+      <c r="DC37" s="8"/>
+      <c r="DD37" s="8"/>
+      <c r="DE37" s="8"/>
+      <c r="DF37" s="8"/>
+      <c r="DG37" s="8"/>
+      <c r="DH37" s="8"/>
     </row>
-    <row r="38" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -8961,8 +10406,24 @@
       <c r="CP38" s="8"/>
       <c r="CQ38" s="8"/>
       <c r="CR38" s="8"/>
+      <c r="CS38" s="8"/>
+      <c r="CT38" s="8"/>
+      <c r="CU38" s="8"/>
+      <c r="CV38" s="8"/>
+      <c r="CW38" s="8"/>
+      <c r="CX38" s="8"/>
+      <c r="CY38" s="8"/>
+      <c r="CZ38" s="8"/>
+      <c r="DA38" s="8"/>
+      <c r="DB38" s="8"/>
+      <c r="DC38" s="8"/>
+      <c r="DD38" s="8"/>
+      <c r="DE38" s="8"/>
+      <c r="DF38" s="8"/>
+      <c r="DG38" s="8"/>
+      <c r="DH38" s="8"/>
     </row>
-    <row r="39" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -9059,8 +10520,24 @@
       <c r="CP39" s="8"/>
       <c r="CQ39" s="8"/>
       <c r="CR39" s="8"/>
+      <c r="CS39" s="8"/>
+      <c r="CT39" s="8"/>
+      <c r="CU39" s="8"/>
+      <c r="CV39" s="8"/>
+      <c r="CW39" s="8"/>
+      <c r="CX39" s="8"/>
+      <c r="CY39" s="8"/>
+      <c r="CZ39" s="8"/>
+      <c r="DA39" s="8"/>
+      <c r="DB39" s="8"/>
+      <c r="DC39" s="8"/>
+      <c r="DD39" s="8"/>
+      <c r="DE39" s="8"/>
+      <c r="DF39" s="8"/>
+      <c r="DG39" s="8"/>
+      <c r="DH39" s="8"/>
     </row>
-    <row r="40" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -9157,8 +10634,24 @@
       <c r="CP40" s="8"/>
       <c r="CQ40" s="8"/>
       <c r="CR40" s="8"/>
+      <c r="CS40" s="8"/>
+      <c r="CT40" s="8"/>
+      <c r="CU40" s="8"/>
+      <c r="CV40" s="8"/>
+      <c r="CW40" s="8"/>
+      <c r="CX40" s="8"/>
+      <c r="CY40" s="8"/>
+      <c r="CZ40" s="8"/>
+      <c r="DA40" s="8"/>
+      <c r="DB40" s="8"/>
+      <c r="DC40" s="8"/>
+      <c r="DD40" s="8"/>
+      <c r="DE40" s="8"/>
+      <c r="DF40" s="8"/>
+      <c r="DG40" s="8"/>
+      <c r="DH40" s="8"/>
     </row>
-    <row r="41" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>16</v>
       </c>
@@ -9291,16 +10784,40 @@
       <c r="CH41" s="8"/>
       <c r="CI41" s="8"/>
       <c r="CJ41" s="8"/>
-      <c r="CK41" s="7"/>
+      <c r="CK41" s="7" t="s">
+        <v>235</v>
+      </c>
       <c r="CL41" s="8"/>
       <c r="CM41" s="8"/>
       <c r="CN41" s="8"/>
-      <c r="CO41" s="9"/>
+      <c r="CO41" s="9" t="s">
+        <v>237</v>
+      </c>
       <c r="CP41" s="8"/>
       <c r="CQ41" s="8"/>
       <c r="CR41" s="8"/>
+      <c r="CS41" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="CT41" s="8"/>
+      <c r="CU41" s="8"/>
+      <c r="CV41" s="8"/>
+      <c r="CW41" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="CX41" s="8"/>
+      <c r="CY41" s="8"/>
+      <c r="CZ41" s="8"/>
+      <c r="DA41" s="7"/>
+      <c r="DB41" s="8"/>
+      <c r="DC41" s="8"/>
+      <c r="DD41" s="8"/>
+      <c r="DE41" s="9"/>
+      <c r="DF41" s="8"/>
+      <c r="DG41" s="8"/>
+      <c r="DH41" s="8"/>
     </row>
-    <row r="42" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -9397,8 +10914,24 @@
       <c r="CP42" s="8"/>
       <c r="CQ42" s="8"/>
       <c r="CR42" s="8"/>
+      <c r="CS42" s="8"/>
+      <c r="CT42" s="8"/>
+      <c r="CU42" s="8"/>
+      <c r="CV42" s="8"/>
+      <c r="CW42" s="8"/>
+      <c r="CX42" s="8"/>
+      <c r="CY42" s="8"/>
+      <c r="CZ42" s="8"/>
+      <c r="DA42" s="8"/>
+      <c r="DB42" s="8"/>
+      <c r="DC42" s="8"/>
+      <c r="DD42" s="8"/>
+      <c r="DE42" s="8"/>
+      <c r="DF42" s="8"/>
+      <c r="DG42" s="8"/>
+      <c r="DH42" s="8"/>
     </row>
-    <row r="43" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -9495,8 +11028,24 @@
       <c r="CP43" s="8"/>
       <c r="CQ43" s="8"/>
       <c r="CR43" s="8"/>
+      <c r="CS43" s="8"/>
+      <c r="CT43" s="8"/>
+      <c r="CU43" s="8"/>
+      <c r="CV43" s="8"/>
+      <c r="CW43" s="8"/>
+      <c r="CX43" s="8"/>
+      <c r="CY43" s="8"/>
+      <c r="CZ43" s="8"/>
+      <c r="DA43" s="8"/>
+      <c r="DB43" s="8"/>
+      <c r="DC43" s="8"/>
+      <c r="DD43" s="8"/>
+      <c r="DE43" s="8"/>
+      <c r="DF43" s="8"/>
+      <c r="DG43" s="8"/>
+      <c r="DH43" s="8"/>
     </row>
-    <row r="44" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -9593,8 +11142,24 @@
       <c r="CP44" s="8"/>
       <c r="CQ44" s="8"/>
       <c r="CR44" s="8"/>
+      <c r="CS44" s="8"/>
+      <c r="CT44" s="8"/>
+      <c r="CU44" s="8"/>
+      <c r="CV44" s="8"/>
+      <c r="CW44" s="8"/>
+      <c r="CX44" s="8"/>
+      <c r="CY44" s="8"/>
+      <c r="CZ44" s="8"/>
+      <c r="DA44" s="8"/>
+      <c r="DB44" s="8"/>
+      <c r="DC44" s="8"/>
+      <c r="DD44" s="8"/>
+      <c r="DE44" s="8"/>
+      <c r="DF44" s="8"/>
+      <c r="DG44" s="8"/>
+      <c r="DH44" s="8"/>
     </row>
-    <row r="45" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -9691,8 +11256,24 @@
       <c r="CP45" s="8"/>
       <c r="CQ45" s="8"/>
       <c r="CR45" s="8"/>
+      <c r="CS45" s="8"/>
+      <c r="CT45" s="8"/>
+      <c r="CU45" s="8"/>
+      <c r="CV45" s="8"/>
+      <c r="CW45" s="8"/>
+      <c r="CX45" s="8"/>
+      <c r="CY45" s="8"/>
+      <c r="CZ45" s="8"/>
+      <c r="DA45" s="8"/>
+      <c r="DB45" s="8"/>
+      <c r="DC45" s="8"/>
+      <c r="DD45" s="8"/>
+      <c r="DE45" s="8"/>
+      <c r="DF45" s="8"/>
+      <c r="DG45" s="8"/>
+      <c r="DH45" s="8"/>
     </row>
-    <row r="46" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -9789,8 +11370,24 @@
       <c r="CP46" s="8"/>
       <c r="CQ46" s="8"/>
       <c r="CR46" s="8"/>
+      <c r="CS46" s="8"/>
+      <c r="CT46" s="8"/>
+      <c r="CU46" s="8"/>
+      <c r="CV46" s="8"/>
+      <c r="CW46" s="8"/>
+      <c r="CX46" s="8"/>
+      <c r="CY46" s="8"/>
+      <c r="CZ46" s="8"/>
+      <c r="DA46" s="8"/>
+      <c r="DB46" s="8"/>
+      <c r="DC46" s="8"/>
+      <c r="DD46" s="8"/>
+      <c r="DE46" s="8"/>
+      <c r="DF46" s="8"/>
+      <c r="DG46" s="8"/>
+      <c r="DH46" s="8"/>
     </row>
-    <row r="47" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -9887,8 +11484,24 @@
       <c r="CP47" s="8"/>
       <c r="CQ47" s="8"/>
       <c r="CR47" s="8"/>
+      <c r="CS47" s="8"/>
+      <c r="CT47" s="8"/>
+      <c r="CU47" s="8"/>
+      <c r="CV47" s="8"/>
+      <c r="CW47" s="8"/>
+      <c r="CX47" s="8"/>
+      <c r="CY47" s="8"/>
+      <c r="CZ47" s="8"/>
+      <c r="DA47" s="8"/>
+      <c r="DB47" s="8"/>
+      <c r="DC47" s="8"/>
+      <c r="DD47" s="8"/>
+      <c r="DE47" s="8"/>
+      <c r="DF47" s="8"/>
+      <c r="DG47" s="8"/>
+      <c r="DH47" s="8"/>
     </row>
-    <row r="48" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -9985,8 +11598,24 @@
       <c r="CP48" s="8"/>
       <c r="CQ48" s="8"/>
       <c r="CR48" s="8"/>
+      <c r="CS48" s="8"/>
+      <c r="CT48" s="8"/>
+      <c r="CU48" s="8"/>
+      <c r="CV48" s="8"/>
+      <c r="CW48" s="8"/>
+      <c r="CX48" s="8"/>
+      <c r="CY48" s="8"/>
+      <c r="CZ48" s="8"/>
+      <c r="DA48" s="8"/>
+      <c r="DB48" s="8"/>
+      <c r="DC48" s="8"/>
+      <c r="DD48" s="8"/>
+      <c r="DE48" s="8"/>
+      <c r="DF48" s="8"/>
+      <c r="DG48" s="8"/>
+      <c r="DH48" s="8"/>
     </row>
-    <row r="49" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -10083,8 +11712,24 @@
       <c r="CP49" s="8"/>
       <c r="CQ49" s="8"/>
       <c r="CR49" s="8"/>
+      <c r="CS49" s="8"/>
+      <c r="CT49" s="8"/>
+      <c r="CU49" s="8"/>
+      <c r="CV49" s="8"/>
+      <c r="CW49" s="8"/>
+      <c r="CX49" s="8"/>
+      <c r="CY49" s="8"/>
+      <c r="CZ49" s="8"/>
+      <c r="DA49" s="8"/>
+      <c r="DB49" s="8"/>
+      <c r="DC49" s="8"/>
+      <c r="DD49" s="8"/>
+      <c r="DE49" s="8"/>
+      <c r="DF49" s="8"/>
+      <c r="DG49" s="8"/>
+      <c r="DH49" s="8"/>
     </row>
-    <row r="50" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -10181,8 +11826,24 @@
       <c r="CP50" s="8"/>
       <c r="CQ50" s="8"/>
       <c r="CR50" s="8"/>
+      <c r="CS50" s="8"/>
+      <c r="CT50" s="8"/>
+      <c r="CU50" s="8"/>
+      <c r="CV50" s="8"/>
+      <c r="CW50" s="8"/>
+      <c r="CX50" s="8"/>
+      <c r="CY50" s="8"/>
+      <c r="CZ50" s="8"/>
+      <c r="DA50" s="8"/>
+      <c r="DB50" s="8"/>
+      <c r="DC50" s="8"/>
+      <c r="DD50" s="8"/>
+      <c r="DE50" s="8"/>
+      <c r="DF50" s="8"/>
+      <c r="DG50" s="8"/>
+      <c r="DH50" s="8"/>
     </row>
-    <row r="51" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>6</v>
       </c>
@@ -10327,8 +11988,32 @@
       <c r="CP51" s="6"/>
       <c r="CQ51" s="6"/>
       <c r="CR51" s="6"/>
+      <c r="CS51" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="CT51" s="6"/>
+      <c r="CU51" s="6"/>
+      <c r="CV51" s="6"/>
+      <c r="CW51" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="CX51" s="6"/>
+      <c r="CY51" s="6"/>
+      <c r="CZ51" s="6"/>
+      <c r="DA51" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="DB51" s="6"/>
+      <c r="DC51" s="6"/>
+      <c r="DD51" s="6"/>
+      <c r="DE51" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="DF51" s="6"/>
+      <c r="DG51" s="6"/>
+      <c r="DH51" s="6"/>
     </row>
-    <row r="52" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -10425,8 +12110,24 @@
       <c r="CP52" s="6"/>
       <c r="CQ52" s="6"/>
       <c r="CR52" s="6"/>
+      <c r="CS52" s="6"/>
+      <c r="CT52" s="6"/>
+      <c r="CU52" s="6"/>
+      <c r="CV52" s="6"/>
+      <c r="CW52" s="6"/>
+      <c r="CX52" s="6"/>
+      <c r="CY52" s="6"/>
+      <c r="CZ52" s="6"/>
+      <c r="DA52" s="6"/>
+      <c r="DB52" s="6"/>
+      <c r="DC52" s="6"/>
+      <c r="DD52" s="6"/>
+      <c r="DE52" s="6"/>
+      <c r="DF52" s="6"/>
+      <c r="DG52" s="6"/>
+      <c r="DH52" s="6"/>
     </row>
-    <row r="53" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -10523,8 +12224,24 @@
       <c r="CP53" s="6"/>
       <c r="CQ53" s="6"/>
       <c r="CR53" s="6"/>
+      <c r="CS53" s="6"/>
+      <c r="CT53" s="6"/>
+      <c r="CU53" s="6"/>
+      <c r="CV53" s="6"/>
+      <c r="CW53" s="6"/>
+      <c r="CX53" s="6"/>
+      <c r="CY53" s="6"/>
+      <c r="CZ53" s="6"/>
+      <c r="DA53" s="6"/>
+      <c r="DB53" s="6"/>
+      <c r="DC53" s="6"/>
+      <c r="DD53" s="6"/>
+      <c r="DE53" s="6"/>
+      <c r="DF53" s="6"/>
+      <c r="DG53" s="6"/>
+      <c r="DH53" s="6"/>
     </row>
-    <row r="54" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -10621,8 +12338,24 @@
       <c r="CP54" s="6"/>
       <c r="CQ54" s="6"/>
       <c r="CR54" s="6"/>
+      <c r="CS54" s="6"/>
+      <c r="CT54" s="6"/>
+      <c r="CU54" s="6"/>
+      <c r="CV54" s="6"/>
+      <c r="CW54" s="6"/>
+      <c r="CX54" s="6"/>
+      <c r="CY54" s="6"/>
+      <c r="CZ54" s="6"/>
+      <c r="DA54" s="6"/>
+      <c r="DB54" s="6"/>
+      <c r="DC54" s="6"/>
+      <c r="DD54" s="6"/>
+      <c r="DE54" s="6"/>
+      <c r="DF54" s="6"/>
+      <c r="DG54" s="6"/>
+      <c r="DH54" s="6"/>
     </row>
-    <row r="55" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -10719,8 +12452,24 @@
       <c r="CP55" s="6"/>
       <c r="CQ55" s="6"/>
       <c r="CR55" s="6"/>
+      <c r="CS55" s="6"/>
+      <c r="CT55" s="6"/>
+      <c r="CU55" s="6"/>
+      <c r="CV55" s="6"/>
+      <c r="CW55" s="6"/>
+      <c r="CX55" s="6"/>
+      <c r="CY55" s="6"/>
+      <c r="CZ55" s="6"/>
+      <c r="DA55" s="6"/>
+      <c r="DB55" s="6"/>
+      <c r="DC55" s="6"/>
+      <c r="DD55" s="6"/>
+      <c r="DE55" s="6"/>
+      <c r="DF55" s="6"/>
+      <c r="DG55" s="6"/>
+      <c r="DH55" s="6"/>
     </row>
-    <row r="56" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -10817,8 +12566,24 @@
       <c r="CP56" s="6"/>
       <c r="CQ56" s="6"/>
       <c r="CR56" s="6"/>
+      <c r="CS56" s="6"/>
+      <c r="CT56" s="6"/>
+      <c r="CU56" s="6"/>
+      <c r="CV56" s="6"/>
+      <c r="CW56" s="6"/>
+      <c r="CX56" s="6"/>
+      <c r="CY56" s="6"/>
+      <c r="CZ56" s="6"/>
+      <c r="DA56" s="6"/>
+      <c r="DB56" s="6"/>
+      <c r="DC56" s="6"/>
+      <c r="DD56" s="6"/>
+      <c r="DE56" s="6"/>
+      <c r="DF56" s="6"/>
+      <c r="DG56" s="6"/>
+      <c r="DH56" s="6"/>
     </row>
-    <row r="57" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -10915,8 +12680,24 @@
       <c r="CP57" s="6"/>
       <c r="CQ57" s="6"/>
       <c r="CR57" s="6"/>
+      <c r="CS57" s="6"/>
+      <c r="CT57" s="6"/>
+      <c r="CU57" s="6"/>
+      <c r="CV57" s="6"/>
+      <c r="CW57" s="6"/>
+      <c r="CX57" s="6"/>
+      <c r="CY57" s="6"/>
+      <c r="CZ57" s="6"/>
+      <c r="DA57" s="6"/>
+      <c r="DB57" s="6"/>
+      <c r="DC57" s="6"/>
+      <c r="DD57" s="6"/>
+      <c r="DE57" s="6"/>
+      <c r="DF57" s="6"/>
+      <c r="DG57" s="6"/>
+      <c r="DH57" s="6"/>
     </row>
-    <row r="58" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -11013,8 +12794,24 @@
       <c r="CP58" s="6"/>
       <c r="CQ58" s="6"/>
       <c r="CR58" s="6"/>
+      <c r="CS58" s="6"/>
+      <c r="CT58" s="6"/>
+      <c r="CU58" s="6"/>
+      <c r="CV58" s="6"/>
+      <c r="CW58" s="6"/>
+      <c r="CX58" s="6"/>
+      <c r="CY58" s="6"/>
+      <c r="CZ58" s="6"/>
+      <c r="DA58" s="6"/>
+      <c r="DB58" s="6"/>
+      <c r="DC58" s="6"/>
+      <c r="DD58" s="6"/>
+      <c r="DE58" s="6"/>
+      <c r="DF58" s="6"/>
+      <c r="DG58" s="6"/>
+      <c r="DH58" s="6"/>
     </row>
-    <row r="59" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -11111,8 +12908,24 @@
       <c r="CP59" s="6"/>
       <c r="CQ59" s="6"/>
       <c r="CR59" s="6"/>
+      <c r="CS59" s="6"/>
+      <c r="CT59" s="6"/>
+      <c r="CU59" s="6"/>
+      <c r="CV59" s="6"/>
+      <c r="CW59" s="6"/>
+      <c r="CX59" s="6"/>
+      <c r="CY59" s="6"/>
+      <c r="CZ59" s="6"/>
+      <c r="DA59" s="6"/>
+      <c r="DB59" s="6"/>
+      <c r="DC59" s="6"/>
+      <c r="DD59" s="6"/>
+      <c r="DE59" s="6"/>
+      <c r="DF59" s="6"/>
+      <c r="DG59" s="6"/>
+      <c r="DH59" s="6"/>
     </row>
-    <row r="60" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -11209,8 +13022,24 @@
       <c r="CP60" s="6"/>
       <c r="CQ60" s="6"/>
       <c r="CR60" s="6"/>
+      <c r="CS60" s="6"/>
+      <c r="CT60" s="6"/>
+      <c r="CU60" s="6"/>
+      <c r="CV60" s="6"/>
+      <c r="CW60" s="6"/>
+      <c r="CX60" s="6"/>
+      <c r="CY60" s="6"/>
+      <c r="CZ60" s="6"/>
+      <c r="DA60" s="6"/>
+      <c r="DB60" s="6"/>
+      <c r="DC60" s="6"/>
+      <c r="DD60" s="6"/>
+      <c r="DE60" s="6"/>
+      <c r="DF60" s="6"/>
+      <c r="DG60" s="6"/>
+      <c r="DH60" s="6"/>
     </row>
-    <row r="61" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>8</v>
       </c>
@@ -11355,8 +13184,32 @@
       <c r="CP61" s="6"/>
       <c r="CQ61" s="6"/>
       <c r="CR61" s="6"/>
+      <c r="CS61" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="CT61" s="6"/>
+      <c r="CU61" s="6"/>
+      <c r="CV61" s="6"/>
+      <c r="CW61" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="CX61" s="6"/>
+      <c r="CY61" s="6"/>
+      <c r="CZ61" s="6"/>
+      <c r="DA61" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="DB61" s="6"/>
+      <c r="DC61" s="6"/>
+      <c r="DD61" s="6"/>
+      <c r="DE61" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="DF61" s="6"/>
+      <c r="DG61" s="6"/>
+      <c r="DH61" s="6"/>
     </row>
-    <row r="62" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -11453,8 +13306,24 @@
       <c r="CP62" s="6"/>
       <c r="CQ62" s="6"/>
       <c r="CR62" s="6"/>
+      <c r="CS62" s="6"/>
+      <c r="CT62" s="6"/>
+      <c r="CU62" s="6"/>
+      <c r="CV62" s="6"/>
+      <c r="CW62" s="6"/>
+      <c r="CX62" s="6"/>
+      <c r="CY62" s="6"/>
+      <c r="CZ62" s="6"/>
+      <c r="DA62" s="6"/>
+      <c r="DB62" s="6"/>
+      <c r="DC62" s="6"/>
+      <c r="DD62" s="6"/>
+      <c r="DE62" s="6"/>
+      <c r="DF62" s="6"/>
+      <c r="DG62" s="6"/>
+      <c r="DH62" s="6"/>
     </row>
-    <row r="63" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -11551,8 +13420,24 @@
       <c r="CP63" s="6"/>
       <c r="CQ63" s="6"/>
       <c r="CR63" s="6"/>
+      <c r="CS63" s="6"/>
+      <c r="CT63" s="6"/>
+      <c r="CU63" s="6"/>
+      <c r="CV63" s="6"/>
+      <c r="CW63" s="6"/>
+      <c r="CX63" s="6"/>
+      <c r="CY63" s="6"/>
+      <c r="CZ63" s="6"/>
+      <c r="DA63" s="6"/>
+      <c r="DB63" s="6"/>
+      <c r="DC63" s="6"/>
+      <c r="DD63" s="6"/>
+      <c r="DE63" s="6"/>
+      <c r="DF63" s="6"/>
+      <c r="DG63" s="6"/>
+      <c r="DH63" s="6"/>
     </row>
-    <row r="64" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -11649,8 +13534,24 @@
       <c r="CP64" s="6"/>
       <c r="CQ64" s="6"/>
       <c r="CR64" s="6"/>
+      <c r="CS64" s="6"/>
+      <c r="CT64" s="6"/>
+      <c r="CU64" s="6"/>
+      <c r="CV64" s="6"/>
+      <c r="CW64" s="6"/>
+      <c r="CX64" s="6"/>
+      <c r="CY64" s="6"/>
+      <c r="CZ64" s="6"/>
+      <c r="DA64" s="6"/>
+      <c r="DB64" s="6"/>
+      <c r="DC64" s="6"/>
+      <c r="DD64" s="6"/>
+      <c r="DE64" s="6"/>
+      <c r="DF64" s="6"/>
+      <c r="DG64" s="6"/>
+      <c r="DH64" s="6"/>
     </row>
-    <row r="65" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -11747,8 +13648,24 @@
       <c r="CP65" s="6"/>
       <c r="CQ65" s="6"/>
       <c r="CR65" s="6"/>
+      <c r="CS65" s="6"/>
+      <c r="CT65" s="6"/>
+      <c r="CU65" s="6"/>
+      <c r="CV65" s="6"/>
+      <c r="CW65" s="6"/>
+      <c r="CX65" s="6"/>
+      <c r="CY65" s="6"/>
+      <c r="CZ65" s="6"/>
+      <c r="DA65" s="6"/>
+      <c r="DB65" s="6"/>
+      <c r="DC65" s="6"/>
+      <c r="DD65" s="6"/>
+      <c r="DE65" s="6"/>
+      <c r="DF65" s="6"/>
+      <c r="DG65" s="6"/>
+      <c r="DH65" s="6"/>
     </row>
-    <row r="66" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -11845,8 +13762,24 @@
       <c r="CP66" s="6"/>
       <c r="CQ66" s="6"/>
       <c r="CR66" s="6"/>
+      <c r="CS66" s="6"/>
+      <c r="CT66" s="6"/>
+      <c r="CU66" s="6"/>
+      <c r="CV66" s="6"/>
+      <c r="CW66" s="6"/>
+      <c r="CX66" s="6"/>
+      <c r="CY66" s="6"/>
+      <c r="CZ66" s="6"/>
+      <c r="DA66" s="6"/>
+      <c r="DB66" s="6"/>
+      <c r="DC66" s="6"/>
+      <c r="DD66" s="6"/>
+      <c r="DE66" s="6"/>
+      <c r="DF66" s="6"/>
+      <c r="DG66" s="6"/>
+      <c r="DH66" s="6"/>
     </row>
-    <row r="67" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -11943,8 +13876,24 @@
       <c r="CP67" s="6"/>
       <c r="CQ67" s="6"/>
       <c r="CR67" s="6"/>
+      <c r="CS67" s="6"/>
+      <c r="CT67" s="6"/>
+      <c r="CU67" s="6"/>
+      <c r="CV67" s="6"/>
+      <c r="CW67" s="6"/>
+      <c r="CX67" s="6"/>
+      <c r="CY67" s="6"/>
+      <c r="CZ67" s="6"/>
+      <c r="DA67" s="6"/>
+      <c r="DB67" s="6"/>
+      <c r="DC67" s="6"/>
+      <c r="DD67" s="6"/>
+      <c r="DE67" s="6"/>
+      <c r="DF67" s="6"/>
+      <c r="DG67" s="6"/>
+      <c r="DH67" s="6"/>
     </row>
-    <row r="68" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -12041,8 +13990,24 @@
       <c r="CP68" s="6"/>
       <c r="CQ68" s="6"/>
       <c r="CR68" s="6"/>
+      <c r="CS68" s="6"/>
+      <c r="CT68" s="6"/>
+      <c r="CU68" s="6"/>
+      <c r="CV68" s="6"/>
+      <c r="CW68" s="6"/>
+      <c r="CX68" s="6"/>
+      <c r="CY68" s="6"/>
+      <c r="CZ68" s="6"/>
+      <c r="DA68" s="6"/>
+      <c r="DB68" s="6"/>
+      <c r="DC68" s="6"/>
+      <c r="DD68" s="6"/>
+      <c r="DE68" s="6"/>
+      <c r="DF68" s="6"/>
+      <c r="DG68" s="6"/>
+      <c r="DH68" s="6"/>
     </row>
-    <row r="69" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -12139,8 +14104,24 @@
       <c r="CP69" s="6"/>
       <c r="CQ69" s="6"/>
       <c r="CR69" s="6"/>
+      <c r="CS69" s="6"/>
+      <c r="CT69" s="6"/>
+      <c r="CU69" s="6"/>
+      <c r="CV69" s="6"/>
+      <c r="CW69" s="6"/>
+      <c r="CX69" s="6"/>
+      <c r="CY69" s="6"/>
+      <c r="CZ69" s="6"/>
+      <c r="DA69" s="6"/>
+      <c r="DB69" s="6"/>
+      <c r="DC69" s="6"/>
+      <c r="DD69" s="6"/>
+      <c r="DE69" s="6"/>
+      <c r="DF69" s="6"/>
+      <c r="DG69" s="6"/>
+      <c r="DH69" s="6"/>
     </row>
-    <row r="70" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -12237,8 +14218,24 @@
       <c r="CP70" s="6"/>
       <c r="CQ70" s="6"/>
       <c r="CR70" s="6"/>
+      <c r="CS70" s="6"/>
+      <c r="CT70" s="6"/>
+      <c r="CU70" s="6"/>
+      <c r="CV70" s="6"/>
+      <c r="CW70" s="6"/>
+      <c r="CX70" s="6"/>
+      <c r="CY70" s="6"/>
+      <c r="CZ70" s="6"/>
+      <c r="DA70" s="6"/>
+      <c r="DB70" s="6"/>
+      <c r="DC70" s="6"/>
+      <c r="DD70" s="6"/>
+      <c r="DE70" s="6"/>
+      <c r="DF70" s="6"/>
+      <c r="DG70" s="6"/>
+      <c r="DH70" s="6"/>
     </row>
-    <row r="71" spans="1:96" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:112" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>11</v>
       </c>
@@ -12383,8 +14380,30 @@
       <c r="CP71" s="6"/>
       <c r="CQ71" s="6"/>
       <c r="CR71" s="6"/>
+      <c r="CS71" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="CT71" s="6"/>
+      <c r="CU71" s="6"/>
+      <c r="CV71" s="6"/>
+      <c r="CW71" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="CX71" s="6"/>
+      <c r="CY71" s="6"/>
+      <c r="CZ71" s="6"/>
+      <c r="DA71" s="5"/>
+      <c r="DB71" s="6"/>
+      <c r="DC71" s="6"/>
+      <c r="DD71" s="6"/>
+      <c r="DE71" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="DF71" s="6"/>
+      <c r="DG71" s="6"/>
+      <c r="DH71" s="6"/>
     </row>
-    <row r="72" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -12481,8 +14500,24 @@
       <c r="CP72" s="6"/>
       <c r="CQ72" s="6"/>
       <c r="CR72" s="6"/>
+      <c r="CS72" s="6"/>
+      <c r="CT72" s="6"/>
+      <c r="CU72" s="6"/>
+      <c r="CV72" s="6"/>
+      <c r="CW72" s="6"/>
+      <c r="CX72" s="6"/>
+      <c r="CY72" s="6"/>
+      <c r="CZ72" s="6"/>
+      <c r="DA72" s="6"/>
+      <c r="DB72" s="6"/>
+      <c r="DC72" s="6"/>
+      <c r="DD72" s="6"/>
+      <c r="DE72" s="6"/>
+      <c r="DF72" s="6"/>
+      <c r="DG72" s="6"/>
+      <c r="DH72" s="6"/>
     </row>
-    <row r="73" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -12579,8 +14614,24 @@
       <c r="CP73" s="6"/>
       <c r="CQ73" s="6"/>
       <c r="CR73" s="6"/>
+      <c r="CS73" s="6"/>
+      <c r="CT73" s="6"/>
+      <c r="CU73" s="6"/>
+      <c r="CV73" s="6"/>
+      <c r="CW73" s="6"/>
+      <c r="CX73" s="6"/>
+      <c r="CY73" s="6"/>
+      <c r="CZ73" s="6"/>
+      <c r="DA73" s="6"/>
+      <c r="DB73" s="6"/>
+      <c r="DC73" s="6"/>
+      <c r="DD73" s="6"/>
+      <c r="DE73" s="6"/>
+      <c r="DF73" s="6"/>
+      <c r="DG73" s="6"/>
+      <c r="DH73" s="6"/>
     </row>
-    <row r="74" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -12677,8 +14728,24 @@
       <c r="CP74" s="6"/>
       <c r="CQ74" s="6"/>
       <c r="CR74" s="6"/>
+      <c r="CS74" s="6"/>
+      <c r="CT74" s="6"/>
+      <c r="CU74" s="6"/>
+      <c r="CV74" s="6"/>
+      <c r="CW74" s="6"/>
+      <c r="CX74" s="6"/>
+      <c r="CY74" s="6"/>
+      <c r="CZ74" s="6"/>
+      <c r="DA74" s="6"/>
+      <c r="DB74" s="6"/>
+      <c r="DC74" s="6"/>
+      <c r="DD74" s="6"/>
+      <c r="DE74" s="6"/>
+      <c r="DF74" s="6"/>
+      <c r="DG74" s="6"/>
+      <c r="DH74" s="6"/>
     </row>
-    <row r="75" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -12775,8 +14842,24 @@
       <c r="CP75" s="6"/>
       <c r="CQ75" s="6"/>
       <c r="CR75" s="6"/>
+      <c r="CS75" s="6"/>
+      <c r="CT75" s="6"/>
+      <c r="CU75" s="6"/>
+      <c r="CV75" s="6"/>
+      <c r="CW75" s="6"/>
+      <c r="CX75" s="6"/>
+      <c r="CY75" s="6"/>
+      <c r="CZ75" s="6"/>
+      <c r="DA75" s="6"/>
+      <c r="DB75" s="6"/>
+      <c r="DC75" s="6"/>
+      <c r="DD75" s="6"/>
+      <c r="DE75" s="6"/>
+      <c r="DF75" s="6"/>
+      <c r="DG75" s="6"/>
+      <c r="DH75" s="6"/>
     </row>
-    <row r="76" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -12873,8 +14956,24 @@
       <c r="CP76" s="6"/>
       <c r="CQ76" s="6"/>
       <c r="CR76" s="6"/>
+      <c r="CS76" s="6"/>
+      <c r="CT76" s="6"/>
+      <c r="CU76" s="6"/>
+      <c r="CV76" s="6"/>
+      <c r="CW76" s="6"/>
+      <c r="CX76" s="6"/>
+      <c r="CY76" s="6"/>
+      <c r="CZ76" s="6"/>
+      <c r="DA76" s="6"/>
+      <c r="DB76" s="6"/>
+      <c r="DC76" s="6"/>
+      <c r="DD76" s="6"/>
+      <c r="DE76" s="6"/>
+      <c r="DF76" s="6"/>
+      <c r="DG76" s="6"/>
+      <c r="DH76" s="6"/>
     </row>
-    <row r="77" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -12971,8 +15070,24 @@
       <c r="CP77" s="6"/>
       <c r="CQ77" s="6"/>
       <c r="CR77" s="6"/>
+      <c r="CS77" s="6"/>
+      <c r="CT77" s="6"/>
+      <c r="CU77" s="6"/>
+      <c r="CV77" s="6"/>
+      <c r="CW77" s="6"/>
+      <c r="CX77" s="6"/>
+      <c r="CY77" s="6"/>
+      <c r="CZ77" s="6"/>
+      <c r="DA77" s="6"/>
+      <c r="DB77" s="6"/>
+      <c r="DC77" s="6"/>
+      <c r="DD77" s="6"/>
+      <c r="DE77" s="6"/>
+      <c r="DF77" s="6"/>
+      <c r="DG77" s="6"/>
+      <c r="DH77" s="6"/>
     </row>
-    <row r="78" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -13069,8 +15184,24 @@
       <c r="CP78" s="6"/>
       <c r="CQ78" s="6"/>
       <c r="CR78" s="6"/>
+      <c r="CS78" s="6"/>
+      <c r="CT78" s="6"/>
+      <c r="CU78" s="6"/>
+      <c r="CV78" s="6"/>
+      <c r="CW78" s="6"/>
+      <c r="CX78" s="6"/>
+      <c r="CY78" s="6"/>
+      <c r="CZ78" s="6"/>
+      <c r="DA78" s="6"/>
+      <c r="DB78" s="6"/>
+      <c r="DC78" s="6"/>
+      <c r="DD78" s="6"/>
+      <c r="DE78" s="6"/>
+      <c r="DF78" s="6"/>
+      <c r="DG78" s="6"/>
+      <c r="DH78" s="6"/>
     </row>
-    <row r="79" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -13167,8 +15298,24 @@
       <c r="CP79" s="6"/>
       <c r="CQ79" s="6"/>
       <c r="CR79" s="6"/>
+      <c r="CS79" s="6"/>
+      <c r="CT79" s="6"/>
+      <c r="CU79" s="6"/>
+      <c r="CV79" s="6"/>
+      <c r="CW79" s="6"/>
+      <c r="CX79" s="6"/>
+      <c r="CY79" s="6"/>
+      <c r="CZ79" s="6"/>
+      <c r="DA79" s="6"/>
+      <c r="DB79" s="6"/>
+      <c r="DC79" s="6"/>
+      <c r="DD79" s="6"/>
+      <c r="DE79" s="6"/>
+      <c r="DF79" s="6"/>
+      <c r="DG79" s="6"/>
+      <c r="DH79" s="6"/>
     </row>
-    <row r="80" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -13265,8 +15412,24 @@
       <c r="CP80" s="6"/>
       <c r="CQ80" s="6"/>
       <c r="CR80" s="6"/>
+      <c r="CS80" s="6"/>
+      <c r="CT80" s="6"/>
+      <c r="CU80" s="6"/>
+      <c r="CV80" s="6"/>
+      <c r="CW80" s="6"/>
+      <c r="CX80" s="6"/>
+      <c r="CY80" s="6"/>
+      <c r="CZ80" s="6"/>
+      <c r="DA80" s="6"/>
+      <c r="DB80" s="6"/>
+      <c r="DC80" s="6"/>
+      <c r="DD80" s="6"/>
+      <c r="DE80" s="6"/>
+      <c r="DF80" s="6"/>
+      <c r="DG80" s="6"/>
+      <c r="DH80" s="6"/>
     </row>
-    <row r="81" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>15</v>
       </c>
@@ -13399,7 +15562,9 @@
       <c r="CH81" s="6"/>
       <c r="CI81" s="6"/>
       <c r="CJ81" s="6"/>
-      <c r="CK81" s="5"/>
+      <c r="CK81" s="5" t="s">
+        <v>234</v>
+      </c>
       <c r="CL81" s="6"/>
       <c r="CM81" s="6"/>
       <c r="CN81" s="6"/>
@@ -13409,8 +15574,28 @@
       <c r="CP81" s="6"/>
       <c r="CQ81" s="6"/>
       <c r="CR81" s="6"/>
+      <c r="CS81" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="CT81" s="6"/>
+      <c r="CU81" s="6"/>
+      <c r="CV81" s="6"/>
+      <c r="CW81" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="CX81" s="6"/>
+      <c r="CY81" s="6"/>
+      <c r="CZ81" s="6"/>
+      <c r="DA81" s="5"/>
+      <c r="DB81" s="6"/>
+      <c r="DC81" s="6"/>
+      <c r="DD81" s="6"/>
+      <c r="DE81" s="5"/>
+      <c r="DF81" s="6"/>
+      <c r="DG81" s="6"/>
+      <c r="DH81" s="6"/>
     </row>
-    <row r="82" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -13507,8 +15692,24 @@
       <c r="CP82" s="6"/>
       <c r="CQ82" s="6"/>
       <c r="CR82" s="6"/>
+      <c r="CS82" s="6"/>
+      <c r="CT82" s="6"/>
+      <c r="CU82" s="6"/>
+      <c r="CV82" s="6"/>
+      <c r="CW82" s="6"/>
+      <c r="CX82" s="6"/>
+      <c r="CY82" s="6"/>
+      <c r="CZ82" s="6"/>
+      <c r="DA82" s="6"/>
+      <c r="DB82" s="6"/>
+      <c r="DC82" s="6"/>
+      <c r="DD82" s="6"/>
+      <c r="DE82" s="6"/>
+      <c r="DF82" s="6"/>
+      <c r="DG82" s="6"/>
+      <c r="DH82" s="6"/>
     </row>
-    <row r="83" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -13605,8 +15806,24 @@
       <c r="CP83" s="6"/>
       <c r="CQ83" s="6"/>
       <c r="CR83" s="6"/>
+      <c r="CS83" s="6"/>
+      <c r="CT83" s="6"/>
+      <c r="CU83" s="6"/>
+      <c r="CV83" s="6"/>
+      <c r="CW83" s="6"/>
+      <c r="CX83" s="6"/>
+      <c r="CY83" s="6"/>
+      <c r="CZ83" s="6"/>
+      <c r="DA83" s="6"/>
+      <c r="DB83" s="6"/>
+      <c r="DC83" s="6"/>
+      <c r="DD83" s="6"/>
+      <c r="DE83" s="6"/>
+      <c r="DF83" s="6"/>
+      <c r="DG83" s="6"/>
+      <c r="DH83" s="6"/>
     </row>
-    <row r="84" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -13703,8 +15920,24 @@
       <c r="CP84" s="6"/>
       <c r="CQ84" s="6"/>
       <c r="CR84" s="6"/>
+      <c r="CS84" s="6"/>
+      <c r="CT84" s="6"/>
+      <c r="CU84" s="6"/>
+      <c r="CV84" s="6"/>
+      <c r="CW84" s="6"/>
+      <c r="CX84" s="6"/>
+      <c r="CY84" s="6"/>
+      <c r="CZ84" s="6"/>
+      <c r="DA84" s="6"/>
+      <c r="DB84" s="6"/>
+      <c r="DC84" s="6"/>
+      <c r="DD84" s="6"/>
+      <c r="DE84" s="6"/>
+      <c r="DF84" s="6"/>
+      <c r="DG84" s="6"/>
+      <c r="DH84" s="6"/>
     </row>
-    <row r="85" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -13801,8 +16034,24 @@
       <c r="CP85" s="6"/>
       <c r="CQ85" s="6"/>
       <c r="CR85" s="6"/>
+      <c r="CS85" s="6"/>
+      <c r="CT85" s="6"/>
+      <c r="CU85" s="6"/>
+      <c r="CV85" s="6"/>
+      <c r="CW85" s="6"/>
+      <c r="CX85" s="6"/>
+      <c r="CY85" s="6"/>
+      <c r="CZ85" s="6"/>
+      <c r="DA85" s="6"/>
+      <c r="DB85" s="6"/>
+      <c r="DC85" s="6"/>
+      <c r="DD85" s="6"/>
+      <c r="DE85" s="6"/>
+      <c r="DF85" s="6"/>
+      <c r="DG85" s="6"/>
+      <c r="DH85" s="6"/>
     </row>
-    <row r="86" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -13899,8 +16148,24 @@
       <c r="CP86" s="6"/>
       <c r="CQ86" s="6"/>
       <c r="CR86" s="6"/>
+      <c r="CS86" s="6"/>
+      <c r="CT86" s="6"/>
+      <c r="CU86" s="6"/>
+      <c r="CV86" s="6"/>
+      <c r="CW86" s="6"/>
+      <c r="CX86" s="6"/>
+      <c r="CY86" s="6"/>
+      <c r="CZ86" s="6"/>
+      <c r="DA86" s="6"/>
+      <c r="DB86" s="6"/>
+      <c r="DC86" s="6"/>
+      <c r="DD86" s="6"/>
+      <c r="DE86" s="6"/>
+      <c r="DF86" s="6"/>
+      <c r="DG86" s="6"/>
+      <c r="DH86" s="6"/>
     </row>
-    <row r="87" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -13997,8 +16262,24 @@
       <c r="CP87" s="6"/>
       <c r="CQ87" s="6"/>
       <c r="CR87" s="6"/>
+      <c r="CS87" s="6"/>
+      <c r="CT87" s="6"/>
+      <c r="CU87" s="6"/>
+      <c r="CV87" s="6"/>
+      <c r="CW87" s="6"/>
+      <c r="CX87" s="6"/>
+      <c r="CY87" s="6"/>
+      <c r="CZ87" s="6"/>
+      <c r="DA87" s="6"/>
+      <c r="DB87" s="6"/>
+      <c r="DC87" s="6"/>
+      <c r="DD87" s="6"/>
+      <c r="DE87" s="6"/>
+      <c r="DF87" s="6"/>
+      <c r="DG87" s="6"/>
+      <c r="DH87" s="6"/>
     </row>
-    <row r="88" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -14095,8 +16376,24 @@
       <c r="CP88" s="6"/>
       <c r="CQ88" s="6"/>
       <c r="CR88" s="6"/>
+      <c r="CS88" s="6"/>
+      <c r="CT88" s="6"/>
+      <c r="CU88" s="6"/>
+      <c r="CV88" s="6"/>
+      <c r="CW88" s="6"/>
+      <c r="CX88" s="6"/>
+      <c r="CY88" s="6"/>
+      <c r="CZ88" s="6"/>
+      <c r="DA88" s="6"/>
+      <c r="DB88" s="6"/>
+      <c r="DC88" s="6"/>
+      <c r="DD88" s="6"/>
+      <c r="DE88" s="6"/>
+      <c r="DF88" s="6"/>
+      <c r="DG88" s="6"/>
+      <c r="DH88" s="6"/>
     </row>
-    <row r="89" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -14193,8 +16490,24 @@
       <c r="CP89" s="6"/>
       <c r="CQ89" s="6"/>
       <c r="CR89" s="6"/>
+      <c r="CS89" s="6"/>
+      <c r="CT89" s="6"/>
+      <c r="CU89" s="6"/>
+      <c r="CV89" s="6"/>
+      <c r="CW89" s="6"/>
+      <c r="CX89" s="6"/>
+      <c r="CY89" s="6"/>
+      <c r="CZ89" s="6"/>
+      <c r="DA89" s="6"/>
+      <c r="DB89" s="6"/>
+      <c r="DC89" s="6"/>
+      <c r="DD89" s="6"/>
+      <c r="DE89" s="6"/>
+      <c r="DF89" s="6"/>
+      <c r="DG89" s="6"/>
+      <c r="DH89" s="6"/>
     </row>
-    <row r="90" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -14291,8 +16604,24 @@
       <c r="CP90" s="6"/>
       <c r="CQ90" s="6"/>
       <c r="CR90" s="6"/>
+      <c r="CS90" s="6"/>
+      <c r="CT90" s="6"/>
+      <c r="CU90" s="6"/>
+      <c r="CV90" s="6"/>
+      <c r="CW90" s="6"/>
+      <c r="CX90" s="6"/>
+      <c r="CY90" s="6"/>
+      <c r="CZ90" s="6"/>
+      <c r="DA90" s="6"/>
+      <c r="DB90" s="6"/>
+      <c r="DC90" s="6"/>
+      <c r="DD90" s="6"/>
+      <c r="DE90" s="6"/>
+      <c r="DF90" s="6"/>
+      <c r="DG90" s="6"/>
+      <c r="DH90" s="6"/>
     </row>
-    <row r="91" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>19</v>
       </c>
@@ -14425,16 +16754,40 @@
       <c r="CH91" s="6"/>
       <c r="CI91" s="6"/>
       <c r="CJ91" s="6"/>
-      <c r="CK91" s="5"/>
+      <c r="CK91" s="5" t="s">
+        <v>238</v>
+      </c>
       <c r="CL91" s="6"/>
       <c r="CM91" s="6"/>
       <c r="CN91" s="6"/>
-      <c r="CO91" s="5"/>
+      <c r="CO91" s="5" t="s">
+        <v>236</v>
+      </c>
       <c r="CP91" s="6"/>
       <c r="CQ91" s="6"/>
       <c r="CR91" s="6"/>
+      <c r="CS91" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="CT91" s="6"/>
+      <c r="CU91" s="6"/>
+      <c r="CV91" s="6"/>
+      <c r="CW91" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="CX91" s="6"/>
+      <c r="CY91" s="6"/>
+      <c r="CZ91" s="6"/>
+      <c r="DA91" s="5"/>
+      <c r="DB91" s="6"/>
+      <c r="DC91" s="6"/>
+      <c r="DD91" s="6"/>
+      <c r="DE91" s="5"/>
+      <c r="DF91" s="6"/>
+      <c r="DG91" s="6"/>
+      <c r="DH91" s="6"/>
     </row>
-    <row r="92" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -14531,8 +16884,24 @@
       <c r="CP92" s="6"/>
       <c r="CQ92" s="6"/>
       <c r="CR92" s="6"/>
+      <c r="CS92" s="6"/>
+      <c r="CT92" s="6"/>
+      <c r="CU92" s="6"/>
+      <c r="CV92" s="6"/>
+      <c r="CW92" s="6"/>
+      <c r="CX92" s="6"/>
+      <c r="CY92" s="6"/>
+      <c r="CZ92" s="6"/>
+      <c r="DA92" s="6"/>
+      <c r="DB92" s="6"/>
+      <c r="DC92" s="6"/>
+      <c r="DD92" s="6"/>
+      <c r="DE92" s="6"/>
+      <c r="DF92" s="6"/>
+      <c r="DG92" s="6"/>
+      <c r="DH92" s="6"/>
     </row>
-    <row r="93" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -14629,8 +16998,24 @@
       <c r="CP93" s="6"/>
       <c r="CQ93" s="6"/>
       <c r="CR93" s="6"/>
+      <c r="CS93" s="6"/>
+      <c r="CT93" s="6"/>
+      <c r="CU93" s="6"/>
+      <c r="CV93" s="6"/>
+      <c r="CW93" s="6"/>
+      <c r="CX93" s="6"/>
+      <c r="CY93" s="6"/>
+      <c r="CZ93" s="6"/>
+      <c r="DA93" s="6"/>
+      <c r="DB93" s="6"/>
+      <c r="DC93" s="6"/>
+      <c r="DD93" s="6"/>
+      <c r="DE93" s="6"/>
+      <c r="DF93" s="6"/>
+      <c r="DG93" s="6"/>
+      <c r="DH93" s="6"/>
     </row>
-    <row r="94" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -14727,8 +17112,24 @@
       <c r="CP94" s="6"/>
       <c r="CQ94" s="6"/>
       <c r="CR94" s="6"/>
+      <c r="CS94" s="6"/>
+      <c r="CT94" s="6"/>
+      <c r="CU94" s="6"/>
+      <c r="CV94" s="6"/>
+      <c r="CW94" s="6"/>
+      <c r="CX94" s="6"/>
+      <c r="CY94" s="6"/>
+      <c r="CZ94" s="6"/>
+      <c r="DA94" s="6"/>
+      <c r="DB94" s="6"/>
+      <c r="DC94" s="6"/>
+      <c r="DD94" s="6"/>
+      <c r="DE94" s="6"/>
+      <c r="DF94" s="6"/>
+      <c r="DG94" s="6"/>
+      <c r="DH94" s="6"/>
     </row>
-    <row r="95" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -14825,8 +17226,24 @@
       <c r="CP95" s="6"/>
       <c r="CQ95" s="6"/>
       <c r="CR95" s="6"/>
+      <c r="CS95" s="6"/>
+      <c r="CT95" s="6"/>
+      <c r="CU95" s="6"/>
+      <c r="CV95" s="6"/>
+      <c r="CW95" s="6"/>
+      <c r="CX95" s="6"/>
+      <c r="CY95" s="6"/>
+      <c r="CZ95" s="6"/>
+      <c r="DA95" s="6"/>
+      <c r="DB95" s="6"/>
+      <c r="DC95" s="6"/>
+      <c r="DD95" s="6"/>
+      <c r="DE95" s="6"/>
+      <c r="DF95" s="6"/>
+      <c r="DG95" s="6"/>
+      <c r="DH95" s="6"/>
     </row>
-    <row r="96" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -14923,8 +17340,24 @@
       <c r="CP96" s="6"/>
       <c r="CQ96" s="6"/>
       <c r="CR96" s="6"/>
+      <c r="CS96" s="6"/>
+      <c r="CT96" s="6"/>
+      <c r="CU96" s="6"/>
+      <c r="CV96" s="6"/>
+      <c r="CW96" s="6"/>
+      <c r="CX96" s="6"/>
+      <c r="CY96" s="6"/>
+      <c r="CZ96" s="6"/>
+      <c r="DA96" s="6"/>
+      <c r="DB96" s="6"/>
+      <c r="DC96" s="6"/>
+      <c r="DD96" s="6"/>
+      <c r="DE96" s="6"/>
+      <c r="DF96" s="6"/>
+      <c r="DG96" s="6"/>
+      <c r="DH96" s="6"/>
     </row>
-    <row r="97" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -15021,8 +17454,24 @@
       <c r="CP97" s="6"/>
       <c r="CQ97" s="6"/>
       <c r="CR97" s="6"/>
+      <c r="CS97" s="6"/>
+      <c r="CT97" s="6"/>
+      <c r="CU97" s="6"/>
+      <c r="CV97" s="6"/>
+      <c r="CW97" s="6"/>
+      <c r="CX97" s="6"/>
+      <c r="CY97" s="6"/>
+      <c r="CZ97" s="6"/>
+      <c r="DA97" s="6"/>
+      <c r="DB97" s="6"/>
+      <c r="DC97" s="6"/>
+      <c r="DD97" s="6"/>
+      <c r="DE97" s="6"/>
+      <c r="DF97" s="6"/>
+      <c r="DG97" s="6"/>
+      <c r="DH97" s="6"/>
     </row>
-    <row r="98" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -15119,8 +17568,24 @@
       <c r="CP98" s="6"/>
       <c r="CQ98" s="6"/>
       <c r="CR98" s="6"/>
+      <c r="CS98" s="6"/>
+      <c r="CT98" s="6"/>
+      <c r="CU98" s="6"/>
+      <c r="CV98" s="6"/>
+      <c r="CW98" s="6"/>
+      <c r="CX98" s="6"/>
+      <c r="CY98" s="6"/>
+      <c r="CZ98" s="6"/>
+      <c r="DA98" s="6"/>
+      <c r="DB98" s="6"/>
+      <c r="DC98" s="6"/>
+      <c r="DD98" s="6"/>
+      <c r="DE98" s="6"/>
+      <c r="DF98" s="6"/>
+      <c r="DG98" s="6"/>
+      <c r="DH98" s="6"/>
     </row>
-    <row r="99" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -15217,8 +17682,24 @@
       <c r="CP99" s="6"/>
       <c r="CQ99" s="6"/>
       <c r="CR99" s="6"/>
+      <c r="CS99" s="6"/>
+      <c r="CT99" s="6"/>
+      <c r="CU99" s="6"/>
+      <c r="CV99" s="6"/>
+      <c r="CW99" s="6"/>
+      <c r="CX99" s="6"/>
+      <c r="CY99" s="6"/>
+      <c r="CZ99" s="6"/>
+      <c r="DA99" s="6"/>
+      <c r="DB99" s="6"/>
+      <c r="DC99" s="6"/>
+      <c r="DD99" s="6"/>
+      <c r="DE99" s="6"/>
+      <c r="DF99" s="6"/>
+      <c r="DG99" s="6"/>
+      <c r="DH99" s="6"/>
     </row>
-    <row r="100" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -15315,8 +17796,24 @@
       <c r="CP100" s="6"/>
       <c r="CQ100" s="6"/>
       <c r="CR100" s="6"/>
+      <c r="CS100" s="6"/>
+      <c r="CT100" s="6"/>
+      <c r="CU100" s="6"/>
+      <c r="CV100" s="6"/>
+      <c r="CW100" s="6"/>
+      <c r="CX100" s="6"/>
+      <c r="CY100" s="6"/>
+      <c r="CZ100" s="6"/>
+      <c r="DA100" s="6"/>
+      <c r="DB100" s="6"/>
+      <c r="DC100" s="6"/>
+      <c r="DD100" s="6"/>
+      <c r="DE100" s="6"/>
+      <c r="DF100" s="6"/>
+      <c r="DG100" s="6"/>
+      <c r="DH100" s="6"/>
     </row>
-    <row r="101" spans="1:96" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:112" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -15330,7 +17827,7 @@
       <c r="K101" s="4"/>
       <c r="L101" s="4"/>
     </row>
-    <row r="102" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A102" s="2"/>
       <c r="B102" s="3"/>
       <c r="C102" s="4"/>
@@ -15344,7 +17841,7 @@
       <c r="K102" s="4"/>
       <c r="L102" s="4"/>
     </row>
-    <row r="103" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A103" s="2"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -15358,7 +17855,7 @@
       <c r="K103" s="4"/>
       <c r="L103" s="4"/>
     </row>
-    <row r="104" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A104" s="2"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -15372,7 +17869,7 @@
       <c r="K104" s="4"/>
       <c r="L104" s="4"/>
     </row>
-    <row r="105" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A105" s="2"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -15386,7 +17883,7 @@
       <c r="K105" s="4"/>
       <c r="L105" s="4"/>
     </row>
-    <row r="106" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A106" s="2"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -15400,7 +17897,7 @@
       <c r="K106" s="4"/>
       <c r="L106" s="4"/>
     </row>
-    <row r="107" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A107" s="2"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -15414,7 +17911,7 @@
       <c r="K107" s="4"/>
       <c r="L107" s="4"/>
     </row>
-    <row r="108" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A108" s="2"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -15428,7 +17925,7 @@
       <c r="K108" s="4"/>
       <c r="L108" s="4"/>
     </row>
-    <row r="109" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A109" s="2"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -15442,7 +17939,7 @@
       <c r="K109" s="4"/>
       <c r="L109" s="4"/>
     </row>
-    <row r="110" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A110" s="2"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -15456,7 +17953,7 @@
       <c r="K110" s="4"/>
       <c r="L110" s="4"/>
     </row>
-    <row r="111" spans="1:96" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:112" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -15470,7 +17967,7 @@
       <c r="K111" s="4"/>
       <c r="L111" s="4"/>
     </row>
-    <row r="112" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A112" s="2"/>
       <c r="B112" s="3"/>
       <c r="C112" s="4"/>
@@ -16023,7 +18520,47 @@
       <c r="E151" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="240">
+  <mergeCells count="280">
+    <mergeCell ref="DA51:DD60"/>
+    <mergeCell ref="DE51:DH60"/>
+    <mergeCell ref="DA61:DD70"/>
+    <mergeCell ref="DE61:DH70"/>
+    <mergeCell ref="DA71:DD80"/>
+    <mergeCell ref="DE71:DH80"/>
+    <mergeCell ref="DA81:DD90"/>
+    <mergeCell ref="DE81:DH90"/>
+    <mergeCell ref="DA91:DD100"/>
+    <mergeCell ref="DE91:DH100"/>
+    <mergeCell ref="DA1:DD10"/>
+    <mergeCell ref="DE1:DH10"/>
+    <mergeCell ref="DA11:DD20"/>
+    <mergeCell ref="DE11:DH20"/>
+    <mergeCell ref="DA21:DD30"/>
+    <mergeCell ref="DE21:DH30"/>
+    <mergeCell ref="DA31:DD40"/>
+    <mergeCell ref="DE31:DH40"/>
+    <mergeCell ref="DA41:DD50"/>
+    <mergeCell ref="DE41:DH50"/>
+    <mergeCell ref="CS51:CV60"/>
+    <mergeCell ref="CW51:CZ60"/>
+    <mergeCell ref="CS61:CV70"/>
+    <mergeCell ref="CW61:CZ70"/>
+    <mergeCell ref="CS71:CV80"/>
+    <mergeCell ref="CW71:CZ80"/>
+    <mergeCell ref="CS81:CV90"/>
+    <mergeCell ref="CW81:CZ90"/>
+    <mergeCell ref="CS91:CV100"/>
+    <mergeCell ref="CW91:CZ100"/>
+    <mergeCell ref="CS1:CV10"/>
+    <mergeCell ref="CW1:CZ10"/>
+    <mergeCell ref="CS11:CV20"/>
+    <mergeCell ref="CW11:CZ20"/>
+    <mergeCell ref="CS21:CV30"/>
+    <mergeCell ref="CW21:CZ30"/>
+    <mergeCell ref="CS31:CV40"/>
+    <mergeCell ref="CW31:CZ40"/>
+    <mergeCell ref="CS41:CV50"/>
+    <mergeCell ref="CW41:CZ50"/>
     <mergeCell ref="BU51:BX60"/>
     <mergeCell ref="BY51:CB60"/>
     <mergeCell ref="BU61:BX70"/>

--- a/tanulókártyák/Tanulókártyák.xlsx
+++ b/tanulókártyák/Tanulókártyák.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atesz\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D087CB-FA50-495D-BA4A-83F5B00F82A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96CE3FD-5B42-41A7-B079-2A4EA36B5A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="291">
   <si>
     <r>
       <rPr>
@@ -1817,55 +1817,6 @@
       </rPr>
       <t xml:space="preserve"> - a Java memória egy speciális területe, ahol a JVM a String literálokat tárolja és újrahasznosítja a memóriahatékonyság érdekében.
 Ha két String ugyanazzal az értékkel jön létre literálként, akkor ugyanarra a memóriabeli objektumra hivatkoznak.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Stack - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">a memória azon része, ahol a metódushívásokhoz tartozó lokális változók és a hívási verem (call stack) tárolódik. Gyors, automatikusan kezelt memória, amely LIFO (Last In, First Out) elven működik.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Heap - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>a memória azon része, ahol az objektumok és példányok dinamikusan kerülnek lefoglalásra. A heap memóriát a Garbage Collector kezeli, és az objektumok addig maradnak benne, amíg van rájuk hivatkozás.</t>
     </r>
   </si>
   <si>
@@ -5475,6 +5426,718 @@
   </si>
   <si>
     <t>Mit jelent a cascade, milyen formái vannak?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">API: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>egy előre definiált szabványos felület, amely megmondja, hogyan használhatok valamit anélkül, hogy ismerném a belső működését.
+Web API - itt két alkalmazás kommunikál.
+JPA API - itt nem két alkalmazás kommunikál, hanem a Java programod használ egy szabványos interfészt adatbázis-kezelésre.
+Collections API - itt az API a Java által biztosított gyűjteményosztályok és interfészek összessége.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mit jelent az API?
+Mondj pár példát.</t>
+  </si>
+  <si>
+    <t>Mi az URI?
+Miben tér el az URL-től?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">URI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(uniform resource identifier): egy erőforrás egyedi azonosítója. Segítségével egy erőforrás (pl. felhasználó, fájl, weboldal) azonosítható egy rendszerben.
+Példa: /users/1 vagy /products/42
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">URI vs URL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(uniform resource locator):
+URI = azonosító (/users/1)
+URL = azonosító + elérési hely (https://example.com/users/1)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Stack - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">a memória azon része, ahol a metódushívásokhoz tartozó lokális változók és más fontos adatok tárolódnak. Gyors, automatikusan kezelt memória, amely LIFO (Last In, First Out) elven működik.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Heap - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a memória azon része, ahol az objektumok és példányok dinamikusan kerülnek lefoglalásra. A heap memóriát a Garbage Collector kezeli, és az objektumok addig maradnak benne, amíg van rájuk hivatkozás.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mit tárol pontosan a JVM Stack?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Minden thread-nek saját stack-je van, és ezen belül:
+Stack frame-ek tárolódhatnak.
+Egy frame egy metódushíváshoz tartozik.
+A Stack Frame tartalma:
+lokális változók (primitive-ek és referenciák)
+metódus paraméterek
+operand stack (számítások ideiglenes eredményei)
+visszatérési cím (hova menjen vissza a futás)</t>
+    </r>
+  </si>
+  <si>
+    <t>Mit tárol pontosan a JVM Stack?
+(pontosító kérdés a Stack-hez)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Big O </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">- Az algoritmus futási idejének (vagy memóriahasználatának) növekedési ütemét írja le.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Időkomplexitás</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Megmutatja, hogyan nő a futási idő a bemenet méretével.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Térkomplexitás</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Megmutatja, mennyi extra memória kell az algoritmusnak.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a big O, az időkomplexitás és térkomplexitás?</t>
+  </si>
+  <si>
+    <t>Milyen gyakori komplexitásokat ismersz?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – konstans - a futási idő nem függ a bemenet méretétől. (Tömb elemének elérése)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">O(log n) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">– logaritmikus - a probléma mérete minden lépésben csökken (pl. bináris keresés).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – lineáris - minden elemet egyszer végignéz.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">O(n log n) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">- hatékony rendezési algoritmusok (pl. mergesort, heapsort).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n²)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – kvadratikus - beágyazott ciklusok, minden elem minden elemmel összehasonlítva.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(2ⁿ)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -Exponenciális növekedés, pl. bruteforce.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Big O példák:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1) példa - Tömb egy elemének elérése: arr[5]
+O(n) példa - Lista végigiterálása for ciklussal
+O(n²) példa - Két egymásba ágyazott ciklus
+Adatszerkezetek működése:
+Array - O(1) access, O(n) insert/delete
+LinkedList - O(n) access, O(1) insert/delete (ha a node adott)
+HashMap - Átlag O(1) keresés, beszúrás, törlés</t>
+    </r>
+  </si>
+  <si>
+    <t>Milyen gyakori Big O példákat tudnál mondani?
+(komplexitás / adatszerkezetek működése)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Algoritmus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Lépések sorozata egy probléma megoldására.
+Bemenetet vesz és kimenetet ad.
+Végrehajtható és egyértelmű utasításokból áll.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi az algoritmus?</t>
+  </si>
+  <si>
+    <t>Hogyan működik a binary és a linear search?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Binary Search</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Rendezett listában kereső algoritmus.
+Mindig a középső elemet vizsgálja, és felezi a keresési tartományt.
+Időkomplexitás: O(log n).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linear Search</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Egyszerű keresés, minden elemet sorban végignéz.
+Akkor is működik, ha a lista nincs rendezve.
+Időkomplexitás: O(n).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rekurzió</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Olyan függvényhívás, amely saját magát hívja meg.
+Kell egy base case, hogy megálljon.
+Gyakran fa-szerű problémákra használják (pl. Fibonacci).</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a rekurzió?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Quick Sort - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Pivot elemet választ, és kisebb/nagyobb részre bont. Rekurzívan rendezi a részeket. 
+Átlag: O(n log n), worst case: O(n²)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Merge Sort </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">- Divide and Conquer (oszd meg és uralkodj). A listát felezi, majd összefésüli rendezve.
+Időkomplexitás: O(n log n)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bubble Sort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Rendezési algoritmus, ami szomszédos elemeket hasonlít össze és cserél. A legnagyobb elemek “felbuborékolnak” a végére.
+Időkomplexitás: O(n²).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Selection Sort </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">- Minden lépésben kiválasztja a legkisebb elemet, és előre teszi. A lista elejét fokozatosan “felépíti” rendezetté.
+Időkomplexitás: O(n²)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Insertion Sort </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Egyesével beszúrja az elemeket a már rendezett részbe. Olyan, mint amikor kézzel rendezel kártyákat.
+Időkomplexitás: O(n²) 
+(de majdnem rendezett listán O(n))
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Selection, insertion sort</t>
+  </si>
+  <si>
+    <t>Quick, Merge, Bubble sort</t>
   </si>
 </sst>
 </file>
@@ -5867,13 +6530,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DH151"/>
+  <dimension ref="A1:DP151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="112" width="11" customWidth="1"/>
+    <col min="1" max="120" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -5947,103 +6610,115 @@
       <c r="AU1" s="8"/>
       <c r="AV1" s="8"/>
       <c r="AW1" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AX1" s="8"/>
       <c r="AY1" s="8"/>
       <c r="AZ1" s="8"/>
       <c r="BA1" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BB1" s="8"/>
       <c r="BC1" s="8"/>
       <c r="BD1" s="8"/>
       <c r="BE1" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="BF1" s="8"/>
       <c r="BG1" s="8"/>
       <c r="BH1" s="8"/>
       <c r="BI1" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BJ1" s="8"/>
       <c r="BK1" s="8"/>
       <c r="BL1" s="8"/>
       <c r="BM1" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="BN1" s="8"/>
       <c r="BO1" s="8"/>
       <c r="BP1" s="8"/>
       <c r="BQ1" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="BR1" s="8"/>
       <c r="BS1" s="8"/>
       <c r="BT1" s="8"/>
       <c r="BU1" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="BV1" s="8"/>
       <c r="BW1" s="8"/>
       <c r="BX1" s="8"/>
       <c r="BY1" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="BZ1" s="8"/>
       <c r="CA1" s="8"/>
       <c r="CB1" s="8"/>
       <c r="CC1" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="CD1" s="8"/>
       <c r="CE1" s="8"/>
       <c r="CF1" s="8"/>
       <c r="CG1" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="CH1" s="8"/>
       <c r="CI1" s="8"/>
       <c r="CJ1" s="8"/>
       <c r="CK1" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="CL1" s="8"/>
       <c r="CM1" s="8"/>
       <c r="CN1" s="8"/>
       <c r="CO1" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="CP1" s="8"/>
       <c r="CQ1" s="8"/>
       <c r="CR1" s="8"/>
       <c r="CS1" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="CT1" s="8"/>
       <c r="CU1" s="8"/>
       <c r="CV1" s="8"/>
       <c r="CW1" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="CX1" s="8"/>
       <c r="CY1" s="8"/>
       <c r="CZ1" s="8"/>
       <c r="DA1" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="DB1" s="8"/>
       <c r="DC1" s="8"/>
       <c r="DD1" s="8"/>
       <c r="DE1" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="DF1" s="8"/>
       <c r="DG1" s="8"/>
       <c r="DH1" s="8"/>
+      <c r="DI1" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="DJ1" s="8"/>
+      <c r="DK1" s="8"/>
+      <c r="DL1" s="8"/>
+      <c r="DM1" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="DN1" s="8"/>
+      <c r="DO1" s="8"/>
+      <c r="DP1" s="8"/>
     </row>
-    <row r="2" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -6156,8 +6831,16 @@
       <c r="DF2" s="8"/>
       <c r="DG2" s="8"/>
       <c r="DH2" s="8"/>
+      <c r="DI2" s="8"/>
+      <c r="DJ2" s="8"/>
+      <c r="DK2" s="8"/>
+      <c r="DL2" s="8"/>
+      <c r="DM2" s="8"/>
+      <c r="DN2" s="8"/>
+      <c r="DO2" s="8"/>
+      <c r="DP2" s="8"/>
     </row>
-    <row r="3" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -6270,8 +6953,16 @@
       <c r="DF3" s="8"/>
       <c r="DG3" s="8"/>
       <c r="DH3" s="8"/>
+      <c r="DI3" s="8"/>
+      <c r="DJ3" s="8"/>
+      <c r="DK3" s="8"/>
+      <c r="DL3" s="8"/>
+      <c r="DM3" s="8"/>
+      <c r="DN3" s="8"/>
+      <c r="DO3" s="8"/>
+      <c r="DP3" s="8"/>
     </row>
-    <row r="4" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -6384,8 +7075,16 @@
       <c r="DF4" s="8"/>
       <c r="DG4" s="8"/>
       <c r="DH4" s="8"/>
+      <c r="DI4" s="8"/>
+      <c r="DJ4" s="8"/>
+      <c r="DK4" s="8"/>
+      <c r="DL4" s="8"/>
+      <c r="DM4" s="8"/>
+      <c r="DN4" s="8"/>
+      <c r="DO4" s="8"/>
+      <c r="DP4" s="8"/>
     </row>
-    <row r="5" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -6498,8 +7197,16 @@
       <c r="DF5" s="8"/>
       <c r="DG5" s="8"/>
       <c r="DH5" s="8"/>
+      <c r="DI5" s="8"/>
+      <c r="DJ5" s="8"/>
+      <c r="DK5" s="8"/>
+      <c r="DL5" s="8"/>
+      <c r="DM5" s="8"/>
+      <c r="DN5" s="8"/>
+      <c r="DO5" s="8"/>
+      <c r="DP5" s="8"/>
     </row>
-    <row r="6" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -6612,8 +7319,16 @@
       <c r="DF6" s="8"/>
       <c r="DG6" s="8"/>
       <c r="DH6" s="8"/>
+      <c r="DI6" s="8"/>
+      <c r="DJ6" s="8"/>
+      <c r="DK6" s="8"/>
+      <c r="DL6" s="8"/>
+      <c r="DM6" s="8"/>
+      <c r="DN6" s="8"/>
+      <c r="DO6" s="8"/>
+      <c r="DP6" s="8"/>
     </row>
-    <row r="7" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -6726,8 +7441,16 @@
       <c r="DF7" s="8"/>
       <c r="DG7" s="8"/>
       <c r="DH7" s="8"/>
+      <c r="DI7" s="8"/>
+      <c r="DJ7" s="8"/>
+      <c r="DK7" s="8"/>
+      <c r="DL7" s="8"/>
+      <c r="DM7" s="8"/>
+      <c r="DN7" s="8"/>
+      <c r="DO7" s="8"/>
+      <c r="DP7" s="8"/>
     </row>
-    <row r="8" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -6840,8 +7563,16 @@
       <c r="DF8" s="8"/>
       <c r="DG8" s="8"/>
       <c r="DH8" s="8"/>
+      <c r="DI8" s="8"/>
+      <c r="DJ8" s="8"/>
+      <c r="DK8" s="8"/>
+      <c r="DL8" s="8"/>
+      <c r="DM8" s="8"/>
+      <c r="DN8" s="8"/>
+      <c r="DO8" s="8"/>
+      <c r="DP8" s="8"/>
     </row>
-    <row r="9" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -6954,8 +7685,16 @@
       <c r="DF9" s="8"/>
       <c r="DG9" s="8"/>
       <c r="DH9" s="8"/>
+      <c r="DI9" s="8"/>
+      <c r="DJ9" s="8"/>
+      <c r="DK9" s="8"/>
+      <c r="DL9" s="8"/>
+      <c r="DM9" s="8"/>
+      <c r="DN9" s="8"/>
+      <c r="DO9" s="8"/>
+      <c r="DP9" s="8"/>
     </row>
-    <row r="10" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -7068,8 +7807,16 @@
       <c r="DF10" s="8"/>
       <c r="DG10" s="8"/>
       <c r="DH10" s="8"/>
+      <c r="DI10" s="8"/>
+      <c r="DJ10" s="8"/>
+      <c r="DK10" s="8"/>
+      <c r="DL10" s="8"/>
+      <c r="DM10" s="8"/>
+      <c r="DN10" s="8"/>
+      <c r="DO10" s="8"/>
+      <c r="DP10" s="8"/>
     </row>
-    <row r="11" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>2</v>
       </c>
@@ -7137,109 +7884,121 @@
       <c r="AQ11" s="8"/>
       <c r="AR11" s="8"/>
       <c r="AS11" s="7" t="s">
-        <v>101</v>
+        <v>272</v>
       </c>
       <c r="AT11" s="8"/>
       <c r="AU11" s="8"/>
       <c r="AV11" s="8"/>
       <c r="AW11" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AX11" s="8"/>
       <c r="AY11" s="8"/>
       <c r="AZ11" s="8"/>
       <c r="BA11" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BB11" s="8"/>
       <c r="BC11" s="8"/>
       <c r="BD11" s="8"/>
       <c r="BE11" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="BF11" s="8"/>
       <c r="BG11" s="8"/>
       <c r="BH11" s="8"/>
       <c r="BI11" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BJ11" s="8"/>
       <c r="BK11" s="8"/>
       <c r="BL11" s="8"/>
       <c r="BM11" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="BN11" s="8"/>
       <c r="BO11" s="8"/>
       <c r="BP11" s="8"/>
       <c r="BQ11" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BR11" s="8"/>
       <c r="BS11" s="8"/>
       <c r="BT11" s="8"/>
       <c r="BU11" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BV11" s="8"/>
       <c r="BW11" s="8"/>
       <c r="BX11" s="8"/>
       <c r="BY11" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BZ11" s="8"/>
       <c r="CA11" s="8"/>
       <c r="CB11" s="8"/>
       <c r="CC11" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="CD11" s="8"/>
       <c r="CE11" s="8"/>
       <c r="CF11" s="8"/>
       <c r="CG11" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="CH11" s="8"/>
       <c r="CI11" s="8"/>
       <c r="CJ11" s="8"/>
       <c r="CK11" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="CL11" s="8"/>
       <c r="CM11" s="8"/>
       <c r="CN11" s="8"/>
       <c r="CO11" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="CP11" s="8"/>
       <c r="CQ11" s="8"/>
       <c r="CR11" s="8"/>
       <c r="CS11" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="CT11" s="8"/>
       <c r="CU11" s="8"/>
       <c r="CV11" s="8"/>
       <c r="CW11" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="CX11" s="8"/>
       <c r="CY11" s="8"/>
       <c r="CZ11" s="8"/>
       <c r="DA11" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="DB11" s="8"/>
       <c r="DC11" s="8"/>
       <c r="DD11" s="8"/>
       <c r="DE11" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="DF11" s="8"/>
       <c r="DG11" s="8"/>
       <c r="DH11" s="8"/>
+      <c r="DI11" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="DJ11" s="8"/>
+      <c r="DK11" s="8"/>
+      <c r="DL11" s="8"/>
+      <c r="DM11" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="DN11" s="8"/>
+      <c r="DO11" s="8"/>
+      <c r="DP11" s="8"/>
     </row>
-    <row r="12" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -7352,8 +8111,16 @@
       <c r="DF12" s="8"/>
       <c r="DG12" s="8"/>
       <c r="DH12" s="8"/>
+      <c r="DI12" s="8"/>
+      <c r="DJ12" s="8"/>
+      <c r="DK12" s="8"/>
+      <c r="DL12" s="8"/>
+      <c r="DM12" s="8"/>
+      <c r="DN12" s="8"/>
+      <c r="DO12" s="8"/>
+      <c r="DP12" s="8"/>
     </row>
-    <row r="13" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -7466,8 +8233,16 @@
       <c r="DF13" s="8"/>
       <c r="DG13" s="8"/>
       <c r="DH13" s="8"/>
+      <c r="DI13" s="8"/>
+      <c r="DJ13" s="8"/>
+      <c r="DK13" s="8"/>
+      <c r="DL13" s="8"/>
+      <c r="DM13" s="8"/>
+      <c r="DN13" s="8"/>
+      <c r="DO13" s="8"/>
+      <c r="DP13" s="8"/>
     </row>
-    <row r="14" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -7580,8 +8355,16 @@
       <c r="DF14" s="8"/>
       <c r="DG14" s="8"/>
       <c r="DH14" s="8"/>
+      <c r="DI14" s="8"/>
+      <c r="DJ14" s="8"/>
+      <c r="DK14" s="8"/>
+      <c r="DL14" s="8"/>
+      <c r="DM14" s="8"/>
+      <c r="DN14" s="8"/>
+      <c r="DO14" s="8"/>
+      <c r="DP14" s="8"/>
     </row>
-    <row r="15" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -7694,8 +8477,16 @@
       <c r="DF15" s="8"/>
       <c r="DG15" s="8"/>
       <c r="DH15" s="8"/>
+      <c r="DI15" s="8"/>
+      <c r="DJ15" s="8"/>
+      <c r="DK15" s="8"/>
+      <c r="DL15" s="8"/>
+      <c r="DM15" s="8"/>
+      <c r="DN15" s="8"/>
+      <c r="DO15" s="8"/>
+      <c r="DP15" s="8"/>
     </row>
-    <row r="16" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -7808,8 +8599,16 @@
       <c r="DF16" s="8"/>
       <c r="DG16" s="8"/>
       <c r="DH16" s="8"/>
+      <c r="DI16" s="8"/>
+      <c r="DJ16" s="8"/>
+      <c r="DK16" s="8"/>
+      <c r="DL16" s="8"/>
+      <c r="DM16" s="8"/>
+      <c r="DN16" s="8"/>
+      <c r="DO16" s="8"/>
+      <c r="DP16" s="8"/>
     </row>
-    <row r="17" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -7922,8 +8721,16 @@
       <c r="DF17" s="8"/>
       <c r="DG17" s="8"/>
       <c r="DH17" s="8"/>
+      <c r="DI17" s="8"/>
+      <c r="DJ17" s="8"/>
+      <c r="DK17" s="8"/>
+      <c r="DL17" s="8"/>
+      <c r="DM17" s="8"/>
+      <c r="DN17" s="8"/>
+      <c r="DO17" s="8"/>
+      <c r="DP17" s="8"/>
     </row>
-    <row r="18" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -8036,8 +8843,16 @@
       <c r="DF18" s="8"/>
       <c r="DG18" s="8"/>
       <c r="DH18" s="8"/>
+      <c r="DI18" s="8"/>
+      <c r="DJ18" s="8"/>
+      <c r="DK18" s="8"/>
+      <c r="DL18" s="8"/>
+      <c r="DM18" s="8"/>
+      <c r="DN18" s="8"/>
+      <c r="DO18" s="8"/>
+      <c r="DP18" s="8"/>
     </row>
-    <row r="19" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -8150,8 +8965,16 @@
       <c r="DF19" s="8"/>
       <c r="DG19" s="8"/>
       <c r="DH19" s="8"/>
+      <c r="DI19" s="8"/>
+      <c r="DJ19" s="8"/>
+      <c r="DK19" s="8"/>
+      <c r="DL19" s="8"/>
+      <c r="DM19" s="8"/>
+      <c r="DN19" s="8"/>
+      <c r="DO19" s="8"/>
+      <c r="DP19" s="8"/>
     </row>
-    <row r="20" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -8264,8 +9087,16 @@
       <c r="DF20" s="8"/>
       <c r="DG20" s="8"/>
       <c r="DH20" s="8"/>
+      <c r="DI20" s="8"/>
+      <c r="DJ20" s="8"/>
+      <c r="DK20" s="8"/>
+      <c r="DL20" s="8"/>
+      <c r="DM20" s="8"/>
+      <c r="DN20" s="8"/>
+      <c r="DO20" s="8"/>
+      <c r="DP20" s="8"/>
     </row>
-    <row r="21" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>4</v>
       </c>
@@ -8285,7 +9116,7 @@
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N21" s="8"/>
       <c r="O21" s="8"/>
@@ -8327,113 +9158,127 @@
       <c r="AM21" s="8"/>
       <c r="AN21" s="8"/>
       <c r="AO21" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AP21" s="8"/>
       <c r="AQ21" s="8"/>
       <c r="AR21" s="8"/>
       <c r="AS21" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AT21" s="8"/>
       <c r="AU21" s="8"/>
       <c r="AV21" s="8"/>
       <c r="AW21" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AX21" s="8"/>
       <c r="AY21" s="8"/>
       <c r="AZ21" s="8"/>
       <c r="BA21" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="BB21" s="8"/>
       <c r="BC21" s="8"/>
       <c r="BD21" s="8"/>
       <c r="BE21" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BF21" s="8"/>
       <c r="BG21" s="8"/>
       <c r="BH21" s="8"/>
       <c r="BI21" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="BJ21" s="8"/>
       <c r="BK21" s="8"/>
       <c r="BL21" s="8"/>
       <c r="BM21" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="BN21" s="8"/>
       <c r="BO21" s="8"/>
       <c r="BP21" s="8"/>
       <c r="BQ21" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="BR21" s="8"/>
       <c r="BS21" s="8"/>
       <c r="BT21" s="8"/>
       <c r="BU21" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BV21" s="8"/>
       <c r="BW21" s="8"/>
       <c r="BX21" s="8"/>
       <c r="BY21" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="BZ21" s="8"/>
       <c r="CA21" s="8"/>
       <c r="CB21" s="8"/>
       <c r="CC21" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="CD21" s="8"/>
       <c r="CE21" s="8"/>
       <c r="CF21" s="8"/>
       <c r="CG21" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="CH21" s="8"/>
       <c r="CI21" s="8"/>
       <c r="CJ21" s="8"/>
       <c r="CK21" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="CL21" s="8"/>
       <c r="CM21" s="8"/>
       <c r="CN21" s="8"/>
       <c r="CO21" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="CP21" s="8"/>
       <c r="CQ21" s="8"/>
       <c r="CR21" s="8"/>
       <c r="CS21" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="CT21" s="8"/>
       <c r="CU21" s="8"/>
       <c r="CV21" s="8"/>
       <c r="CW21" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="CX21" s="8"/>
       <c r="CY21" s="8"/>
       <c r="CZ21" s="8"/>
       <c r="DA21" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="DB21" s="8"/>
       <c r="DC21" s="8"/>
       <c r="DD21" s="8"/>
-      <c r="DE21" s="7"/>
+      <c r="DE21" s="7" t="s">
+        <v>268</v>
+      </c>
       <c r="DF21" s="8"/>
       <c r="DG21" s="8"/>
       <c r="DH21" s="8"/>
+      <c r="DI21" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="DJ21" s="8"/>
+      <c r="DK21" s="8"/>
+      <c r="DL21" s="8"/>
+      <c r="DM21" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="DN21" s="8"/>
+      <c r="DO21" s="8"/>
+      <c r="DP21" s="8"/>
     </row>
-    <row r="22" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -8546,8 +9391,16 @@
       <c r="DF22" s="8"/>
       <c r="DG22" s="8"/>
       <c r="DH22" s="8"/>
+      <c r="DI22" s="8"/>
+      <c r="DJ22" s="8"/>
+      <c r="DK22" s="8"/>
+      <c r="DL22" s="8"/>
+      <c r="DM22" s="8"/>
+      <c r="DN22" s="8"/>
+      <c r="DO22" s="8"/>
+      <c r="DP22" s="8"/>
     </row>
-    <row r="23" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -8660,8 +9513,16 @@
       <c r="DF23" s="8"/>
       <c r="DG23" s="8"/>
       <c r="DH23" s="8"/>
+      <c r="DI23" s="8"/>
+      <c r="DJ23" s="8"/>
+      <c r="DK23" s="8"/>
+      <c r="DL23" s="8"/>
+      <c r="DM23" s="8"/>
+      <c r="DN23" s="8"/>
+      <c r="DO23" s="8"/>
+      <c r="DP23" s="8"/>
     </row>
-    <row r="24" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -8774,8 +9635,16 @@
       <c r="DF24" s="8"/>
       <c r="DG24" s="8"/>
       <c r="DH24" s="8"/>
+      <c r="DI24" s="8"/>
+      <c r="DJ24" s="8"/>
+      <c r="DK24" s="8"/>
+      <c r="DL24" s="8"/>
+      <c r="DM24" s="8"/>
+      <c r="DN24" s="8"/>
+      <c r="DO24" s="8"/>
+      <c r="DP24" s="8"/>
     </row>
-    <row r="25" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -8888,8 +9757,16 @@
       <c r="DF25" s="8"/>
       <c r="DG25" s="8"/>
       <c r="DH25" s="8"/>
+      <c r="DI25" s="8"/>
+      <c r="DJ25" s="8"/>
+      <c r="DK25" s="8"/>
+      <c r="DL25" s="8"/>
+      <c r="DM25" s="8"/>
+      <c r="DN25" s="8"/>
+      <c r="DO25" s="8"/>
+      <c r="DP25" s="8"/>
     </row>
-    <row r="26" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -9002,8 +9879,16 @@
       <c r="DF26" s="8"/>
       <c r="DG26" s="8"/>
       <c r="DH26" s="8"/>
+      <c r="DI26" s="8"/>
+      <c r="DJ26" s="8"/>
+      <c r="DK26" s="8"/>
+      <c r="DL26" s="8"/>
+      <c r="DM26" s="8"/>
+      <c r="DN26" s="8"/>
+      <c r="DO26" s="8"/>
+      <c r="DP26" s="8"/>
     </row>
-    <row r="27" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -9116,8 +10001,16 @@
       <c r="DF27" s="8"/>
       <c r="DG27" s="8"/>
       <c r="DH27" s="8"/>
+      <c r="DI27" s="8"/>
+      <c r="DJ27" s="8"/>
+      <c r="DK27" s="8"/>
+      <c r="DL27" s="8"/>
+      <c r="DM27" s="8"/>
+      <c r="DN27" s="8"/>
+      <c r="DO27" s="8"/>
+      <c r="DP27" s="8"/>
     </row>
-    <row r="28" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -9230,8 +10123,16 @@
       <c r="DF28" s="8"/>
       <c r="DG28" s="8"/>
       <c r="DH28" s="8"/>
+      <c r="DI28" s="8"/>
+      <c r="DJ28" s="8"/>
+      <c r="DK28" s="8"/>
+      <c r="DL28" s="8"/>
+      <c r="DM28" s="8"/>
+      <c r="DN28" s="8"/>
+      <c r="DO28" s="8"/>
+      <c r="DP28" s="8"/>
     </row>
-    <row r="29" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -9344,8 +10245,16 @@
       <c r="DF29" s="8"/>
       <c r="DG29" s="8"/>
       <c r="DH29" s="8"/>
+      <c r="DI29" s="8"/>
+      <c r="DJ29" s="8"/>
+      <c r="DK29" s="8"/>
+      <c r="DL29" s="8"/>
+      <c r="DM29" s="8"/>
+      <c r="DN29" s="8"/>
+      <c r="DO29" s="8"/>
+      <c r="DP29" s="8"/>
     </row>
-    <row r="30" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -9458,8 +10367,16 @@
       <c r="DF30" s="8"/>
       <c r="DG30" s="8"/>
       <c r="DH30" s="8"/>
+      <c r="DI30" s="8"/>
+      <c r="DJ30" s="8"/>
+      <c r="DK30" s="8"/>
+      <c r="DL30" s="8"/>
+      <c r="DM30" s="8"/>
+      <c r="DN30" s="8"/>
+      <c r="DO30" s="8"/>
+      <c r="DP30" s="8"/>
     </row>
-    <row r="31" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>13</v>
       </c>
@@ -9521,111 +10438,123 @@
       <c r="AM31" s="8"/>
       <c r="AN31" s="8"/>
       <c r="AO31" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AP31" s="8"/>
       <c r="AQ31" s="8"/>
       <c r="AR31" s="8"/>
       <c r="AS31" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AT31" s="8"/>
       <c r="AU31" s="8"/>
       <c r="AV31" s="8"/>
       <c r="AW31" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AX31" s="8"/>
       <c r="AY31" s="8"/>
       <c r="AZ31" s="8"/>
       <c r="BA31" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BB31" s="8"/>
       <c r="BC31" s="8"/>
       <c r="BD31" s="8"/>
       <c r="BE31" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="BF31" s="8"/>
       <c r="BG31" s="8"/>
       <c r="BH31" s="8"/>
       <c r="BI31" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="BJ31" s="8"/>
       <c r="BK31" s="8"/>
       <c r="BL31" s="8"/>
       <c r="BM31" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BN31" s="8"/>
       <c r="BO31" s="8"/>
       <c r="BP31" s="8"/>
       <c r="BQ31" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="BR31" s="8"/>
       <c r="BS31" s="8"/>
       <c r="BT31" s="8"/>
       <c r="BU31" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BV31" s="8"/>
       <c r="BW31" s="8"/>
       <c r="BX31" s="8"/>
       <c r="BY31" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="BZ31" s="8"/>
       <c r="CA31" s="8"/>
       <c r="CB31" s="8"/>
       <c r="CC31" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="CD31" s="8"/>
       <c r="CE31" s="8"/>
       <c r="CF31" s="8"/>
       <c r="CG31" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="CH31" s="8"/>
       <c r="CI31" s="8"/>
       <c r="CJ31" s="8"/>
       <c r="CK31" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="CL31" s="8"/>
       <c r="CM31" s="8"/>
       <c r="CN31" s="8"/>
       <c r="CO31" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="CP31" s="8"/>
       <c r="CQ31" s="8"/>
       <c r="CR31" s="8"/>
       <c r="CS31" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="CT31" s="8"/>
       <c r="CU31" s="8"/>
       <c r="CV31" s="8"/>
       <c r="CW31" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="CX31" s="8"/>
       <c r="CY31" s="8"/>
       <c r="CZ31" s="8"/>
-      <c r="DA31" s="7"/>
+      <c r="DA31" s="7" t="s">
+        <v>271</v>
+      </c>
       <c r="DB31" s="8"/>
       <c r="DC31" s="8"/>
       <c r="DD31" s="8"/>
-      <c r="DE31" s="7"/>
+      <c r="DE31" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="DF31" s="8"/>
       <c r="DG31" s="8"/>
       <c r="DH31" s="8"/>
+      <c r="DI31" s="7"/>
+      <c r="DJ31" s="8"/>
+      <c r="DK31" s="8"/>
+      <c r="DL31" s="8"/>
+      <c r="DM31" s="7"/>
+      <c r="DN31" s="8"/>
+      <c r="DO31" s="8"/>
+      <c r="DP31" s="8"/>
     </row>
-    <row r="32" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -9738,8 +10667,16 @@
       <c r="DF32" s="8"/>
       <c r="DG32" s="8"/>
       <c r="DH32" s="8"/>
+      <c r="DI32" s="8"/>
+      <c r="DJ32" s="8"/>
+      <c r="DK32" s="8"/>
+      <c r="DL32" s="8"/>
+      <c r="DM32" s="8"/>
+      <c r="DN32" s="8"/>
+      <c r="DO32" s="8"/>
+      <c r="DP32" s="8"/>
     </row>
-    <row r="33" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -9852,8 +10789,16 @@
       <c r="DF33" s="8"/>
       <c r="DG33" s="8"/>
       <c r="DH33" s="8"/>
+      <c r="DI33" s="8"/>
+      <c r="DJ33" s="8"/>
+      <c r="DK33" s="8"/>
+      <c r="DL33" s="8"/>
+      <c r="DM33" s="8"/>
+      <c r="DN33" s="8"/>
+      <c r="DO33" s="8"/>
+      <c r="DP33" s="8"/>
     </row>
-    <row r="34" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -9966,8 +10911,16 @@
       <c r="DF34" s="8"/>
       <c r="DG34" s="8"/>
       <c r="DH34" s="8"/>
+      <c r="DI34" s="8"/>
+      <c r="DJ34" s="8"/>
+      <c r="DK34" s="8"/>
+      <c r="DL34" s="8"/>
+      <c r="DM34" s="8"/>
+      <c r="DN34" s="8"/>
+      <c r="DO34" s="8"/>
+      <c r="DP34" s="8"/>
     </row>
-    <row r="35" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -10080,8 +11033,16 @@
       <c r="DF35" s="8"/>
       <c r="DG35" s="8"/>
       <c r="DH35" s="8"/>
+      <c r="DI35" s="8"/>
+      <c r="DJ35" s="8"/>
+      <c r="DK35" s="8"/>
+      <c r="DL35" s="8"/>
+      <c r="DM35" s="8"/>
+      <c r="DN35" s="8"/>
+      <c r="DO35" s="8"/>
+      <c r="DP35" s="8"/>
     </row>
-    <row r="36" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -10194,8 +11155,16 @@
       <c r="DF36" s="8"/>
       <c r="DG36" s="8"/>
       <c r="DH36" s="8"/>
+      <c r="DI36" s="8"/>
+      <c r="DJ36" s="8"/>
+      <c r="DK36" s="8"/>
+      <c r="DL36" s="8"/>
+      <c r="DM36" s="8"/>
+      <c r="DN36" s="8"/>
+      <c r="DO36" s="8"/>
+      <c r="DP36" s="8"/>
     </row>
-    <row r="37" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -10308,8 +11277,16 @@
       <c r="DF37" s="8"/>
       <c r="DG37" s="8"/>
       <c r="DH37" s="8"/>
+      <c r="DI37" s="8"/>
+      <c r="DJ37" s="8"/>
+      <c r="DK37" s="8"/>
+      <c r="DL37" s="8"/>
+      <c r="DM37" s="8"/>
+      <c r="DN37" s="8"/>
+      <c r="DO37" s="8"/>
+      <c r="DP37" s="8"/>
     </row>
-    <row r="38" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -10422,8 +11399,16 @@
       <c r="DF38" s="8"/>
       <c r="DG38" s="8"/>
       <c r="DH38" s="8"/>
+      <c r="DI38" s="8"/>
+      <c r="DJ38" s="8"/>
+      <c r="DK38" s="8"/>
+      <c r="DL38" s="8"/>
+      <c r="DM38" s="8"/>
+      <c r="DN38" s="8"/>
+      <c r="DO38" s="8"/>
+      <c r="DP38" s="8"/>
     </row>
-    <row r="39" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -10536,8 +11521,16 @@
       <c r="DF39" s="8"/>
       <c r="DG39" s="8"/>
       <c r="DH39" s="8"/>
+      <c r="DI39" s="8"/>
+      <c r="DJ39" s="8"/>
+      <c r="DK39" s="8"/>
+      <c r="DL39" s="8"/>
+      <c r="DM39" s="8"/>
+      <c r="DN39" s="8"/>
+      <c r="DO39" s="8"/>
+      <c r="DP39" s="8"/>
     </row>
-    <row r="40" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -10650,8 +11643,16 @@
       <c r="DF40" s="8"/>
       <c r="DG40" s="8"/>
       <c r="DH40" s="8"/>
+      <c r="DI40" s="8"/>
+      <c r="DJ40" s="8"/>
+      <c r="DK40" s="8"/>
+      <c r="DL40" s="8"/>
+      <c r="DM40" s="8"/>
+      <c r="DN40" s="8"/>
+      <c r="DO40" s="8"/>
+      <c r="DP40" s="8"/>
     </row>
-    <row r="41" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>16</v>
       </c>
@@ -10689,7 +11690,7 @@
       <c r="W41" s="8"/>
       <c r="X41" s="8"/>
       <c r="Y41" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Z41" s="8"/>
       <c r="AA41" s="8"/>
@@ -10713,111 +11714,123 @@
       <c r="AM41" s="8"/>
       <c r="AN41" s="8"/>
       <c r="AO41" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AP41" s="8"/>
       <c r="AQ41" s="8"/>
       <c r="AR41" s="8"/>
       <c r="AS41" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AT41" s="8"/>
       <c r="AU41" s="8"/>
       <c r="AV41" s="8"/>
       <c r="AW41" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AX41" s="8"/>
       <c r="AY41" s="8"/>
       <c r="AZ41" s="8"/>
       <c r="BA41" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="BB41" s="8"/>
       <c r="BC41" s="8"/>
       <c r="BD41" s="8"/>
       <c r="BE41" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="BF41" s="8"/>
       <c r="BG41" s="8"/>
       <c r="BH41" s="8"/>
       <c r="BI41" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="BJ41" s="8"/>
       <c r="BK41" s="8"/>
       <c r="BL41" s="8"/>
       <c r="BM41" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="BN41" s="8"/>
       <c r="BO41" s="8"/>
       <c r="BP41" s="8"/>
       <c r="BQ41" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="BR41" s="8"/>
       <c r="BS41" s="8"/>
       <c r="BT41" s="8"/>
       <c r="BU41" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BV41" s="8"/>
       <c r="BW41" s="8"/>
       <c r="BX41" s="8"/>
       <c r="BY41" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BZ41" s="8"/>
       <c r="CA41" s="8"/>
       <c r="CB41" s="8"/>
       <c r="CC41" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="CD41" s="8"/>
       <c r="CE41" s="8"/>
       <c r="CF41" s="8"/>
       <c r="CG41" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="CH41" s="8"/>
       <c r="CI41" s="8"/>
       <c r="CJ41" s="8"/>
       <c r="CK41" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="CL41" s="8"/>
       <c r="CM41" s="8"/>
       <c r="CN41" s="8"/>
       <c r="CO41" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="CP41" s="8"/>
       <c r="CQ41" s="8"/>
       <c r="CR41" s="8"/>
       <c r="CS41" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="CT41" s="8"/>
       <c r="CU41" s="8"/>
       <c r="CV41" s="8"/>
       <c r="CW41" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="CX41" s="8"/>
       <c r="CY41" s="8"/>
       <c r="CZ41" s="8"/>
-      <c r="DA41" s="7"/>
+      <c r="DA41" s="7" t="s">
+        <v>275</v>
+      </c>
       <c r="DB41" s="8"/>
       <c r="DC41" s="8"/>
       <c r="DD41" s="8"/>
-      <c r="DE41" s="9"/>
+      <c r="DE41" s="9" t="s">
+        <v>278</v>
+      </c>
       <c r="DF41" s="8"/>
       <c r="DG41" s="8"/>
       <c r="DH41" s="8"/>
+      <c r="DI41" s="7"/>
+      <c r="DJ41" s="8"/>
+      <c r="DK41" s="8"/>
+      <c r="DL41" s="8"/>
+      <c r="DM41" s="9"/>
+      <c r="DN41" s="8"/>
+      <c r="DO41" s="8"/>
+      <c r="DP41" s="8"/>
     </row>
-    <row r="42" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -10930,8 +11943,16 @@
       <c r="DF42" s="8"/>
       <c r="DG42" s="8"/>
       <c r="DH42" s="8"/>
+      <c r="DI42" s="8"/>
+      <c r="DJ42" s="8"/>
+      <c r="DK42" s="8"/>
+      <c r="DL42" s="8"/>
+      <c r="DM42" s="8"/>
+      <c r="DN42" s="8"/>
+      <c r="DO42" s="8"/>
+      <c r="DP42" s="8"/>
     </row>
-    <row r="43" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -11044,8 +12065,16 @@
       <c r="DF43" s="8"/>
       <c r="DG43" s="8"/>
       <c r="DH43" s="8"/>
+      <c r="DI43" s="8"/>
+      <c r="DJ43" s="8"/>
+      <c r="DK43" s="8"/>
+      <c r="DL43" s="8"/>
+      <c r="DM43" s="8"/>
+      <c r="DN43" s="8"/>
+      <c r="DO43" s="8"/>
+      <c r="DP43" s="8"/>
     </row>
-    <row r="44" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -11158,8 +12187,16 @@
       <c r="DF44" s="8"/>
       <c r="DG44" s="8"/>
       <c r="DH44" s="8"/>
+      <c r="DI44" s="8"/>
+      <c r="DJ44" s="8"/>
+      <c r="DK44" s="8"/>
+      <c r="DL44" s="8"/>
+      <c r="DM44" s="8"/>
+      <c r="DN44" s="8"/>
+      <c r="DO44" s="8"/>
+      <c r="DP44" s="8"/>
     </row>
-    <row r="45" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -11272,8 +12309,16 @@
       <c r="DF45" s="8"/>
       <c r="DG45" s="8"/>
       <c r="DH45" s="8"/>
+      <c r="DI45" s="8"/>
+      <c r="DJ45" s="8"/>
+      <c r="DK45" s="8"/>
+      <c r="DL45" s="8"/>
+      <c r="DM45" s="8"/>
+      <c r="DN45" s="8"/>
+      <c r="DO45" s="8"/>
+      <c r="DP45" s="8"/>
     </row>
-    <row r="46" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -11386,8 +12431,16 @@
       <c r="DF46" s="8"/>
       <c r="DG46" s="8"/>
       <c r="DH46" s="8"/>
+      <c r="DI46" s="8"/>
+      <c r="DJ46" s="8"/>
+      <c r="DK46" s="8"/>
+      <c r="DL46" s="8"/>
+      <c r="DM46" s="8"/>
+      <c r="DN46" s="8"/>
+      <c r="DO46" s="8"/>
+      <c r="DP46" s="8"/>
     </row>
-    <row r="47" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -11500,8 +12553,16 @@
       <c r="DF47" s="8"/>
       <c r="DG47" s="8"/>
       <c r="DH47" s="8"/>
+      <c r="DI47" s="8"/>
+      <c r="DJ47" s="8"/>
+      <c r="DK47" s="8"/>
+      <c r="DL47" s="8"/>
+      <c r="DM47" s="8"/>
+      <c r="DN47" s="8"/>
+      <c r="DO47" s="8"/>
+      <c r="DP47" s="8"/>
     </row>
-    <row r="48" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -11614,8 +12675,16 @@
       <c r="DF48" s="8"/>
       <c r="DG48" s="8"/>
       <c r="DH48" s="8"/>
+      <c r="DI48" s="8"/>
+      <c r="DJ48" s="8"/>
+      <c r="DK48" s="8"/>
+      <c r="DL48" s="8"/>
+      <c r="DM48" s="8"/>
+      <c r="DN48" s="8"/>
+      <c r="DO48" s="8"/>
+      <c r="DP48" s="8"/>
     </row>
-    <row r="49" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -11728,8 +12797,16 @@
       <c r="DF49" s="8"/>
       <c r="DG49" s="8"/>
       <c r="DH49" s="8"/>
+      <c r="DI49" s="8"/>
+      <c r="DJ49" s="8"/>
+      <c r="DK49" s="8"/>
+      <c r="DL49" s="8"/>
+      <c r="DM49" s="8"/>
+      <c r="DN49" s="8"/>
+      <c r="DO49" s="8"/>
+      <c r="DP49" s="8"/>
     </row>
-    <row r="50" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -11842,8 +12919,16 @@
       <c r="DF50" s="8"/>
       <c r="DG50" s="8"/>
       <c r="DH50" s="8"/>
+      <c r="DI50" s="8"/>
+      <c r="DJ50" s="8"/>
+      <c r="DK50" s="8"/>
+      <c r="DL50" s="8"/>
+      <c r="DM50" s="8"/>
+      <c r="DN50" s="8"/>
+      <c r="DO50" s="8"/>
+      <c r="DP50" s="8"/>
     </row>
-    <row r="51" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>6</v>
       </c>
@@ -11917,103 +13002,115 @@
       <c r="AU51" s="6"/>
       <c r="AV51" s="6"/>
       <c r="AW51" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AX51" s="6"/>
       <c r="AY51" s="6"/>
       <c r="AZ51" s="6"/>
       <c r="BA51" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="BB51" s="6"/>
       <c r="BC51" s="6"/>
       <c r="BD51" s="6"/>
       <c r="BE51" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BF51" s="6"/>
       <c r="BG51" s="6"/>
       <c r="BH51" s="6"/>
       <c r="BI51" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BJ51" s="6"/>
       <c r="BK51" s="6"/>
       <c r="BL51" s="6"/>
       <c r="BM51" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="BN51" s="6"/>
       <c r="BO51" s="6"/>
       <c r="BP51" s="6"/>
       <c r="BQ51" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="BR51" s="6"/>
       <c r="BS51" s="6"/>
       <c r="BT51" s="6"/>
       <c r="BU51" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="BV51" s="6"/>
       <c r="BW51" s="6"/>
       <c r="BX51" s="6"/>
       <c r="BY51" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="BZ51" s="6"/>
       <c r="CA51" s="6"/>
       <c r="CB51" s="6"/>
       <c r="CC51" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="CD51" s="6"/>
       <c r="CE51" s="6"/>
       <c r="CF51" s="6"/>
       <c r="CG51" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="CH51" s="6"/>
       <c r="CI51" s="6"/>
       <c r="CJ51" s="6"/>
       <c r="CK51" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="CL51" s="6"/>
       <c r="CM51" s="6"/>
       <c r="CN51" s="6"/>
       <c r="CO51" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="CP51" s="6"/>
       <c r="CQ51" s="6"/>
       <c r="CR51" s="6"/>
       <c r="CS51" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="CT51" s="6"/>
       <c r="CU51" s="6"/>
       <c r="CV51" s="6"/>
       <c r="CW51" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="CX51" s="6"/>
       <c r="CY51" s="6"/>
       <c r="CZ51" s="6"/>
       <c r="DA51" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="DB51" s="6"/>
       <c r="DC51" s="6"/>
       <c r="DD51" s="6"/>
       <c r="DE51" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="DF51" s="6"/>
       <c r="DG51" s="6"/>
       <c r="DH51" s="6"/>
+      <c r="DI51" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="DJ51" s="6"/>
+      <c r="DK51" s="6"/>
+      <c r="DL51" s="6"/>
+      <c r="DM51" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="DN51" s="6"/>
+      <c r="DO51" s="6"/>
+      <c r="DP51" s="6"/>
     </row>
-    <row r="52" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -12126,8 +13223,16 @@
       <c r="DF52" s="6"/>
       <c r="DG52" s="6"/>
       <c r="DH52" s="6"/>
+      <c r="DI52" s="6"/>
+      <c r="DJ52" s="6"/>
+      <c r="DK52" s="6"/>
+      <c r="DL52" s="6"/>
+      <c r="DM52" s="6"/>
+      <c r="DN52" s="6"/>
+      <c r="DO52" s="6"/>
+      <c r="DP52" s="6"/>
     </row>
-    <row r="53" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -12240,8 +13345,16 @@
       <c r="DF53" s="6"/>
       <c r="DG53" s="6"/>
       <c r="DH53" s="6"/>
+      <c r="DI53" s="6"/>
+      <c r="DJ53" s="6"/>
+      <c r="DK53" s="6"/>
+      <c r="DL53" s="6"/>
+      <c r="DM53" s="6"/>
+      <c r="DN53" s="6"/>
+      <c r="DO53" s="6"/>
+      <c r="DP53" s="6"/>
     </row>
-    <row r="54" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -12354,8 +13467,16 @@
       <c r="DF54" s="6"/>
       <c r="DG54" s="6"/>
       <c r="DH54" s="6"/>
+      <c r="DI54" s="6"/>
+      <c r="DJ54" s="6"/>
+      <c r="DK54" s="6"/>
+      <c r="DL54" s="6"/>
+      <c r="DM54" s="6"/>
+      <c r="DN54" s="6"/>
+      <c r="DO54" s="6"/>
+      <c r="DP54" s="6"/>
     </row>
-    <row r="55" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -12468,8 +13589,16 @@
       <c r="DF55" s="6"/>
       <c r="DG55" s="6"/>
       <c r="DH55" s="6"/>
+      <c r="DI55" s="6"/>
+      <c r="DJ55" s="6"/>
+      <c r="DK55" s="6"/>
+      <c r="DL55" s="6"/>
+      <c r="DM55" s="6"/>
+      <c r="DN55" s="6"/>
+      <c r="DO55" s="6"/>
+      <c r="DP55" s="6"/>
     </row>
-    <row r="56" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -12582,8 +13711,16 @@
       <c r="DF56" s="6"/>
       <c r="DG56" s="6"/>
       <c r="DH56" s="6"/>
+      <c r="DI56" s="6"/>
+      <c r="DJ56" s="6"/>
+      <c r="DK56" s="6"/>
+      <c r="DL56" s="6"/>
+      <c r="DM56" s="6"/>
+      <c r="DN56" s="6"/>
+      <c r="DO56" s="6"/>
+      <c r="DP56" s="6"/>
     </row>
-    <row r="57" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -12696,8 +13833,16 @@
       <c r="DF57" s="6"/>
       <c r="DG57" s="6"/>
       <c r="DH57" s="6"/>
+      <c r="DI57" s="6"/>
+      <c r="DJ57" s="6"/>
+      <c r="DK57" s="6"/>
+      <c r="DL57" s="6"/>
+      <c r="DM57" s="6"/>
+      <c r="DN57" s="6"/>
+      <c r="DO57" s="6"/>
+      <c r="DP57" s="6"/>
     </row>
-    <row r="58" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -12810,8 +13955,16 @@
       <c r="DF58" s="6"/>
       <c r="DG58" s="6"/>
       <c r="DH58" s="6"/>
+      <c r="DI58" s="6"/>
+      <c r="DJ58" s="6"/>
+      <c r="DK58" s="6"/>
+      <c r="DL58" s="6"/>
+      <c r="DM58" s="6"/>
+      <c r="DN58" s="6"/>
+      <c r="DO58" s="6"/>
+      <c r="DP58" s="6"/>
     </row>
-    <row r="59" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -12924,8 +14077,16 @@
       <c r="DF59" s="6"/>
       <c r="DG59" s="6"/>
       <c r="DH59" s="6"/>
+      <c r="DI59" s="6"/>
+      <c r="DJ59" s="6"/>
+      <c r="DK59" s="6"/>
+      <c r="DL59" s="6"/>
+      <c r="DM59" s="6"/>
+      <c r="DN59" s="6"/>
+      <c r="DO59" s="6"/>
+      <c r="DP59" s="6"/>
     </row>
-    <row r="60" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -13038,8 +14199,16 @@
       <c r="DF60" s="6"/>
       <c r="DG60" s="6"/>
       <c r="DH60" s="6"/>
+      <c r="DI60" s="6"/>
+      <c r="DJ60" s="6"/>
+      <c r="DK60" s="6"/>
+      <c r="DL60" s="6"/>
+      <c r="DM60" s="6"/>
+      <c r="DN60" s="6"/>
+      <c r="DO60" s="6"/>
+      <c r="DP60" s="6"/>
     </row>
-    <row r="61" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>8</v>
       </c>
@@ -13089,7 +14258,7 @@
       <c r="AE61" s="6"/>
       <c r="AF61" s="6"/>
       <c r="AG61" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AH61" s="6"/>
       <c r="AI61" s="6"/>
@@ -13101,115 +14270,127 @@
       <c r="AM61" s="6"/>
       <c r="AN61" s="6"/>
       <c r="AO61" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AP61" s="6"/>
       <c r="AQ61" s="6"/>
       <c r="AR61" s="6"/>
       <c r="AS61" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AT61" s="6"/>
       <c r="AU61" s="6"/>
       <c r="AV61" s="6"/>
       <c r="AW61" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AX61" s="6"/>
       <c r="AY61" s="6"/>
       <c r="AZ61" s="6"/>
       <c r="BA61" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BB61" s="6"/>
       <c r="BC61" s="6"/>
       <c r="BD61" s="6"/>
       <c r="BE61" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="BF61" s="6"/>
       <c r="BG61" s="6"/>
       <c r="BH61" s="6"/>
       <c r="BI61" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="BJ61" s="6"/>
       <c r="BK61" s="6"/>
       <c r="BL61" s="6"/>
       <c r="BM61" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="BN61" s="6"/>
       <c r="BO61" s="6"/>
       <c r="BP61" s="6"/>
       <c r="BQ61" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="BR61" s="6"/>
       <c r="BS61" s="6"/>
       <c r="BT61" s="6"/>
       <c r="BU61" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BV61" s="6"/>
       <c r="BW61" s="6"/>
       <c r="BX61" s="6"/>
       <c r="BY61" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BZ61" s="6"/>
       <c r="CA61" s="6"/>
       <c r="CB61" s="6"/>
       <c r="CC61" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="CD61" s="6"/>
       <c r="CE61" s="6"/>
       <c r="CF61" s="6"/>
       <c r="CG61" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="CH61" s="6"/>
       <c r="CI61" s="6"/>
       <c r="CJ61" s="6"/>
       <c r="CK61" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="CL61" s="6"/>
       <c r="CM61" s="6"/>
       <c r="CN61" s="6"/>
       <c r="CO61" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="CP61" s="6"/>
       <c r="CQ61" s="6"/>
       <c r="CR61" s="6"/>
       <c r="CS61" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="CT61" s="6"/>
       <c r="CU61" s="6"/>
       <c r="CV61" s="6"/>
       <c r="CW61" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="CX61" s="6"/>
       <c r="CY61" s="6"/>
       <c r="CZ61" s="6"/>
       <c r="DA61" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="DB61" s="6"/>
       <c r="DC61" s="6"/>
       <c r="DD61" s="6"/>
       <c r="DE61" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="DF61" s="6"/>
       <c r="DG61" s="6"/>
       <c r="DH61" s="6"/>
+      <c r="DI61" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="DJ61" s="6"/>
+      <c r="DK61" s="6"/>
+      <c r="DL61" s="6"/>
+      <c r="DM61" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="DN61" s="6"/>
+      <c r="DO61" s="6"/>
+      <c r="DP61" s="6"/>
     </row>
-    <row r="62" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -13322,8 +14503,16 @@
       <c r="DF62" s="6"/>
       <c r="DG62" s="6"/>
       <c r="DH62" s="6"/>
+      <c r="DI62" s="6"/>
+      <c r="DJ62" s="6"/>
+      <c r="DK62" s="6"/>
+      <c r="DL62" s="6"/>
+      <c r="DM62" s="6"/>
+      <c r="DN62" s="6"/>
+      <c r="DO62" s="6"/>
+      <c r="DP62" s="6"/>
     </row>
-    <row r="63" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -13436,8 +14625,16 @@
       <c r="DF63" s="6"/>
       <c r="DG63" s="6"/>
       <c r="DH63" s="6"/>
+      <c r="DI63" s="6"/>
+      <c r="DJ63" s="6"/>
+      <c r="DK63" s="6"/>
+      <c r="DL63" s="6"/>
+      <c r="DM63" s="6"/>
+      <c r="DN63" s="6"/>
+      <c r="DO63" s="6"/>
+      <c r="DP63" s="6"/>
     </row>
-    <row r="64" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -13550,8 +14747,16 @@
       <c r="DF64" s="6"/>
       <c r="DG64" s="6"/>
       <c r="DH64" s="6"/>
+      <c r="DI64" s="6"/>
+      <c r="DJ64" s="6"/>
+      <c r="DK64" s="6"/>
+      <c r="DL64" s="6"/>
+      <c r="DM64" s="6"/>
+      <c r="DN64" s="6"/>
+      <c r="DO64" s="6"/>
+      <c r="DP64" s="6"/>
     </row>
-    <row r="65" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -13664,8 +14869,16 @@
       <c r="DF65" s="6"/>
       <c r="DG65" s="6"/>
       <c r="DH65" s="6"/>
+      <c r="DI65" s="6"/>
+      <c r="DJ65" s="6"/>
+      <c r="DK65" s="6"/>
+      <c r="DL65" s="6"/>
+      <c r="DM65" s="6"/>
+      <c r="DN65" s="6"/>
+      <c r="DO65" s="6"/>
+      <c r="DP65" s="6"/>
     </row>
-    <row r="66" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -13778,8 +14991,16 @@
       <c r="DF66" s="6"/>
       <c r="DG66" s="6"/>
       <c r="DH66" s="6"/>
+      <c r="DI66" s="6"/>
+      <c r="DJ66" s="6"/>
+      <c r="DK66" s="6"/>
+      <c r="DL66" s="6"/>
+      <c r="DM66" s="6"/>
+      <c r="DN66" s="6"/>
+      <c r="DO66" s="6"/>
+      <c r="DP66" s="6"/>
     </row>
-    <row r="67" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -13892,8 +15113,16 @@
       <c r="DF67" s="6"/>
       <c r="DG67" s="6"/>
       <c r="DH67" s="6"/>
+      <c r="DI67" s="6"/>
+      <c r="DJ67" s="6"/>
+      <c r="DK67" s="6"/>
+      <c r="DL67" s="6"/>
+      <c r="DM67" s="6"/>
+      <c r="DN67" s="6"/>
+      <c r="DO67" s="6"/>
+      <c r="DP67" s="6"/>
     </row>
-    <row r="68" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -14006,8 +15235,16 @@
       <c r="DF68" s="6"/>
       <c r="DG68" s="6"/>
       <c r="DH68" s="6"/>
+      <c r="DI68" s="6"/>
+      <c r="DJ68" s="6"/>
+      <c r="DK68" s="6"/>
+      <c r="DL68" s="6"/>
+      <c r="DM68" s="6"/>
+      <c r="DN68" s="6"/>
+      <c r="DO68" s="6"/>
+      <c r="DP68" s="6"/>
     </row>
-    <row r="69" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -14120,8 +15357,16 @@
       <c r="DF69" s="6"/>
       <c r="DG69" s="6"/>
       <c r="DH69" s="6"/>
+      <c r="DI69" s="6"/>
+      <c r="DJ69" s="6"/>
+      <c r="DK69" s="6"/>
+      <c r="DL69" s="6"/>
+      <c r="DM69" s="6"/>
+      <c r="DN69" s="6"/>
+      <c r="DO69" s="6"/>
+      <c r="DP69" s="6"/>
     </row>
-    <row r="70" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -14234,8 +15479,16 @@
       <c r="DF70" s="6"/>
       <c r="DG70" s="6"/>
       <c r="DH70" s="6"/>
+      <c r="DI70" s="6"/>
+      <c r="DJ70" s="6"/>
+      <c r="DK70" s="6"/>
+      <c r="DL70" s="6"/>
+      <c r="DM70" s="6"/>
+      <c r="DN70" s="6"/>
+      <c r="DO70" s="6"/>
+      <c r="DP70" s="6"/>
     </row>
-    <row r="71" spans="1:112" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:120" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>11</v>
       </c>
@@ -14297,113 +15550,127 @@
       <c r="AM71" s="6"/>
       <c r="AN71" s="6"/>
       <c r="AO71" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AP71" s="6"/>
       <c r="AQ71" s="6"/>
       <c r="AR71" s="6"/>
       <c r="AS71" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AT71" s="6"/>
       <c r="AU71" s="6"/>
       <c r="AV71" s="6"/>
       <c r="AW71" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AX71" s="6"/>
       <c r="AY71" s="6"/>
       <c r="AZ71" s="6"/>
       <c r="BA71" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BB71" s="6"/>
       <c r="BC71" s="6"/>
       <c r="BD71" s="6"/>
       <c r="BE71" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="BF71" s="6"/>
       <c r="BG71" s="6"/>
       <c r="BH71" s="6"/>
       <c r="BI71" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="BJ71" s="6"/>
       <c r="BK71" s="6"/>
       <c r="BL71" s="6"/>
       <c r="BM71" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="BN71" s="6"/>
       <c r="BO71" s="6"/>
       <c r="BP71" s="6"/>
       <c r="BQ71" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="BR71" s="6"/>
       <c r="BS71" s="6"/>
       <c r="BT71" s="6"/>
       <c r="BU71" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BV71" s="6"/>
       <c r="BW71" s="6"/>
       <c r="BX71" s="6"/>
       <c r="BY71" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BZ71" s="6"/>
       <c r="CA71" s="6"/>
       <c r="CB71" s="6"/>
       <c r="CC71" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="CD71" s="6"/>
       <c r="CE71" s="6"/>
       <c r="CF71" s="6"/>
       <c r="CG71" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="CH71" s="6"/>
       <c r="CI71" s="6"/>
       <c r="CJ71" s="6"/>
       <c r="CK71" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="CL71" s="6"/>
       <c r="CM71" s="6"/>
       <c r="CN71" s="6"/>
       <c r="CO71" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="CP71" s="6"/>
       <c r="CQ71" s="6"/>
       <c r="CR71" s="6"/>
       <c r="CS71" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="CT71" s="6"/>
       <c r="CU71" s="6"/>
       <c r="CV71" s="6"/>
       <c r="CW71" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="CX71" s="6"/>
       <c r="CY71" s="6"/>
       <c r="CZ71" s="6"/>
-      <c r="DA71" s="5"/>
+      <c r="DA71" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="DB71" s="6"/>
       <c r="DC71" s="6"/>
       <c r="DD71" s="6"/>
       <c r="DE71" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="DF71" s="6"/>
       <c r="DG71" s="6"/>
       <c r="DH71" s="6"/>
+      <c r="DI71" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="DJ71" s="6"/>
+      <c r="DK71" s="6"/>
+      <c r="DL71" s="6"/>
+      <c r="DM71" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="DN71" s="6"/>
+      <c r="DO71" s="6"/>
+      <c r="DP71" s="6"/>
     </row>
-    <row r="72" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -14516,8 +15783,16 @@
       <c r="DF72" s="6"/>
       <c r="DG72" s="6"/>
       <c r="DH72" s="6"/>
+      <c r="DI72" s="6"/>
+      <c r="DJ72" s="6"/>
+      <c r="DK72" s="6"/>
+      <c r="DL72" s="6"/>
+      <c r="DM72" s="6"/>
+      <c r="DN72" s="6"/>
+      <c r="DO72" s="6"/>
+      <c r="DP72" s="6"/>
     </row>
-    <row r="73" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -14630,8 +15905,16 @@
       <c r="DF73" s="6"/>
       <c r="DG73" s="6"/>
       <c r="DH73" s="6"/>
+      <c r="DI73" s="6"/>
+      <c r="DJ73" s="6"/>
+      <c r="DK73" s="6"/>
+      <c r="DL73" s="6"/>
+      <c r="DM73" s="6"/>
+      <c r="DN73" s="6"/>
+      <c r="DO73" s="6"/>
+      <c r="DP73" s="6"/>
     </row>
-    <row r="74" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -14744,8 +16027,16 @@
       <c r="DF74" s="6"/>
       <c r="DG74" s="6"/>
       <c r="DH74" s="6"/>
+      <c r="DI74" s="6"/>
+      <c r="DJ74" s="6"/>
+      <c r="DK74" s="6"/>
+      <c r="DL74" s="6"/>
+      <c r="DM74" s="6"/>
+      <c r="DN74" s="6"/>
+      <c r="DO74" s="6"/>
+      <c r="DP74" s="6"/>
     </row>
-    <row r="75" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -14858,8 +16149,16 @@
       <c r="DF75" s="6"/>
       <c r="DG75" s="6"/>
       <c r="DH75" s="6"/>
+      <c r="DI75" s="6"/>
+      <c r="DJ75" s="6"/>
+      <c r="DK75" s="6"/>
+      <c r="DL75" s="6"/>
+      <c r="DM75" s="6"/>
+      <c r="DN75" s="6"/>
+      <c r="DO75" s="6"/>
+      <c r="DP75" s="6"/>
     </row>
-    <row r="76" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -14972,8 +16271,16 @@
       <c r="DF76" s="6"/>
       <c r="DG76" s="6"/>
       <c r="DH76" s="6"/>
+      <c r="DI76" s="6"/>
+      <c r="DJ76" s="6"/>
+      <c r="DK76" s="6"/>
+      <c r="DL76" s="6"/>
+      <c r="DM76" s="6"/>
+      <c r="DN76" s="6"/>
+      <c r="DO76" s="6"/>
+      <c r="DP76" s="6"/>
     </row>
-    <row r="77" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -15086,8 +16393,16 @@
       <c r="DF77" s="6"/>
       <c r="DG77" s="6"/>
       <c r="DH77" s="6"/>
+      <c r="DI77" s="6"/>
+      <c r="DJ77" s="6"/>
+      <c r="DK77" s="6"/>
+      <c r="DL77" s="6"/>
+      <c r="DM77" s="6"/>
+      <c r="DN77" s="6"/>
+      <c r="DO77" s="6"/>
+      <c r="DP77" s="6"/>
     </row>
-    <row r="78" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -15200,8 +16515,16 @@
       <c r="DF78" s="6"/>
       <c r="DG78" s="6"/>
       <c r="DH78" s="6"/>
+      <c r="DI78" s="6"/>
+      <c r="DJ78" s="6"/>
+      <c r="DK78" s="6"/>
+      <c r="DL78" s="6"/>
+      <c r="DM78" s="6"/>
+      <c r="DN78" s="6"/>
+      <c r="DO78" s="6"/>
+      <c r="DP78" s="6"/>
     </row>
-    <row r="79" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -15314,8 +16637,16 @@
       <c r="DF79" s="6"/>
       <c r="DG79" s="6"/>
       <c r="DH79" s="6"/>
+      <c r="DI79" s="6"/>
+      <c r="DJ79" s="6"/>
+      <c r="DK79" s="6"/>
+      <c r="DL79" s="6"/>
+      <c r="DM79" s="6"/>
+      <c r="DN79" s="6"/>
+      <c r="DO79" s="6"/>
+      <c r="DP79" s="6"/>
     </row>
-    <row r="80" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -15428,8 +16759,16 @@
       <c r="DF80" s="6"/>
       <c r="DG80" s="6"/>
       <c r="DH80" s="6"/>
+      <c r="DI80" s="6"/>
+      <c r="DJ80" s="6"/>
+      <c r="DK80" s="6"/>
+      <c r="DL80" s="6"/>
+      <c r="DM80" s="6"/>
+      <c r="DN80" s="6"/>
+      <c r="DO80" s="6"/>
+      <c r="DP80" s="6"/>
     </row>
-    <row r="81" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>15</v>
       </c>
@@ -15491,111 +16830,123 @@
       <c r="AM81" s="6"/>
       <c r="AN81" s="6"/>
       <c r="AO81" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AP81" s="6"/>
       <c r="AQ81" s="6"/>
       <c r="AR81" s="6"/>
       <c r="AS81" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AT81" s="6"/>
       <c r="AU81" s="6"/>
       <c r="AV81" s="6"/>
       <c r="AW81" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AX81" s="6"/>
       <c r="AY81" s="6"/>
       <c r="AZ81" s="6"/>
       <c r="BA81" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="BB81" s="6"/>
       <c r="BC81" s="6"/>
       <c r="BD81" s="6"/>
       <c r="BE81" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="BF81" s="6"/>
       <c r="BG81" s="6"/>
       <c r="BH81" s="6"/>
       <c r="BI81" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="BJ81" s="6"/>
       <c r="BK81" s="6"/>
       <c r="BL81" s="6"/>
       <c r="BM81" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="BN81" s="6"/>
       <c r="BO81" s="6"/>
       <c r="BP81" s="6"/>
       <c r="BQ81" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="BR81" s="6"/>
       <c r="BS81" s="6"/>
       <c r="BT81" s="6"/>
       <c r="BU81" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="BV81" s="6"/>
       <c r="BW81" s="6"/>
       <c r="BX81" s="6"/>
       <c r="BY81" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BZ81" s="6"/>
       <c r="CA81" s="6"/>
       <c r="CB81" s="6"/>
       <c r="CC81" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="CD81" s="6"/>
       <c r="CE81" s="6"/>
       <c r="CF81" s="6"/>
       <c r="CG81" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="CH81" s="6"/>
       <c r="CI81" s="6"/>
       <c r="CJ81" s="6"/>
       <c r="CK81" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="CL81" s="6"/>
       <c r="CM81" s="6"/>
       <c r="CN81" s="6"/>
       <c r="CO81" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="CP81" s="6"/>
       <c r="CQ81" s="6"/>
       <c r="CR81" s="6"/>
       <c r="CS81" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="CT81" s="6"/>
       <c r="CU81" s="6"/>
       <c r="CV81" s="6"/>
       <c r="CW81" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="CX81" s="6"/>
       <c r="CY81" s="6"/>
       <c r="CZ81" s="6"/>
-      <c r="DA81" s="5"/>
+      <c r="DA81" s="5" t="s">
+        <v>274</v>
+      </c>
       <c r="DB81" s="6"/>
       <c r="DC81" s="6"/>
       <c r="DD81" s="6"/>
-      <c r="DE81" s="5"/>
+      <c r="DE81" s="5" t="s">
+        <v>270</v>
+      </c>
       <c r="DF81" s="6"/>
       <c r="DG81" s="6"/>
       <c r="DH81" s="6"/>
+      <c r="DI81" s="5"/>
+      <c r="DJ81" s="6"/>
+      <c r="DK81" s="6"/>
+      <c r="DL81" s="6"/>
+      <c r="DM81" s="5"/>
+      <c r="DN81" s="6"/>
+      <c r="DO81" s="6"/>
+      <c r="DP81" s="6"/>
     </row>
-    <row r="82" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -15708,8 +17059,16 @@
       <c r="DF82" s="6"/>
       <c r="DG82" s="6"/>
       <c r="DH82" s="6"/>
+      <c r="DI82" s="6"/>
+      <c r="DJ82" s="6"/>
+      <c r="DK82" s="6"/>
+      <c r="DL82" s="6"/>
+      <c r="DM82" s="6"/>
+      <c r="DN82" s="6"/>
+      <c r="DO82" s="6"/>
+      <c r="DP82" s="6"/>
     </row>
-    <row r="83" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -15822,8 +17181,16 @@
       <c r="DF83" s="6"/>
       <c r="DG83" s="6"/>
       <c r="DH83" s="6"/>
+      <c r="DI83" s="6"/>
+      <c r="DJ83" s="6"/>
+      <c r="DK83" s="6"/>
+      <c r="DL83" s="6"/>
+      <c r="DM83" s="6"/>
+      <c r="DN83" s="6"/>
+      <c r="DO83" s="6"/>
+      <c r="DP83" s="6"/>
     </row>
-    <row r="84" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -15936,8 +17303,16 @@
       <c r="DF84" s="6"/>
       <c r="DG84" s="6"/>
       <c r="DH84" s="6"/>
+      <c r="DI84" s="6"/>
+      <c r="DJ84" s="6"/>
+      <c r="DK84" s="6"/>
+      <c r="DL84" s="6"/>
+      <c r="DM84" s="6"/>
+      <c r="DN84" s="6"/>
+      <c r="DO84" s="6"/>
+      <c r="DP84" s="6"/>
     </row>
-    <row r="85" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -16050,8 +17425,16 @@
       <c r="DF85" s="6"/>
       <c r="DG85" s="6"/>
       <c r="DH85" s="6"/>
+      <c r="DI85" s="6"/>
+      <c r="DJ85" s="6"/>
+      <c r="DK85" s="6"/>
+      <c r="DL85" s="6"/>
+      <c r="DM85" s="6"/>
+      <c r="DN85" s="6"/>
+      <c r="DO85" s="6"/>
+      <c r="DP85" s="6"/>
     </row>
-    <row r="86" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -16164,8 +17547,16 @@
       <c r="DF86" s="6"/>
       <c r="DG86" s="6"/>
       <c r="DH86" s="6"/>
+      <c r="DI86" s="6"/>
+      <c r="DJ86" s="6"/>
+      <c r="DK86" s="6"/>
+      <c r="DL86" s="6"/>
+      <c r="DM86" s="6"/>
+      <c r="DN86" s="6"/>
+      <c r="DO86" s="6"/>
+      <c r="DP86" s="6"/>
     </row>
-    <row r="87" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -16278,8 +17669,16 @@
       <c r="DF87" s="6"/>
       <c r="DG87" s="6"/>
       <c r="DH87" s="6"/>
+      <c r="DI87" s="6"/>
+      <c r="DJ87" s="6"/>
+      <c r="DK87" s="6"/>
+      <c r="DL87" s="6"/>
+      <c r="DM87" s="6"/>
+      <c r="DN87" s="6"/>
+      <c r="DO87" s="6"/>
+      <c r="DP87" s="6"/>
     </row>
-    <row r="88" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -16392,8 +17791,16 @@
       <c r="DF88" s="6"/>
       <c r="DG88" s="6"/>
       <c r="DH88" s="6"/>
+      <c r="DI88" s="6"/>
+      <c r="DJ88" s="6"/>
+      <c r="DK88" s="6"/>
+      <c r="DL88" s="6"/>
+      <c r="DM88" s="6"/>
+      <c r="DN88" s="6"/>
+      <c r="DO88" s="6"/>
+      <c r="DP88" s="6"/>
     </row>
-    <row r="89" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -16506,8 +17913,16 @@
       <c r="DF89" s="6"/>
       <c r="DG89" s="6"/>
       <c r="DH89" s="6"/>
+      <c r="DI89" s="6"/>
+      <c r="DJ89" s="6"/>
+      <c r="DK89" s="6"/>
+      <c r="DL89" s="6"/>
+      <c r="DM89" s="6"/>
+      <c r="DN89" s="6"/>
+      <c r="DO89" s="6"/>
+      <c r="DP89" s="6"/>
     </row>
-    <row r="90" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -16620,8 +18035,16 @@
       <c r="DF90" s="6"/>
       <c r="DG90" s="6"/>
       <c r="DH90" s="6"/>
+      <c r="DI90" s="6"/>
+      <c r="DJ90" s="6"/>
+      <c r="DK90" s="6"/>
+      <c r="DL90" s="6"/>
+      <c r="DM90" s="6"/>
+      <c r="DN90" s="6"/>
+      <c r="DO90" s="6"/>
+      <c r="DP90" s="6"/>
     </row>
-    <row r="91" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>19</v>
       </c>
@@ -16683,111 +18106,123 @@
       <c r="AM91" s="6"/>
       <c r="AN91" s="6"/>
       <c r="AO91" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AP91" s="6"/>
       <c r="AQ91" s="6"/>
       <c r="AR91" s="6"/>
       <c r="AS91" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AT91" s="6"/>
       <c r="AU91" s="6"/>
       <c r="AV91" s="6"/>
       <c r="AW91" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AX91" s="6"/>
       <c r="AY91" s="6"/>
       <c r="AZ91" s="6"/>
       <c r="BA91" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="BB91" s="6"/>
       <c r="BC91" s="6"/>
       <c r="BD91" s="6"/>
       <c r="BE91" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="BF91" s="6"/>
       <c r="BG91" s="6"/>
       <c r="BH91" s="6"/>
       <c r="BI91" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="BJ91" s="6"/>
       <c r="BK91" s="6"/>
       <c r="BL91" s="6"/>
       <c r="BM91" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BN91" s="6"/>
       <c r="BO91" s="6"/>
       <c r="BP91" s="6"/>
       <c r="BQ91" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="BR91" s="6"/>
       <c r="BS91" s="6"/>
       <c r="BT91" s="6"/>
       <c r="BU91" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BV91" s="6"/>
       <c r="BW91" s="6"/>
       <c r="BX91" s="6"/>
       <c r="BY91" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BZ91" s="6"/>
       <c r="CA91" s="6"/>
       <c r="CB91" s="6"/>
       <c r="CC91" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="CD91" s="6"/>
       <c r="CE91" s="6"/>
       <c r="CF91" s="6"/>
       <c r="CG91" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="CH91" s="6"/>
       <c r="CI91" s="6"/>
       <c r="CJ91" s="6"/>
       <c r="CK91" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="CL91" s="6"/>
       <c r="CM91" s="6"/>
       <c r="CN91" s="6"/>
       <c r="CO91" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="CP91" s="6"/>
       <c r="CQ91" s="6"/>
       <c r="CR91" s="6"/>
       <c r="CS91" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="CT91" s="6"/>
       <c r="CU91" s="6"/>
       <c r="CV91" s="6"/>
       <c r="CW91" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="CX91" s="6"/>
       <c r="CY91" s="6"/>
       <c r="CZ91" s="6"/>
-      <c r="DA91" s="5"/>
+      <c r="DA91" s="5" t="s">
+        <v>277</v>
+      </c>
       <c r="DB91" s="6"/>
       <c r="DC91" s="6"/>
       <c r="DD91" s="6"/>
-      <c r="DE91" s="5"/>
+      <c r="DE91" s="5" t="s">
+        <v>276</v>
+      </c>
       <c r="DF91" s="6"/>
       <c r="DG91" s="6"/>
       <c r="DH91" s="6"/>
+      <c r="DI91" s="5"/>
+      <c r="DJ91" s="6"/>
+      <c r="DK91" s="6"/>
+      <c r="DL91" s="6"/>
+      <c r="DM91" s="5"/>
+      <c r="DN91" s="6"/>
+      <c r="DO91" s="6"/>
+      <c r="DP91" s="6"/>
     </row>
-    <row r="92" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -16900,8 +18335,16 @@
       <c r="DF92" s="6"/>
       <c r="DG92" s="6"/>
       <c r="DH92" s="6"/>
+      <c r="DI92" s="6"/>
+      <c r="DJ92" s="6"/>
+      <c r="DK92" s="6"/>
+      <c r="DL92" s="6"/>
+      <c r="DM92" s="6"/>
+      <c r="DN92" s="6"/>
+      <c r="DO92" s="6"/>
+      <c r="DP92" s="6"/>
     </row>
-    <row r="93" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -17014,8 +18457,16 @@
       <c r="DF93" s="6"/>
       <c r="DG93" s="6"/>
       <c r="DH93" s="6"/>
+      <c r="DI93" s="6"/>
+      <c r="DJ93" s="6"/>
+      <c r="DK93" s="6"/>
+      <c r="DL93" s="6"/>
+      <c r="DM93" s="6"/>
+      <c r="DN93" s="6"/>
+      <c r="DO93" s="6"/>
+      <c r="DP93" s="6"/>
     </row>
-    <row r="94" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -17128,8 +18579,16 @@
       <c r="DF94" s="6"/>
       <c r="DG94" s="6"/>
       <c r="DH94" s="6"/>
+      <c r="DI94" s="6"/>
+      <c r="DJ94" s="6"/>
+      <c r="DK94" s="6"/>
+      <c r="DL94" s="6"/>
+      <c r="DM94" s="6"/>
+      <c r="DN94" s="6"/>
+      <c r="DO94" s="6"/>
+      <c r="DP94" s="6"/>
     </row>
-    <row r="95" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -17242,8 +18701,16 @@
       <c r="DF95" s="6"/>
       <c r="DG95" s="6"/>
       <c r="DH95" s="6"/>
+      <c r="DI95" s="6"/>
+      <c r="DJ95" s="6"/>
+      <c r="DK95" s="6"/>
+      <c r="DL95" s="6"/>
+      <c r="DM95" s="6"/>
+      <c r="DN95" s="6"/>
+      <c r="DO95" s="6"/>
+      <c r="DP95" s="6"/>
     </row>
-    <row r="96" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -17356,8 +18823,16 @@
       <c r="DF96" s="6"/>
       <c r="DG96" s="6"/>
       <c r="DH96" s="6"/>
+      <c r="DI96" s="6"/>
+      <c r="DJ96" s="6"/>
+      <c r="DK96" s="6"/>
+      <c r="DL96" s="6"/>
+      <c r="DM96" s="6"/>
+      <c r="DN96" s="6"/>
+      <c r="DO96" s="6"/>
+      <c r="DP96" s="6"/>
     </row>
-    <row r="97" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -17470,8 +18945,16 @@
       <c r="DF97" s="6"/>
       <c r="DG97" s="6"/>
       <c r="DH97" s="6"/>
+      <c r="DI97" s="6"/>
+      <c r="DJ97" s="6"/>
+      <c r="DK97" s="6"/>
+      <c r="DL97" s="6"/>
+      <c r="DM97" s="6"/>
+      <c r="DN97" s="6"/>
+      <c r="DO97" s="6"/>
+      <c r="DP97" s="6"/>
     </row>
-    <row r="98" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -17584,8 +19067,16 @@
       <c r="DF98" s="6"/>
       <c r="DG98" s="6"/>
       <c r="DH98" s="6"/>
+      <c r="DI98" s="6"/>
+      <c r="DJ98" s="6"/>
+      <c r="DK98" s="6"/>
+      <c r="DL98" s="6"/>
+      <c r="DM98" s="6"/>
+      <c r="DN98" s="6"/>
+      <c r="DO98" s="6"/>
+      <c r="DP98" s="6"/>
     </row>
-    <row r="99" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -17698,8 +19189,16 @@
       <c r="DF99" s="6"/>
       <c r="DG99" s="6"/>
       <c r="DH99" s="6"/>
+      <c r="DI99" s="6"/>
+      <c r="DJ99" s="6"/>
+      <c r="DK99" s="6"/>
+      <c r="DL99" s="6"/>
+      <c r="DM99" s="6"/>
+      <c r="DN99" s="6"/>
+      <c r="DO99" s="6"/>
+      <c r="DP99" s="6"/>
     </row>
-    <row r="100" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -17812,8 +19311,16 @@
       <c r="DF100" s="6"/>
       <c r="DG100" s="6"/>
       <c r="DH100" s="6"/>
+      <c r="DI100" s="6"/>
+      <c r="DJ100" s="6"/>
+      <c r="DK100" s="6"/>
+      <c r="DL100" s="6"/>
+      <c r="DM100" s="6"/>
+      <c r="DN100" s="6"/>
+      <c r="DO100" s="6"/>
+      <c r="DP100" s="6"/>
     </row>
-    <row r="101" spans="1:112" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:120" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -17827,7 +19334,7 @@
       <c r="K101" s="4"/>
       <c r="L101" s="4"/>
     </row>
-    <row r="102" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A102" s="2"/>
       <c r="B102" s="3"/>
       <c r="C102" s="4"/>
@@ -17841,7 +19348,7 @@
       <c r="K102" s="4"/>
       <c r="L102" s="4"/>
     </row>
-    <row r="103" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A103" s="2"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -17855,7 +19362,7 @@
       <c r="K103" s="4"/>
       <c r="L103" s="4"/>
     </row>
-    <row r="104" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A104" s="2"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -17869,7 +19376,7 @@
       <c r="K104" s="4"/>
       <c r="L104" s="4"/>
     </row>
-    <row r="105" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A105" s="2"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -17883,7 +19390,7 @@
       <c r="K105" s="4"/>
       <c r="L105" s="4"/>
     </row>
-    <row r="106" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A106" s="2"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -17897,7 +19404,7 @@
       <c r="K106" s="4"/>
       <c r="L106" s="4"/>
     </row>
-    <row r="107" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A107" s="2"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -17911,7 +19418,7 @@
       <c r="K107" s="4"/>
       <c r="L107" s="4"/>
     </row>
-    <row r="108" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A108" s="2"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -17925,7 +19432,7 @@
       <c r="K108" s="4"/>
       <c r="L108" s="4"/>
     </row>
-    <row r="109" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A109" s="2"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -17939,7 +19446,7 @@
       <c r="K109" s="4"/>
       <c r="L109" s="4"/>
     </row>
-    <row r="110" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A110" s="2"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -17953,7 +19460,7 @@
       <c r="K110" s="4"/>
       <c r="L110" s="4"/>
     </row>
-    <row r="111" spans="1:112" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:120" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -17967,7 +19474,7 @@
       <c r="K111" s="4"/>
       <c r="L111" s="4"/>
     </row>
-    <row r="112" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:120" x14ac:dyDescent="0.3">
       <c r="A112" s="2"/>
       <c r="B112" s="3"/>
       <c r="C112" s="4"/>
@@ -18520,107 +20027,183 @@
       <c r="E151" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="280">
-    <mergeCell ref="DA51:DD60"/>
-    <mergeCell ref="DE51:DH60"/>
-    <mergeCell ref="DA61:DD70"/>
-    <mergeCell ref="DE61:DH70"/>
-    <mergeCell ref="DA71:DD80"/>
-    <mergeCell ref="DE71:DH80"/>
-    <mergeCell ref="DA81:DD90"/>
-    <mergeCell ref="DE81:DH90"/>
-    <mergeCell ref="DA91:DD100"/>
-    <mergeCell ref="DE91:DH100"/>
-    <mergeCell ref="DA1:DD10"/>
-    <mergeCell ref="DE1:DH10"/>
-    <mergeCell ref="DA11:DD20"/>
-    <mergeCell ref="DE11:DH20"/>
-    <mergeCell ref="DA21:DD30"/>
-    <mergeCell ref="DE21:DH30"/>
-    <mergeCell ref="DA31:DD40"/>
-    <mergeCell ref="DE31:DH40"/>
-    <mergeCell ref="DA41:DD50"/>
-    <mergeCell ref="DE41:DH50"/>
-    <mergeCell ref="CS51:CV60"/>
-    <mergeCell ref="CW51:CZ60"/>
-    <mergeCell ref="CS61:CV70"/>
-    <mergeCell ref="CW61:CZ70"/>
-    <mergeCell ref="CS71:CV80"/>
-    <mergeCell ref="CW71:CZ80"/>
-    <mergeCell ref="CS81:CV90"/>
-    <mergeCell ref="CW81:CZ90"/>
-    <mergeCell ref="CS91:CV100"/>
-    <mergeCell ref="CW91:CZ100"/>
-    <mergeCell ref="CS1:CV10"/>
-    <mergeCell ref="CW1:CZ10"/>
-    <mergeCell ref="CS11:CV20"/>
-    <mergeCell ref="CW11:CZ20"/>
-    <mergeCell ref="CS21:CV30"/>
-    <mergeCell ref="CW21:CZ30"/>
-    <mergeCell ref="CS31:CV40"/>
-    <mergeCell ref="CW31:CZ40"/>
-    <mergeCell ref="CS41:CV50"/>
-    <mergeCell ref="CW41:CZ50"/>
-    <mergeCell ref="BU51:BX60"/>
-    <mergeCell ref="BY51:CB60"/>
-    <mergeCell ref="BU61:BX70"/>
-    <mergeCell ref="BY61:CB70"/>
-    <mergeCell ref="BU71:BX80"/>
-    <mergeCell ref="BY71:CB80"/>
-    <mergeCell ref="BU81:BX90"/>
-    <mergeCell ref="BY81:CB90"/>
-    <mergeCell ref="BU91:BX100"/>
-    <mergeCell ref="BY91:CB100"/>
-    <mergeCell ref="BU1:BX10"/>
-    <mergeCell ref="BY1:CB10"/>
-    <mergeCell ref="BU11:BX20"/>
-    <mergeCell ref="BY11:CB20"/>
-    <mergeCell ref="BU21:BX30"/>
-    <mergeCell ref="BY21:CB30"/>
-    <mergeCell ref="BU31:BX40"/>
-    <mergeCell ref="BY31:CB40"/>
-    <mergeCell ref="BU41:BX50"/>
-    <mergeCell ref="BY41:CB50"/>
-    <mergeCell ref="BM51:BP60"/>
-    <mergeCell ref="BQ51:BT60"/>
-    <mergeCell ref="BM61:BP70"/>
-    <mergeCell ref="BQ61:BT70"/>
-    <mergeCell ref="BM71:BP80"/>
-    <mergeCell ref="BQ71:BT80"/>
-    <mergeCell ref="BM81:BP90"/>
-    <mergeCell ref="BQ81:BT90"/>
-    <mergeCell ref="BM91:BP100"/>
-    <mergeCell ref="BQ91:BT100"/>
-    <mergeCell ref="BM1:BP10"/>
-    <mergeCell ref="BQ1:BT10"/>
-    <mergeCell ref="BM11:BP20"/>
-    <mergeCell ref="BQ11:BT20"/>
-    <mergeCell ref="BM21:BP30"/>
-    <mergeCell ref="BQ21:BT30"/>
-    <mergeCell ref="BM31:BP40"/>
-    <mergeCell ref="BQ31:BT40"/>
-    <mergeCell ref="BM41:BP50"/>
-    <mergeCell ref="BQ41:BT50"/>
-    <mergeCell ref="BE51:BH60"/>
-    <mergeCell ref="BI51:BL60"/>
-    <mergeCell ref="BE61:BH70"/>
-    <mergeCell ref="BI61:BL70"/>
-    <mergeCell ref="BE71:BH80"/>
-    <mergeCell ref="BI71:BL80"/>
-    <mergeCell ref="BE81:BH90"/>
-    <mergeCell ref="BI81:BL90"/>
-    <mergeCell ref="BE91:BH100"/>
-    <mergeCell ref="BI91:BL100"/>
-    <mergeCell ref="BE1:BH10"/>
-    <mergeCell ref="BI1:BL10"/>
-    <mergeCell ref="BE11:BH20"/>
-    <mergeCell ref="BI11:BL20"/>
-    <mergeCell ref="BE21:BH30"/>
-    <mergeCell ref="BI21:BL30"/>
-    <mergeCell ref="BE31:BH40"/>
-    <mergeCell ref="BI31:BL40"/>
-    <mergeCell ref="BE41:BH50"/>
-    <mergeCell ref="BI41:BL50"/>
+  <mergeCells count="300">
+    <mergeCell ref="DI51:DL60"/>
+    <mergeCell ref="DM51:DP60"/>
+    <mergeCell ref="DI61:DL70"/>
+    <mergeCell ref="DM61:DP70"/>
+    <mergeCell ref="DI71:DL80"/>
+    <mergeCell ref="DM71:DP80"/>
+    <mergeCell ref="DI81:DL90"/>
+    <mergeCell ref="DM81:DP90"/>
+    <mergeCell ref="DI91:DL100"/>
+    <mergeCell ref="DM91:DP100"/>
+    <mergeCell ref="DI1:DL10"/>
+    <mergeCell ref="DM1:DP10"/>
+    <mergeCell ref="DI11:DL20"/>
+    <mergeCell ref="DM11:DP20"/>
+    <mergeCell ref="DI21:DL30"/>
+    <mergeCell ref="DM21:DP30"/>
+    <mergeCell ref="DI31:DL40"/>
+    <mergeCell ref="DM31:DP40"/>
+    <mergeCell ref="DI41:DL50"/>
+    <mergeCell ref="DM41:DP50"/>
+    <mergeCell ref="CK51:CN60"/>
+    <mergeCell ref="CO51:CR60"/>
+    <mergeCell ref="CK61:CN70"/>
+    <mergeCell ref="CO61:CR70"/>
+    <mergeCell ref="CK71:CN80"/>
+    <mergeCell ref="CO71:CR80"/>
+    <mergeCell ref="CK81:CN90"/>
+    <mergeCell ref="CO81:CR90"/>
+    <mergeCell ref="CK91:CN100"/>
+    <mergeCell ref="CO91:CR100"/>
+    <mergeCell ref="CK1:CN10"/>
+    <mergeCell ref="CO1:CR10"/>
+    <mergeCell ref="CK11:CN20"/>
+    <mergeCell ref="CO11:CR20"/>
+    <mergeCell ref="CK21:CN30"/>
+    <mergeCell ref="CO21:CR30"/>
+    <mergeCell ref="CK31:CN40"/>
+    <mergeCell ref="CO31:CR40"/>
+    <mergeCell ref="CK41:CN50"/>
+    <mergeCell ref="CO41:CR50"/>
+    <mergeCell ref="CC51:CF60"/>
+    <mergeCell ref="CG51:CJ60"/>
+    <mergeCell ref="CC61:CF70"/>
+    <mergeCell ref="CG61:CJ70"/>
+    <mergeCell ref="CC71:CF80"/>
+    <mergeCell ref="CG71:CJ80"/>
+    <mergeCell ref="CC81:CF90"/>
+    <mergeCell ref="CG81:CJ90"/>
+    <mergeCell ref="CC91:CF100"/>
+    <mergeCell ref="CG91:CJ100"/>
+    <mergeCell ref="CC1:CF10"/>
+    <mergeCell ref="CG1:CJ10"/>
+    <mergeCell ref="CC11:CF20"/>
+    <mergeCell ref="CG11:CJ20"/>
+    <mergeCell ref="CC21:CF30"/>
+    <mergeCell ref="CG21:CJ30"/>
+    <mergeCell ref="CC31:CF40"/>
+    <mergeCell ref="CG31:CJ40"/>
+    <mergeCell ref="CC41:CF50"/>
+    <mergeCell ref="CG41:CJ50"/>
+    <mergeCell ref="AS91:AV100"/>
+    <mergeCell ref="AS61:AV70"/>
+    <mergeCell ref="AO71:AR80"/>
+    <mergeCell ref="AS71:AV80"/>
+    <mergeCell ref="AO81:AR90"/>
+    <mergeCell ref="AS81:AV90"/>
+    <mergeCell ref="AO31:AR40"/>
+    <mergeCell ref="AS31:AV40"/>
+    <mergeCell ref="AO41:AR50"/>
+    <mergeCell ref="AS41:AV50"/>
+    <mergeCell ref="AO51:AR60"/>
+    <mergeCell ref="AS51:AV60"/>
+    <mergeCell ref="AO1:AR10"/>
+    <mergeCell ref="AS1:AV10"/>
+    <mergeCell ref="AO11:AR20"/>
+    <mergeCell ref="AS11:AV20"/>
+    <mergeCell ref="AO21:AR30"/>
+    <mergeCell ref="AS21:AV30"/>
+    <mergeCell ref="AG81:AJ90"/>
+    <mergeCell ref="AK81:AN90"/>
+    <mergeCell ref="AG91:AJ100"/>
+    <mergeCell ref="AK91:AN100"/>
+    <mergeCell ref="AO91:AR100"/>
+    <mergeCell ref="AG51:AJ60"/>
+    <mergeCell ref="AK51:AN60"/>
+    <mergeCell ref="AG61:AJ70"/>
+    <mergeCell ref="AK61:AN70"/>
+    <mergeCell ref="AO61:AR70"/>
+    <mergeCell ref="AG1:AJ10"/>
+    <mergeCell ref="AK1:AN10"/>
+    <mergeCell ref="AG11:AJ20"/>
+    <mergeCell ref="AK11:AN20"/>
+    <mergeCell ref="AG21:AJ30"/>
+    <mergeCell ref="AK21:AN30"/>
+    <mergeCell ref="AG31:AJ40"/>
+    <mergeCell ref="AK31:AN40"/>
+    <mergeCell ref="AG41:AJ50"/>
+    <mergeCell ref="AK41:AN50"/>
+    <mergeCell ref="AG71:AJ80"/>
+    <mergeCell ref="AK71:AN80"/>
+    <mergeCell ref="A1:D10"/>
+    <mergeCell ref="E1:H10"/>
+    <mergeCell ref="A11:D20"/>
+    <mergeCell ref="E11:H20"/>
+    <mergeCell ref="A21:D30"/>
+    <mergeCell ref="E21:H30"/>
+    <mergeCell ref="M31:P40"/>
+    <mergeCell ref="I41:L50"/>
+    <mergeCell ref="M41:P50"/>
+    <mergeCell ref="A31:D40"/>
+    <mergeCell ref="E31:H40"/>
+    <mergeCell ref="A41:D50"/>
+    <mergeCell ref="E41:H50"/>
+    <mergeCell ref="I31:L40"/>
+    <mergeCell ref="I1:L10"/>
+    <mergeCell ref="M1:P10"/>
+    <mergeCell ref="I11:L20"/>
+    <mergeCell ref="M11:P20"/>
+    <mergeCell ref="I21:L30"/>
+    <mergeCell ref="M21:P30"/>
+    <mergeCell ref="A81:D90"/>
+    <mergeCell ref="E81:H90"/>
+    <mergeCell ref="A91:D100"/>
+    <mergeCell ref="E91:H100"/>
+    <mergeCell ref="A51:D60"/>
+    <mergeCell ref="E51:H60"/>
+    <mergeCell ref="A61:D70"/>
+    <mergeCell ref="E61:H70"/>
+    <mergeCell ref="A71:D80"/>
+    <mergeCell ref="E71:H80"/>
+    <mergeCell ref="I81:L90"/>
+    <mergeCell ref="M81:P90"/>
+    <mergeCell ref="I91:L100"/>
+    <mergeCell ref="M91:P100"/>
+    <mergeCell ref="I51:L60"/>
+    <mergeCell ref="M51:P60"/>
+    <mergeCell ref="I61:L70"/>
+    <mergeCell ref="M61:P70"/>
+    <mergeCell ref="I71:L80"/>
+    <mergeCell ref="M71:P80"/>
+    <mergeCell ref="Q1:T10"/>
+    <mergeCell ref="U1:X10"/>
+    <mergeCell ref="Y1:AB10"/>
+    <mergeCell ref="AC1:AF10"/>
+    <mergeCell ref="Q11:T20"/>
+    <mergeCell ref="U11:X20"/>
+    <mergeCell ref="Y11:AB20"/>
+    <mergeCell ref="AC11:AF20"/>
+    <mergeCell ref="Q21:T30"/>
+    <mergeCell ref="U21:X30"/>
+    <mergeCell ref="Y21:AB30"/>
+    <mergeCell ref="AC21:AF30"/>
+    <mergeCell ref="Q31:T40"/>
+    <mergeCell ref="U31:X40"/>
+    <mergeCell ref="Y31:AB40"/>
+    <mergeCell ref="AC31:AF40"/>
+    <mergeCell ref="Q41:T50"/>
+    <mergeCell ref="U41:X50"/>
+    <mergeCell ref="Y41:AB50"/>
+    <mergeCell ref="AC41:AF50"/>
+    <mergeCell ref="Q51:T60"/>
+    <mergeCell ref="U51:X60"/>
+    <mergeCell ref="Y51:AB60"/>
+    <mergeCell ref="AC51:AF60"/>
+    <mergeCell ref="Q61:T70"/>
+    <mergeCell ref="U61:X70"/>
+    <mergeCell ref="Y61:AB70"/>
+    <mergeCell ref="AC61:AF70"/>
+    <mergeCell ref="Q71:T80"/>
+    <mergeCell ref="U71:X80"/>
+    <mergeCell ref="Y71:AB80"/>
+    <mergeCell ref="AC71:AF80"/>
+    <mergeCell ref="Q81:T90"/>
+    <mergeCell ref="U81:X90"/>
+    <mergeCell ref="Y81:AB90"/>
+    <mergeCell ref="AC81:AF90"/>
     <mergeCell ref="Q91:T100"/>
     <mergeCell ref="U91:X100"/>
     <mergeCell ref="Y91:AB100"/>
@@ -18645,162 +20228,106 @@
     <mergeCell ref="BA81:BD90"/>
     <mergeCell ref="AW91:AZ100"/>
     <mergeCell ref="BA91:BD100"/>
-    <mergeCell ref="Q61:T70"/>
-    <mergeCell ref="U61:X70"/>
-    <mergeCell ref="Y61:AB70"/>
-    <mergeCell ref="AC61:AF70"/>
-    <mergeCell ref="Q71:T80"/>
-    <mergeCell ref="U71:X80"/>
-    <mergeCell ref="Y71:AB80"/>
-    <mergeCell ref="AC71:AF80"/>
-    <mergeCell ref="Q81:T90"/>
-    <mergeCell ref="U81:X90"/>
-    <mergeCell ref="Y81:AB90"/>
-    <mergeCell ref="AC81:AF90"/>
-    <mergeCell ref="Q31:T40"/>
-    <mergeCell ref="U31:X40"/>
-    <mergeCell ref="Y31:AB40"/>
-    <mergeCell ref="AC31:AF40"/>
-    <mergeCell ref="Q41:T50"/>
-    <mergeCell ref="U41:X50"/>
-    <mergeCell ref="Y41:AB50"/>
-    <mergeCell ref="AC41:AF50"/>
-    <mergeCell ref="Q51:T60"/>
-    <mergeCell ref="U51:X60"/>
-    <mergeCell ref="Y51:AB60"/>
-    <mergeCell ref="AC51:AF60"/>
-    <mergeCell ref="Q1:T10"/>
-    <mergeCell ref="U1:X10"/>
-    <mergeCell ref="Y1:AB10"/>
-    <mergeCell ref="AC1:AF10"/>
-    <mergeCell ref="Q11:T20"/>
-    <mergeCell ref="U11:X20"/>
-    <mergeCell ref="Y11:AB20"/>
-    <mergeCell ref="AC11:AF20"/>
-    <mergeCell ref="Q21:T30"/>
-    <mergeCell ref="U21:X30"/>
-    <mergeCell ref="Y21:AB30"/>
-    <mergeCell ref="AC21:AF30"/>
-    <mergeCell ref="I81:L90"/>
-    <mergeCell ref="M81:P90"/>
-    <mergeCell ref="I91:L100"/>
-    <mergeCell ref="M91:P100"/>
-    <mergeCell ref="I51:L60"/>
-    <mergeCell ref="M51:P60"/>
-    <mergeCell ref="I61:L70"/>
-    <mergeCell ref="M61:P70"/>
-    <mergeCell ref="I71:L80"/>
-    <mergeCell ref="M71:P80"/>
-    <mergeCell ref="A81:D90"/>
-    <mergeCell ref="E81:H90"/>
-    <mergeCell ref="A91:D100"/>
-    <mergeCell ref="E91:H100"/>
-    <mergeCell ref="A51:D60"/>
-    <mergeCell ref="E51:H60"/>
-    <mergeCell ref="A61:D70"/>
-    <mergeCell ref="E61:H70"/>
-    <mergeCell ref="A71:D80"/>
-    <mergeCell ref="E71:H80"/>
-    <mergeCell ref="AG41:AJ50"/>
-    <mergeCell ref="AK41:AN50"/>
-    <mergeCell ref="AG71:AJ80"/>
-    <mergeCell ref="AK71:AN80"/>
-    <mergeCell ref="A1:D10"/>
-    <mergeCell ref="E1:H10"/>
-    <mergeCell ref="A11:D20"/>
-    <mergeCell ref="E11:H20"/>
-    <mergeCell ref="A21:D30"/>
-    <mergeCell ref="E21:H30"/>
-    <mergeCell ref="M31:P40"/>
-    <mergeCell ref="I41:L50"/>
-    <mergeCell ref="M41:P50"/>
-    <mergeCell ref="A31:D40"/>
-    <mergeCell ref="E31:H40"/>
-    <mergeCell ref="A41:D50"/>
-    <mergeCell ref="E41:H50"/>
-    <mergeCell ref="I31:L40"/>
-    <mergeCell ref="I1:L10"/>
-    <mergeCell ref="M1:P10"/>
-    <mergeCell ref="I11:L20"/>
-    <mergeCell ref="M11:P20"/>
-    <mergeCell ref="I21:L30"/>
-    <mergeCell ref="M21:P30"/>
-    <mergeCell ref="AO1:AR10"/>
-    <mergeCell ref="AS1:AV10"/>
-    <mergeCell ref="AO11:AR20"/>
-    <mergeCell ref="AS11:AV20"/>
-    <mergeCell ref="AO21:AR30"/>
-    <mergeCell ref="AS21:AV30"/>
-    <mergeCell ref="AG81:AJ90"/>
-    <mergeCell ref="AK81:AN90"/>
-    <mergeCell ref="AG91:AJ100"/>
-    <mergeCell ref="AK91:AN100"/>
-    <mergeCell ref="AO91:AR100"/>
-    <mergeCell ref="AG51:AJ60"/>
-    <mergeCell ref="AK51:AN60"/>
-    <mergeCell ref="AG61:AJ70"/>
-    <mergeCell ref="AK61:AN70"/>
-    <mergeCell ref="AO61:AR70"/>
-    <mergeCell ref="AG1:AJ10"/>
-    <mergeCell ref="AK1:AN10"/>
-    <mergeCell ref="AG11:AJ20"/>
-    <mergeCell ref="AK11:AN20"/>
-    <mergeCell ref="AG21:AJ30"/>
-    <mergeCell ref="AK21:AN30"/>
-    <mergeCell ref="AG31:AJ40"/>
-    <mergeCell ref="AK31:AN40"/>
-    <mergeCell ref="AS91:AV100"/>
-    <mergeCell ref="AS61:AV70"/>
-    <mergeCell ref="AO71:AR80"/>
-    <mergeCell ref="AS71:AV80"/>
-    <mergeCell ref="AO81:AR90"/>
-    <mergeCell ref="AS81:AV90"/>
-    <mergeCell ref="AO31:AR40"/>
-    <mergeCell ref="AS31:AV40"/>
-    <mergeCell ref="AO41:AR50"/>
-    <mergeCell ref="AS41:AV50"/>
-    <mergeCell ref="AO51:AR60"/>
-    <mergeCell ref="AS51:AV60"/>
-    <mergeCell ref="CC1:CF10"/>
-    <mergeCell ref="CG1:CJ10"/>
-    <mergeCell ref="CC11:CF20"/>
-    <mergeCell ref="CG11:CJ20"/>
-    <mergeCell ref="CC21:CF30"/>
-    <mergeCell ref="CG21:CJ30"/>
-    <mergeCell ref="CC31:CF40"/>
-    <mergeCell ref="CG31:CJ40"/>
-    <mergeCell ref="CC41:CF50"/>
-    <mergeCell ref="CG41:CJ50"/>
-    <mergeCell ref="CC51:CF60"/>
-    <mergeCell ref="CG51:CJ60"/>
-    <mergeCell ref="CC61:CF70"/>
-    <mergeCell ref="CG61:CJ70"/>
-    <mergeCell ref="CC71:CF80"/>
-    <mergeCell ref="CG71:CJ80"/>
-    <mergeCell ref="CC81:CF90"/>
-    <mergeCell ref="CG81:CJ90"/>
-    <mergeCell ref="CC91:CF100"/>
-    <mergeCell ref="CG91:CJ100"/>
-    <mergeCell ref="CK1:CN10"/>
-    <mergeCell ref="CO1:CR10"/>
-    <mergeCell ref="CK11:CN20"/>
-    <mergeCell ref="CO11:CR20"/>
-    <mergeCell ref="CK21:CN30"/>
-    <mergeCell ref="CO21:CR30"/>
-    <mergeCell ref="CK31:CN40"/>
-    <mergeCell ref="CO31:CR40"/>
-    <mergeCell ref="CK41:CN50"/>
-    <mergeCell ref="CO41:CR50"/>
-    <mergeCell ref="CK51:CN60"/>
-    <mergeCell ref="CO51:CR60"/>
-    <mergeCell ref="CK61:CN70"/>
-    <mergeCell ref="CO61:CR70"/>
-    <mergeCell ref="CK71:CN80"/>
-    <mergeCell ref="CO71:CR80"/>
-    <mergeCell ref="CK81:CN90"/>
-    <mergeCell ref="CO81:CR90"/>
-    <mergeCell ref="CK91:CN100"/>
-    <mergeCell ref="CO91:CR100"/>
+    <mergeCell ref="BE1:BH10"/>
+    <mergeCell ref="BI1:BL10"/>
+    <mergeCell ref="BE11:BH20"/>
+    <mergeCell ref="BI11:BL20"/>
+    <mergeCell ref="BE21:BH30"/>
+    <mergeCell ref="BI21:BL30"/>
+    <mergeCell ref="BE31:BH40"/>
+    <mergeCell ref="BI31:BL40"/>
+    <mergeCell ref="BE41:BH50"/>
+    <mergeCell ref="BI41:BL50"/>
+    <mergeCell ref="BE51:BH60"/>
+    <mergeCell ref="BI51:BL60"/>
+    <mergeCell ref="BE61:BH70"/>
+    <mergeCell ref="BI61:BL70"/>
+    <mergeCell ref="BE71:BH80"/>
+    <mergeCell ref="BI71:BL80"/>
+    <mergeCell ref="BE81:BH90"/>
+    <mergeCell ref="BI81:BL90"/>
+    <mergeCell ref="BE91:BH100"/>
+    <mergeCell ref="BI91:BL100"/>
+    <mergeCell ref="BM1:BP10"/>
+    <mergeCell ref="BQ1:BT10"/>
+    <mergeCell ref="BM11:BP20"/>
+    <mergeCell ref="BQ11:BT20"/>
+    <mergeCell ref="BM21:BP30"/>
+    <mergeCell ref="BQ21:BT30"/>
+    <mergeCell ref="BM31:BP40"/>
+    <mergeCell ref="BQ31:BT40"/>
+    <mergeCell ref="BM41:BP50"/>
+    <mergeCell ref="BQ41:BT50"/>
+    <mergeCell ref="BM51:BP60"/>
+    <mergeCell ref="BQ51:BT60"/>
+    <mergeCell ref="BM61:BP70"/>
+    <mergeCell ref="BQ61:BT70"/>
+    <mergeCell ref="BM71:BP80"/>
+    <mergeCell ref="BQ71:BT80"/>
+    <mergeCell ref="BM81:BP90"/>
+    <mergeCell ref="BQ81:BT90"/>
+    <mergeCell ref="BM91:BP100"/>
+    <mergeCell ref="BQ91:BT100"/>
+    <mergeCell ref="BU1:BX10"/>
+    <mergeCell ref="BY1:CB10"/>
+    <mergeCell ref="BU11:BX20"/>
+    <mergeCell ref="BY11:CB20"/>
+    <mergeCell ref="BU21:BX30"/>
+    <mergeCell ref="BY21:CB30"/>
+    <mergeCell ref="BU31:BX40"/>
+    <mergeCell ref="BY31:CB40"/>
+    <mergeCell ref="BU41:BX50"/>
+    <mergeCell ref="BY41:CB50"/>
+    <mergeCell ref="BU51:BX60"/>
+    <mergeCell ref="BY51:CB60"/>
+    <mergeCell ref="BU61:BX70"/>
+    <mergeCell ref="BY61:CB70"/>
+    <mergeCell ref="BU71:BX80"/>
+    <mergeCell ref="BY71:CB80"/>
+    <mergeCell ref="BU81:BX90"/>
+    <mergeCell ref="BY81:CB90"/>
+    <mergeCell ref="BU91:BX100"/>
+    <mergeCell ref="BY91:CB100"/>
+    <mergeCell ref="CS1:CV10"/>
+    <mergeCell ref="CW1:CZ10"/>
+    <mergeCell ref="CS11:CV20"/>
+    <mergeCell ref="CW11:CZ20"/>
+    <mergeCell ref="CS21:CV30"/>
+    <mergeCell ref="CW21:CZ30"/>
+    <mergeCell ref="CS31:CV40"/>
+    <mergeCell ref="CW31:CZ40"/>
+    <mergeCell ref="CS41:CV50"/>
+    <mergeCell ref="CW41:CZ50"/>
+    <mergeCell ref="CS51:CV60"/>
+    <mergeCell ref="CW51:CZ60"/>
+    <mergeCell ref="CS61:CV70"/>
+    <mergeCell ref="CW61:CZ70"/>
+    <mergeCell ref="CS71:CV80"/>
+    <mergeCell ref="CW71:CZ80"/>
+    <mergeCell ref="CS81:CV90"/>
+    <mergeCell ref="CW81:CZ90"/>
+    <mergeCell ref="CS91:CV100"/>
+    <mergeCell ref="CW91:CZ100"/>
+    <mergeCell ref="DA1:DD10"/>
+    <mergeCell ref="DE1:DH10"/>
+    <mergeCell ref="DA11:DD20"/>
+    <mergeCell ref="DE11:DH20"/>
+    <mergeCell ref="DA21:DD30"/>
+    <mergeCell ref="DE21:DH30"/>
+    <mergeCell ref="DA31:DD40"/>
+    <mergeCell ref="DE31:DH40"/>
+    <mergeCell ref="DA41:DD50"/>
+    <mergeCell ref="DE41:DH50"/>
+    <mergeCell ref="DA51:DD60"/>
+    <mergeCell ref="DE51:DH60"/>
+    <mergeCell ref="DA61:DD70"/>
+    <mergeCell ref="DE61:DH70"/>
+    <mergeCell ref="DA71:DD80"/>
+    <mergeCell ref="DE71:DH80"/>
+    <mergeCell ref="DA81:DD90"/>
+    <mergeCell ref="DE81:DH90"/>
+    <mergeCell ref="DA91:DD100"/>
+    <mergeCell ref="DE91:DH100"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.6692913385826772" right="0.6692913385826772" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/tanulókártyák/Tanulókártyák.xlsx
+++ b/tanulókártyák/Tanulókártyák.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atesz\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96CE3FD-5B42-41A7-B079-2A4EA36B5A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A359B90F-60B4-41DD-A9FA-BEE3512008FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5602,79 +5602,6 @@
 (pontosító kérdés a Stack-hez)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Big O </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">- Az algoritmus futási idejének (vagy memóriahasználatának) növekedési ütemét írja le.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Időkomplexitás</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Megmutatja, hogyan nő a futási idő a bemenet méretével.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Térkomplexitás</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Megmutatja, mennyi extra memória kell az algoritmusnak.</t>
-    </r>
-  </si>
-  <si>
     <t>Mi a big O, az időkomplexitás és térkomplexitás?</t>
   </si>
   <si>
@@ -6138,6 +6065,102 @@
   </si>
   <si>
     <t>Quick, Merge, Bubble sort</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Big O </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Order of growth)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">- Az algoritmus futási idejének (vagy memóriahasználatának) növekedési ütemét írja le.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Időkomplexitás</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Megmutatja, hogyan nő a futási idő a bemenet méretével.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Térkomplexitás</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Megmutatja, mennyi extra memória kell az algoritmusnak.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -6706,13 +6729,13 @@
       <c r="DG1" s="8"/>
       <c r="DH1" s="8"/>
       <c r="DI1" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="DJ1" s="8"/>
       <c r="DK1" s="8"/>
       <c r="DL1" s="8"/>
       <c r="DM1" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="DN1" s="8"/>
       <c r="DO1" s="8"/>
@@ -7986,13 +8009,13 @@
       <c r="DG11" s="8"/>
       <c r="DH11" s="8"/>
       <c r="DI11" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="DJ11" s="8"/>
       <c r="DK11" s="8"/>
       <c r="DL11" s="8"/>
       <c r="DM11" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="DN11" s="8"/>
       <c r="DO11" s="8"/>
@@ -9266,13 +9289,13 @@
       <c r="DG21" s="8"/>
       <c r="DH21" s="8"/>
       <c r="DI21" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="DJ21" s="8"/>
       <c r="DK21" s="8"/>
       <c r="DL21" s="8"/>
       <c r="DM21" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="DN21" s="8"/>
       <c r="DO21" s="8"/>
@@ -11810,13 +11833,13 @@
       <c r="CY41" s="8"/>
       <c r="CZ41" s="8"/>
       <c r="DA41" s="7" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="DB41" s="8"/>
       <c r="DC41" s="8"/>
       <c r="DD41" s="8"/>
       <c r="DE41" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="DF41" s="8"/>
       <c r="DG41" s="8"/>
@@ -13098,13 +13121,13 @@
       <c r="DG51" s="6"/>
       <c r="DH51" s="6"/>
       <c r="DI51" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="DJ51" s="6"/>
       <c r="DK51" s="6"/>
       <c r="DL51" s="6"/>
       <c r="DM51" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="DN51" s="6"/>
       <c r="DO51" s="6"/>
@@ -14378,13 +14401,13 @@
       <c r="DG61" s="6"/>
       <c r="DH61" s="6"/>
       <c r="DI61" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="DJ61" s="6"/>
       <c r="DK61" s="6"/>
       <c r="DL61" s="6"/>
       <c r="DM61" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="DN61" s="6"/>
       <c r="DO61" s="6"/>
@@ -15658,13 +15681,13 @@
       <c r="DG71" s="6"/>
       <c r="DH71" s="6"/>
       <c r="DI71" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="DJ71" s="6"/>
       <c r="DK71" s="6"/>
       <c r="DL71" s="6"/>
       <c r="DM71" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="DN71" s="6"/>
       <c r="DO71" s="6"/>
@@ -18202,13 +18225,13 @@
       <c r="CY91" s="6"/>
       <c r="CZ91" s="6"/>
       <c r="DA91" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="DB91" s="6"/>
       <c r="DC91" s="6"/>
       <c r="DD91" s="6"/>
       <c r="DE91" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="DF91" s="6"/>
       <c r="DG91" s="6"/>
@@ -20028,78 +20051,210 @@
     </row>
   </sheetData>
   <mergeCells count="300">
-    <mergeCell ref="DI51:DL60"/>
-    <mergeCell ref="DM51:DP60"/>
-    <mergeCell ref="DI61:DL70"/>
-    <mergeCell ref="DM61:DP70"/>
-    <mergeCell ref="DI71:DL80"/>
-    <mergeCell ref="DM71:DP80"/>
-    <mergeCell ref="DI81:DL90"/>
-    <mergeCell ref="DM81:DP90"/>
-    <mergeCell ref="DI91:DL100"/>
-    <mergeCell ref="DM91:DP100"/>
-    <mergeCell ref="DI1:DL10"/>
-    <mergeCell ref="DM1:DP10"/>
-    <mergeCell ref="DI11:DL20"/>
-    <mergeCell ref="DM11:DP20"/>
-    <mergeCell ref="DI21:DL30"/>
-    <mergeCell ref="DM21:DP30"/>
-    <mergeCell ref="DI31:DL40"/>
-    <mergeCell ref="DM31:DP40"/>
-    <mergeCell ref="DI41:DL50"/>
-    <mergeCell ref="DM41:DP50"/>
-    <mergeCell ref="CK51:CN60"/>
-    <mergeCell ref="CO51:CR60"/>
-    <mergeCell ref="CK61:CN70"/>
-    <mergeCell ref="CO61:CR70"/>
-    <mergeCell ref="CK71:CN80"/>
-    <mergeCell ref="CO71:CR80"/>
-    <mergeCell ref="CK81:CN90"/>
-    <mergeCell ref="CO81:CR90"/>
-    <mergeCell ref="CK91:CN100"/>
-    <mergeCell ref="CO91:CR100"/>
-    <mergeCell ref="CK1:CN10"/>
-    <mergeCell ref="CO1:CR10"/>
-    <mergeCell ref="CK11:CN20"/>
-    <mergeCell ref="CO11:CR20"/>
-    <mergeCell ref="CK21:CN30"/>
-    <mergeCell ref="CO21:CR30"/>
-    <mergeCell ref="CK31:CN40"/>
-    <mergeCell ref="CO31:CR40"/>
-    <mergeCell ref="CK41:CN50"/>
-    <mergeCell ref="CO41:CR50"/>
-    <mergeCell ref="CC51:CF60"/>
-    <mergeCell ref="CG51:CJ60"/>
-    <mergeCell ref="CC61:CF70"/>
-    <mergeCell ref="CG61:CJ70"/>
-    <mergeCell ref="CC71:CF80"/>
-    <mergeCell ref="CG71:CJ80"/>
-    <mergeCell ref="CC81:CF90"/>
-    <mergeCell ref="CG81:CJ90"/>
-    <mergeCell ref="CC91:CF100"/>
-    <mergeCell ref="CG91:CJ100"/>
-    <mergeCell ref="CC1:CF10"/>
-    <mergeCell ref="CG1:CJ10"/>
-    <mergeCell ref="CC11:CF20"/>
-    <mergeCell ref="CG11:CJ20"/>
-    <mergeCell ref="CC21:CF30"/>
-    <mergeCell ref="CG21:CJ30"/>
-    <mergeCell ref="CC31:CF40"/>
-    <mergeCell ref="CG31:CJ40"/>
-    <mergeCell ref="CC41:CF50"/>
-    <mergeCell ref="CG41:CJ50"/>
-    <mergeCell ref="AS91:AV100"/>
-    <mergeCell ref="AS61:AV70"/>
-    <mergeCell ref="AO71:AR80"/>
-    <mergeCell ref="AS71:AV80"/>
-    <mergeCell ref="AO81:AR90"/>
-    <mergeCell ref="AS81:AV90"/>
-    <mergeCell ref="AO31:AR40"/>
-    <mergeCell ref="AS31:AV40"/>
-    <mergeCell ref="AO41:AR50"/>
-    <mergeCell ref="AS41:AV50"/>
-    <mergeCell ref="AO51:AR60"/>
-    <mergeCell ref="AS51:AV60"/>
+    <mergeCell ref="DA51:DD60"/>
+    <mergeCell ref="DE51:DH60"/>
+    <mergeCell ref="DA61:DD70"/>
+    <mergeCell ref="DE61:DH70"/>
+    <mergeCell ref="DA71:DD80"/>
+    <mergeCell ref="DE71:DH80"/>
+    <mergeCell ref="DA81:DD90"/>
+    <mergeCell ref="DE81:DH90"/>
+    <mergeCell ref="DA91:DD100"/>
+    <mergeCell ref="DE91:DH100"/>
+    <mergeCell ref="DA1:DD10"/>
+    <mergeCell ref="DE1:DH10"/>
+    <mergeCell ref="DA11:DD20"/>
+    <mergeCell ref="DE11:DH20"/>
+    <mergeCell ref="DA21:DD30"/>
+    <mergeCell ref="DE21:DH30"/>
+    <mergeCell ref="DA31:DD40"/>
+    <mergeCell ref="DE31:DH40"/>
+    <mergeCell ref="DA41:DD50"/>
+    <mergeCell ref="DE41:DH50"/>
+    <mergeCell ref="CS51:CV60"/>
+    <mergeCell ref="CW51:CZ60"/>
+    <mergeCell ref="CS61:CV70"/>
+    <mergeCell ref="CW61:CZ70"/>
+    <mergeCell ref="CS71:CV80"/>
+    <mergeCell ref="CW71:CZ80"/>
+    <mergeCell ref="CS81:CV90"/>
+    <mergeCell ref="CW81:CZ90"/>
+    <mergeCell ref="CS91:CV100"/>
+    <mergeCell ref="CW91:CZ100"/>
+    <mergeCell ref="CS1:CV10"/>
+    <mergeCell ref="CW1:CZ10"/>
+    <mergeCell ref="CS11:CV20"/>
+    <mergeCell ref="CW11:CZ20"/>
+    <mergeCell ref="CS21:CV30"/>
+    <mergeCell ref="CW21:CZ30"/>
+    <mergeCell ref="CS31:CV40"/>
+    <mergeCell ref="CW31:CZ40"/>
+    <mergeCell ref="CS41:CV50"/>
+    <mergeCell ref="CW41:CZ50"/>
+    <mergeCell ref="BU51:BX60"/>
+    <mergeCell ref="BY51:CB60"/>
+    <mergeCell ref="BU61:BX70"/>
+    <mergeCell ref="BY61:CB70"/>
+    <mergeCell ref="BU71:BX80"/>
+    <mergeCell ref="BY71:CB80"/>
+    <mergeCell ref="BU81:BX90"/>
+    <mergeCell ref="BY81:CB90"/>
+    <mergeCell ref="BU91:BX100"/>
+    <mergeCell ref="BY91:CB100"/>
+    <mergeCell ref="BU1:BX10"/>
+    <mergeCell ref="BY1:CB10"/>
+    <mergeCell ref="BU11:BX20"/>
+    <mergeCell ref="BY11:CB20"/>
+    <mergeCell ref="BU21:BX30"/>
+    <mergeCell ref="BY21:CB30"/>
+    <mergeCell ref="BU31:BX40"/>
+    <mergeCell ref="BY31:CB40"/>
+    <mergeCell ref="BU41:BX50"/>
+    <mergeCell ref="BY41:CB50"/>
+    <mergeCell ref="BM51:BP60"/>
+    <mergeCell ref="BQ51:BT60"/>
+    <mergeCell ref="BM61:BP70"/>
+    <mergeCell ref="BQ61:BT70"/>
+    <mergeCell ref="BM71:BP80"/>
+    <mergeCell ref="BQ71:BT80"/>
+    <mergeCell ref="BM81:BP90"/>
+    <mergeCell ref="BQ81:BT90"/>
+    <mergeCell ref="BM91:BP100"/>
+    <mergeCell ref="BQ91:BT100"/>
+    <mergeCell ref="BM1:BP10"/>
+    <mergeCell ref="BQ1:BT10"/>
+    <mergeCell ref="BM11:BP20"/>
+    <mergeCell ref="BQ11:BT20"/>
+    <mergeCell ref="BM21:BP30"/>
+    <mergeCell ref="BQ21:BT30"/>
+    <mergeCell ref="BM31:BP40"/>
+    <mergeCell ref="BQ31:BT40"/>
+    <mergeCell ref="BM41:BP50"/>
+    <mergeCell ref="BQ41:BT50"/>
+    <mergeCell ref="BE51:BH60"/>
+    <mergeCell ref="BI51:BL60"/>
+    <mergeCell ref="BE61:BH70"/>
+    <mergeCell ref="BI61:BL70"/>
+    <mergeCell ref="BE71:BH80"/>
+    <mergeCell ref="BI71:BL80"/>
+    <mergeCell ref="BE81:BH90"/>
+    <mergeCell ref="BI81:BL90"/>
+    <mergeCell ref="BE91:BH100"/>
+    <mergeCell ref="BI91:BL100"/>
+    <mergeCell ref="BE1:BH10"/>
+    <mergeCell ref="BI1:BL10"/>
+    <mergeCell ref="BE11:BH20"/>
+    <mergeCell ref="BI11:BL20"/>
+    <mergeCell ref="BE21:BH30"/>
+    <mergeCell ref="BI21:BL30"/>
+    <mergeCell ref="BE31:BH40"/>
+    <mergeCell ref="BI31:BL40"/>
+    <mergeCell ref="BE41:BH50"/>
+    <mergeCell ref="BI41:BL50"/>
+    <mergeCell ref="Q91:T100"/>
+    <mergeCell ref="U91:X100"/>
+    <mergeCell ref="Y91:AB100"/>
+    <mergeCell ref="AC91:AF100"/>
+    <mergeCell ref="AW1:AZ10"/>
+    <mergeCell ref="BA1:BD10"/>
+    <mergeCell ref="AW11:AZ20"/>
+    <mergeCell ref="BA11:BD20"/>
+    <mergeCell ref="AW21:AZ30"/>
+    <mergeCell ref="BA21:BD30"/>
+    <mergeCell ref="AW31:AZ40"/>
+    <mergeCell ref="BA31:BD40"/>
+    <mergeCell ref="AW41:AZ50"/>
+    <mergeCell ref="BA41:BD50"/>
+    <mergeCell ref="AW51:AZ60"/>
+    <mergeCell ref="BA51:BD60"/>
+    <mergeCell ref="AW61:AZ70"/>
+    <mergeCell ref="BA61:BD70"/>
+    <mergeCell ref="AW71:AZ80"/>
+    <mergeCell ref="BA71:BD80"/>
+    <mergeCell ref="AW81:AZ90"/>
+    <mergeCell ref="BA81:BD90"/>
+    <mergeCell ref="AW91:AZ100"/>
+    <mergeCell ref="BA91:BD100"/>
+    <mergeCell ref="Q61:T70"/>
+    <mergeCell ref="U61:X70"/>
+    <mergeCell ref="Y61:AB70"/>
+    <mergeCell ref="AC61:AF70"/>
+    <mergeCell ref="Q71:T80"/>
+    <mergeCell ref="U71:X80"/>
+    <mergeCell ref="Y71:AB80"/>
+    <mergeCell ref="AC71:AF80"/>
+    <mergeCell ref="Q81:T90"/>
+    <mergeCell ref="U81:X90"/>
+    <mergeCell ref="Y81:AB90"/>
+    <mergeCell ref="AC81:AF90"/>
+    <mergeCell ref="Q31:T40"/>
+    <mergeCell ref="U31:X40"/>
+    <mergeCell ref="Y31:AB40"/>
+    <mergeCell ref="AC31:AF40"/>
+    <mergeCell ref="Q41:T50"/>
+    <mergeCell ref="U41:X50"/>
+    <mergeCell ref="Y41:AB50"/>
+    <mergeCell ref="AC41:AF50"/>
+    <mergeCell ref="Q51:T60"/>
+    <mergeCell ref="U51:X60"/>
+    <mergeCell ref="Y51:AB60"/>
+    <mergeCell ref="AC51:AF60"/>
+    <mergeCell ref="Q1:T10"/>
+    <mergeCell ref="U1:X10"/>
+    <mergeCell ref="Y1:AB10"/>
+    <mergeCell ref="AC1:AF10"/>
+    <mergeCell ref="Q11:T20"/>
+    <mergeCell ref="U11:X20"/>
+    <mergeCell ref="Y11:AB20"/>
+    <mergeCell ref="AC11:AF20"/>
+    <mergeCell ref="Q21:T30"/>
+    <mergeCell ref="U21:X30"/>
+    <mergeCell ref="Y21:AB30"/>
+    <mergeCell ref="AC21:AF30"/>
+    <mergeCell ref="I81:L90"/>
+    <mergeCell ref="M81:P90"/>
+    <mergeCell ref="I91:L100"/>
+    <mergeCell ref="M91:P100"/>
+    <mergeCell ref="I51:L60"/>
+    <mergeCell ref="M51:P60"/>
+    <mergeCell ref="I61:L70"/>
+    <mergeCell ref="M61:P70"/>
+    <mergeCell ref="I71:L80"/>
+    <mergeCell ref="M71:P80"/>
+    <mergeCell ref="A81:D90"/>
+    <mergeCell ref="E81:H90"/>
+    <mergeCell ref="A91:D100"/>
+    <mergeCell ref="E91:H100"/>
+    <mergeCell ref="A51:D60"/>
+    <mergeCell ref="E51:H60"/>
+    <mergeCell ref="A61:D70"/>
+    <mergeCell ref="E61:H70"/>
+    <mergeCell ref="A71:D80"/>
+    <mergeCell ref="E71:H80"/>
+    <mergeCell ref="AG41:AJ50"/>
+    <mergeCell ref="AK41:AN50"/>
+    <mergeCell ref="AG71:AJ80"/>
+    <mergeCell ref="AK71:AN80"/>
+    <mergeCell ref="A1:D10"/>
+    <mergeCell ref="E1:H10"/>
+    <mergeCell ref="A11:D20"/>
+    <mergeCell ref="E11:H20"/>
+    <mergeCell ref="A21:D30"/>
+    <mergeCell ref="E21:H30"/>
+    <mergeCell ref="M31:P40"/>
+    <mergeCell ref="I41:L50"/>
+    <mergeCell ref="M41:P50"/>
+    <mergeCell ref="A31:D40"/>
+    <mergeCell ref="E31:H40"/>
+    <mergeCell ref="A41:D50"/>
+    <mergeCell ref="E41:H50"/>
+    <mergeCell ref="I31:L40"/>
+    <mergeCell ref="I1:L10"/>
+    <mergeCell ref="M1:P10"/>
+    <mergeCell ref="I11:L20"/>
+    <mergeCell ref="M11:P20"/>
+    <mergeCell ref="I21:L30"/>
+    <mergeCell ref="M21:P30"/>
     <mergeCell ref="AO1:AR10"/>
     <mergeCell ref="AS1:AV10"/>
     <mergeCell ref="AO11:AR20"/>
@@ -20124,210 +20279,78 @@
     <mergeCell ref="AK21:AN30"/>
     <mergeCell ref="AG31:AJ40"/>
     <mergeCell ref="AK31:AN40"/>
-    <mergeCell ref="AG41:AJ50"/>
-    <mergeCell ref="AK41:AN50"/>
-    <mergeCell ref="AG71:AJ80"/>
-    <mergeCell ref="AK71:AN80"/>
-    <mergeCell ref="A1:D10"/>
-    <mergeCell ref="E1:H10"/>
-    <mergeCell ref="A11:D20"/>
-    <mergeCell ref="E11:H20"/>
-    <mergeCell ref="A21:D30"/>
-    <mergeCell ref="E21:H30"/>
-    <mergeCell ref="M31:P40"/>
-    <mergeCell ref="I41:L50"/>
-    <mergeCell ref="M41:P50"/>
-    <mergeCell ref="A31:D40"/>
-    <mergeCell ref="E31:H40"/>
-    <mergeCell ref="A41:D50"/>
-    <mergeCell ref="E41:H50"/>
-    <mergeCell ref="I31:L40"/>
-    <mergeCell ref="I1:L10"/>
-    <mergeCell ref="M1:P10"/>
-    <mergeCell ref="I11:L20"/>
-    <mergeCell ref="M11:P20"/>
-    <mergeCell ref="I21:L30"/>
-    <mergeCell ref="M21:P30"/>
-    <mergeCell ref="A81:D90"/>
-    <mergeCell ref="E81:H90"/>
-    <mergeCell ref="A91:D100"/>
-    <mergeCell ref="E91:H100"/>
-    <mergeCell ref="A51:D60"/>
-    <mergeCell ref="E51:H60"/>
-    <mergeCell ref="A61:D70"/>
-    <mergeCell ref="E61:H70"/>
-    <mergeCell ref="A71:D80"/>
-    <mergeCell ref="E71:H80"/>
-    <mergeCell ref="I81:L90"/>
-    <mergeCell ref="M81:P90"/>
-    <mergeCell ref="I91:L100"/>
-    <mergeCell ref="M91:P100"/>
-    <mergeCell ref="I51:L60"/>
-    <mergeCell ref="M51:P60"/>
-    <mergeCell ref="I61:L70"/>
-    <mergeCell ref="M61:P70"/>
-    <mergeCell ref="I71:L80"/>
-    <mergeCell ref="M71:P80"/>
-    <mergeCell ref="Q1:T10"/>
-    <mergeCell ref="U1:X10"/>
-    <mergeCell ref="Y1:AB10"/>
-    <mergeCell ref="AC1:AF10"/>
-    <mergeCell ref="Q11:T20"/>
-    <mergeCell ref="U11:X20"/>
-    <mergeCell ref="Y11:AB20"/>
-    <mergeCell ref="AC11:AF20"/>
-    <mergeCell ref="Q21:T30"/>
-    <mergeCell ref="U21:X30"/>
-    <mergeCell ref="Y21:AB30"/>
-    <mergeCell ref="AC21:AF30"/>
-    <mergeCell ref="Q31:T40"/>
-    <mergeCell ref="U31:X40"/>
-    <mergeCell ref="Y31:AB40"/>
-    <mergeCell ref="AC31:AF40"/>
-    <mergeCell ref="Q41:T50"/>
-    <mergeCell ref="U41:X50"/>
-    <mergeCell ref="Y41:AB50"/>
-    <mergeCell ref="AC41:AF50"/>
-    <mergeCell ref="Q51:T60"/>
-    <mergeCell ref="U51:X60"/>
-    <mergeCell ref="Y51:AB60"/>
-    <mergeCell ref="AC51:AF60"/>
-    <mergeCell ref="Q61:T70"/>
-    <mergeCell ref="U61:X70"/>
-    <mergeCell ref="Y61:AB70"/>
-    <mergeCell ref="AC61:AF70"/>
-    <mergeCell ref="Q71:T80"/>
-    <mergeCell ref="U71:X80"/>
-    <mergeCell ref="Y71:AB80"/>
-    <mergeCell ref="AC71:AF80"/>
-    <mergeCell ref="Q81:T90"/>
-    <mergeCell ref="U81:X90"/>
-    <mergeCell ref="Y81:AB90"/>
-    <mergeCell ref="AC81:AF90"/>
-    <mergeCell ref="Q91:T100"/>
-    <mergeCell ref="U91:X100"/>
-    <mergeCell ref="Y91:AB100"/>
-    <mergeCell ref="AC91:AF100"/>
-    <mergeCell ref="AW1:AZ10"/>
-    <mergeCell ref="BA1:BD10"/>
-    <mergeCell ref="AW11:AZ20"/>
-    <mergeCell ref="BA11:BD20"/>
-    <mergeCell ref="AW21:AZ30"/>
-    <mergeCell ref="BA21:BD30"/>
-    <mergeCell ref="AW31:AZ40"/>
-    <mergeCell ref="BA31:BD40"/>
-    <mergeCell ref="AW41:AZ50"/>
-    <mergeCell ref="BA41:BD50"/>
-    <mergeCell ref="AW51:AZ60"/>
-    <mergeCell ref="BA51:BD60"/>
-    <mergeCell ref="AW61:AZ70"/>
-    <mergeCell ref="BA61:BD70"/>
-    <mergeCell ref="AW71:AZ80"/>
-    <mergeCell ref="BA71:BD80"/>
-    <mergeCell ref="AW81:AZ90"/>
-    <mergeCell ref="BA81:BD90"/>
-    <mergeCell ref="AW91:AZ100"/>
-    <mergeCell ref="BA91:BD100"/>
-    <mergeCell ref="BE1:BH10"/>
-    <mergeCell ref="BI1:BL10"/>
-    <mergeCell ref="BE11:BH20"/>
-    <mergeCell ref="BI11:BL20"/>
-    <mergeCell ref="BE21:BH30"/>
-    <mergeCell ref="BI21:BL30"/>
-    <mergeCell ref="BE31:BH40"/>
-    <mergeCell ref="BI31:BL40"/>
-    <mergeCell ref="BE41:BH50"/>
-    <mergeCell ref="BI41:BL50"/>
-    <mergeCell ref="BE51:BH60"/>
-    <mergeCell ref="BI51:BL60"/>
-    <mergeCell ref="BE61:BH70"/>
-    <mergeCell ref="BI61:BL70"/>
-    <mergeCell ref="BE71:BH80"/>
-    <mergeCell ref="BI71:BL80"/>
-    <mergeCell ref="BE81:BH90"/>
-    <mergeCell ref="BI81:BL90"/>
-    <mergeCell ref="BE91:BH100"/>
-    <mergeCell ref="BI91:BL100"/>
-    <mergeCell ref="BM1:BP10"/>
-    <mergeCell ref="BQ1:BT10"/>
-    <mergeCell ref="BM11:BP20"/>
-    <mergeCell ref="BQ11:BT20"/>
-    <mergeCell ref="BM21:BP30"/>
-    <mergeCell ref="BQ21:BT30"/>
-    <mergeCell ref="BM31:BP40"/>
-    <mergeCell ref="BQ31:BT40"/>
-    <mergeCell ref="BM41:BP50"/>
-    <mergeCell ref="BQ41:BT50"/>
-    <mergeCell ref="BM51:BP60"/>
-    <mergeCell ref="BQ51:BT60"/>
-    <mergeCell ref="BM61:BP70"/>
-    <mergeCell ref="BQ61:BT70"/>
-    <mergeCell ref="BM71:BP80"/>
-    <mergeCell ref="BQ71:BT80"/>
-    <mergeCell ref="BM81:BP90"/>
-    <mergeCell ref="BQ81:BT90"/>
-    <mergeCell ref="BM91:BP100"/>
-    <mergeCell ref="BQ91:BT100"/>
-    <mergeCell ref="BU1:BX10"/>
-    <mergeCell ref="BY1:CB10"/>
-    <mergeCell ref="BU11:BX20"/>
-    <mergeCell ref="BY11:CB20"/>
-    <mergeCell ref="BU21:BX30"/>
-    <mergeCell ref="BY21:CB30"/>
-    <mergeCell ref="BU31:BX40"/>
-    <mergeCell ref="BY31:CB40"/>
-    <mergeCell ref="BU41:BX50"/>
-    <mergeCell ref="BY41:CB50"/>
-    <mergeCell ref="BU51:BX60"/>
-    <mergeCell ref="BY51:CB60"/>
-    <mergeCell ref="BU61:BX70"/>
-    <mergeCell ref="BY61:CB70"/>
-    <mergeCell ref="BU71:BX80"/>
-    <mergeCell ref="BY71:CB80"/>
-    <mergeCell ref="BU81:BX90"/>
-    <mergeCell ref="BY81:CB90"/>
-    <mergeCell ref="BU91:BX100"/>
-    <mergeCell ref="BY91:CB100"/>
-    <mergeCell ref="CS1:CV10"/>
-    <mergeCell ref="CW1:CZ10"/>
-    <mergeCell ref="CS11:CV20"/>
-    <mergeCell ref="CW11:CZ20"/>
-    <mergeCell ref="CS21:CV30"/>
-    <mergeCell ref="CW21:CZ30"/>
-    <mergeCell ref="CS31:CV40"/>
-    <mergeCell ref="CW31:CZ40"/>
-    <mergeCell ref="CS41:CV50"/>
-    <mergeCell ref="CW41:CZ50"/>
-    <mergeCell ref="CS51:CV60"/>
-    <mergeCell ref="CW51:CZ60"/>
-    <mergeCell ref="CS61:CV70"/>
-    <mergeCell ref="CW61:CZ70"/>
-    <mergeCell ref="CS71:CV80"/>
-    <mergeCell ref="CW71:CZ80"/>
-    <mergeCell ref="CS81:CV90"/>
-    <mergeCell ref="CW81:CZ90"/>
-    <mergeCell ref="CS91:CV100"/>
-    <mergeCell ref="CW91:CZ100"/>
-    <mergeCell ref="DA1:DD10"/>
-    <mergeCell ref="DE1:DH10"/>
-    <mergeCell ref="DA11:DD20"/>
-    <mergeCell ref="DE11:DH20"/>
-    <mergeCell ref="DA21:DD30"/>
-    <mergeCell ref="DE21:DH30"/>
-    <mergeCell ref="DA31:DD40"/>
-    <mergeCell ref="DE31:DH40"/>
-    <mergeCell ref="DA41:DD50"/>
-    <mergeCell ref="DE41:DH50"/>
-    <mergeCell ref="DA51:DD60"/>
-    <mergeCell ref="DE51:DH60"/>
-    <mergeCell ref="DA61:DD70"/>
-    <mergeCell ref="DE61:DH70"/>
-    <mergeCell ref="DA71:DD80"/>
-    <mergeCell ref="DE71:DH80"/>
-    <mergeCell ref="DA81:DD90"/>
-    <mergeCell ref="DE81:DH90"/>
-    <mergeCell ref="DA91:DD100"/>
-    <mergeCell ref="DE91:DH100"/>
+    <mergeCell ref="AS91:AV100"/>
+    <mergeCell ref="AS61:AV70"/>
+    <mergeCell ref="AO71:AR80"/>
+    <mergeCell ref="AS71:AV80"/>
+    <mergeCell ref="AO81:AR90"/>
+    <mergeCell ref="AS81:AV90"/>
+    <mergeCell ref="AO31:AR40"/>
+    <mergeCell ref="AS31:AV40"/>
+    <mergeCell ref="AO41:AR50"/>
+    <mergeCell ref="AS41:AV50"/>
+    <mergeCell ref="AO51:AR60"/>
+    <mergeCell ref="AS51:AV60"/>
+    <mergeCell ref="CC1:CF10"/>
+    <mergeCell ref="CG1:CJ10"/>
+    <mergeCell ref="CC11:CF20"/>
+    <mergeCell ref="CG11:CJ20"/>
+    <mergeCell ref="CC21:CF30"/>
+    <mergeCell ref="CG21:CJ30"/>
+    <mergeCell ref="CC31:CF40"/>
+    <mergeCell ref="CG31:CJ40"/>
+    <mergeCell ref="CC41:CF50"/>
+    <mergeCell ref="CG41:CJ50"/>
+    <mergeCell ref="CC51:CF60"/>
+    <mergeCell ref="CG51:CJ60"/>
+    <mergeCell ref="CC61:CF70"/>
+    <mergeCell ref="CG61:CJ70"/>
+    <mergeCell ref="CC71:CF80"/>
+    <mergeCell ref="CG71:CJ80"/>
+    <mergeCell ref="CC81:CF90"/>
+    <mergeCell ref="CG81:CJ90"/>
+    <mergeCell ref="CC91:CF100"/>
+    <mergeCell ref="CG91:CJ100"/>
+    <mergeCell ref="CK1:CN10"/>
+    <mergeCell ref="CO1:CR10"/>
+    <mergeCell ref="CK11:CN20"/>
+    <mergeCell ref="CO11:CR20"/>
+    <mergeCell ref="CK21:CN30"/>
+    <mergeCell ref="CO21:CR30"/>
+    <mergeCell ref="CK31:CN40"/>
+    <mergeCell ref="CO31:CR40"/>
+    <mergeCell ref="CK41:CN50"/>
+    <mergeCell ref="CO41:CR50"/>
+    <mergeCell ref="CK51:CN60"/>
+    <mergeCell ref="CO51:CR60"/>
+    <mergeCell ref="CK61:CN70"/>
+    <mergeCell ref="CO61:CR70"/>
+    <mergeCell ref="CK71:CN80"/>
+    <mergeCell ref="CO71:CR80"/>
+    <mergeCell ref="CK81:CN90"/>
+    <mergeCell ref="CO81:CR90"/>
+    <mergeCell ref="CK91:CN100"/>
+    <mergeCell ref="CO91:CR100"/>
+    <mergeCell ref="DI1:DL10"/>
+    <mergeCell ref="DM1:DP10"/>
+    <mergeCell ref="DI11:DL20"/>
+    <mergeCell ref="DM11:DP20"/>
+    <mergeCell ref="DI21:DL30"/>
+    <mergeCell ref="DM21:DP30"/>
+    <mergeCell ref="DI31:DL40"/>
+    <mergeCell ref="DM31:DP40"/>
+    <mergeCell ref="DI41:DL50"/>
+    <mergeCell ref="DM41:DP50"/>
+    <mergeCell ref="DI51:DL60"/>
+    <mergeCell ref="DM51:DP60"/>
+    <mergeCell ref="DI61:DL70"/>
+    <mergeCell ref="DM61:DP70"/>
+    <mergeCell ref="DI71:DL80"/>
+    <mergeCell ref="DM71:DP80"/>
+    <mergeCell ref="DI81:DL90"/>
+    <mergeCell ref="DM81:DP90"/>
+    <mergeCell ref="DI91:DL100"/>
+    <mergeCell ref="DM91:DP100"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.6692913385826772" right="0.6692913385826772" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/tanulókártyák/Tanulókártyák.xlsx
+++ b/tanulókártyák/Tanulókártyák.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atesz\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A359B90F-60B4-41DD-A9FA-BEE3512008FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FC1C67-2A45-4257-AA32-C39BD9A3BB22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="340">
   <si>
     <r>
       <rPr>
@@ -1117,32 +1117,6 @@
   <si>
     <t>Magyarázd el:
 String, StringBuilder, StringBuffer</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Immutable object</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Olyan objektum, melynek állapota a létrehozása után nem változtatható meg. Minden „módosítás” valójában egy új objektum létrehozását jelenti. 
-Példa: String.</t>
-    </r>
   </si>
   <si>
     <t>Mit jelent a kifejezés, hogy immutable object?</t>
@@ -1205,10 +1179,6 @@
       <t xml:space="preserve"> - Az autoboxing a Java fordító által végzett automatikus átalakítás, amely a primitív adattípusokat a hozzájuk tartozó wrapper osztályokká alakítja. Például egy int → Integer, vagy egy double → Double konverzió.
 Az unboxing ennek a fordított folyamata, amikor egy wrapper objektum visszaalakításra kerül primitív adattípussá.</t>
     </r>
-  </si>
-  <si>
-    <t>Magyarázd el:
-Autobixing, unboxing</t>
   </si>
   <si>
     <r>
@@ -6160,6 +6130,1178 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> - Megmutatja, mennyi extra memória kell az algoritmusnak.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">spring annotiációk </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dependency</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (függőség):
+Egy külső könyvtár vagy komponens, amelyre egy program működéséhez szükség van. A projekt nem működik nélküle vagy csak korlátozottan.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mit jelent a dependency (függőség)?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Maven:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Egy nagyon elterjedt Java-alapú build- és dependency-kezelő eszköz, amely automatikusan kezeli a függőségeket, fordítást és csomagolást. 
+Konfigurációhoz egy XML-alapú projektobjektum-modell (POM) fájlt használ.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a Maven?</t>
+  </si>
+  <si>
+    <t>Mi az XML file?</t>
+  </si>
+  <si>
+    <t>Mi a YAML file?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">XML file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(eXtensible Markup Language):
+Egy strukturált szövegformátum, amely adatokat hierarchikusan tárol címkék (tagek) segítségével. Gyakori konfigurációs formátum (pl. Maven-ben a pom.xml).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">YAML file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Yet Another Markup Language):</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Egy ember által könnyen olvasható konfigurációs formátum, amely kulcs–érték párokra és behúzásos struktúrára épül. Gyakran használják konfigurációhoz (pl. Docker, Spring).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PaaS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Platform as a Service):
+Egy felhőalapú számítástechnikai modell, amelyben egy külső szolgáltató hardver- és szoftvereszközöket biztosít a felhasználók számára az interneten keresztül. Egy teljes, azonnal használható környezetet nyújt a fejlesztőknek, amelyben alkalmazásokat hozhatnak létre, tesztelhetnek, telepíthetnek és kezelhetnek anélkül, hogy az alapul szolgáló infrastruktúrát fel kellene építeniük vagy karban kellene tartaniuk.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Library</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (könyvtár):
+Egy újrahasználható kódrészlet-gyűjtemény, amit a program hív meg szükség esetén. A vezérlés a programnál marad.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Framework</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (keretrendszer):
+Egy szoftveres keretrendszer, amely meghatározza az alkalmazás struktúráját, és ő hívja meg a te kódodat (inverz vezérlés).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Library vs Framework:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Library esetén te hívod a kódot, framework esetén a framework hívja a te kódodat.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a PaaS?</t>
+  </si>
+  <si>
+    <t>Mi a library?</t>
+  </si>
+  <si>
+    <t>Mi a Framework?
+Mi a különbség Library és Framework között?</t>
+  </si>
+  <si>
+    <t>Mi az Inversion of Control?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dependency Injection (DI):
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Egy tervezési minta, amelyben a függőségeket nem a class hozza létre, hanem kívülről kapja meg (pl. konstruktoron vagy setteren keresztül).</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+IoC vs DI:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Az IoC egy általános elv (a vezérlés átkerül a frameworkhöz), míg a DI ennek egy konkrét megvalósítása, amely a függőségek külső beadására fókuszál.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a Dependency Injection?
+IoC vs DI?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Mitől „entitás” az entitás?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Attól, hogy van egyedi azonosítója (ID), és az élete a perzisztens tárolóban (pl. adatbázisban) is értelmezett. Élete cikluson megy keresztül (létrejön, módosul, törlődik) és domain logikához kötődik. 
+Az entitás nem csak adat, hanem egy „valós világbeli” fogalom (pl. User, Order), amelynek állapota időben változhat.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mitől „entitás” az entitás?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Data Transfer Object</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (DTO):
+Egy egyszerű objektum, amely adatot szállít rétegek vagy rendszerek között, üzleti logika nélkül.
+Jellemzői:
+Nincs üzleti logikája
+Általában nincs adatbázis-kapcsolata
+Csak adat továbbításra szolgál (pl. API ↔ frontend)
+Gyakran csak a szükséges mezőket tartalmazza</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi az a Data Transfer Object?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Inversion of Control (IoC):
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Egy programozási elv, ahol a vezérlés nem a saját kódban van, hanem egy külső keretrendszer (framework) irányítja a program működését és a komponensek életciklusát.
+A Spring konténer gondoskodik a különböző objektumok függőségeinek összekapcsolásáról (wiring), ahelyett hogy az objektumok maguk hoznák létre vagy keresnék meg a függőségeiket.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a Spring Framework?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Spring Framework:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A legszélesebb körben használt keretrendszer Java Enterprise Edition alkalmazások fejlesztéséhez. Emellett a Spring alapvető funkciói bármilyen Java alkalmazás fejlesztésében felhasználhatók.
+Kiterjesztéseit különböző webalkalmazások építésére használjuk a Jakarta EE platformon. Emellett akár önálló (standalone) alkalmazásokban is használhatjuk pusztán a függőség-injektálási (dependency injection) lehetőségeit.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Spring Bean:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+A Spring Bean-ek olyan Java objektumok, amelyeket a Spring IoC konténer inicializál.
+A Springben a</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bean scope</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> határozza meg az életciklust:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>singleton (default)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - egyetlen példány az egész Spring containerben
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>prototype</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - minden kérésre új példány
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>request</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - egy HTTP kérésenként egy példány
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>session</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - egy felhasználói session-önként egy példány
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a Bean és milyen scope-jai lehetnek Spring-ben?</t>
+  </si>
+  <si>
+    <t>Mi a Spring Controller réteg?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Spring rétegek kapcsolódása:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Controller - Service - Repository - Database
+A Controller fogadja a kérést, a Service feldolgozza az üzleti logikát, a Repository pedig az adatbázissal kommunikál.
+Azért létezik ez a rétegzés, hogy szétválasszuk a felelősségeket (Separation of Concerns), így a kód átláthatóbb, tesztelhetőbb és könnyebben karbantartható.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Spring </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Service</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> réteg:
+A Service réteg tartalmazza az üzleti logikát. Itt történik a „valódi munka”, például számítások, szabályok alkalmazása, több repository hívás összekötése.
+A Service réteg általában nem beszél közvetlenül a HTTP világgal (pl. request/response). Ez segít abban, hogy az üzleti logika független maradjon a webes rétegtől, így könnyebben tesztelhető és újrahasznosítható.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Spring </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Repository</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> réteg:
+A Repository réteg felelős az adatbázis műveletekért (CRUD). Ez a réteg kommunikál közvetlenül az adatbázissal, például JPA/Hibernate segítségével.
+A Repository réteg tipikusan Spring Data JPA interfészekkel van megvalósítva, így sok esetben nem is kell SQL-t írni. A Spring automatikusan implementálja az alap CRUD műveleteket.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Spring </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Controller</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> réteg: kezeli a bejövő HTTP kéréseket (requesteket), feldolgozza őket a Service réteg segítségével, majd visszaadja a választ (response-t), általában JSON formában egy REST API-ban.
+Nem tartalmaz üzleti logikát, csak „irányít”. Feladata, hogy a HTTP réteg és az alkalmazás belső logikája között kapcsolatot teremtsen. Gyakran használ DTO-kat a bemenet és kimenet kezelésére, hogy ne közvetlenül az entity-k kerüljenek ki az API-n keresztül.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a Spring Service réteg?</t>
+  </si>
+  <si>
+    <t>Mi a Spring Repository réteg?</t>
+  </si>
+  <si>
+    <t>Hogyan kapcsolódnak a Spring rétegek egymáshoz?
+Miért létezik ez a rétegzés?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Az </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>autowiring</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a Spring Dependency Injection mechanizmusa, amely automatikusan „beilleszti” a szükséges függőségeket.
+A @Autowired annotációval a Spring automatikusan összeköti a bean-eket típus alapján.
+Ez tesztelhetőbb és immutable objektumokat eredményez.
+Modern Spring gyakorlatban inkább a constructor injection ajánlott, ahol a függőségek a konstruktoron keresztül érkeznek.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Spring annotáció </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">egy Java nyelvi metaadat, amellyel a Spring keretrendszernek adunk utasításokat az osztályok, metódusok vagy mezők szerepéről és kezeléséről a dependency injection és az alkalmazás működése során.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a Spring annotáció?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">@Controller </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">klasszikus Spring MVC vezérlő, amely általában HTML nézeteket (view-kat) ad vissza.
+A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">@RestController </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ennek egy speciális változata, ami automatikusan JSON (vagy más adat) választ ad vissza.
+Valójában a @RestController = @Controller + @ResponseBody.
+REST API-k esetén szinte mindig @RestController-t használunk, mert nem view-kat, hanem adatot szolgáltatunk.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@Component</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> az általános alap annotáció, minden más ebből „specializált” szerepkör.
+A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@Service</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> az üzleti logikát tartalmazó service réteget jelöli.
+A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@Repository</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> az adatbázis-hozzáférési réteget jelöli, és extra kivételkezelést is biztosít (pl. JPA exception).
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Annotációk:
+@Component,
+@Service,
+@Repository</t>
+  </si>
+  <si>
+    <t>Annotációk:
+@Controller,
+@RestController</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Springben a REST API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-k általában @RestController-rel készülnek, és JSON formátumban kommunikálnak.
+A műveletek HTTP metódusokra vannak leképezve (GET, POST, PUT, DELETE), amelyek CRUD műveleteket reprezentálnak.
+A kliens (pl. frontend) HTTP kéréseket küld, a szerver pedig válaszokat ad vissza DTO-k vagy JSON objektumok formájában.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi az autowiring?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">@RequestMapping </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">az alap annotáció HTTP endpointok definiálására, és bármilyen HTTP metódust kezelhet.
+A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@GetMapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@PostMapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@PutMapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@DeleteMapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ennek rövidített, specifikus változatai.
+Ezek egyértelműen jelzik, hogy az adott metódus milyen HTTP műveletet kezel.
+A mappingek segítségével URL-eket kötünk Java metódusokhoz.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Annotációk:
+@RequestMapping,
+@GetMapping,
+@PostMapping,
+@PutMapping,
+@DeleteMapping</t>
+  </si>
+  <si>
+    <t>REST API alapok Spring-ben?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Spring MVC vezérlő</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (controller) egy olyan komponens, amely a bejövő HTTP kéréseket fogadja, feldolgozásra továbbítja a megfelelő szolgáltatási (service) rétegnek, majd a kapott eredményt HTTP válaszként visszaküldi a kliensnek.
+Az </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">MVC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Model–View–Controller) szoftverarchitektúra minta, amely az alkalmazást három részre osztja: a Model az adatokat és üzleti logikát, a View a megjelenítést, a Controller pedig a felhasználói kérések kezelését és a két réteg összekapcsolását végzi.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a Spring MVC vezérlő?
+Mit jelent az MVC?</t>
+  </si>
+  <si>
+    <t>Magyarázd el:
+Autoboxing, unboxing</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Immutable object</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Olyan objektum, melynek állapota a létrehozása után nem változtatható meg. Minden „módosítás” valójában egy új objektum létrehozását jelenti. 
+Példa: String, Wrapper objects, java.time package (majdnem) minden eleme</t>
     </r>
   </si>
 </sst>
@@ -6244,7 +7386,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" shrinkToFit="1"/>
@@ -6271,6 +7413,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -6553,13 +7698,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DP151"/>
+  <dimension ref="A1:EF151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="120" width="11" customWidth="1"/>
+    <col min="1" max="136" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -6603,145 +7748,169 @@
       <c r="AA1" s="8"/>
       <c r="AB1" s="8"/>
       <c r="AC1" s="7" t="s">
-        <v>61</v>
+        <v>339</v>
       </c>
       <c r="AD1" s="8"/>
       <c r="AE1" s="8"/>
       <c r="AF1" s="8"/>
       <c r="AG1" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AH1" s="8"/>
       <c r="AI1" s="8"/>
       <c r="AJ1" s="8"/>
       <c r="AK1" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AL1" s="8"/>
       <c r="AM1" s="8"/>
       <c r="AN1" s="8"/>
       <c r="AO1" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AP1" s="8"/>
       <c r="AQ1" s="8"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AT1" s="8"/>
       <c r="AU1" s="8"/>
       <c r="AV1" s="8"/>
       <c r="AW1" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AX1" s="8"/>
       <c r="AY1" s="8"/>
       <c r="AZ1" s="8"/>
       <c r="BA1" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="BB1" s="8"/>
       <c r="BC1" s="8"/>
       <c r="BD1" s="8"/>
       <c r="BE1" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="BF1" s="8"/>
       <c r="BG1" s="8"/>
       <c r="BH1" s="8"/>
       <c r="BI1" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="BJ1" s="8"/>
       <c r="BK1" s="8"/>
       <c r="BL1" s="8"/>
       <c r="BM1" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BN1" s="8"/>
       <c r="BO1" s="8"/>
       <c r="BP1" s="8"/>
       <c r="BQ1" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="BR1" s="8"/>
       <c r="BS1" s="8"/>
       <c r="BT1" s="8"/>
       <c r="BU1" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="BV1" s="8"/>
       <c r="BW1" s="8"/>
       <c r="BX1" s="8"/>
       <c r="BY1" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="BZ1" s="8"/>
       <c r="CA1" s="8"/>
       <c r="CB1" s="8"/>
       <c r="CC1" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="CD1" s="8"/>
       <c r="CE1" s="8"/>
       <c r="CF1" s="8"/>
       <c r="CG1" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="CH1" s="8"/>
       <c r="CI1" s="8"/>
       <c r="CJ1" s="8"/>
       <c r="CK1" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="CL1" s="8"/>
       <c r="CM1" s="8"/>
       <c r="CN1" s="8"/>
       <c r="CO1" s="7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="CP1" s="8"/>
       <c r="CQ1" s="8"/>
       <c r="CR1" s="8"/>
       <c r="CS1" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="CT1" s="8"/>
       <c r="CU1" s="8"/>
       <c r="CV1" s="8"/>
       <c r="CW1" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="CX1" s="8"/>
       <c r="CY1" s="8"/>
       <c r="CZ1" s="8"/>
       <c r="DA1" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="DB1" s="8"/>
       <c r="DC1" s="8"/>
       <c r="DD1" s="8"/>
       <c r="DE1" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="DF1" s="8"/>
       <c r="DG1" s="8"/>
       <c r="DH1" s="8"/>
       <c r="DI1" s="7" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="DJ1" s="8"/>
       <c r="DK1" s="8"/>
       <c r="DL1" s="8"/>
       <c r="DM1" s="7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="DN1" s="8"/>
       <c r="DO1" s="8"/>
       <c r="DP1" s="8"/>
+      <c r="DQ1" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="DR1" s="8"/>
+      <c r="DS1" s="8"/>
+      <c r="DT1" s="8"/>
+      <c r="DU1" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="DV1" s="8"/>
+      <c r="DW1" s="8"/>
+      <c r="DX1" s="8"/>
+      <c r="DY1" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="DZ1" s="8"/>
+      <c r="EA1" s="8"/>
+      <c r="EB1" s="8"/>
+      <c r="EC1" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="ED1" s="8"/>
+      <c r="EE1" s="8"/>
+      <c r="EF1" s="8"/>
     </row>
-    <row r="2" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -6862,8 +8031,24 @@
       <c r="DN2" s="8"/>
       <c r="DO2" s="8"/>
       <c r="DP2" s="8"/>
+      <c r="DQ2" s="8"/>
+      <c r="DR2" s="8"/>
+      <c r="DS2" s="8"/>
+      <c r="DT2" s="8"/>
+      <c r="DU2" s="8"/>
+      <c r="DV2" s="8"/>
+      <c r="DW2" s="8"/>
+      <c r="DX2" s="8"/>
+      <c r="DY2" s="8"/>
+      <c r="DZ2" s="8"/>
+      <c r="EA2" s="8"/>
+      <c r="EB2" s="8"/>
+      <c r="EC2" s="8"/>
+      <c r="ED2" s="8"/>
+      <c r="EE2" s="8"/>
+      <c r="EF2" s="8"/>
     </row>
-    <row r="3" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -6984,8 +8169,24 @@
       <c r="DN3" s="8"/>
       <c r="DO3" s="8"/>
       <c r="DP3" s="8"/>
+      <c r="DQ3" s="8"/>
+      <c r="DR3" s="8"/>
+      <c r="DS3" s="8"/>
+      <c r="DT3" s="8"/>
+      <c r="DU3" s="8"/>
+      <c r="DV3" s="8"/>
+      <c r="DW3" s="8"/>
+      <c r="DX3" s="8"/>
+      <c r="DY3" s="8"/>
+      <c r="DZ3" s="8"/>
+      <c r="EA3" s="8"/>
+      <c r="EB3" s="8"/>
+      <c r="EC3" s="8"/>
+      <c r="ED3" s="8"/>
+      <c r="EE3" s="8"/>
+      <c r="EF3" s="8"/>
     </row>
-    <row r="4" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -7106,8 +8307,24 @@
       <c r="DN4" s="8"/>
       <c r="DO4" s="8"/>
       <c r="DP4" s="8"/>
+      <c r="DQ4" s="8"/>
+      <c r="DR4" s="8"/>
+      <c r="DS4" s="8"/>
+      <c r="DT4" s="8"/>
+      <c r="DU4" s="8"/>
+      <c r="DV4" s="8"/>
+      <c r="DW4" s="8"/>
+      <c r="DX4" s="8"/>
+      <c r="DY4" s="8"/>
+      <c r="DZ4" s="8"/>
+      <c r="EA4" s="8"/>
+      <c r="EB4" s="8"/>
+      <c r="EC4" s="8"/>
+      <c r="ED4" s="8"/>
+      <c r="EE4" s="8"/>
+      <c r="EF4" s="8"/>
     </row>
-    <row r="5" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -7228,8 +8445,24 @@
       <c r="DN5" s="8"/>
       <c r="DO5" s="8"/>
       <c r="DP5" s="8"/>
+      <c r="DQ5" s="8"/>
+      <c r="DR5" s="8"/>
+      <c r="DS5" s="8"/>
+      <c r="DT5" s="8"/>
+      <c r="DU5" s="8"/>
+      <c r="DV5" s="8"/>
+      <c r="DW5" s="8"/>
+      <c r="DX5" s="8"/>
+      <c r="DY5" s="8"/>
+      <c r="DZ5" s="8"/>
+      <c r="EA5" s="8"/>
+      <c r="EB5" s="8"/>
+      <c r="EC5" s="8"/>
+      <c r="ED5" s="8"/>
+      <c r="EE5" s="8"/>
+      <c r="EF5" s="8"/>
     </row>
-    <row r="6" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -7350,8 +8583,24 @@
       <c r="DN6" s="8"/>
       <c r="DO6" s="8"/>
       <c r="DP6" s="8"/>
+      <c r="DQ6" s="8"/>
+      <c r="DR6" s="8"/>
+      <c r="DS6" s="8"/>
+      <c r="DT6" s="8"/>
+      <c r="DU6" s="8"/>
+      <c r="DV6" s="8"/>
+      <c r="DW6" s="8"/>
+      <c r="DX6" s="8"/>
+      <c r="DY6" s="8"/>
+      <c r="DZ6" s="8"/>
+      <c r="EA6" s="8"/>
+      <c r="EB6" s="8"/>
+      <c r="EC6" s="8"/>
+      <c r="ED6" s="8"/>
+      <c r="EE6" s="8"/>
+      <c r="EF6" s="8"/>
     </row>
-    <row r="7" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -7472,8 +8721,24 @@
       <c r="DN7" s="8"/>
       <c r="DO7" s="8"/>
       <c r="DP7" s="8"/>
+      <c r="DQ7" s="8"/>
+      <c r="DR7" s="8"/>
+      <c r="DS7" s="8"/>
+      <c r="DT7" s="8"/>
+      <c r="DU7" s="8"/>
+      <c r="DV7" s="8"/>
+      <c r="DW7" s="8"/>
+      <c r="DX7" s="8"/>
+      <c r="DY7" s="8"/>
+      <c r="DZ7" s="8"/>
+      <c r="EA7" s="8"/>
+      <c r="EB7" s="8"/>
+      <c r="EC7" s="8"/>
+      <c r="ED7" s="8"/>
+      <c r="EE7" s="8"/>
+      <c r="EF7" s="8"/>
     </row>
-    <row r="8" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -7594,8 +8859,24 @@
       <c r="DN8" s="8"/>
       <c r="DO8" s="8"/>
       <c r="DP8" s="8"/>
+      <c r="DQ8" s="8"/>
+      <c r="DR8" s="8"/>
+      <c r="DS8" s="8"/>
+      <c r="DT8" s="8"/>
+      <c r="DU8" s="8"/>
+      <c r="DV8" s="8"/>
+      <c r="DW8" s="8"/>
+      <c r="DX8" s="8"/>
+      <c r="DY8" s="8"/>
+      <c r="DZ8" s="8"/>
+      <c r="EA8" s="8"/>
+      <c r="EB8" s="8"/>
+      <c r="EC8" s="8"/>
+      <c r="ED8" s="8"/>
+      <c r="EE8" s="8"/>
+      <c r="EF8" s="8"/>
     </row>
-    <row r="9" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -7716,8 +8997,24 @@
       <c r="DN9" s="8"/>
       <c r="DO9" s="8"/>
       <c r="DP9" s="8"/>
+      <c r="DQ9" s="8"/>
+      <c r="DR9" s="8"/>
+      <c r="DS9" s="8"/>
+      <c r="DT9" s="8"/>
+      <c r="DU9" s="8"/>
+      <c r="DV9" s="8"/>
+      <c r="DW9" s="8"/>
+      <c r="DX9" s="8"/>
+      <c r="DY9" s="8"/>
+      <c r="DZ9" s="8"/>
+      <c r="EA9" s="8"/>
+      <c r="EB9" s="8"/>
+      <c r="EC9" s="8"/>
+      <c r="ED9" s="8"/>
+      <c r="EE9" s="8"/>
+      <c r="EF9" s="8"/>
     </row>
-    <row r="10" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -7838,8 +9135,24 @@
       <c r="DN10" s="8"/>
       <c r="DO10" s="8"/>
       <c r="DP10" s="8"/>
+      <c r="DQ10" s="8"/>
+      <c r="DR10" s="8"/>
+      <c r="DS10" s="8"/>
+      <c r="DT10" s="8"/>
+      <c r="DU10" s="8"/>
+      <c r="DV10" s="8"/>
+      <c r="DW10" s="8"/>
+      <c r="DX10" s="8"/>
+      <c r="DY10" s="8"/>
+      <c r="DZ10" s="8"/>
+      <c r="EA10" s="8"/>
+      <c r="EB10" s="8"/>
+      <c r="EC10" s="8"/>
+      <c r="ED10" s="8"/>
+      <c r="EE10" s="8"/>
+      <c r="EF10" s="8"/>
     </row>
-    <row r="11" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>2</v>
       </c>
@@ -7877,151 +9190,175 @@
       <c r="W11" s="8"/>
       <c r="X11" s="8"/>
       <c r="Y11" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Z11" s="8"/>
       <c r="AA11" s="8"/>
       <c r="AB11" s="8"/>
       <c r="AC11" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AD11" s="8"/>
       <c r="AE11" s="8"/>
       <c r="AF11" s="8"/>
       <c r="AG11" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AH11" s="8"/>
       <c r="AI11" s="8"/>
       <c r="AJ11" s="8"/>
       <c r="AK11" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AL11" s="8"/>
       <c r="AM11" s="8"/>
       <c r="AN11" s="8"/>
       <c r="AO11" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AP11" s="8"/>
       <c r="AQ11" s="8"/>
       <c r="AR11" s="8"/>
       <c r="AS11" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AT11" s="8"/>
       <c r="AU11" s="8"/>
       <c r="AV11" s="8"/>
       <c r="AW11" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AX11" s="8"/>
       <c r="AY11" s="8"/>
       <c r="AZ11" s="8"/>
       <c r="BA11" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="BB11" s="8"/>
       <c r="BC11" s="8"/>
       <c r="BD11" s="8"/>
       <c r="BE11" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="BF11" s="8"/>
       <c r="BG11" s="8"/>
       <c r="BH11" s="8"/>
       <c r="BI11" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="BJ11" s="8"/>
       <c r="BK11" s="8"/>
       <c r="BL11" s="8"/>
       <c r="BM11" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="BN11" s="8"/>
       <c r="BO11" s="8"/>
       <c r="BP11" s="8"/>
       <c r="BQ11" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="BR11" s="8"/>
       <c r="BS11" s="8"/>
       <c r="BT11" s="8"/>
       <c r="BU11" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="BV11" s="8"/>
       <c r="BW11" s="8"/>
       <c r="BX11" s="8"/>
       <c r="BY11" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="BZ11" s="8"/>
       <c r="CA11" s="8"/>
       <c r="CB11" s="8"/>
       <c r="CC11" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="CD11" s="8"/>
       <c r="CE11" s="8"/>
       <c r="CF11" s="8"/>
       <c r="CG11" s="7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="CH11" s="8"/>
       <c r="CI11" s="8"/>
       <c r="CJ11" s="8"/>
       <c r="CK11" s="7" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="CL11" s="8"/>
       <c r="CM11" s="8"/>
       <c r="CN11" s="8"/>
       <c r="CO11" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="CP11" s="8"/>
       <c r="CQ11" s="8"/>
       <c r="CR11" s="8"/>
       <c r="CS11" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="CT11" s="8"/>
       <c r="CU11" s="8"/>
       <c r="CV11" s="8"/>
       <c r="CW11" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="CX11" s="8"/>
       <c r="CY11" s="8"/>
       <c r="CZ11" s="8"/>
       <c r="DA11" s="7" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="DB11" s="8"/>
       <c r="DC11" s="8"/>
       <c r="DD11" s="8"/>
       <c r="DE11" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="DF11" s="8"/>
       <c r="DG11" s="8"/>
       <c r="DH11" s="8"/>
       <c r="DI11" s="7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="DJ11" s="8"/>
       <c r="DK11" s="8"/>
       <c r="DL11" s="8"/>
       <c r="DM11" s="7" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="DN11" s="8"/>
       <c r="DO11" s="8"/>
       <c r="DP11" s="8"/>
+      <c r="DQ11" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="DR11" s="8"/>
+      <c r="DS11" s="8"/>
+      <c r="DT11" s="8"/>
+      <c r="DU11" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="DV11" s="8"/>
+      <c r="DW11" s="8"/>
+      <c r="DX11" s="8"/>
+      <c r="DY11" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="DZ11" s="8"/>
+      <c r="EA11" s="8"/>
+      <c r="EB11" s="8"/>
+      <c r="EC11" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="ED11" s="8"/>
+      <c r="EE11" s="8"/>
+      <c r="EF11" s="8"/>
     </row>
-    <row r="12" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -8142,8 +9479,24 @@
       <c r="DN12" s="8"/>
       <c r="DO12" s="8"/>
       <c r="DP12" s="8"/>
+      <c r="DQ12" s="8"/>
+      <c r="DR12" s="8"/>
+      <c r="DS12" s="8"/>
+      <c r="DT12" s="8"/>
+      <c r="DU12" s="8"/>
+      <c r="DV12" s="8"/>
+      <c r="DW12" s="8"/>
+      <c r="DX12" s="8"/>
+      <c r="DY12" s="8"/>
+      <c r="DZ12" s="8"/>
+      <c r="EA12" s="8"/>
+      <c r="EB12" s="8"/>
+      <c r="EC12" s="8"/>
+      <c r="ED12" s="8"/>
+      <c r="EE12" s="8"/>
+      <c r="EF12" s="8"/>
     </row>
-    <row r="13" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -8264,8 +9617,24 @@
       <c r="DN13" s="8"/>
       <c r="DO13" s="8"/>
       <c r="DP13" s="8"/>
+      <c r="DQ13" s="8"/>
+      <c r="DR13" s="8"/>
+      <c r="DS13" s="8"/>
+      <c r="DT13" s="8"/>
+      <c r="DU13" s="8"/>
+      <c r="DV13" s="8"/>
+      <c r="DW13" s="8"/>
+      <c r="DX13" s="8"/>
+      <c r="DY13" s="8"/>
+      <c r="DZ13" s="8"/>
+      <c r="EA13" s="8"/>
+      <c r="EB13" s="8"/>
+      <c r="EC13" s="8"/>
+      <c r="ED13" s="8"/>
+      <c r="EE13" s="8"/>
+      <c r="EF13" s="8"/>
     </row>
-    <row r="14" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -8386,8 +9755,24 @@
       <c r="DN14" s="8"/>
       <c r="DO14" s="8"/>
       <c r="DP14" s="8"/>
+      <c r="DQ14" s="8"/>
+      <c r="DR14" s="8"/>
+      <c r="DS14" s="8"/>
+      <c r="DT14" s="8"/>
+      <c r="DU14" s="8"/>
+      <c r="DV14" s="8"/>
+      <c r="DW14" s="8"/>
+      <c r="DX14" s="8"/>
+      <c r="DY14" s="8"/>
+      <c r="DZ14" s="8"/>
+      <c r="EA14" s="8"/>
+      <c r="EB14" s="8"/>
+      <c r="EC14" s="8"/>
+      <c r="ED14" s="8"/>
+      <c r="EE14" s="8"/>
+      <c r="EF14" s="8"/>
     </row>
-    <row r="15" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -8508,8 +9893,24 @@
       <c r="DN15" s="8"/>
       <c r="DO15" s="8"/>
       <c r="DP15" s="8"/>
+      <c r="DQ15" s="8"/>
+      <c r="DR15" s="8"/>
+      <c r="DS15" s="8"/>
+      <c r="DT15" s="8"/>
+      <c r="DU15" s="8"/>
+      <c r="DV15" s="8"/>
+      <c r="DW15" s="8"/>
+      <c r="DX15" s="8"/>
+      <c r="DY15" s="8"/>
+      <c r="DZ15" s="8"/>
+      <c r="EA15" s="8"/>
+      <c r="EB15" s="8"/>
+      <c r="EC15" s="8"/>
+      <c r="ED15" s="8"/>
+      <c r="EE15" s="8"/>
+      <c r="EF15" s="8"/>
     </row>
-    <row r="16" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -8630,8 +10031,24 @@
       <c r="DN16" s="8"/>
       <c r="DO16" s="8"/>
       <c r="DP16" s="8"/>
+      <c r="DQ16" s="8"/>
+      <c r="DR16" s="8"/>
+      <c r="DS16" s="8"/>
+      <c r="DT16" s="8"/>
+      <c r="DU16" s="8"/>
+      <c r="DV16" s="8"/>
+      <c r="DW16" s="8"/>
+      <c r="DX16" s="8"/>
+      <c r="DY16" s="8"/>
+      <c r="DZ16" s="8"/>
+      <c r="EA16" s="8"/>
+      <c r="EB16" s="8"/>
+      <c r="EC16" s="8"/>
+      <c r="ED16" s="8"/>
+      <c r="EE16" s="8"/>
+      <c r="EF16" s="8"/>
     </row>
-    <row r="17" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -8752,8 +10169,24 @@
       <c r="DN17" s="8"/>
       <c r="DO17" s="8"/>
       <c r="DP17" s="8"/>
+      <c r="DQ17" s="8"/>
+      <c r="DR17" s="8"/>
+      <c r="DS17" s="8"/>
+      <c r="DT17" s="8"/>
+      <c r="DU17" s="8"/>
+      <c r="DV17" s="8"/>
+      <c r="DW17" s="8"/>
+      <c r="DX17" s="8"/>
+      <c r="DY17" s="8"/>
+      <c r="DZ17" s="8"/>
+      <c r="EA17" s="8"/>
+      <c r="EB17" s="8"/>
+      <c r="EC17" s="8"/>
+      <c r="ED17" s="8"/>
+      <c r="EE17" s="8"/>
+      <c r="EF17" s="8"/>
     </row>
-    <row r="18" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -8874,8 +10307,24 @@
       <c r="DN18" s="8"/>
       <c r="DO18" s="8"/>
       <c r="DP18" s="8"/>
+      <c r="DQ18" s="8"/>
+      <c r="DR18" s="8"/>
+      <c r="DS18" s="8"/>
+      <c r="DT18" s="8"/>
+      <c r="DU18" s="8"/>
+      <c r="DV18" s="8"/>
+      <c r="DW18" s="8"/>
+      <c r="DX18" s="8"/>
+      <c r="DY18" s="8"/>
+      <c r="DZ18" s="8"/>
+      <c r="EA18" s="8"/>
+      <c r="EB18" s="8"/>
+      <c r="EC18" s="8"/>
+      <c r="ED18" s="8"/>
+      <c r="EE18" s="8"/>
+      <c r="EF18" s="8"/>
     </row>
-    <row r="19" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -8996,8 +10445,24 @@
       <c r="DN19" s="8"/>
       <c r="DO19" s="8"/>
       <c r="DP19" s="8"/>
+      <c r="DQ19" s="8"/>
+      <c r="DR19" s="8"/>
+      <c r="DS19" s="8"/>
+      <c r="DT19" s="8"/>
+      <c r="DU19" s="8"/>
+      <c r="DV19" s="8"/>
+      <c r="DW19" s="8"/>
+      <c r="DX19" s="8"/>
+      <c r="DY19" s="8"/>
+      <c r="DZ19" s="8"/>
+      <c r="EA19" s="8"/>
+      <c r="EB19" s="8"/>
+      <c r="EC19" s="8"/>
+      <c r="ED19" s="8"/>
+      <c r="EE19" s="8"/>
+      <c r="EF19" s="8"/>
     </row>
-    <row r="20" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -9118,8 +10583,24 @@
       <c r="DN20" s="8"/>
       <c r="DO20" s="8"/>
       <c r="DP20" s="8"/>
+      <c r="DQ20" s="8"/>
+      <c r="DR20" s="8"/>
+      <c r="DS20" s="8"/>
+      <c r="DT20" s="8"/>
+      <c r="DU20" s="8"/>
+      <c r="DV20" s="8"/>
+      <c r="DW20" s="8"/>
+      <c r="DX20" s="8"/>
+      <c r="DY20" s="8"/>
+      <c r="DZ20" s="8"/>
+      <c r="EA20" s="8"/>
+      <c r="EB20" s="8"/>
+      <c r="EC20" s="8"/>
+      <c r="ED20" s="8"/>
+      <c r="EE20" s="8"/>
+      <c r="EF20" s="8"/>
     </row>
-    <row r="21" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>4</v>
       </c>
@@ -9139,7 +10620,7 @@
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N21" s="8"/>
       <c r="O21" s="8"/>
@@ -9157,151 +10638,175 @@
       <c r="W21" s="8"/>
       <c r="X21" s="8"/>
       <c r="Y21" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z21" s="8"/>
       <c r="AA21" s="8"/>
       <c r="AB21" s="8"/>
       <c r="AC21" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AD21" s="8"/>
       <c r="AE21" s="8"/>
       <c r="AF21" s="8"/>
       <c r="AG21" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AH21" s="8"/>
       <c r="AI21" s="8"/>
       <c r="AJ21" s="8"/>
       <c r="AK21" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AL21" s="8"/>
       <c r="AM21" s="8"/>
       <c r="AN21" s="8"/>
       <c r="AO21" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AP21" s="8"/>
       <c r="AQ21" s="8"/>
       <c r="AR21" s="8"/>
       <c r="AS21" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AT21" s="8"/>
       <c r="AU21" s="8"/>
       <c r="AV21" s="8"/>
       <c r="AW21" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AX21" s="8"/>
       <c r="AY21" s="8"/>
       <c r="AZ21" s="8"/>
       <c r="BA21" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="BB21" s="8"/>
       <c r="BC21" s="8"/>
       <c r="BD21" s="8"/>
       <c r="BE21" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BF21" s="8"/>
       <c r="BG21" s="8"/>
       <c r="BH21" s="8"/>
       <c r="BI21" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="BJ21" s="8"/>
       <c r="BK21" s="8"/>
       <c r="BL21" s="8"/>
       <c r="BM21" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="BN21" s="8"/>
       <c r="BO21" s="8"/>
       <c r="BP21" s="8"/>
       <c r="BQ21" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="BR21" s="8"/>
       <c r="BS21" s="8"/>
       <c r="BT21" s="8"/>
       <c r="BU21" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="BV21" s="8"/>
       <c r="BW21" s="8"/>
       <c r="BX21" s="8"/>
       <c r="BY21" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="BZ21" s="8"/>
       <c r="CA21" s="8"/>
       <c r="CB21" s="8"/>
       <c r="CC21" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="CD21" s="8"/>
       <c r="CE21" s="8"/>
       <c r="CF21" s="8"/>
       <c r="CG21" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="CH21" s="8"/>
       <c r="CI21" s="8"/>
       <c r="CJ21" s="8"/>
       <c r="CK21" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="CL21" s="8"/>
       <c r="CM21" s="8"/>
       <c r="CN21" s="8"/>
       <c r="CO21" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="CP21" s="8"/>
       <c r="CQ21" s="8"/>
       <c r="CR21" s="8"/>
       <c r="CS21" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="CT21" s="8"/>
       <c r="CU21" s="8"/>
       <c r="CV21" s="8"/>
       <c r="CW21" s="7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="CX21" s="8"/>
       <c r="CY21" s="8"/>
       <c r="CZ21" s="8"/>
       <c r="DA21" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="DB21" s="8"/>
       <c r="DC21" s="8"/>
       <c r="DD21" s="8"/>
       <c r="DE21" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="DF21" s="8"/>
       <c r="DG21" s="8"/>
       <c r="DH21" s="8"/>
       <c r="DI21" s="7" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="DJ21" s="8"/>
       <c r="DK21" s="8"/>
       <c r="DL21" s="8"/>
       <c r="DM21" s="7" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="DN21" s="8"/>
       <c r="DO21" s="8"/>
       <c r="DP21" s="8"/>
+      <c r="DQ21" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="DR21" s="8"/>
+      <c r="DS21" s="8"/>
+      <c r="DT21" s="8"/>
+      <c r="DU21" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="DV21" s="8"/>
+      <c r="DW21" s="8"/>
+      <c r="DX21" s="8"/>
+      <c r="DY21" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="DZ21" s="8"/>
+      <c r="EA21" s="8"/>
+      <c r="EB21" s="8"/>
+      <c r="EC21" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="ED21" s="8"/>
+      <c r="EE21" s="8"/>
+      <c r="EF21" s="8"/>
     </row>
-    <row r="22" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -9422,8 +10927,24 @@
       <c r="DN22" s="8"/>
       <c r="DO22" s="8"/>
       <c r="DP22" s="8"/>
+      <c r="DQ22" s="8"/>
+      <c r="DR22" s="8"/>
+      <c r="DS22" s="8"/>
+      <c r="DT22" s="8"/>
+      <c r="DU22" s="8"/>
+      <c r="DV22" s="8"/>
+      <c r="DW22" s="8"/>
+      <c r="DX22" s="8"/>
+      <c r="DY22" s="8"/>
+      <c r="DZ22" s="8"/>
+      <c r="EA22" s="8"/>
+      <c r="EB22" s="8"/>
+      <c r="EC22" s="8"/>
+      <c r="ED22" s="8"/>
+      <c r="EE22" s="8"/>
+      <c r="EF22" s="8"/>
     </row>
-    <row r="23" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -9544,8 +11065,24 @@
       <c r="DN23" s="8"/>
       <c r="DO23" s="8"/>
       <c r="DP23" s="8"/>
+      <c r="DQ23" s="8"/>
+      <c r="DR23" s="8"/>
+      <c r="DS23" s="8"/>
+      <c r="DT23" s="8"/>
+      <c r="DU23" s="8"/>
+      <c r="DV23" s="8"/>
+      <c r="DW23" s="8"/>
+      <c r="DX23" s="8"/>
+      <c r="DY23" s="8"/>
+      <c r="DZ23" s="8"/>
+      <c r="EA23" s="8"/>
+      <c r="EB23" s="8"/>
+      <c r="EC23" s="8"/>
+      <c r="ED23" s="8"/>
+      <c r="EE23" s="8"/>
+      <c r="EF23" s="8"/>
     </row>
-    <row r="24" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -9666,8 +11203,24 @@
       <c r="DN24" s="8"/>
       <c r="DO24" s="8"/>
       <c r="DP24" s="8"/>
+      <c r="DQ24" s="8"/>
+      <c r="DR24" s="8"/>
+      <c r="DS24" s="8"/>
+      <c r="DT24" s="8"/>
+      <c r="DU24" s="8"/>
+      <c r="DV24" s="8"/>
+      <c r="DW24" s="8"/>
+      <c r="DX24" s="8"/>
+      <c r="DY24" s="8"/>
+      <c r="DZ24" s="8"/>
+      <c r="EA24" s="8"/>
+      <c r="EB24" s="8"/>
+      <c r="EC24" s="8"/>
+      <c r="ED24" s="8"/>
+      <c r="EE24" s="8"/>
+      <c r="EF24" s="8"/>
     </row>
-    <row r="25" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -9788,8 +11341,24 @@
       <c r="DN25" s="8"/>
       <c r="DO25" s="8"/>
       <c r="DP25" s="8"/>
+      <c r="DQ25" s="8"/>
+      <c r="DR25" s="8"/>
+      <c r="DS25" s="8"/>
+      <c r="DT25" s="8"/>
+      <c r="DU25" s="8"/>
+      <c r="DV25" s="8"/>
+      <c r="DW25" s="8"/>
+      <c r="DX25" s="8"/>
+      <c r="DY25" s="8"/>
+      <c r="DZ25" s="8"/>
+      <c r="EA25" s="8"/>
+      <c r="EB25" s="8"/>
+      <c r="EC25" s="8"/>
+      <c r="ED25" s="8"/>
+      <c r="EE25" s="8"/>
+      <c r="EF25" s="8"/>
     </row>
-    <row r="26" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -9910,8 +11479,24 @@
       <c r="DN26" s="8"/>
       <c r="DO26" s="8"/>
       <c r="DP26" s="8"/>
+      <c r="DQ26" s="8"/>
+      <c r="DR26" s="8"/>
+      <c r="DS26" s="8"/>
+      <c r="DT26" s="8"/>
+      <c r="DU26" s="8"/>
+      <c r="DV26" s="8"/>
+      <c r="DW26" s="8"/>
+      <c r="DX26" s="8"/>
+      <c r="DY26" s="8"/>
+      <c r="DZ26" s="8"/>
+      <c r="EA26" s="8"/>
+      <c r="EB26" s="8"/>
+      <c r="EC26" s="8"/>
+      <c r="ED26" s="8"/>
+      <c r="EE26" s="8"/>
+      <c r="EF26" s="8"/>
     </row>
-    <row r="27" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -10032,8 +11617,24 @@
       <c r="DN27" s="8"/>
       <c r="DO27" s="8"/>
       <c r="DP27" s="8"/>
+      <c r="DQ27" s="8"/>
+      <c r="DR27" s="8"/>
+      <c r="DS27" s="8"/>
+      <c r="DT27" s="8"/>
+      <c r="DU27" s="8"/>
+      <c r="DV27" s="8"/>
+      <c r="DW27" s="8"/>
+      <c r="DX27" s="8"/>
+      <c r="DY27" s="8"/>
+      <c r="DZ27" s="8"/>
+      <c r="EA27" s="8"/>
+      <c r="EB27" s="8"/>
+      <c r="EC27" s="8"/>
+      <c r="ED27" s="8"/>
+      <c r="EE27" s="8"/>
+      <c r="EF27" s="8"/>
     </row>
-    <row r="28" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -10154,8 +11755,24 @@
       <c r="DN28" s="8"/>
       <c r="DO28" s="8"/>
       <c r="DP28" s="8"/>
+      <c r="DQ28" s="8"/>
+      <c r="DR28" s="8"/>
+      <c r="DS28" s="8"/>
+      <c r="DT28" s="8"/>
+      <c r="DU28" s="8"/>
+      <c r="DV28" s="8"/>
+      <c r="DW28" s="8"/>
+      <c r="DX28" s="8"/>
+      <c r="DY28" s="8"/>
+      <c r="DZ28" s="8"/>
+      <c r="EA28" s="8"/>
+      <c r="EB28" s="8"/>
+      <c r="EC28" s="8"/>
+      <c r="ED28" s="8"/>
+      <c r="EE28" s="8"/>
+      <c r="EF28" s="8"/>
     </row>
-    <row r="29" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -10276,8 +11893,24 @@
       <c r="DN29" s="8"/>
       <c r="DO29" s="8"/>
       <c r="DP29" s="8"/>
+      <c r="DQ29" s="8"/>
+      <c r="DR29" s="8"/>
+      <c r="DS29" s="8"/>
+      <c r="DT29" s="8"/>
+      <c r="DU29" s="8"/>
+      <c r="DV29" s="8"/>
+      <c r="DW29" s="8"/>
+      <c r="DX29" s="8"/>
+      <c r="DY29" s="8"/>
+      <c r="DZ29" s="8"/>
+      <c r="EA29" s="8"/>
+      <c r="EB29" s="8"/>
+      <c r="EC29" s="8"/>
+      <c r="ED29" s="8"/>
+      <c r="EE29" s="8"/>
+      <c r="EF29" s="8"/>
     </row>
-    <row r="30" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -10398,8 +12031,24 @@
       <c r="DN30" s="8"/>
       <c r="DO30" s="8"/>
       <c r="DP30" s="8"/>
+      <c r="DQ30" s="8"/>
+      <c r="DR30" s="8"/>
+      <c r="DS30" s="8"/>
+      <c r="DT30" s="8"/>
+      <c r="DU30" s="8"/>
+      <c r="DV30" s="8"/>
+      <c r="DW30" s="8"/>
+      <c r="DX30" s="8"/>
+      <c r="DY30" s="8"/>
+      <c r="DZ30" s="8"/>
+      <c r="EA30" s="8"/>
+      <c r="EB30" s="8"/>
+      <c r="EC30" s="8"/>
+      <c r="ED30" s="8"/>
+      <c r="EE30" s="8"/>
+      <c r="EF30" s="8"/>
     </row>
-    <row r="31" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>13</v>
       </c>
@@ -10437,147 +12086,175 @@
       <c r="W31" s="8"/>
       <c r="X31" s="8"/>
       <c r="Y31" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Z31" s="8"/>
       <c r="AA31" s="8"/>
       <c r="AB31" s="8"/>
       <c r="AC31" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AD31" s="8"/>
       <c r="AE31" s="8"/>
       <c r="AF31" s="8"/>
       <c r="AG31" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AH31" s="8"/>
       <c r="AI31" s="8"/>
       <c r="AJ31" s="8"/>
       <c r="AK31" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AL31" s="8"/>
       <c r="AM31" s="8"/>
       <c r="AN31" s="8"/>
       <c r="AO31" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AP31" s="8"/>
       <c r="AQ31" s="8"/>
       <c r="AR31" s="8"/>
       <c r="AS31" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AT31" s="8"/>
       <c r="AU31" s="8"/>
       <c r="AV31" s="8"/>
       <c r="AW31" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AX31" s="8"/>
       <c r="AY31" s="8"/>
       <c r="AZ31" s="8"/>
       <c r="BA31" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="BB31" s="8"/>
       <c r="BC31" s="8"/>
       <c r="BD31" s="8"/>
       <c r="BE31" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="BF31" s="8"/>
       <c r="BG31" s="8"/>
       <c r="BH31" s="8"/>
       <c r="BI31" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="BJ31" s="8"/>
       <c r="BK31" s="8"/>
       <c r="BL31" s="8"/>
       <c r="BM31" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="BN31" s="8"/>
       <c r="BO31" s="8"/>
       <c r="BP31" s="8"/>
       <c r="BQ31" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="BR31" s="8"/>
       <c r="BS31" s="8"/>
       <c r="BT31" s="8"/>
       <c r="BU31" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="BV31" s="8"/>
       <c r="BW31" s="8"/>
       <c r="BX31" s="8"/>
       <c r="BY31" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="BZ31" s="8"/>
       <c r="CA31" s="8"/>
       <c r="CB31" s="8"/>
       <c r="CC31" s="7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="CD31" s="8"/>
       <c r="CE31" s="8"/>
       <c r="CF31" s="8"/>
       <c r="CG31" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="CH31" s="8"/>
       <c r="CI31" s="8"/>
       <c r="CJ31" s="8"/>
       <c r="CK31" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="CL31" s="8"/>
       <c r="CM31" s="8"/>
       <c r="CN31" s="8"/>
       <c r="CO31" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="CP31" s="8"/>
       <c r="CQ31" s="8"/>
       <c r="CR31" s="8"/>
       <c r="CS31" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="CT31" s="8"/>
       <c r="CU31" s="8"/>
       <c r="CV31" s="8"/>
       <c r="CW31" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="CX31" s="8"/>
       <c r="CY31" s="8"/>
       <c r="CZ31" s="8"/>
       <c r="DA31" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="DB31" s="8"/>
       <c r="DC31" s="8"/>
       <c r="DD31" s="8"/>
       <c r="DE31" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="DF31" s="8"/>
       <c r="DG31" s="8"/>
       <c r="DH31" s="8"/>
-      <c r="DI31" s="7"/>
+      <c r="DI31" s="7" t="s">
+        <v>292</v>
+      </c>
       <c r="DJ31" s="8"/>
       <c r="DK31" s="8"/>
       <c r="DL31" s="8"/>
-      <c r="DM31" s="7"/>
+      <c r="DM31" s="7" t="s">
+        <v>290</v>
+      </c>
       <c r="DN31" s="8"/>
       <c r="DO31" s="8"/>
       <c r="DP31" s="8"/>
+      <c r="DQ31" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="DR31" s="8"/>
+      <c r="DS31" s="8"/>
+      <c r="DT31" s="8"/>
+      <c r="DU31" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="DV31" s="8"/>
+      <c r="DW31" s="8"/>
+      <c r="DX31" s="8"/>
+      <c r="DY31" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="DZ31" s="8"/>
+      <c r="EA31" s="8"/>
+      <c r="EB31" s="8"/>
+      <c r="EC31" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="ED31" s="8"/>
+      <c r="EE31" s="8"/>
+      <c r="EF31" s="8"/>
     </row>
-    <row r="32" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -10698,8 +12375,24 @@
       <c r="DN32" s="8"/>
       <c r="DO32" s="8"/>
       <c r="DP32" s="8"/>
+      <c r="DQ32" s="8"/>
+      <c r="DR32" s="8"/>
+      <c r="DS32" s="8"/>
+      <c r="DT32" s="8"/>
+      <c r="DU32" s="8"/>
+      <c r="DV32" s="8"/>
+      <c r="DW32" s="8"/>
+      <c r="DX32" s="8"/>
+      <c r="DY32" s="8"/>
+      <c r="DZ32" s="8"/>
+      <c r="EA32" s="8"/>
+      <c r="EB32" s="8"/>
+      <c r="EC32" s="8"/>
+      <c r="ED32" s="8"/>
+      <c r="EE32" s="8"/>
+      <c r="EF32" s="8"/>
     </row>
-    <row r="33" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -10820,8 +12513,24 @@
       <c r="DN33" s="8"/>
       <c r="DO33" s="8"/>
       <c r="DP33" s="8"/>
+      <c r="DQ33" s="8"/>
+      <c r="DR33" s="8"/>
+      <c r="DS33" s="8"/>
+      <c r="DT33" s="8"/>
+      <c r="DU33" s="8"/>
+      <c r="DV33" s="8"/>
+      <c r="DW33" s="8"/>
+      <c r="DX33" s="8"/>
+      <c r="DY33" s="8"/>
+      <c r="DZ33" s="8"/>
+      <c r="EA33" s="8"/>
+      <c r="EB33" s="8"/>
+      <c r="EC33" s="8"/>
+      <c r="ED33" s="8"/>
+      <c r="EE33" s="8"/>
+      <c r="EF33" s="8"/>
     </row>
-    <row r="34" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -10942,8 +12651,24 @@
       <c r="DN34" s="8"/>
       <c r="DO34" s="8"/>
       <c r="DP34" s="8"/>
+      <c r="DQ34" s="8"/>
+      <c r="DR34" s="8"/>
+      <c r="DS34" s="8"/>
+      <c r="DT34" s="8"/>
+      <c r="DU34" s="8"/>
+      <c r="DV34" s="8"/>
+      <c r="DW34" s="8"/>
+      <c r="DX34" s="8"/>
+      <c r="DY34" s="8"/>
+      <c r="DZ34" s="8"/>
+      <c r="EA34" s="8"/>
+      <c r="EB34" s="8"/>
+      <c r="EC34" s="8"/>
+      <c r="ED34" s="8"/>
+      <c r="EE34" s="8"/>
+      <c r="EF34" s="8"/>
     </row>
-    <row r="35" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -11064,8 +12789,24 @@
       <c r="DN35" s="8"/>
       <c r="DO35" s="8"/>
       <c r="DP35" s="8"/>
+      <c r="DQ35" s="8"/>
+      <c r="DR35" s="8"/>
+      <c r="DS35" s="8"/>
+      <c r="DT35" s="8"/>
+      <c r="DU35" s="8"/>
+      <c r="DV35" s="8"/>
+      <c r="DW35" s="8"/>
+      <c r="DX35" s="8"/>
+      <c r="DY35" s="8"/>
+      <c r="DZ35" s="8"/>
+      <c r="EA35" s="8"/>
+      <c r="EB35" s="8"/>
+      <c r="EC35" s="8"/>
+      <c r="ED35" s="8"/>
+      <c r="EE35" s="8"/>
+      <c r="EF35" s="8"/>
     </row>
-    <row r="36" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -11186,8 +12927,24 @@
       <c r="DN36" s="8"/>
       <c r="DO36" s="8"/>
       <c r="DP36" s="8"/>
+      <c r="DQ36" s="8"/>
+      <c r="DR36" s="8"/>
+      <c r="DS36" s="8"/>
+      <c r="DT36" s="8"/>
+      <c r="DU36" s="8"/>
+      <c r="DV36" s="8"/>
+      <c r="DW36" s="8"/>
+      <c r="DX36" s="8"/>
+      <c r="DY36" s="8"/>
+      <c r="DZ36" s="8"/>
+      <c r="EA36" s="8"/>
+      <c r="EB36" s="8"/>
+      <c r="EC36" s="8"/>
+      <c r="ED36" s="8"/>
+      <c r="EE36" s="8"/>
+      <c r="EF36" s="8"/>
     </row>
-    <row r="37" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -11308,8 +13065,24 @@
       <c r="DN37" s="8"/>
       <c r="DO37" s="8"/>
       <c r="DP37" s="8"/>
+      <c r="DQ37" s="8"/>
+      <c r="DR37" s="8"/>
+      <c r="DS37" s="8"/>
+      <c r="DT37" s="8"/>
+      <c r="DU37" s="8"/>
+      <c r="DV37" s="8"/>
+      <c r="DW37" s="8"/>
+      <c r="DX37" s="8"/>
+      <c r="DY37" s="8"/>
+      <c r="DZ37" s="8"/>
+      <c r="EA37" s="8"/>
+      <c r="EB37" s="8"/>
+      <c r="EC37" s="8"/>
+      <c r="ED37" s="8"/>
+      <c r="EE37" s="8"/>
+      <c r="EF37" s="8"/>
     </row>
-    <row r="38" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -11430,8 +13203,24 @@
       <c r="DN38" s="8"/>
       <c r="DO38" s="8"/>
       <c r="DP38" s="8"/>
+      <c r="DQ38" s="8"/>
+      <c r="DR38" s="8"/>
+      <c r="DS38" s="8"/>
+      <c r="DT38" s="8"/>
+      <c r="DU38" s="8"/>
+      <c r="DV38" s="8"/>
+      <c r="DW38" s="8"/>
+      <c r="DX38" s="8"/>
+      <c r="DY38" s="8"/>
+      <c r="DZ38" s="8"/>
+      <c r="EA38" s="8"/>
+      <c r="EB38" s="8"/>
+      <c r="EC38" s="8"/>
+      <c r="ED38" s="8"/>
+      <c r="EE38" s="8"/>
+      <c r="EF38" s="8"/>
     </row>
-    <row r="39" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -11552,8 +13341,24 @@
       <c r="DN39" s="8"/>
       <c r="DO39" s="8"/>
       <c r="DP39" s="8"/>
+      <c r="DQ39" s="8"/>
+      <c r="DR39" s="8"/>
+      <c r="DS39" s="8"/>
+      <c r="DT39" s="8"/>
+      <c r="DU39" s="8"/>
+      <c r="DV39" s="8"/>
+      <c r="DW39" s="8"/>
+      <c r="DX39" s="8"/>
+      <c r="DY39" s="8"/>
+      <c r="DZ39" s="8"/>
+      <c r="EA39" s="8"/>
+      <c r="EB39" s="8"/>
+      <c r="EC39" s="8"/>
+      <c r="ED39" s="8"/>
+      <c r="EE39" s="8"/>
+      <c r="EF39" s="8"/>
     </row>
-    <row r="40" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -11674,8 +13479,24 @@
       <c r="DN40" s="8"/>
       <c r="DO40" s="8"/>
       <c r="DP40" s="8"/>
+      <c r="DQ40" s="8"/>
+      <c r="DR40" s="8"/>
+      <c r="DS40" s="8"/>
+      <c r="DT40" s="8"/>
+      <c r="DU40" s="8"/>
+      <c r="DV40" s="8"/>
+      <c r="DW40" s="8"/>
+      <c r="DX40" s="8"/>
+      <c r="DY40" s="8"/>
+      <c r="DZ40" s="8"/>
+      <c r="EA40" s="8"/>
+      <c r="EB40" s="8"/>
+      <c r="EC40" s="8"/>
+      <c r="ED40" s="8"/>
+      <c r="EE40" s="8"/>
+      <c r="EF40" s="8"/>
     </row>
-    <row r="41" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>16</v>
       </c>
@@ -11713,147 +13534,175 @@
       <c r="W41" s="8"/>
       <c r="X41" s="8"/>
       <c r="Y41" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="Z41" s="8"/>
       <c r="AA41" s="8"/>
       <c r="AB41" s="8"/>
       <c r="AC41" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AD41" s="8"/>
       <c r="AE41" s="8"/>
       <c r="AF41" s="8"/>
       <c r="AG41" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AH41" s="8"/>
       <c r="AI41" s="8"/>
       <c r="AJ41" s="8"/>
       <c r="AK41" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AL41" s="8"/>
       <c r="AM41" s="8"/>
       <c r="AN41" s="8"/>
       <c r="AO41" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AP41" s="8"/>
       <c r="AQ41" s="8"/>
       <c r="AR41" s="8"/>
       <c r="AS41" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AT41" s="8"/>
       <c r="AU41" s="8"/>
       <c r="AV41" s="8"/>
       <c r="AW41" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AX41" s="8"/>
       <c r="AY41" s="8"/>
       <c r="AZ41" s="8"/>
       <c r="BA41" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="BB41" s="8"/>
       <c r="BC41" s="8"/>
       <c r="BD41" s="8"/>
       <c r="BE41" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="BF41" s="8"/>
       <c r="BG41" s="8"/>
       <c r="BH41" s="8"/>
       <c r="BI41" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="BJ41" s="8"/>
       <c r="BK41" s="8"/>
       <c r="BL41" s="8"/>
       <c r="BM41" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="BN41" s="8"/>
       <c r="BO41" s="8"/>
       <c r="BP41" s="8"/>
       <c r="BQ41" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="BR41" s="8"/>
       <c r="BS41" s="8"/>
       <c r="BT41" s="8"/>
       <c r="BU41" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="BV41" s="8"/>
       <c r="BW41" s="8"/>
       <c r="BX41" s="8"/>
       <c r="BY41" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="BZ41" s="8"/>
       <c r="CA41" s="8"/>
       <c r="CB41" s="8"/>
       <c r="CC41" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="CD41" s="8"/>
       <c r="CE41" s="8"/>
       <c r="CF41" s="8"/>
       <c r="CG41" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="CH41" s="8"/>
       <c r="CI41" s="8"/>
       <c r="CJ41" s="8"/>
       <c r="CK41" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="CL41" s="8"/>
       <c r="CM41" s="8"/>
       <c r="CN41" s="8"/>
       <c r="CO41" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="CP41" s="8"/>
       <c r="CQ41" s="8"/>
       <c r="CR41" s="8"/>
       <c r="CS41" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="CT41" s="8"/>
       <c r="CU41" s="8"/>
       <c r="CV41" s="8"/>
       <c r="CW41" s="9" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="CX41" s="8"/>
       <c r="CY41" s="8"/>
       <c r="CZ41" s="8"/>
       <c r="DA41" s="7" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="DB41" s="8"/>
       <c r="DC41" s="8"/>
       <c r="DD41" s="8"/>
       <c r="DE41" s="9" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="DF41" s="8"/>
       <c r="DG41" s="8"/>
       <c r="DH41" s="8"/>
-      <c r="DI41" s="7"/>
+      <c r="DI41" s="7" t="s">
+        <v>297</v>
+      </c>
       <c r="DJ41" s="8"/>
       <c r="DK41" s="8"/>
       <c r="DL41" s="8"/>
-      <c r="DM41" s="9"/>
+      <c r="DM41" s="9" t="s">
+        <v>296</v>
+      </c>
       <c r="DN41" s="8"/>
       <c r="DO41" s="8"/>
       <c r="DP41" s="8"/>
+      <c r="DQ41" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="DR41" s="8"/>
+      <c r="DS41" s="8"/>
+      <c r="DT41" s="8"/>
+      <c r="DU41" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="DV41" s="8"/>
+      <c r="DW41" s="8"/>
+      <c r="DX41" s="8"/>
+      <c r="DY41" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="DZ41" s="8"/>
+      <c r="EA41" s="8"/>
+      <c r="EB41" s="8"/>
+      <c r="EC41" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="ED41" s="8"/>
+      <c r="EE41" s="8"/>
+      <c r="EF41" s="8"/>
     </row>
-    <row r="42" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -11974,8 +13823,24 @@
       <c r="DN42" s="8"/>
       <c r="DO42" s="8"/>
       <c r="DP42" s="8"/>
+      <c r="DQ42" s="8"/>
+      <c r="DR42" s="8"/>
+      <c r="DS42" s="8"/>
+      <c r="DT42" s="8"/>
+      <c r="DU42" s="8"/>
+      <c r="DV42" s="8"/>
+      <c r="DW42" s="8"/>
+      <c r="DX42" s="8"/>
+      <c r="DY42" s="8"/>
+      <c r="DZ42" s="8"/>
+      <c r="EA42" s="8"/>
+      <c r="EB42" s="8"/>
+      <c r="EC42" s="8"/>
+      <c r="ED42" s="8"/>
+      <c r="EE42" s="8"/>
+      <c r="EF42" s="8"/>
     </row>
-    <row r="43" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -12096,8 +13961,24 @@
       <c r="DN43" s="8"/>
       <c r="DO43" s="8"/>
       <c r="DP43" s="8"/>
+      <c r="DQ43" s="8"/>
+      <c r="DR43" s="8"/>
+      <c r="DS43" s="8"/>
+      <c r="DT43" s="8"/>
+      <c r="DU43" s="8"/>
+      <c r="DV43" s="8"/>
+      <c r="DW43" s="8"/>
+      <c r="DX43" s="8"/>
+      <c r="DY43" s="8"/>
+      <c r="DZ43" s="8"/>
+      <c r="EA43" s="8"/>
+      <c r="EB43" s="8"/>
+      <c r="EC43" s="8"/>
+      <c r="ED43" s="8"/>
+      <c r="EE43" s="8"/>
+      <c r="EF43" s="8"/>
     </row>
-    <row r="44" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -12218,8 +14099,24 @@
       <c r="DN44" s="8"/>
       <c r="DO44" s="8"/>
       <c r="DP44" s="8"/>
+      <c r="DQ44" s="8"/>
+      <c r="DR44" s="8"/>
+      <c r="DS44" s="8"/>
+      <c r="DT44" s="8"/>
+      <c r="DU44" s="8"/>
+      <c r="DV44" s="8"/>
+      <c r="DW44" s="8"/>
+      <c r="DX44" s="8"/>
+      <c r="DY44" s="8"/>
+      <c r="DZ44" s="8"/>
+      <c r="EA44" s="8"/>
+      <c r="EB44" s="8"/>
+      <c r="EC44" s="8"/>
+      <c r="ED44" s="8"/>
+      <c r="EE44" s="8"/>
+      <c r="EF44" s="8"/>
     </row>
-    <row r="45" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -12340,8 +14237,24 @@
       <c r="DN45" s="8"/>
       <c r="DO45" s="8"/>
       <c r="DP45" s="8"/>
+      <c r="DQ45" s="8"/>
+      <c r="DR45" s="8"/>
+      <c r="DS45" s="8"/>
+      <c r="DT45" s="8"/>
+      <c r="DU45" s="8"/>
+      <c r="DV45" s="8"/>
+      <c r="DW45" s="8"/>
+      <c r="DX45" s="8"/>
+      <c r="DY45" s="8"/>
+      <c r="DZ45" s="8"/>
+      <c r="EA45" s="8"/>
+      <c r="EB45" s="8"/>
+      <c r="EC45" s="8"/>
+      <c r="ED45" s="8"/>
+      <c r="EE45" s="8"/>
+      <c r="EF45" s="8"/>
     </row>
-    <row r="46" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -12462,8 +14375,24 @@
       <c r="DN46" s="8"/>
       <c r="DO46" s="8"/>
       <c r="DP46" s="8"/>
+      <c r="DQ46" s="8"/>
+      <c r="DR46" s="8"/>
+      <c r="DS46" s="8"/>
+      <c r="DT46" s="8"/>
+      <c r="DU46" s="8"/>
+      <c r="DV46" s="8"/>
+      <c r="DW46" s="8"/>
+      <c r="DX46" s="8"/>
+      <c r="DY46" s="8"/>
+      <c r="DZ46" s="8"/>
+      <c r="EA46" s="8"/>
+      <c r="EB46" s="8"/>
+      <c r="EC46" s="8"/>
+      <c r="ED46" s="8"/>
+      <c r="EE46" s="8"/>
+      <c r="EF46" s="8"/>
     </row>
-    <row r="47" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -12584,8 +14513,24 @@
       <c r="DN47" s="8"/>
       <c r="DO47" s="8"/>
       <c r="DP47" s="8"/>
+      <c r="DQ47" s="8"/>
+      <c r="DR47" s="8"/>
+      <c r="DS47" s="8"/>
+      <c r="DT47" s="8"/>
+      <c r="DU47" s="8"/>
+      <c r="DV47" s="8"/>
+      <c r="DW47" s="8"/>
+      <c r="DX47" s="8"/>
+      <c r="DY47" s="8"/>
+      <c r="DZ47" s="8"/>
+      <c r="EA47" s="8"/>
+      <c r="EB47" s="8"/>
+      <c r="EC47" s="8"/>
+      <c r="ED47" s="8"/>
+      <c r="EE47" s="8"/>
+      <c r="EF47" s="8"/>
     </row>
-    <row r="48" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -12706,8 +14651,24 @@
       <c r="DN48" s="8"/>
       <c r="DO48" s="8"/>
       <c r="DP48" s="8"/>
+      <c r="DQ48" s="8"/>
+      <c r="DR48" s="8"/>
+      <c r="DS48" s="8"/>
+      <c r="DT48" s="8"/>
+      <c r="DU48" s="8"/>
+      <c r="DV48" s="8"/>
+      <c r="DW48" s="8"/>
+      <c r="DX48" s="8"/>
+      <c r="DY48" s="8"/>
+      <c r="DZ48" s="8"/>
+      <c r="EA48" s="8"/>
+      <c r="EB48" s="8"/>
+      <c r="EC48" s="8"/>
+      <c r="ED48" s="8"/>
+      <c r="EE48" s="8"/>
+      <c r="EF48" s="8"/>
     </row>
-    <row r="49" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -12828,8 +14789,24 @@
       <c r="DN49" s="8"/>
       <c r="DO49" s="8"/>
       <c r="DP49" s="8"/>
+      <c r="DQ49" s="8"/>
+      <c r="DR49" s="8"/>
+      <c r="DS49" s="8"/>
+      <c r="DT49" s="8"/>
+      <c r="DU49" s="8"/>
+      <c r="DV49" s="8"/>
+      <c r="DW49" s="8"/>
+      <c r="DX49" s="8"/>
+      <c r="DY49" s="8"/>
+      <c r="DZ49" s="8"/>
+      <c r="EA49" s="8"/>
+      <c r="EB49" s="8"/>
+      <c r="EC49" s="8"/>
+      <c r="ED49" s="8"/>
+      <c r="EE49" s="8"/>
+      <c r="EF49" s="8"/>
     </row>
-    <row r="50" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -12950,8 +14927,24 @@
       <c r="DN50" s="8"/>
       <c r="DO50" s="8"/>
       <c r="DP50" s="8"/>
+      <c r="DQ50" s="8"/>
+      <c r="DR50" s="8"/>
+      <c r="DS50" s="8"/>
+      <c r="DT50" s="8"/>
+      <c r="DU50" s="8"/>
+      <c r="DV50" s="8"/>
+      <c r="DW50" s="8"/>
+      <c r="DX50" s="8"/>
+      <c r="DY50" s="8"/>
+      <c r="DZ50" s="8"/>
+      <c r="EA50" s="8"/>
+      <c r="EB50" s="8"/>
+      <c r="EC50" s="8"/>
+      <c r="ED50" s="8"/>
+      <c r="EE50" s="8"/>
+      <c r="EF50" s="8"/>
     </row>
-    <row r="51" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>6</v>
       </c>
@@ -12989,7 +14982,7 @@
       <c r="W51" s="6"/>
       <c r="X51" s="6"/>
       <c r="Y51" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Z51" s="6"/>
       <c r="AA51" s="6"/>
@@ -13001,139 +14994,163 @@
       <c r="AE51" s="6"/>
       <c r="AF51" s="6"/>
       <c r="AG51" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AH51" s="6"/>
       <c r="AI51" s="6"/>
       <c r="AJ51" s="6"/>
       <c r="AK51" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AL51" s="6"/>
       <c r="AM51" s="6"/>
       <c r="AN51" s="6"/>
       <c r="AO51" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AP51" s="6"/>
       <c r="AQ51" s="6"/>
       <c r="AR51" s="6"/>
       <c r="AS51" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AT51" s="6"/>
       <c r="AU51" s="6"/>
       <c r="AV51" s="6"/>
       <c r="AW51" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AX51" s="6"/>
       <c r="AY51" s="6"/>
       <c r="AZ51" s="6"/>
       <c r="BA51" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="BB51" s="6"/>
       <c r="BC51" s="6"/>
       <c r="BD51" s="6"/>
       <c r="BE51" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="BF51" s="6"/>
       <c r="BG51" s="6"/>
       <c r="BH51" s="6"/>
       <c r="BI51" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="BJ51" s="6"/>
       <c r="BK51" s="6"/>
       <c r="BL51" s="6"/>
       <c r="BM51" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="BN51" s="6"/>
       <c r="BO51" s="6"/>
       <c r="BP51" s="6"/>
       <c r="BQ51" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="BR51" s="6"/>
       <c r="BS51" s="6"/>
       <c r="BT51" s="6"/>
       <c r="BU51" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="BV51" s="6"/>
       <c r="BW51" s="6"/>
       <c r="BX51" s="6"/>
       <c r="BY51" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="BZ51" s="6"/>
       <c r="CA51" s="6"/>
       <c r="CB51" s="6"/>
       <c r="CC51" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="CD51" s="6"/>
       <c r="CE51" s="6"/>
       <c r="CF51" s="6"/>
       <c r="CG51" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="CH51" s="6"/>
       <c r="CI51" s="6"/>
       <c r="CJ51" s="6"/>
       <c r="CK51" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="CL51" s="6"/>
       <c r="CM51" s="6"/>
       <c r="CN51" s="6"/>
       <c r="CO51" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="CP51" s="6"/>
       <c r="CQ51" s="6"/>
       <c r="CR51" s="6"/>
       <c r="CS51" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="CT51" s="6"/>
       <c r="CU51" s="6"/>
       <c r="CV51" s="6"/>
       <c r="CW51" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="CX51" s="6"/>
       <c r="CY51" s="6"/>
       <c r="CZ51" s="6"/>
       <c r="DA51" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="DB51" s="6"/>
       <c r="DC51" s="6"/>
       <c r="DD51" s="6"/>
       <c r="DE51" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="DF51" s="6"/>
       <c r="DG51" s="6"/>
       <c r="DH51" s="6"/>
       <c r="DI51" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="DJ51" s="6"/>
       <c r="DK51" s="6"/>
       <c r="DL51" s="6"/>
       <c r="DM51" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="DN51" s="6"/>
       <c r="DO51" s="6"/>
       <c r="DP51" s="6"/>
+      <c r="DQ51" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="DR51" s="6"/>
+      <c r="DS51" s="6"/>
+      <c r="DT51" s="6"/>
+      <c r="DU51" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="DV51" s="6"/>
+      <c r="DW51" s="6"/>
+      <c r="DX51" s="6"/>
+      <c r="DY51" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="DZ51" s="6"/>
+      <c r="EA51" s="6"/>
+      <c r="EB51" s="6"/>
+      <c r="EC51" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="ED51" s="6"/>
+      <c r="EE51" s="6"/>
+      <c r="EF51" s="6"/>
     </row>
-    <row r="52" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -13254,8 +15271,24 @@
       <c r="DN52" s="6"/>
       <c r="DO52" s="6"/>
       <c r="DP52" s="6"/>
+      <c r="DQ52" s="6"/>
+      <c r="DR52" s="6"/>
+      <c r="DS52" s="6"/>
+      <c r="DT52" s="6"/>
+      <c r="DU52" s="6"/>
+      <c r="DV52" s="6"/>
+      <c r="DW52" s="6"/>
+      <c r="DX52" s="6"/>
+      <c r="DY52" s="6"/>
+      <c r="DZ52" s="6"/>
+      <c r="EA52" s="6"/>
+      <c r="EB52" s="6"/>
+      <c r="EC52" s="6"/>
+      <c r="ED52" s="6"/>
+      <c r="EE52" s="6"/>
+      <c r="EF52" s="6"/>
     </row>
-    <row r="53" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -13376,8 +15409,24 @@
       <c r="DN53" s="6"/>
       <c r="DO53" s="6"/>
       <c r="DP53" s="6"/>
+      <c r="DQ53" s="6"/>
+      <c r="DR53" s="6"/>
+      <c r="DS53" s="6"/>
+      <c r="DT53" s="6"/>
+      <c r="DU53" s="6"/>
+      <c r="DV53" s="6"/>
+      <c r="DW53" s="6"/>
+      <c r="DX53" s="6"/>
+      <c r="DY53" s="6"/>
+      <c r="DZ53" s="6"/>
+      <c r="EA53" s="6"/>
+      <c r="EB53" s="6"/>
+      <c r="EC53" s="6"/>
+      <c r="ED53" s="6"/>
+      <c r="EE53" s="6"/>
+      <c r="EF53" s="6"/>
     </row>
-    <row r="54" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -13498,8 +15547,24 @@
       <c r="DN54" s="6"/>
       <c r="DO54" s="6"/>
       <c r="DP54" s="6"/>
+      <c r="DQ54" s="6"/>
+      <c r="DR54" s="6"/>
+      <c r="DS54" s="6"/>
+      <c r="DT54" s="6"/>
+      <c r="DU54" s="6"/>
+      <c r="DV54" s="6"/>
+      <c r="DW54" s="6"/>
+      <c r="DX54" s="6"/>
+      <c r="DY54" s="6"/>
+      <c r="DZ54" s="6"/>
+      <c r="EA54" s="6"/>
+      <c r="EB54" s="6"/>
+      <c r="EC54" s="6"/>
+      <c r="ED54" s="6"/>
+      <c r="EE54" s="6"/>
+      <c r="EF54" s="6"/>
     </row>
-    <row r="55" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -13620,8 +15685,24 @@
       <c r="DN55" s="6"/>
       <c r="DO55" s="6"/>
       <c r="DP55" s="6"/>
+      <c r="DQ55" s="6"/>
+      <c r="DR55" s="6"/>
+      <c r="DS55" s="6"/>
+      <c r="DT55" s="6"/>
+      <c r="DU55" s="6"/>
+      <c r="DV55" s="6"/>
+      <c r="DW55" s="6"/>
+      <c r="DX55" s="6"/>
+      <c r="DY55" s="6"/>
+      <c r="DZ55" s="6"/>
+      <c r="EA55" s="6"/>
+      <c r="EB55" s="6"/>
+      <c r="EC55" s="6"/>
+      <c r="ED55" s="6"/>
+      <c r="EE55" s="6"/>
+      <c r="EF55" s="6"/>
     </row>
-    <row r="56" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -13742,8 +15823,24 @@
       <c r="DN56" s="6"/>
       <c r="DO56" s="6"/>
       <c r="DP56" s="6"/>
+      <c r="DQ56" s="6"/>
+      <c r="DR56" s="6"/>
+      <c r="DS56" s="6"/>
+      <c r="DT56" s="6"/>
+      <c r="DU56" s="6"/>
+      <c r="DV56" s="6"/>
+      <c r="DW56" s="6"/>
+      <c r="DX56" s="6"/>
+      <c r="DY56" s="6"/>
+      <c r="DZ56" s="6"/>
+      <c r="EA56" s="6"/>
+      <c r="EB56" s="6"/>
+      <c r="EC56" s="6"/>
+      <c r="ED56" s="6"/>
+      <c r="EE56" s="6"/>
+      <c r="EF56" s="6"/>
     </row>
-    <row r="57" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -13864,8 +15961,24 @@
       <c r="DN57" s="6"/>
       <c r="DO57" s="6"/>
       <c r="DP57" s="6"/>
+      <c r="DQ57" s="6"/>
+      <c r="DR57" s="6"/>
+      <c r="DS57" s="6"/>
+      <c r="DT57" s="6"/>
+      <c r="DU57" s="6"/>
+      <c r="DV57" s="6"/>
+      <c r="DW57" s="6"/>
+      <c r="DX57" s="6"/>
+      <c r="DY57" s="6"/>
+      <c r="DZ57" s="6"/>
+      <c r="EA57" s="6"/>
+      <c r="EB57" s="6"/>
+      <c r="EC57" s="6"/>
+      <c r="ED57" s="6"/>
+      <c r="EE57" s="6"/>
+      <c r="EF57" s="6"/>
     </row>
-    <row r="58" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -13986,8 +16099,24 @@
       <c r="DN58" s="6"/>
       <c r="DO58" s="6"/>
       <c r="DP58" s="6"/>
+      <c r="DQ58" s="6"/>
+      <c r="DR58" s="6"/>
+      <c r="DS58" s="6"/>
+      <c r="DT58" s="6"/>
+      <c r="DU58" s="6"/>
+      <c r="DV58" s="6"/>
+      <c r="DW58" s="6"/>
+      <c r="DX58" s="6"/>
+      <c r="DY58" s="6"/>
+      <c r="DZ58" s="6"/>
+      <c r="EA58" s="6"/>
+      <c r="EB58" s="6"/>
+      <c r="EC58" s="6"/>
+      <c r="ED58" s="6"/>
+      <c r="EE58" s="6"/>
+      <c r="EF58" s="6"/>
     </row>
-    <row r="59" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -14108,8 +16237,24 @@
       <c r="DN59" s="6"/>
       <c r="DO59" s="6"/>
       <c r="DP59" s="6"/>
+      <c r="DQ59" s="6"/>
+      <c r="DR59" s="6"/>
+      <c r="DS59" s="6"/>
+      <c r="DT59" s="6"/>
+      <c r="DU59" s="6"/>
+      <c r="DV59" s="6"/>
+      <c r="DW59" s="6"/>
+      <c r="DX59" s="6"/>
+      <c r="DY59" s="6"/>
+      <c r="DZ59" s="6"/>
+      <c r="EA59" s="6"/>
+      <c r="EB59" s="6"/>
+      <c r="EC59" s="6"/>
+      <c r="ED59" s="6"/>
+      <c r="EE59" s="6"/>
+      <c r="EF59" s="6"/>
     </row>
-    <row r="60" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -14230,8 +16375,24 @@
       <c r="DN60" s="6"/>
       <c r="DO60" s="6"/>
       <c r="DP60" s="6"/>
+      <c r="DQ60" s="6"/>
+      <c r="DR60" s="6"/>
+      <c r="DS60" s="6"/>
+      <c r="DT60" s="6"/>
+      <c r="DU60" s="6"/>
+      <c r="DV60" s="6"/>
+      <c r="DW60" s="6"/>
+      <c r="DX60" s="6"/>
+      <c r="DY60" s="6"/>
+      <c r="DZ60" s="6"/>
+      <c r="EA60" s="6"/>
+      <c r="EB60" s="6"/>
+      <c r="EC60" s="6"/>
+      <c r="ED60" s="6"/>
+      <c r="EE60" s="6"/>
+      <c r="EF60" s="6"/>
     </row>
-    <row r="61" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>8</v>
       </c>
@@ -14269,151 +16430,175 @@
       <c r="W61" s="6"/>
       <c r="X61" s="6"/>
       <c r="Y61" s="5" t="s">
-        <v>66</v>
+        <v>338</v>
       </c>
       <c r="Z61" s="6"/>
       <c r="AA61" s="6"/>
       <c r="AB61" s="6"/>
       <c r="AC61" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AD61" s="6"/>
       <c r="AE61" s="6"/>
       <c r="AF61" s="6"/>
       <c r="AG61" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AH61" s="6"/>
       <c r="AI61" s="6"/>
       <c r="AJ61" s="6"/>
       <c r="AK61" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AL61" s="6"/>
       <c r="AM61" s="6"/>
       <c r="AN61" s="6"/>
       <c r="AO61" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AP61" s="6"/>
       <c r="AQ61" s="6"/>
       <c r="AR61" s="6"/>
       <c r="AS61" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AT61" s="6"/>
       <c r="AU61" s="6"/>
       <c r="AV61" s="6"/>
       <c r="AW61" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AX61" s="6"/>
       <c r="AY61" s="6"/>
       <c r="AZ61" s="6"/>
       <c r="BA61" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="BB61" s="6"/>
       <c r="BC61" s="6"/>
       <c r="BD61" s="6"/>
       <c r="BE61" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="BF61" s="6"/>
       <c r="BG61" s="6"/>
       <c r="BH61" s="6"/>
       <c r="BI61" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="BJ61" s="6"/>
       <c r="BK61" s="6"/>
       <c r="BL61" s="6"/>
       <c r="BM61" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="BN61" s="6"/>
       <c r="BO61" s="6"/>
       <c r="BP61" s="6"/>
       <c r="BQ61" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="BR61" s="6"/>
       <c r="BS61" s="6"/>
       <c r="BT61" s="6"/>
       <c r="BU61" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="BV61" s="6"/>
       <c r="BW61" s="6"/>
       <c r="BX61" s="6"/>
       <c r="BY61" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="BZ61" s="6"/>
       <c r="CA61" s="6"/>
       <c r="CB61" s="6"/>
       <c r="CC61" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="CD61" s="6"/>
       <c r="CE61" s="6"/>
       <c r="CF61" s="6"/>
       <c r="CG61" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="CH61" s="6"/>
       <c r="CI61" s="6"/>
       <c r="CJ61" s="6"/>
       <c r="CK61" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="CL61" s="6"/>
       <c r="CM61" s="6"/>
       <c r="CN61" s="6"/>
       <c r="CO61" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="CP61" s="6"/>
       <c r="CQ61" s="6"/>
       <c r="CR61" s="6"/>
       <c r="CS61" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="CT61" s="6"/>
       <c r="CU61" s="6"/>
       <c r="CV61" s="6"/>
       <c r="CW61" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="CX61" s="6"/>
       <c r="CY61" s="6"/>
       <c r="CZ61" s="6"/>
       <c r="DA61" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="DB61" s="6"/>
       <c r="DC61" s="6"/>
       <c r="DD61" s="6"/>
       <c r="DE61" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="DF61" s="6"/>
       <c r="DG61" s="6"/>
       <c r="DH61" s="6"/>
       <c r="DI61" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="DJ61" s="6"/>
       <c r="DK61" s="6"/>
       <c r="DL61" s="6"/>
       <c r="DM61" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="DN61" s="6"/>
       <c r="DO61" s="6"/>
       <c r="DP61" s="6"/>
+      <c r="DQ61" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="DR61" s="6"/>
+      <c r="DS61" s="6"/>
+      <c r="DT61" s="6"/>
+      <c r="DU61" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="DV61" s="6"/>
+      <c r="DW61" s="6"/>
+      <c r="DX61" s="6"/>
+      <c r="DY61" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="DZ61" s="6"/>
+      <c r="EA61" s="6"/>
+      <c r="EB61" s="6"/>
+      <c r="EC61" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="ED61" s="6"/>
+      <c r="EE61" s="6"/>
+      <c r="EF61" s="6"/>
     </row>
-    <row r="62" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -14534,8 +16719,24 @@
       <c r="DN62" s="6"/>
       <c r="DO62" s="6"/>
       <c r="DP62" s="6"/>
+      <c r="DQ62" s="6"/>
+      <c r="DR62" s="6"/>
+      <c r="DS62" s="6"/>
+      <c r="DT62" s="6"/>
+      <c r="DU62" s="6"/>
+      <c r="DV62" s="6"/>
+      <c r="DW62" s="6"/>
+      <c r="DX62" s="6"/>
+      <c r="DY62" s="6"/>
+      <c r="DZ62" s="6"/>
+      <c r="EA62" s="6"/>
+      <c r="EB62" s="6"/>
+      <c r="EC62" s="6"/>
+      <c r="ED62" s="6"/>
+      <c r="EE62" s="6"/>
+      <c r="EF62" s="6"/>
     </row>
-    <row r="63" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -14656,8 +16857,24 @@
       <c r="DN63" s="6"/>
       <c r="DO63" s="6"/>
       <c r="DP63" s="6"/>
+      <c r="DQ63" s="6"/>
+      <c r="DR63" s="6"/>
+      <c r="DS63" s="6"/>
+      <c r="DT63" s="6"/>
+      <c r="DU63" s="6"/>
+      <c r="DV63" s="6"/>
+      <c r="DW63" s="6"/>
+      <c r="DX63" s="6"/>
+      <c r="DY63" s="6"/>
+      <c r="DZ63" s="6"/>
+      <c r="EA63" s="6"/>
+      <c r="EB63" s="6"/>
+      <c r="EC63" s="6"/>
+      <c r="ED63" s="6"/>
+      <c r="EE63" s="6"/>
+      <c r="EF63" s="6"/>
     </row>
-    <row r="64" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -14778,8 +16995,24 @@
       <c r="DN64" s="6"/>
       <c r="DO64" s="6"/>
       <c r="DP64" s="6"/>
+      <c r="DQ64" s="6"/>
+      <c r="DR64" s="6"/>
+      <c r="DS64" s="6"/>
+      <c r="DT64" s="6"/>
+      <c r="DU64" s="6"/>
+      <c r="DV64" s="6"/>
+      <c r="DW64" s="6"/>
+      <c r="DX64" s="6"/>
+      <c r="DY64" s="6"/>
+      <c r="DZ64" s="6"/>
+      <c r="EA64" s="6"/>
+      <c r="EB64" s="6"/>
+      <c r="EC64" s="6"/>
+      <c r="ED64" s="6"/>
+      <c r="EE64" s="6"/>
+      <c r="EF64" s="6"/>
     </row>
-    <row r="65" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -14900,8 +17133,24 @@
       <c r="DN65" s="6"/>
       <c r="DO65" s="6"/>
       <c r="DP65" s="6"/>
+      <c r="DQ65" s="6"/>
+      <c r="DR65" s="6"/>
+      <c r="DS65" s="6"/>
+      <c r="DT65" s="6"/>
+      <c r="DU65" s="6"/>
+      <c r="DV65" s="6"/>
+      <c r="DW65" s="6"/>
+      <c r="DX65" s="6"/>
+      <c r="DY65" s="6"/>
+      <c r="DZ65" s="6"/>
+      <c r="EA65" s="6"/>
+      <c r="EB65" s="6"/>
+      <c r="EC65" s="6"/>
+      <c r="ED65" s="6"/>
+      <c r="EE65" s="6"/>
+      <c r="EF65" s="6"/>
     </row>
-    <row r="66" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -15022,8 +17271,24 @@
       <c r="DN66" s="6"/>
       <c r="DO66" s="6"/>
       <c r="DP66" s="6"/>
+      <c r="DQ66" s="6"/>
+      <c r="DR66" s="6"/>
+      <c r="DS66" s="6"/>
+      <c r="DT66" s="6"/>
+      <c r="DU66" s="6"/>
+      <c r="DV66" s="6"/>
+      <c r="DW66" s="6"/>
+      <c r="DX66" s="6"/>
+      <c r="DY66" s="6"/>
+      <c r="DZ66" s="6"/>
+      <c r="EA66" s="6"/>
+      <c r="EB66" s="6"/>
+      <c r="EC66" s="6"/>
+      <c r="ED66" s="6"/>
+      <c r="EE66" s="6"/>
+      <c r="EF66" s="6"/>
     </row>
-    <row r="67" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -15144,8 +17409,24 @@
       <c r="DN67" s="6"/>
       <c r="DO67" s="6"/>
       <c r="DP67" s="6"/>
+      <c r="DQ67" s="6"/>
+      <c r="DR67" s="6"/>
+      <c r="DS67" s="6"/>
+      <c r="DT67" s="6"/>
+      <c r="DU67" s="6"/>
+      <c r="DV67" s="6"/>
+      <c r="DW67" s="6"/>
+      <c r="DX67" s="6"/>
+      <c r="DY67" s="6"/>
+      <c r="DZ67" s="6"/>
+      <c r="EA67" s="6"/>
+      <c r="EB67" s="6"/>
+      <c r="EC67" s="6"/>
+      <c r="ED67" s="6"/>
+      <c r="EE67" s="6"/>
+      <c r="EF67" s="6"/>
     </row>
-    <row r="68" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -15266,8 +17547,24 @@
       <c r="DN68" s="6"/>
       <c r="DO68" s="6"/>
       <c r="DP68" s="6"/>
+      <c r="DQ68" s="6"/>
+      <c r="DR68" s="6"/>
+      <c r="DS68" s="6"/>
+      <c r="DT68" s="6"/>
+      <c r="DU68" s="6"/>
+      <c r="DV68" s="6"/>
+      <c r="DW68" s="6"/>
+      <c r="DX68" s="6"/>
+      <c r="DY68" s="6"/>
+      <c r="DZ68" s="6"/>
+      <c r="EA68" s="6"/>
+      <c r="EB68" s="6"/>
+      <c r="EC68" s="6"/>
+      <c r="ED68" s="6"/>
+      <c r="EE68" s="6"/>
+      <c r="EF68" s="6"/>
     </row>
-    <row r="69" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -15388,8 +17685,24 @@
       <c r="DN69" s="6"/>
       <c r="DO69" s="6"/>
       <c r="DP69" s="6"/>
+      <c r="DQ69" s="6"/>
+      <c r="DR69" s="6"/>
+      <c r="DS69" s="6"/>
+      <c r="DT69" s="6"/>
+      <c r="DU69" s="6"/>
+      <c r="DV69" s="6"/>
+      <c r="DW69" s="6"/>
+      <c r="DX69" s="6"/>
+      <c r="DY69" s="6"/>
+      <c r="DZ69" s="6"/>
+      <c r="EA69" s="6"/>
+      <c r="EB69" s="6"/>
+      <c r="EC69" s="6"/>
+      <c r="ED69" s="6"/>
+      <c r="EE69" s="6"/>
+      <c r="EF69" s="6"/>
     </row>
-    <row r="70" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -15510,8 +17823,24 @@
       <c r="DN70" s="6"/>
       <c r="DO70" s="6"/>
       <c r="DP70" s="6"/>
+      <c r="DQ70" s="6"/>
+      <c r="DR70" s="6"/>
+      <c r="DS70" s="6"/>
+      <c r="DT70" s="6"/>
+      <c r="DU70" s="6"/>
+      <c r="DV70" s="6"/>
+      <c r="DW70" s="6"/>
+      <c r="DX70" s="6"/>
+      <c r="DY70" s="6"/>
+      <c r="DZ70" s="6"/>
+      <c r="EA70" s="6"/>
+      <c r="EB70" s="6"/>
+      <c r="EC70" s="6"/>
+      <c r="ED70" s="6"/>
+      <c r="EE70" s="6"/>
+      <c r="EF70" s="6"/>
     </row>
-    <row r="71" spans="1:120" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:136" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>11</v>
       </c>
@@ -15549,151 +17878,175 @@
       <c r="W71" s="6"/>
       <c r="X71" s="6"/>
       <c r="Y71" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z71" s="6"/>
       <c r="AA71" s="6"/>
       <c r="AB71" s="6"/>
       <c r="AC71" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AD71" s="6"/>
       <c r="AE71" s="6"/>
       <c r="AF71" s="6"/>
       <c r="AG71" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AH71" s="6"/>
       <c r="AI71" s="6"/>
       <c r="AJ71" s="6"/>
       <c r="AK71" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AL71" s="6"/>
       <c r="AM71" s="6"/>
       <c r="AN71" s="6"/>
       <c r="AO71" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AP71" s="6"/>
       <c r="AQ71" s="6"/>
       <c r="AR71" s="6"/>
       <c r="AS71" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AT71" s="6"/>
       <c r="AU71" s="6"/>
       <c r="AV71" s="6"/>
       <c r="AW71" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AX71" s="6"/>
       <c r="AY71" s="6"/>
       <c r="AZ71" s="6"/>
       <c r="BA71" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="BB71" s="6"/>
       <c r="BC71" s="6"/>
       <c r="BD71" s="6"/>
       <c r="BE71" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="BF71" s="6"/>
       <c r="BG71" s="6"/>
       <c r="BH71" s="6"/>
       <c r="BI71" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="BJ71" s="6"/>
       <c r="BK71" s="6"/>
       <c r="BL71" s="6"/>
       <c r="BM71" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="BN71" s="6"/>
       <c r="BO71" s="6"/>
       <c r="BP71" s="6"/>
       <c r="BQ71" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="BR71" s="6"/>
       <c r="BS71" s="6"/>
       <c r="BT71" s="6"/>
       <c r="BU71" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="BV71" s="6"/>
       <c r="BW71" s="6"/>
       <c r="BX71" s="6"/>
       <c r="BY71" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="BZ71" s="6"/>
       <c r="CA71" s="6"/>
       <c r="CB71" s="6"/>
       <c r="CC71" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="CD71" s="6"/>
       <c r="CE71" s="6"/>
       <c r="CF71" s="6"/>
       <c r="CG71" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="CH71" s="6"/>
       <c r="CI71" s="6"/>
       <c r="CJ71" s="6"/>
       <c r="CK71" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="CL71" s="6"/>
       <c r="CM71" s="6"/>
       <c r="CN71" s="6"/>
       <c r="CO71" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="CP71" s="6"/>
       <c r="CQ71" s="6"/>
       <c r="CR71" s="6"/>
       <c r="CS71" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="CT71" s="6"/>
       <c r="CU71" s="6"/>
       <c r="CV71" s="6"/>
       <c r="CW71" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="CX71" s="6"/>
       <c r="CY71" s="6"/>
       <c r="CZ71" s="6"/>
       <c r="DA71" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="DB71" s="6"/>
       <c r="DC71" s="6"/>
       <c r="DD71" s="6"/>
       <c r="DE71" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="DF71" s="6"/>
       <c r="DG71" s="6"/>
       <c r="DH71" s="6"/>
       <c r="DI71" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="DJ71" s="6"/>
       <c r="DK71" s="6"/>
       <c r="DL71" s="6"/>
       <c r="DM71" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="DN71" s="6"/>
       <c r="DO71" s="6"/>
       <c r="DP71" s="6"/>
+      <c r="DQ71" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="DR71" s="6"/>
+      <c r="DS71" s="6"/>
+      <c r="DT71" s="6"/>
+      <c r="DU71" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="DV71" s="6"/>
+      <c r="DW71" s="6"/>
+      <c r="DX71" s="6"/>
+      <c r="DY71" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="DZ71" s="6"/>
+      <c r="EA71" s="6"/>
+      <c r="EB71" s="6"/>
+      <c r="EC71" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="ED71" s="6"/>
+      <c r="EE71" s="6"/>
+      <c r="EF71" s="6"/>
     </row>
-    <row r="72" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -15814,8 +18167,24 @@
       <c r="DN72" s="6"/>
       <c r="DO72" s="6"/>
       <c r="DP72" s="6"/>
+      <c r="DQ72" s="6"/>
+      <c r="DR72" s="6"/>
+      <c r="DS72" s="6"/>
+      <c r="DT72" s="6"/>
+      <c r="DU72" s="6"/>
+      <c r="DV72" s="6"/>
+      <c r="DW72" s="6"/>
+      <c r="DX72" s="6"/>
+      <c r="DY72" s="6"/>
+      <c r="DZ72" s="6"/>
+      <c r="EA72" s="6"/>
+      <c r="EB72" s="6"/>
+      <c r="EC72" s="6"/>
+      <c r="ED72" s="6"/>
+      <c r="EE72" s="6"/>
+      <c r="EF72" s="6"/>
     </row>
-    <row r="73" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -15936,8 +18305,24 @@
       <c r="DN73" s="6"/>
       <c r="DO73" s="6"/>
       <c r="DP73" s="6"/>
+      <c r="DQ73" s="6"/>
+      <c r="DR73" s="6"/>
+      <c r="DS73" s="6"/>
+      <c r="DT73" s="6"/>
+      <c r="DU73" s="6"/>
+      <c r="DV73" s="6"/>
+      <c r="DW73" s="6"/>
+      <c r="DX73" s="6"/>
+      <c r="DY73" s="6"/>
+      <c r="DZ73" s="6"/>
+      <c r="EA73" s="6"/>
+      <c r="EB73" s="6"/>
+      <c r="EC73" s="6"/>
+      <c r="ED73" s="6"/>
+      <c r="EE73" s="6"/>
+      <c r="EF73" s="6"/>
     </row>
-    <row r="74" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -16058,8 +18443,24 @@
       <c r="DN74" s="6"/>
       <c r="DO74" s="6"/>
       <c r="DP74" s="6"/>
+      <c r="DQ74" s="6"/>
+      <c r="DR74" s="6"/>
+      <c r="DS74" s="6"/>
+      <c r="DT74" s="6"/>
+      <c r="DU74" s="6"/>
+      <c r="DV74" s="6"/>
+      <c r="DW74" s="6"/>
+      <c r="DX74" s="6"/>
+      <c r="DY74" s="6"/>
+      <c r="DZ74" s="6"/>
+      <c r="EA74" s="6"/>
+      <c r="EB74" s="6"/>
+      <c r="EC74" s="6"/>
+      <c r="ED74" s="6"/>
+      <c r="EE74" s="6"/>
+      <c r="EF74" s="6"/>
     </row>
-    <row r="75" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -16180,8 +18581,24 @@
       <c r="DN75" s="6"/>
       <c r="DO75" s="6"/>
       <c r="DP75" s="6"/>
+      <c r="DQ75" s="6"/>
+      <c r="DR75" s="6"/>
+      <c r="DS75" s="6"/>
+      <c r="DT75" s="6"/>
+      <c r="DU75" s="6"/>
+      <c r="DV75" s="6"/>
+      <c r="DW75" s="6"/>
+      <c r="DX75" s="6"/>
+      <c r="DY75" s="6"/>
+      <c r="DZ75" s="6"/>
+      <c r="EA75" s="6"/>
+      <c r="EB75" s="6"/>
+      <c r="EC75" s="6"/>
+      <c r="ED75" s="6"/>
+      <c r="EE75" s="6"/>
+      <c r="EF75" s="6"/>
     </row>
-    <row r="76" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -16302,8 +18719,24 @@
       <c r="DN76" s="6"/>
       <c r="DO76" s="6"/>
       <c r="DP76" s="6"/>
+      <c r="DQ76" s="6"/>
+      <c r="DR76" s="6"/>
+      <c r="DS76" s="6"/>
+      <c r="DT76" s="6"/>
+      <c r="DU76" s="6"/>
+      <c r="DV76" s="6"/>
+      <c r="DW76" s="6"/>
+      <c r="DX76" s="6"/>
+      <c r="DY76" s="6"/>
+      <c r="DZ76" s="6"/>
+      <c r="EA76" s="6"/>
+      <c r="EB76" s="6"/>
+      <c r="EC76" s="6"/>
+      <c r="ED76" s="6"/>
+      <c r="EE76" s="6"/>
+      <c r="EF76" s="6"/>
     </row>
-    <row r="77" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -16424,8 +18857,24 @@
       <c r="DN77" s="6"/>
       <c r="DO77" s="6"/>
       <c r="DP77" s="6"/>
+      <c r="DQ77" s="6"/>
+      <c r="DR77" s="6"/>
+      <c r="DS77" s="6"/>
+      <c r="DT77" s="6"/>
+      <c r="DU77" s="6"/>
+      <c r="DV77" s="6"/>
+      <c r="DW77" s="6"/>
+      <c r="DX77" s="6"/>
+      <c r="DY77" s="6"/>
+      <c r="DZ77" s="6"/>
+      <c r="EA77" s="6"/>
+      <c r="EB77" s="6"/>
+      <c r="EC77" s="6"/>
+      <c r="ED77" s="6"/>
+      <c r="EE77" s="6"/>
+      <c r="EF77" s="6"/>
     </row>
-    <row r="78" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -16546,8 +18995,24 @@
       <c r="DN78" s="6"/>
       <c r="DO78" s="6"/>
       <c r="DP78" s="6"/>
+      <c r="DQ78" s="6"/>
+      <c r="DR78" s="6"/>
+      <c r="DS78" s="6"/>
+      <c r="DT78" s="6"/>
+      <c r="DU78" s="6"/>
+      <c r="DV78" s="6"/>
+      <c r="DW78" s="6"/>
+      <c r="DX78" s="6"/>
+      <c r="DY78" s="6"/>
+      <c r="DZ78" s="6"/>
+      <c r="EA78" s="6"/>
+      <c r="EB78" s="6"/>
+      <c r="EC78" s="6"/>
+      <c r="ED78" s="6"/>
+      <c r="EE78" s="6"/>
+      <c r="EF78" s="6"/>
     </row>
-    <row r="79" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -16668,8 +19133,24 @@
       <c r="DN79" s="6"/>
       <c r="DO79" s="6"/>
       <c r="DP79" s="6"/>
+      <c r="DQ79" s="6"/>
+      <c r="DR79" s="6"/>
+      <c r="DS79" s="6"/>
+      <c r="DT79" s="6"/>
+      <c r="DU79" s="6"/>
+      <c r="DV79" s="6"/>
+      <c r="DW79" s="6"/>
+      <c r="DX79" s="6"/>
+      <c r="DY79" s="6"/>
+      <c r="DZ79" s="6"/>
+      <c r="EA79" s="6"/>
+      <c r="EB79" s="6"/>
+      <c r="EC79" s="6"/>
+      <c r="ED79" s="6"/>
+      <c r="EE79" s="6"/>
+      <c r="EF79" s="6"/>
     </row>
-    <row r="80" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -16790,8 +19271,24 @@
       <c r="DN80" s="6"/>
       <c r="DO80" s="6"/>
       <c r="DP80" s="6"/>
+      <c r="DQ80" s="6"/>
+      <c r="DR80" s="6"/>
+      <c r="DS80" s="6"/>
+      <c r="DT80" s="6"/>
+      <c r="DU80" s="6"/>
+      <c r="DV80" s="6"/>
+      <c r="DW80" s="6"/>
+      <c r="DX80" s="6"/>
+      <c r="DY80" s="6"/>
+      <c r="DZ80" s="6"/>
+      <c r="EA80" s="6"/>
+      <c r="EB80" s="6"/>
+      <c r="EC80" s="6"/>
+      <c r="ED80" s="6"/>
+      <c r="EE80" s="6"/>
+      <c r="EF80" s="6"/>
     </row>
-    <row r="81" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>15</v>
       </c>
@@ -16829,147 +19326,175 @@
       <c r="W81" s="6"/>
       <c r="X81" s="6"/>
       <c r="Y81" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Z81" s="6"/>
       <c r="AA81" s="6"/>
       <c r="AB81" s="6"/>
       <c r="AC81" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AD81" s="6"/>
       <c r="AE81" s="6"/>
       <c r="AF81" s="6"/>
       <c r="AG81" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AH81" s="6"/>
       <c r="AI81" s="6"/>
       <c r="AJ81" s="6"/>
       <c r="AK81" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AL81" s="6"/>
       <c r="AM81" s="6"/>
       <c r="AN81" s="6"/>
       <c r="AO81" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP81" s="6"/>
       <c r="AQ81" s="6"/>
       <c r="AR81" s="6"/>
       <c r="AS81" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AT81" s="6"/>
       <c r="AU81" s="6"/>
       <c r="AV81" s="6"/>
       <c r="AW81" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AX81" s="6"/>
       <c r="AY81" s="6"/>
       <c r="AZ81" s="6"/>
       <c r="BA81" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="BB81" s="6"/>
       <c r="BC81" s="6"/>
       <c r="BD81" s="6"/>
       <c r="BE81" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="BF81" s="6"/>
       <c r="BG81" s="6"/>
       <c r="BH81" s="6"/>
       <c r="BI81" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="BJ81" s="6"/>
       <c r="BK81" s="6"/>
       <c r="BL81" s="6"/>
       <c r="BM81" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="BN81" s="6"/>
       <c r="BO81" s="6"/>
       <c r="BP81" s="6"/>
       <c r="BQ81" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="BR81" s="6"/>
       <c r="BS81" s="6"/>
       <c r="BT81" s="6"/>
       <c r="BU81" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="BV81" s="6"/>
       <c r="BW81" s="6"/>
       <c r="BX81" s="6"/>
       <c r="BY81" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="BZ81" s="6"/>
       <c r="CA81" s="6"/>
       <c r="CB81" s="6"/>
       <c r="CC81" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="CD81" s="6"/>
       <c r="CE81" s="6"/>
       <c r="CF81" s="6"/>
       <c r="CG81" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="CH81" s="6"/>
       <c r="CI81" s="6"/>
       <c r="CJ81" s="6"/>
       <c r="CK81" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="CL81" s="6"/>
       <c r="CM81" s="6"/>
       <c r="CN81" s="6"/>
       <c r="CO81" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="CP81" s="6"/>
       <c r="CQ81" s="6"/>
       <c r="CR81" s="6"/>
       <c r="CS81" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="CT81" s="6"/>
       <c r="CU81" s="6"/>
       <c r="CV81" s="6"/>
       <c r="CW81" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="CX81" s="6"/>
       <c r="CY81" s="6"/>
       <c r="CZ81" s="6"/>
       <c r="DA81" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="DB81" s="6"/>
       <c r="DC81" s="6"/>
       <c r="DD81" s="6"/>
       <c r="DE81" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="DF81" s="6"/>
       <c r="DG81" s="6"/>
       <c r="DH81" s="6"/>
-      <c r="DI81" s="5"/>
+      <c r="DI81" s="5" t="s">
+        <v>291</v>
+      </c>
       <c r="DJ81" s="6"/>
       <c r="DK81" s="6"/>
       <c r="DL81" s="6"/>
-      <c r="DM81" s="5"/>
+      <c r="DM81" s="5" t="s">
+        <v>293</v>
+      </c>
       <c r="DN81" s="6"/>
       <c r="DO81" s="6"/>
       <c r="DP81" s="6"/>
+      <c r="DQ81" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="DR81" s="6"/>
+      <c r="DS81" s="6"/>
+      <c r="DT81" s="6"/>
+      <c r="DU81" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="DV81" s="6"/>
+      <c r="DW81" s="6"/>
+      <c r="DX81" s="6"/>
+      <c r="DY81" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="DZ81" s="6"/>
+      <c r="EA81" s="6"/>
+      <c r="EB81" s="6"/>
+      <c r="EC81" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="ED81" s="6"/>
+      <c r="EE81" s="6"/>
+      <c r="EF81" s="6"/>
     </row>
-    <row r="82" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -17090,8 +19615,24 @@
       <c r="DN82" s="6"/>
       <c r="DO82" s="6"/>
       <c r="DP82" s="6"/>
+      <c r="DQ82" s="6"/>
+      <c r="DR82" s="6"/>
+      <c r="DS82" s="6"/>
+      <c r="DT82" s="6"/>
+      <c r="DU82" s="6"/>
+      <c r="DV82" s="6"/>
+      <c r="DW82" s="6"/>
+      <c r="DX82" s="6"/>
+      <c r="DY82" s="6"/>
+      <c r="DZ82" s="6"/>
+      <c r="EA82" s="6"/>
+      <c r="EB82" s="6"/>
+      <c r="EC82" s="6"/>
+      <c r="ED82" s="6"/>
+      <c r="EE82" s="6"/>
+      <c r="EF82" s="6"/>
     </row>
-    <row r="83" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -17212,8 +19753,24 @@
       <c r="DN83" s="6"/>
       <c r="DO83" s="6"/>
       <c r="DP83" s="6"/>
+      <c r="DQ83" s="6"/>
+      <c r="DR83" s="6"/>
+      <c r="DS83" s="6"/>
+      <c r="DT83" s="6"/>
+      <c r="DU83" s="6"/>
+      <c r="DV83" s="6"/>
+      <c r="DW83" s="6"/>
+      <c r="DX83" s="6"/>
+      <c r="DY83" s="6"/>
+      <c r="DZ83" s="6"/>
+      <c r="EA83" s="6"/>
+      <c r="EB83" s="6"/>
+      <c r="EC83" s="6"/>
+      <c r="ED83" s="6"/>
+      <c r="EE83" s="6"/>
+      <c r="EF83" s="6"/>
     </row>
-    <row r="84" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -17334,8 +19891,24 @@
       <c r="DN84" s="6"/>
       <c r="DO84" s="6"/>
       <c r="DP84" s="6"/>
+      <c r="DQ84" s="6"/>
+      <c r="DR84" s="6"/>
+      <c r="DS84" s="6"/>
+      <c r="DT84" s="6"/>
+      <c r="DU84" s="6"/>
+      <c r="DV84" s="6"/>
+      <c r="DW84" s="6"/>
+      <c r="DX84" s="6"/>
+      <c r="DY84" s="6"/>
+      <c r="DZ84" s="6"/>
+      <c r="EA84" s="6"/>
+      <c r="EB84" s="6"/>
+      <c r="EC84" s="6"/>
+      <c r="ED84" s="6"/>
+      <c r="EE84" s="6"/>
+      <c r="EF84" s="6"/>
     </row>
-    <row r="85" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -17456,8 +20029,24 @@
       <c r="DN85" s="6"/>
       <c r="DO85" s="6"/>
       <c r="DP85" s="6"/>
+      <c r="DQ85" s="6"/>
+      <c r="DR85" s="6"/>
+      <c r="DS85" s="6"/>
+      <c r="DT85" s="6"/>
+      <c r="DU85" s="6"/>
+      <c r="DV85" s="6"/>
+      <c r="DW85" s="6"/>
+      <c r="DX85" s="6"/>
+      <c r="DY85" s="6"/>
+      <c r="DZ85" s="6"/>
+      <c r="EA85" s="6"/>
+      <c r="EB85" s="6"/>
+      <c r="EC85" s="6"/>
+      <c r="ED85" s="6"/>
+      <c r="EE85" s="6"/>
+      <c r="EF85" s="6"/>
     </row>
-    <row r="86" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -17578,8 +20167,24 @@
       <c r="DN86" s="6"/>
       <c r="DO86" s="6"/>
       <c r="DP86" s="6"/>
+      <c r="DQ86" s="6"/>
+      <c r="DR86" s="6"/>
+      <c r="DS86" s="6"/>
+      <c r="DT86" s="6"/>
+      <c r="DU86" s="6"/>
+      <c r="DV86" s="6"/>
+      <c r="DW86" s="6"/>
+      <c r="DX86" s="6"/>
+      <c r="DY86" s="6"/>
+      <c r="DZ86" s="6"/>
+      <c r="EA86" s="6"/>
+      <c r="EB86" s="6"/>
+      <c r="EC86" s="6"/>
+      <c r="ED86" s="6"/>
+      <c r="EE86" s="6"/>
+      <c r="EF86" s="6"/>
     </row>
-    <row r="87" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -17700,8 +20305,24 @@
       <c r="DN87" s="6"/>
       <c r="DO87" s="6"/>
       <c r="DP87" s="6"/>
+      <c r="DQ87" s="6"/>
+      <c r="DR87" s="6"/>
+      <c r="DS87" s="6"/>
+      <c r="DT87" s="6"/>
+      <c r="DU87" s="6"/>
+      <c r="DV87" s="6"/>
+      <c r="DW87" s="6"/>
+      <c r="DX87" s="6"/>
+      <c r="DY87" s="6"/>
+      <c r="DZ87" s="6"/>
+      <c r="EA87" s="6"/>
+      <c r="EB87" s="6"/>
+      <c r="EC87" s="6"/>
+      <c r="ED87" s="6"/>
+      <c r="EE87" s="6"/>
+      <c r="EF87" s="6"/>
     </row>
-    <row r="88" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -17822,8 +20443,24 @@
       <c r="DN88" s="6"/>
       <c r="DO88" s="6"/>
       <c r="DP88" s="6"/>
+      <c r="DQ88" s="6"/>
+      <c r="DR88" s="6"/>
+      <c r="DS88" s="6"/>
+      <c r="DT88" s="6"/>
+      <c r="DU88" s="6"/>
+      <c r="DV88" s="6"/>
+      <c r="DW88" s="6"/>
+      <c r="DX88" s="6"/>
+      <c r="DY88" s="6"/>
+      <c r="DZ88" s="6"/>
+      <c r="EA88" s="6"/>
+      <c r="EB88" s="6"/>
+      <c r="EC88" s="6"/>
+      <c r="ED88" s="6"/>
+      <c r="EE88" s="6"/>
+      <c r="EF88" s="6"/>
     </row>
-    <row r="89" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -17944,8 +20581,24 @@
       <c r="DN89" s="6"/>
       <c r="DO89" s="6"/>
       <c r="DP89" s="6"/>
+      <c r="DQ89" s="6"/>
+      <c r="DR89" s="6"/>
+      <c r="DS89" s="6"/>
+      <c r="DT89" s="6"/>
+      <c r="DU89" s="6"/>
+      <c r="DV89" s="6"/>
+      <c r="DW89" s="6"/>
+      <c r="DX89" s="6"/>
+      <c r="DY89" s="6"/>
+      <c r="DZ89" s="6"/>
+      <c r="EA89" s="6"/>
+      <c r="EB89" s="6"/>
+      <c r="EC89" s="6"/>
+      <c r="ED89" s="6"/>
+      <c r="EE89" s="6"/>
+      <c r="EF89" s="6"/>
     </row>
-    <row r="90" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -18066,8 +20719,24 @@
       <c r="DN90" s="6"/>
       <c r="DO90" s="6"/>
       <c r="DP90" s="6"/>
+      <c r="DQ90" s="6"/>
+      <c r="DR90" s="6"/>
+      <c r="DS90" s="6"/>
+      <c r="DT90" s="6"/>
+      <c r="DU90" s="6"/>
+      <c r="DV90" s="6"/>
+      <c r="DW90" s="6"/>
+      <c r="DX90" s="6"/>
+      <c r="DY90" s="6"/>
+      <c r="DZ90" s="6"/>
+      <c r="EA90" s="6"/>
+      <c r="EB90" s="6"/>
+      <c r="EC90" s="6"/>
+      <c r="ED90" s="6"/>
+      <c r="EE90" s="6"/>
+      <c r="EF90" s="6"/>
     </row>
-    <row r="91" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>19</v>
       </c>
@@ -18105,147 +20774,175 @@
       <c r="W91" s="6"/>
       <c r="X91" s="6"/>
       <c r="Y91" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Z91" s="6"/>
       <c r="AA91" s="6"/>
       <c r="AB91" s="6"/>
       <c r="AC91" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AD91" s="6"/>
       <c r="AE91" s="6"/>
       <c r="AF91" s="6"/>
       <c r="AG91" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AH91" s="6"/>
       <c r="AI91" s="6"/>
       <c r="AJ91" s="6"/>
       <c r="AK91" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AL91" s="6"/>
       <c r="AM91" s="6"/>
       <c r="AN91" s="6"/>
       <c r="AO91" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AP91" s="6"/>
       <c r="AQ91" s="6"/>
       <c r="AR91" s="6"/>
       <c r="AS91" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AT91" s="6"/>
       <c r="AU91" s="6"/>
       <c r="AV91" s="6"/>
       <c r="AW91" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AX91" s="6"/>
       <c r="AY91" s="6"/>
       <c r="AZ91" s="6"/>
       <c r="BA91" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="BB91" s="6"/>
       <c r="BC91" s="6"/>
       <c r="BD91" s="6"/>
       <c r="BE91" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="BF91" s="6"/>
       <c r="BG91" s="6"/>
       <c r="BH91" s="6"/>
       <c r="BI91" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="BJ91" s="6"/>
       <c r="BK91" s="6"/>
       <c r="BL91" s="6"/>
       <c r="BM91" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="BN91" s="6"/>
       <c r="BO91" s="6"/>
       <c r="BP91" s="6"/>
       <c r="BQ91" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="BR91" s="6"/>
       <c r="BS91" s="6"/>
       <c r="BT91" s="6"/>
       <c r="BU91" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="BV91" s="6"/>
       <c r="BW91" s="6"/>
       <c r="BX91" s="6"/>
       <c r="BY91" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BZ91" s="6"/>
       <c r="CA91" s="6"/>
       <c r="CB91" s="6"/>
       <c r="CC91" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="CD91" s="6"/>
       <c r="CE91" s="6"/>
       <c r="CF91" s="6"/>
       <c r="CG91" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="CH91" s="6"/>
       <c r="CI91" s="6"/>
       <c r="CJ91" s="6"/>
       <c r="CK91" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="CL91" s="6"/>
       <c r="CM91" s="6"/>
       <c r="CN91" s="6"/>
       <c r="CO91" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="CP91" s="6"/>
       <c r="CQ91" s="6"/>
       <c r="CR91" s="6"/>
       <c r="CS91" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="CT91" s="6"/>
       <c r="CU91" s="6"/>
       <c r="CV91" s="6"/>
       <c r="CW91" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="CX91" s="6"/>
       <c r="CY91" s="6"/>
       <c r="CZ91" s="6"/>
       <c r="DA91" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="DB91" s="6"/>
       <c r="DC91" s="6"/>
       <c r="DD91" s="6"/>
       <c r="DE91" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="DF91" s="6"/>
       <c r="DG91" s="6"/>
       <c r="DH91" s="6"/>
-      <c r="DI91" s="5"/>
+      <c r="DI91" s="5" t="s">
+        <v>294</v>
+      </c>
       <c r="DJ91" s="6"/>
       <c r="DK91" s="6"/>
       <c r="DL91" s="6"/>
-      <c r="DM91" s="5"/>
+      <c r="DM91" s="5" t="s">
+        <v>295</v>
+      </c>
       <c r="DN91" s="6"/>
       <c r="DO91" s="6"/>
       <c r="DP91" s="6"/>
+      <c r="DQ91" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="DR91" s="6"/>
+      <c r="DS91" s="6"/>
+      <c r="DT91" s="6"/>
+      <c r="DU91" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="DV91" s="6"/>
+      <c r="DW91" s="6"/>
+      <c r="DX91" s="6"/>
+      <c r="DY91" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="DZ91" s="6"/>
+      <c r="EA91" s="6"/>
+      <c r="EB91" s="6"/>
+      <c r="EC91" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="ED91" s="6"/>
+      <c r="EE91" s="6"/>
+      <c r="EF91" s="6"/>
     </row>
-    <row r="92" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -18366,8 +21063,24 @@
       <c r="DN92" s="6"/>
       <c r="DO92" s="6"/>
       <c r="DP92" s="6"/>
+      <c r="DQ92" s="6"/>
+      <c r="DR92" s="6"/>
+      <c r="DS92" s="6"/>
+      <c r="DT92" s="6"/>
+      <c r="DU92" s="6"/>
+      <c r="DV92" s="6"/>
+      <c r="DW92" s="6"/>
+      <c r="DX92" s="6"/>
+      <c r="DY92" s="6"/>
+      <c r="DZ92" s="6"/>
+      <c r="EA92" s="6"/>
+      <c r="EB92" s="6"/>
+      <c r="EC92" s="6"/>
+      <c r="ED92" s="6"/>
+      <c r="EE92" s="6"/>
+      <c r="EF92" s="6"/>
     </row>
-    <row r="93" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -18488,8 +21201,24 @@
       <c r="DN93" s="6"/>
       <c r="DO93" s="6"/>
       <c r="DP93" s="6"/>
+      <c r="DQ93" s="6"/>
+      <c r="DR93" s="6"/>
+      <c r="DS93" s="6"/>
+      <c r="DT93" s="6"/>
+      <c r="DU93" s="6"/>
+      <c r="DV93" s="6"/>
+      <c r="DW93" s="6"/>
+      <c r="DX93" s="6"/>
+      <c r="DY93" s="6"/>
+      <c r="DZ93" s="6"/>
+      <c r="EA93" s="6"/>
+      <c r="EB93" s="6"/>
+      <c r="EC93" s="6"/>
+      <c r="ED93" s="6"/>
+      <c r="EE93" s="6"/>
+      <c r="EF93" s="6"/>
     </row>
-    <row r="94" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -18610,8 +21339,24 @@
       <c r="DN94" s="6"/>
       <c r="DO94" s="6"/>
       <c r="DP94" s="6"/>
+      <c r="DQ94" s="6"/>
+      <c r="DR94" s="6"/>
+      <c r="DS94" s="6"/>
+      <c r="DT94" s="6"/>
+      <c r="DU94" s="6"/>
+      <c r="DV94" s="6"/>
+      <c r="DW94" s="6"/>
+      <c r="DX94" s="6"/>
+      <c r="DY94" s="6"/>
+      <c r="DZ94" s="6"/>
+      <c r="EA94" s="6"/>
+      <c r="EB94" s="6"/>
+      <c r="EC94" s="6"/>
+      <c r="ED94" s="6"/>
+      <c r="EE94" s="6"/>
+      <c r="EF94" s="6"/>
     </row>
-    <row r="95" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -18732,8 +21477,24 @@
       <c r="DN95" s="6"/>
       <c r="DO95" s="6"/>
       <c r="DP95" s="6"/>
+      <c r="DQ95" s="6"/>
+      <c r="DR95" s="6"/>
+      <c r="DS95" s="6"/>
+      <c r="DT95" s="6"/>
+      <c r="DU95" s="6"/>
+      <c r="DV95" s="6"/>
+      <c r="DW95" s="6"/>
+      <c r="DX95" s="6"/>
+      <c r="DY95" s="6"/>
+      <c r="DZ95" s="6"/>
+      <c r="EA95" s="6"/>
+      <c r="EB95" s="6"/>
+      <c r="EC95" s="6"/>
+      <c r="ED95" s="6"/>
+      <c r="EE95" s="6"/>
+      <c r="EF95" s="6"/>
     </row>
-    <row r="96" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -18854,8 +21615,24 @@
       <c r="DN96" s="6"/>
       <c r="DO96" s="6"/>
       <c r="DP96" s="6"/>
+      <c r="DQ96" s="6"/>
+      <c r="DR96" s="6"/>
+      <c r="DS96" s="6"/>
+      <c r="DT96" s="6"/>
+      <c r="DU96" s="6"/>
+      <c r="DV96" s="6"/>
+      <c r="DW96" s="6"/>
+      <c r="DX96" s="6"/>
+      <c r="DY96" s="6"/>
+      <c r="DZ96" s="6"/>
+      <c r="EA96" s="6"/>
+      <c r="EB96" s="6"/>
+      <c r="EC96" s="6"/>
+      <c r="ED96" s="6"/>
+      <c r="EE96" s="6"/>
+      <c r="EF96" s="6"/>
     </row>
-    <row r="97" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -18976,8 +21753,24 @@
       <c r="DN97" s="6"/>
       <c r="DO97" s="6"/>
       <c r="DP97" s="6"/>
+      <c r="DQ97" s="6"/>
+      <c r="DR97" s="6"/>
+      <c r="DS97" s="6"/>
+      <c r="DT97" s="6"/>
+      <c r="DU97" s="6"/>
+      <c r="DV97" s="6"/>
+      <c r="DW97" s="6"/>
+      <c r="DX97" s="6"/>
+      <c r="DY97" s="6"/>
+      <c r="DZ97" s="6"/>
+      <c r="EA97" s="6"/>
+      <c r="EB97" s="6"/>
+      <c r="EC97" s="6"/>
+      <c r="ED97" s="6"/>
+      <c r="EE97" s="6"/>
+      <c r="EF97" s="6"/>
     </row>
-    <row r="98" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -19098,8 +21891,24 @@
       <c r="DN98" s="6"/>
       <c r="DO98" s="6"/>
       <c r="DP98" s="6"/>
+      <c r="DQ98" s="6"/>
+      <c r="DR98" s="6"/>
+      <c r="DS98" s="6"/>
+      <c r="DT98" s="6"/>
+      <c r="DU98" s="6"/>
+      <c r="DV98" s="6"/>
+      <c r="DW98" s="6"/>
+      <c r="DX98" s="6"/>
+      <c r="DY98" s="6"/>
+      <c r="DZ98" s="6"/>
+      <c r="EA98" s="6"/>
+      <c r="EB98" s="6"/>
+      <c r="EC98" s="6"/>
+      <c r="ED98" s="6"/>
+      <c r="EE98" s="6"/>
+      <c r="EF98" s="6"/>
     </row>
-    <row r="99" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -19220,8 +22029,24 @@
       <c r="DN99" s="6"/>
       <c r="DO99" s="6"/>
       <c r="DP99" s="6"/>
+      <c r="DQ99" s="6"/>
+      <c r="DR99" s="6"/>
+      <c r="DS99" s="6"/>
+      <c r="DT99" s="6"/>
+      <c r="DU99" s="6"/>
+      <c r="DV99" s="6"/>
+      <c r="DW99" s="6"/>
+      <c r="DX99" s="6"/>
+      <c r="DY99" s="6"/>
+      <c r="DZ99" s="6"/>
+      <c r="EA99" s="6"/>
+      <c r="EB99" s="6"/>
+      <c r="EC99" s="6"/>
+      <c r="ED99" s="6"/>
+      <c r="EE99" s="6"/>
+      <c r="EF99" s="6"/>
     </row>
-    <row r="100" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -19342,8 +22167,24 @@
       <c r="DN100" s="6"/>
       <c r="DO100" s="6"/>
       <c r="DP100" s="6"/>
+      <c r="DQ100" s="6"/>
+      <c r="DR100" s="6"/>
+      <c r="DS100" s="6"/>
+      <c r="DT100" s="6"/>
+      <c r="DU100" s="6"/>
+      <c r="DV100" s="6"/>
+      <c r="DW100" s="6"/>
+      <c r="DX100" s="6"/>
+      <c r="DY100" s="6"/>
+      <c r="DZ100" s="6"/>
+      <c r="EA100" s="6"/>
+      <c r="EB100" s="6"/>
+      <c r="EC100" s="6"/>
+      <c r="ED100" s="6"/>
+      <c r="EE100" s="6"/>
+      <c r="EF100" s="6"/>
     </row>
-    <row r="101" spans="1:120" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:136" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -19357,7 +22198,7 @@
       <c r="K101" s="4"/>
       <c r="L101" s="4"/>
     </row>
-    <row r="102" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A102" s="2"/>
       <c r="B102" s="3"/>
       <c r="C102" s="4"/>
@@ -19371,7 +22212,7 @@
       <c r="K102" s="4"/>
       <c r="L102" s="4"/>
     </row>
-    <row r="103" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A103" s="2"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -19385,7 +22226,7 @@
       <c r="K103" s="4"/>
       <c r="L103" s="4"/>
     </row>
-    <row r="104" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A104" s="2"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -19399,7 +22240,7 @@
       <c r="K104" s="4"/>
       <c r="L104" s="4"/>
     </row>
-    <row r="105" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A105" s="2"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -19412,8 +22253,11 @@
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
       <c r="L105" s="4"/>
+      <c r="DM105" t="s">
+        <v>289</v>
+      </c>
     </row>
-    <row r="106" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A106" s="2"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -19427,7 +22271,7 @@
       <c r="K106" s="4"/>
       <c r="L106" s="4"/>
     </row>
-    <row r="107" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A107" s="2"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -19441,7 +22285,7 @@
       <c r="K107" s="4"/>
       <c r="L107" s="4"/>
     </row>
-    <row r="108" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A108" s="2"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -19455,7 +22299,7 @@
       <c r="K108" s="4"/>
       <c r="L108" s="4"/>
     </row>
-    <row r="109" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A109" s="2"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -19469,7 +22313,7 @@
       <c r="K109" s="4"/>
       <c r="L109" s="4"/>
     </row>
-    <row r="110" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A110" s="2"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -19483,7 +22327,7 @@
       <c r="K110" s="4"/>
       <c r="L110" s="4"/>
     </row>
-    <row r="111" spans="1:120" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:136" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -19497,7 +22341,7 @@
       <c r="K111" s="4"/>
       <c r="L111" s="4"/>
     </row>
-    <row r="112" spans="1:120" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A112" s="2"/>
       <c r="B112" s="3"/>
       <c r="C112" s="4"/>
@@ -20050,107 +22894,223 @@
       <c r="E151" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="300">
-    <mergeCell ref="DA51:DD60"/>
-    <mergeCell ref="DE51:DH60"/>
-    <mergeCell ref="DA61:DD70"/>
-    <mergeCell ref="DE61:DH70"/>
-    <mergeCell ref="DA71:DD80"/>
-    <mergeCell ref="DE71:DH80"/>
-    <mergeCell ref="DA81:DD90"/>
-    <mergeCell ref="DE81:DH90"/>
-    <mergeCell ref="DA91:DD100"/>
-    <mergeCell ref="DE91:DH100"/>
-    <mergeCell ref="DA1:DD10"/>
-    <mergeCell ref="DE1:DH10"/>
-    <mergeCell ref="DA11:DD20"/>
-    <mergeCell ref="DE11:DH20"/>
-    <mergeCell ref="DA21:DD30"/>
-    <mergeCell ref="DE21:DH30"/>
-    <mergeCell ref="DA31:DD40"/>
-    <mergeCell ref="DE31:DH40"/>
-    <mergeCell ref="DA41:DD50"/>
-    <mergeCell ref="DE41:DH50"/>
-    <mergeCell ref="CS51:CV60"/>
-    <mergeCell ref="CW51:CZ60"/>
-    <mergeCell ref="CS61:CV70"/>
-    <mergeCell ref="CW61:CZ70"/>
-    <mergeCell ref="CS71:CV80"/>
-    <mergeCell ref="CW71:CZ80"/>
-    <mergeCell ref="CS81:CV90"/>
-    <mergeCell ref="CW81:CZ90"/>
-    <mergeCell ref="CS91:CV100"/>
-    <mergeCell ref="CW91:CZ100"/>
-    <mergeCell ref="CS1:CV10"/>
-    <mergeCell ref="CW1:CZ10"/>
-    <mergeCell ref="CS11:CV20"/>
-    <mergeCell ref="CW11:CZ20"/>
-    <mergeCell ref="CS21:CV30"/>
-    <mergeCell ref="CW21:CZ30"/>
-    <mergeCell ref="CS31:CV40"/>
-    <mergeCell ref="CW31:CZ40"/>
-    <mergeCell ref="CS41:CV50"/>
-    <mergeCell ref="CW41:CZ50"/>
-    <mergeCell ref="BU51:BX60"/>
-    <mergeCell ref="BY51:CB60"/>
-    <mergeCell ref="BU61:BX70"/>
-    <mergeCell ref="BY61:CB70"/>
-    <mergeCell ref="BU71:BX80"/>
-    <mergeCell ref="BY71:CB80"/>
-    <mergeCell ref="BU81:BX90"/>
-    <mergeCell ref="BY81:CB90"/>
-    <mergeCell ref="BU91:BX100"/>
-    <mergeCell ref="BY91:CB100"/>
-    <mergeCell ref="BU1:BX10"/>
-    <mergeCell ref="BY1:CB10"/>
-    <mergeCell ref="BU11:BX20"/>
-    <mergeCell ref="BY11:CB20"/>
-    <mergeCell ref="BU21:BX30"/>
-    <mergeCell ref="BY21:CB30"/>
-    <mergeCell ref="BU31:BX40"/>
-    <mergeCell ref="BY31:CB40"/>
-    <mergeCell ref="BU41:BX50"/>
-    <mergeCell ref="BY41:CB50"/>
-    <mergeCell ref="BM51:BP60"/>
-    <mergeCell ref="BQ51:BT60"/>
-    <mergeCell ref="BM61:BP70"/>
-    <mergeCell ref="BQ61:BT70"/>
-    <mergeCell ref="BM71:BP80"/>
-    <mergeCell ref="BQ71:BT80"/>
-    <mergeCell ref="BM81:BP90"/>
-    <mergeCell ref="BQ81:BT90"/>
-    <mergeCell ref="BM91:BP100"/>
-    <mergeCell ref="BQ91:BT100"/>
-    <mergeCell ref="BM1:BP10"/>
-    <mergeCell ref="BQ1:BT10"/>
-    <mergeCell ref="BM11:BP20"/>
-    <mergeCell ref="BQ11:BT20"/>
-    <mergeCell ref="BM21:BP30"/>
-    <mergeCell ref="BQ21:BT30"/>
-    <mergeCell ref="BM31:BP40"/>
-    <mergeCell ref="BQ31:BT40"/>
-    <mergeCell ref="BM41:BP50"/>
-    <mergeCell ref="BQ41:BT50"/>
-    <mergeCell ref="BE51:BH60"/>
-    <mergeCell ref="BI51:BL60"/>
-    <mergeCell ref="BE61:BH70"/>
-    <mergeCell ref="BI61:BL70"/>
-    <mergeCell ref="BE71:BH80"/>
-    <mergeCell ref="BI71:BL80"/>
-    <mergeCell ref="BE81:BH90"/>
-    <mergeCell ref="BI81:BL90"/>
-    <mergeCell ref="BE91:BH100"/>
-    <mergeCell ref="BI91:BL100"/>
-    <mergeCell ref="BE1:BH10"/>
-    <mergeCell ref="BI1:BL10"/>
-    <mergeCell ref="BE11:BH20"/>
-    <mergeCell ref="BI11:BL20"/>
-    <mergeCell ref="BE21:BH30"/>
-    <mergeCell ref="BI21:BL30"/>
-    <mergeCell ref="BE31:BH40"/>
-    <mergeCell ref="BI31:BL40"/>
-    <mergeCell ref="BE41:BH50"/>
-    <mergeCell ref="BI41:BL50"/>
+  <mergeCells count="340">
+    <mergeCell ref="DY51:EB60"/>
+    <mergeCell ref="EC51:EF60"/>
+    <mergeCell ref="DY71:EB80"/>
+    <mergeCell ref="EC71:EF80"/>
+    <mergeCell ref="DY81:EB90"/>
+    <mergeCell ref="EC81:EF90"/>
+    <mergeCell ref="DY91:EB100"/>
+    <mergeCell ref="EC91:EF100"/>
+    <mergeCell ref="DY61:EB70"/>
+    <mergeCell ref="EC61:EF70"/>
+    <mergeCell ref="DY1:EB10"/>
+    <mergeCell ref="EC1:EF10"/>
+    <mergeCell ref="DY11:EB20"/>
+    <mergeCell ref="EC11:EF20"/>
+    <mergeCell ref="DY21:EB30"/>
+    <mergeCell ref="EC21:EF30"/>
+    <mergeCell ref="DY31:EB40"/>
+    <mergeCell ref="EC31:EF40"/>
+    <mergeCell ref="DY41:EB50"/>
+    <mergeCell ref="EC41:EF50"/>
+    <mergeCell ref="DQ51:DT60"/>
+    <mergeCell ref="DU51:DX60"/>
+    <mergeCell ref="DQ61:DT70"/>
+    <mergeCell ref="DU61:DX70"/>
+    <mergeCell ref="DQ71:DT80"/>
+    <mergeCell ref="DU71:DX80"/>
+    <mergeCell ref="DQ81:DT90"/>
+    <mergeCell ref="DU81:DX90"/>
+    <mergeCell ref="DQ91:DT100"/>
+    <mergeCell ref="DU91:DX100"/>
+    <mergeCell ref="DQ1:DT10"/>
+    <mergeCell ref="DU1:DX10"/>
+    <mergeCell ref="DQ11:DT20"/>
+    <mergeCell ref="DU11:DX20"/>
+    <mergeCell ref="DQ21:DT30"/>
+    <mergeCell ref="DU21:DX30"/>
+    <mergeCell ref="DQ31:DT40"/>
+    <mergeCell ref="DU31:DX40"/>
+    <mergeCell ref="DQ41:DT50"/>
+    <mergeCell ref="DU41:DX50"/>
+    <mergeCell ref="DI51:DL60"/>
+    <mergeCell ref="DM51:DP60"/>
+    <mergeCell ref="DI61:DL70"/>
+    <mergeCell ref="DM61:DP70"/>
+    <mergeCell ref="DI71:DL80"/>
+    <mergeCell ref="DM71:DP80"/>
+    <mergeCell ref="DI81:DL90"/>
+    <mergeCell ref="DM81:DP90"/>
+    <mergeCell ref="DI91:DL100"/>
+    <mergeCell ref="DM91:DP100"/>
+    <mergeCell ref="DI1:DL10"/>
+    <mergeCell ref="DM1:DP10"/>
+    <mergeCell ref="DI11:DL20"/>
+    <mergeCell ref="DM11:DP20"/>
+    <mergeCell ref="DI21:DL30"/>
+    <mergeCell ref="DM21:DP30"/>
+    <mergeCell ref="DI31:DL40"/>
+    <mergeCell ref="DM31:DP40"/>
+    <mergeCell ref="DI41:DL50"/>
+    <mergeCell ref="DM41:DP50"/>
+    <mergeCell ref="CK51:CN60"/>
+    <mergeCell ref="CO51:CR60"/>
+    <mergeCell ref="CK61:CN70"/>
+    <mergeCell ref="CO61:CR70"/>
+    <mergeCell ref="CK71:CN80"/>
+    <mergeCell ref="CO71:CR80"/>
+    <mergeCell ref="CK81:CN90"/>
+    <mergeCell ref="CO81:CR90"/>
+    <mergeCell ref="CK91:CN100"/>
+    <mergeCell ref="CO91:CR100"/>
+    <mergeCell ref="CK1:CN10"/>
+    <mergeCell ref="CO1:CR10"/>
+    <mergeCell ref="CK11:CN20"/>
+    <mergeCell ref="CO11:CR20"/>
+    <mergeCell ref="CK21:CN30"/>
+    <mergeCell ref="CO21:CR30"/>
+    <mergeCell ref="CK31:CN40"/>
+    <mergeCell ref="CO31:CR40"/>
+    <mergeCell ref="CK41:CN50"/>
+    <mergeCell ref="CO41:CR50"/>
+    <mergeCell ref="CC51:CF60"/>
+    <mergeCell ref="CG51:CJ60"/>
+    <mergeCell ref="CC61:CF70"/>
+    <mergeCell ref="CG61:CJ70"/>
+    <mergeCell ref="CC71:CF80"/>
+    <mergeCell ref="CG71:CJ80"/>
+    <mergeCell ref="CC81:CF90"/>
+    <mergeCell ref="CG81:CJ90"/>
+    <mergeCell ref="CC91:CF100"/>
+    <mergeCell ref="CG91:CJ100"/>
+    <mergeCell ref="CC1:CF10"/>
+    <mergeCell ref="CG1:CJ10"/>
+    <mergeCell ref="CC11:CF20"/>
+    <mergeCell ref="CG11:CJ20"/>
+    <mergeCell ref="CC21:CF30"/>
+    <mergeCell ref="CG21:CJ30"/>
+    <mergeCell ref="CC31:CF40"/>
+    <mergeCell ref="CG31:CJ40"/>
+    <mergeCell ref="CC41:CF50"/>
+    <mergeCell ref="CG41:CJ50"/>
+    <mergeCell ref="AS91:AV100"/>
+    <mergeCell ref="AS61:AV70"/>
+    <mergeCell ref="AO71:AR80"/>
+    <mergeCell ref="AS71:AV80"/>
+    <mergeCell ref="AO81:AR90"/>
+    <mergeCell ref="AS81:AV90"/>
+    <mergeCell ref="AO31:AR40"/>
+    <mergeCell ref="AS31:AV40"/>
+    <mergeCell ref="AO41:AR50"/>
+    <mergeCell ref="AS41:AV50"/>
+    <mergeCell ref="AO51:AR60"/>
+    <mergeCell ref="AS51:AV60"/>
+    <mergeCell ref="AO1:AR10"/>
+    <mergeCell ref="AS1:AV10"/>
+    <mergeCell ref="AO11:AR20"/>
+    <mergeCell ref="AS11:AV20"/>
+    <mergeCell ref="AO21:AR30"/>
+    <mergeCell ref="AS21:AV30"/>
+    <mergeCell ref="AG81:AJ90"/>
+    <mergeCell ref="AK81:AN90"/>
+    <mergeCell ref="AG91:AJ100"/>
+    <mergeCell ref="AK91:AN100"/>
+    <mergeCell ref="AO91:AR100"/>
+    <mergeCell ref="AG51:AJ60"/>
+    <mergeCell ref="AK51:AN60"/>
+    <mergeCell ref="AG61:AJ70"/>
+    <mergeCell ref="AK61:AN70"/>
+    <mergeCell ref="AO61:AR70"/>
+    <mergeCell ref="AG1:AJ10"/>
+    <mergeCell ref="AK1:AN10"/>
+    <mergeCell ref="AG11:AJ20"/>
+    <mergeCell ref="AK11:AN20"/>
+    <mergeCell ref="AG21:AJ30"/>
+    <mergeCell ref="AK21:AN30"/>
+    <mergeCell ref="AG31:AJ40"/>
+    <mergeCell ref="AK31:AN40"/>
+    <mergeCell ref="AG41:AJ50"/>
+    <mergeCell ref="AK41:AN50"/>
+    <mergeCell ref="AG71:AJ80"/>
+    <mergeCell ref="AK71:AN80"/>
+    <mergeCell ref="A1:D10"/>
+    <mergeCell ref="E1:H10"/>
+    <mergeCell ref="A11:D20"/>
+    <mergeCell ref="E11:H20"/>
+    <mergeCell ref="A21:D30"/>
+    <mergeCell ref="E21:H30"/>
+    <mergeCell ref="M31:P40"/>
+    <mergeCell ref="I41:L50"/>
+    <mergeCell ref="M41:P50"/>
+    <mergeCell ref="A31:D40"/>
+    <mergeCell ref="E31:H40"/>
+    <mergeCell ref="A41:D50"/>
+    <mergeCell ref="E41:H50"/>
+    <mergeCell ref="I31:L40"/>
+    <mergeCell ref="I1:L10"/>
+    <mergeCell ref="M1:P10"/>
+    <mergeCell ref="I11:L20"/>
+    <mergeCell ref="M11:P20"/>
+    <mergeCell ref="I21:L30"/>
+    <mergeCell ref="M21:P30"/>
+    <mergeCell ref="A81:D90"/>
+    <mergeCell ref="E81:H90"/>
+    <mergeCell ref="A91:D100"/>
+    <mergeCell ref="E91:H100"/>
+    <mergeCell ref="A51:D60"/>
+    <mergeCell ref="E51:H60"/>
+    <mergeCell ref="A61:D70"/>
+    <mergeCell ref="E61:H70"/>
+    <mergeCell ref="A71:D80"/>
+    <mergeCell ref="E71:H80"/>
+    <mergeCell ref="I81:L90"/>
+    <mergeCell ref="M81:P90"/>
+    <mergeCell ref="I91:L100"/>
+    <mergeCell ref="M91:P100"/>
+    <mergeCell ref="I51:L60"/>
+    <mergeCell ref="M51:P60"/>
+    <mergeCell ref="I61:L70"/>
+    <mergeCell ref="M61:P70"/>
+    <mergeCell ref="I71:L80"/>
+    <mergeCell ref="M71:P80"/>
+    <mergeCell ref="Q1:T10"/>
+    <mergeCell ref="U1:X10"/>
+    <mergeCell ref="Y1:AB10"/>
+    <mergeCell ref="AC1:AF10"/>
+    <mergeCell ref="Q11:T20"/>
+    <mergeCell ref="U11:X20"/>
+    <mergeCell ref="Y11:AB20"/>
+    <mergeCell ref="AC11:AF20"/>
+    <mergeCell ref="Q21:T30"/>
+    <mergeCell ref="U21:X30"/>
+    <mergeCell ref="Y21:AB30"/>
+    <mergeCell ref="AC21:AF30"/>
+    <mergeCell ref="Q31:T40"/>
+    <mergeCell ref="U31:X40"/>
+    <mergeCell ref="Y31:AB40"/>
+    <mergeCell ref="AC31:AF40"/>
+    <mergeCell ref="Q41:T50"/>
+    <mergeCell ref="U41:X50"/>
+    <mergeCell ref="Y41:AB50"/>
+    <mergeCell ref="AC41:AF50"/>
+    <mergeCell ref="Q51:T60"/>
+    <mergeCell ref="U51:X60"/>
+    <mergeCell ref="Y51:AB60"/>
+    <mergeCell ref="AC51:AF60"/>
+    <mergeCell ref="Q61:T70"/>
+    <mergeCell ref="U61:X70"/>
+    <mergeCell ref="Y61:AB70"/>
+    <mergeCell ref="AC61:AF70"/>
+    <mergeCell ref="Q71:T80"/>
+    <mergeCell ref="U71:X80"/>
+    <mergeCell ref="Y71:AB80"/>
+    <mergeCell ref="AC71:AF80"/>
+    <mergeCell ref="Q81:T90"/>
+    <mergeCell ref="U81:X90"/>
+    <mergeCell ref="Y81:AB90"/>
+    <mergeCell ref="AC81:AF90"/>
     <mergeCell ref="Q91:T100"/>
     <mergeCell ref="U91:X100"/>
     <mergeCell ref="Y91:AB100"/>
@@ -20175,182 +23135,106 @@
     <mergeCell ref="BA81:BD90"/>
     <mergeCell ref="AW91:AZ100"/>
     <mergeCell ref="BA91:BD100"/>
-    <mergeCell ref="Q61:T70"/>
-    <mergeCell ref="U61:X70"/>
-    <mergeCell ref="Y61:AB70"/>
-    <mergeCell ref="AC61:AF70"/>
-    <mergeCell ref="Q71:T80"/>
-    <mergeCell ref="U71:X80"/>
-    <mergeCell ref="Y71:AB80"/>
-    <mergeCell ref="AC71:AF80"/>
-    <mergeCell ref="Q81:T90"/>
-    <mergeCell ref="U81:X90"/>
-    <mergeCell ref="Y81:AB90"/>
-    <mergeCell ref="AC81:AF90"/>
-    <mergeCell ref="Q31:T40"/>
-    <mergeCell ref="U31:X40"/>
-    <mergeCell ref="Y31:AB40"/>
-    <mergeCell ref="AC31:AF40"/>
-    <mergeCell ref="Q41:T50"/>
-    <mergeCell ref="U41:X50"/>
-    <mergeCell ref="Y41:AB50"/>
-    <mergeCell ref="AC41:AF50"/>
-    <mergeCell ref="Q51:T60"/>
-    <mergeCell ref="U51:X60"/>
-    <mergeCell ref="Y51:AB60"/>
-    <mergeCell ref="AC51:AF60"/>
-    <mergeCell ref="Q1:T10"/>
-    <mergeCell ref="U1:X10"/>
-    <mergeCell ref="Y1:AB10"/>
-    <mergeCell ref="AC1:AF10"/>
-    <mergeCell ref="Q11:T20"/>
-    <mergeCell ref="U11:X20"/>
-    <mergeCell ref="Y11:AB20"/>
-    <mergeCell ref="AC11:AF20"/>
-    <mergeCell ref="Q21:T30"/>
-    <mergeCell ref="U21:X30"/>
-    <mergeCell ref="Y21:AB30"/>
-    <mergeCell ref="AC21:AF30"/>
-    <mergeCell ref="I81:L90"/>
-    <mergeCell ref="M81:P90"/>
-    <mergeCell ref="I91:L100"/>
-    <mergeCell ref="M91:P100"/>
-    <mergeCell ref="I51:L60"/>
-    <mergeCell ref="M51:P60"/>
-    <mergeCell ref="I61:L70"/>
-    <mergeCell ref="M61:P70"/>
-    <mergeCell ref="I71:L80"/>
-    <mergeCell ref="M71:P80"/>
-    <mergeCell ref="A81:D90"/>
-    <mergeCell ref="E81:H90"/>
-    <mergeCell ref="A91:D100"/>
-    <mergeCell ref="E91:H100"/>
-    <mergeCell ref="A51:D60"/>
-    <mergeCell ref="E51:H60"/>
-    <mergeCell ref="A61:D70"/>
-    <mergeCell ref="E61:H70"/>
-    <mergeCell ref="A71:D80"/>
-    <mergeCell ref="E71:H80"/>
-    <mergeCell ref="AG41:AJ50"/>
-    <mergeCell ref="AK41:AN50"/>
-    <mergeCell ref="AG71:AJ80"/>
-    <mergeCell ref="AK71:AN80"/>
-    <mergeCell ref="A1:D10"/>
-    <mergeCell ref="E1:H10"/>
-    <mergeCell ref="A11:D20"/>
-    <mergeCell ref="E11:H20"/>
-    <mergeCell ref="A21:D30"/>
-    <mergeCell ref="E21:H30"/>
-    <mergeCell ref="M31:P40"/>
-    <mergeCell ref="I41:L50"/>
-    <mergeCell ref="M41:P50"/>
-    <mergeCell ref="A31:D40"/>
-    <mergeCell ref="E31:H40"/>
-    <mergeCell ref="A41:D50"/>
-    <mergeCell ref="E41:H50"/>
-    <mergeCell ref="I31:L40"/>
-    <mergeCell ref="I1:L10"/>
-    <mergeCell ref="M1:P10"/>
-    <mergeCell ref="I11:L20"/>
-    <mergeCell ref="M11:P20"/>
-    <mergeCell ref="I21:L30"/>
-    <mergeCell ref="M21:P30"/>
-    <mergeCell ref="AO1:AR10"/>
-    <mergeCell ref="AS1:AV10"/>
-    <mergeCell ref="AO11:AR20"/>
-    <mergeCell ref="AS11:AV20"/>
-    <mergeCell ref="AO21:AR30"/>
-    <mergeCell ref="AS21:AV30"/>
-    <mergeCell ref="AG81:AJ90"/>
-    <mergeCell ref="AK81:AN90"/>
-    <mergeCell ref="AG91:AJ100"/>
-    <mergeCell ref="AK91:AN100"/>
-    <mergeCell ref="AO91:AR100"/>
-    <mergeCell ref="AG51:AJ60"/>
-    <mergeCell ref="AK51:AN60"/>
-    <mergeCell ref="AG61:AJ70"/>
-    <mergeCell ref="AK61:AN70"/>
-    <mergeCell ref="AO61:AR70"/>
-    <mergeCell ref="AG1:AJ10"/>
-    <mergeCell ref="AK1:AN10"/>
-    <mergeCell ref="AG11:AJ20"/>
-    <mergeCell ref="AK11:AN20"/>
-    <mergeCell ref="AG21:AJ30"/>
-    <mergeCell ref="AK21:AN30"/>
-    <mergeCell ref="AG31:AJ40"/>
-    <mergeCell ref="AK31:AN40"/>
-    <mergeCell ref="AS91:AV100"/>
-    <mergeCell ref="AS61:AV70"/>
-    <mergeCell ref="AO71:AR80"/>
-    <mergeCell ref="AS71:AV80"/>
-    <mergeCell ref="AO81:AR90"/>
-    <mergeCell ref="AS81:AV90"/>
-    <mergeCell ref="AO31:AR40"/>
-    <mergeCell ref="AS31:AV40"/>
-    <mergeCell ref="AO41:AR50"/>
-    <mergeCell ref="AS41:AV50"/>
-    <mergeCell ref="AO51:AR60"/>
-    <mergeCell ref="AS51:AV60"/>
-    <mergeCell ref="CC1:CF10"/>
-    <mergeCell ref="CG1:CJ10"/>
-    <mergeCell ref="CC11:CF20"/>
-    <mergeCell ref="CG11:CJ20"/>
-    <mergeCell ref="CC21:CF30"/>
-    <mergeCell ref="CG21:CJ30"/>
-    <mergeCell ref="CC31:CF40"/>
-    <mergeCell ref="CG31:CJ40"/>
-    <mergeCell ref="CC41:CF50"/>
-    <mergeCell ref="CG41:CJ50"/>
-    <mergeCell ref="CC51:CF60"/>
-    <mergeCell ref="CG51:CJ60"/>
-    <mergeCell ref="CC61:CF70"/>
-    <mergeCell ref="CG61:CJ70"/>
-    <mergeCell ref="CC71:CF80"/>
-    <mergeCell ref="CG71:CJ80"/>
-    <mergeCell ref="CC81:CF90"/>
-    <mergeCell ref="CG81:CJ90"/>
-    <mergeCell ref="CC91:CF100"/>
-    <mergeCell ref="CG91:CJ100"/>
-    <mergeCell ref="CK1:CN10"/>
-    <mergeCell ref="CO1:CR10"/>
-    <mergeCell ref="CK11:CN20"/>
-    <mergeCell ref="CO11:CR20"/>
-    <mergeCell ref="CK21:CN30"/>
-    <mergeCell ref="CO21:CR30"/>
-    <mergeCell ref="CK31:CN40"/>
-    <mergeCell ref="CO31:CR40"/>
-    <mergeCell ref="CK41:CN50"/>
-    <mergeCell ref="CO41:CR50"/>
-    <mergeCell ref="CK51:CN60"/>
-    <mergeCell ref="CO51:CR60"/>
-    <mergeCell ref="CK61:CN70"/>
-    <mergeCell ref="CO61:CR70"/>
-    <mergeCell ref="CK71:CN80"/>
-    <mergeCell ref="CO71:CR80"/>
-    <mergeCell ref="CK81:CN90"/>
-    <mergeCell ref="CO81:CR90"/>
-    <mergeCell ref="CK91:CN100"/>
-    <mergeCell ref="CO91:CR100"/>
-    <mergeCell ref="DI1:DL10"/>
-    <mergeCell ref="DM1:DP10"/>
-    <mergeCell ref="DI11:DL20"/>
-    <mergeCell ref="DM11:DP20"/>
-    <mergeCell ref="DI21:DL30"/>
-    <mergeCell ref="DM21:DP30"/>
-    <mergeCell ref="DI31:DL40"/>
-    <mergeCell ref="DM31:DP40"/>
-    <mergeCell ref="DI41:DL50"/>
-    <mergeCell ref="DM41:DP50"/>
-    <mergeCell ref="DI51:DL60"/>
-    <mergeCell ref="DM51:DP60"/>
-    <mergeCell ref="DI61:DL70"/>
-    <mergeCell ref="DM61:DP70"/>
-    <mergeCell ref="DI71:DL80"/>
-    <mergeCell ref="DM71:DP80"/>
-    <mergeCell ref="DI81:DL90"/>
-    <mergeCell ref="DM81:DP90"/>
-    <mergeCell ref="DI91:DL100"/>
-    <mergeCell ref="DM91:DP100"/>
+    <mergeCell ref="BE1:BH10"/>
+    <mergeCell ref="BI1:BL10"/>
+    <mergeCell ref="BE11:BH20"/>
+    <mergeCell ref="BI11:BL20"/>
+    <mergeCell ref="BE21:BH30"/>
+    <mergeCell ref="BI21:BL30"/>
+    <mergeCell ref="BE31:BH40"/>
+    <mergeCell ref="BI31:BL40"/>
+    <mergeCell ref="BE41:BH50"/>
+    <mergeCell ref="BI41:BL50"/>
+    <mergeCell ref="BE51:BH60"/>
+    <mergeCell ref="BI51:BL60"/>
+    <mergeCell ref="BE61:BH70"/>
+    <mergeCell ref="BI61:BL70"/>
+    <mergeCell ref="BE71:BH80"/>
+    <mergeCell ref="BI71:BL80"/>
+    <mergeCell ref="BE81:BH90"/>
+    <mergeCell ref="BI81:BL90"/>
+    <mergeCell ref="BE91:BH100"/>
+    <mergeCell ref="BI91:BL100"/>
+    <mergeCell ref="BM1:BP10"/>
+    <mergeCell ref="BQ1:BT10"/>
+    <mergeCell ref="BM11:BP20"/>
+    <mergeCell ref="BQ11:BT20"/>
+    <mergeCell ref="BM21:BP30"/>
+    <mergeCell ref="BQ21:BT30"/>
+    <mergeCell ref="BM31:BP40"/>
+    <mergeCell ref="BQ31:BT40"/>
+    <mergeCell ref="BM41:BP50"/>
+    <mergeCell ref="BQ41:BT50"/>
+    <mergeCell ref="BM51:BP60"/>
+    <mergeCell ref="BQ51:BT60"/>
+    <mergeCell ref="BM61:BP70"/>
+    <mergeCell ref="BQ61:BT70"/>
+    <mergeCell ref="BM71:BP80"/>
+    <mergeCell ref="BQ71:BT80"/>
+    <mergeCell ref="BM81:BP90"/>
+    <mergeCell ref="BQ81:BT90"/>
+    <mergeCell ref="BM91:BP100"/>
+    <mergeCell ref="BQ91:BT100"/>
+    <mergeCell ref="BU1:BX10"/>
+    <mergeCell ref="BY1:CB10"/>
+    <mergeCell ref="BU11:BX20"/>
+    <mergeCell ref="BY11:CB20"/>
+    <mergeCell ref="BU21:BX30"/>
+    <mergeCell ref="BY21:CB30"/>
+    <mergeCell ref="BU31:BX40"/>
+    <mergeCell ref="BY31:CB40"/>
+    <mergeCell ref="BU41:BX50"/>
+    <mergeCell ref="BY41:CB50"/>
+    <mergeCell ref="BU51:BX60"/>
+    <mergeCell ref="BY51:CB60"/>
+    <mergeCell ref="BU61:BX70"/>
+    <mergeCell ref="BY61:CB70"/>
+    <mergeCell ref="BU71:BX80"/>
+    <mergeCell ref="BY71:CB80"/>
+    <mergeCell ref="BU81:BX90"/>
+    <mergeCell ref="BY81:CB90"/>
+    <mergeCell ref="BU91:BX100"/>
+    <mergeCell ref="BY91:CB100"/>
+    <mergeCell ref="CS1:CV10"/>
+    <mergeCell ref="CW1:CZ10"/>
+    <mergeCell ref="CS11:CV20"/>
+    <mergeCell ref="CW11:CZ20"/>
+    <mergeCell ref="CS21:CV30"/>
+    <mergeCell ref="CW21:CZ30"/>
+    <mergeCell ref="CS31:CV40"/>
+    <mergeCell ref="CW31:CZ40"/>
+    <mergeCell ref="CS41:CV50"/>
+    <mergeCell ref="CW41:CZ50"/>
+    <mergeCell ref="CS51:CV60"/>
+    <mergeCell ref="CW51:CZ60"/>
+    <mergeCell ref="CS61:CV70"/>
+    <mergeCell ref="CW61:CZ70"/>
+    <mergeCell ref="CS71:CV80"/>
+    <mergeCell ref="CW71:CZ80"/>
+    <mergeCell ref="CS81:CV90"/>
+    <mergeCell ref="CW81:CZ90"/>
+    <mergeCell ref="CS91:CV100"/>
+    <mergeCell ref="CW91:CZ100"/>
+    <mergeCell ref="DA1:DD10"/>
+    <mergeCell ref="DE1:DH10"/>
+    <mergeCell ref="DA11:DD20"/>
+    <mergeCell ref="DE11:DH20"/>
+    <mergeCell ref="DA21:DD30"/>
+    <mergeCell ref="DE21:DH30"/>
+    <mergeCell ref="DA31:DD40"/>
+    <mergeCell ref="DE31:DH40"/>
+    <mergeCell ref="DA41:DD50"/>
+    <mergeCell ref="DE41:DH50"/>
+    <mergeCell ref="DA51:DD60"/>
+    <mergeCell ref="DE51:DH60"/>
+    <mergeCell ref="DA61:DD70"/>
+    <mergeCell ref="DE61:DH70"/>
+    <mergeCell ref="DA71:DD80"/>
+    <mergeCell ref="DE71:DH80"/>
+    <mergeCell ref="DA81:DD90"/>
+    <mergeCell ref="DE81:DH90"/>
+    <mergeCell ref="DA91:DD100"/>
+    <mergeCell ref="DE91:DH100"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.6692913385826772" right="0.6692913385826772" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/tanulókártyák/Tanulókártyák.xlsx
+++ b/tanulókártyák/Tanulókártyák.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atesz\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FC1C67-2A45-4257-AA32-C39BD9A3BB22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851F31B6-9251-447D-82FC-1E667113CFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="339">
   <si>
     <r>
       <rPr>
@@ -6131,9 +6131,6 @@
       </rPr>
       <t xml:space="preserve"> - Megmutatja, mennyi extra memória kell az algoritmusnak.</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">spring annotiációk </t>
   </si>
   <si>
     <r>
@@ -7412,10 +7409,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -7748,7 +7745,7 @@
       <c r="AA1" s="8"/>
       <c r="AB1" s="8"/>
       <c r="AC1" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AD1" s="8"/>
       <c r="AE1" s="8"/>
@@ -7886,25 +7883,25 @@
       <c r="DO1" s="8"/>
       <c r="DP1" s="8"/>
       <c r="DQ1" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="DR1" s="8"/>
       <c r="DS1" s="8"/>
       <c r="DT1" s="8"/>
       <c r="DU1" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="DV1" s="8"/>
       <c r="DW1" s="8"/>
       <c r="DX1" s="8"/>
       <c r="DY1" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="DZ1" s="8"/>
       <c r="EA1" s="8"/>
       <c r="EB1" s="8"/>
       <c r="EC1" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="ED1" s="8"/>
       <c r="EE1" s="8"/>
@@ -9334,25 +9331,25 @@
       <c r="DO11" s="8"/>
       <c r="DP11" s="8"/>
       <c r="DQ11" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="DR11" s="8"/>
       <c r="DS11" s="8"/>
       <c r="DT11" s="8"/>
       <c r="DU11" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="DV11" s="8"/>
       <c r="DW11" s="8"/>
       <c r="DX11" s="8"/>
       <c r="DY11" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="DZ11" s="8"/>
       <c r="EA11" s="8"/>
       <c r="EB11" s="8"/>
       <c r="EC11" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="ED11" s="8"/>
       <c r="EE11" s="8"/>
@@ -10781,26 +10778,26 @@
       <c r="DN21" s="8"/>
       <c r="DO21" s="8"/>
       <c r="DP21" s="8"/>
-      <c r="DQ21" s="10" t="s">
-        <v>305</v>
+      <c r="DQ21" s="9" t="s">
+        <v>304</v>
       </c>
       <c r="DR21" s="8"/>
       <c r="DS21" s="8"/>
       <c r="DT21" s="8"/>
       <c r="DU21" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="DV21" s="8"/>
       <c r="DW21" s="8"/>
       <c r="DX21" s="8"/>
-      <c r="DY21" s="10" t="s">
-        <v>324</v>
+      <c r="DY21" s="9" t="s">
+        <v>323</v>
       </c>
       <c r="DZ21" s="8"/>
       <c r="EA21" s="8"/>
       <c r="EB21" s="8"/>
       <c r="EC21" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="ED21" s="8"/>
       <c r="EE21" s="8"/>
@@ -12218,37 +12215,37 @@
       <c r="DG31" s="8"/>
       <c r="DH31" s="8"/>
       <c r="DI31" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="DJ31" s="8"/>
       <c r="DK31" s="8"/>
       <c r="DL31" s="8"/>
       <c r="DM31" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="DN31" s="8"/>
       <c r="DO31" s="8"/>
       <c r="DP31" s="8"/>
       <c r="DQ31" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="DR31" s="8"/>
       <c r="DS31" s="8"/>
       <c r="DT31" s="8"/>
       <c r="DU31" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="DV31" s="8"/>
       <c r="DW31" s="8"/>
       <c r="DX31" s="8"/>
       <c r="DY31" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="DZ31" s="8"/>
       <c r="EA31" s="8"/>
       <c r="EB31" s="8"/>
       <c r="EC31" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="ED31" s="8"/>
       <c r="EE31" s="8"/>
@@ -13599,7 +13596,7 @@
       <c r="BN41" s="8"/>
       <c r="BO41" s="8"/>
       <c r="BP41" s="8"/>
-      <c r="BQ41" s="9" t="s">
+      <c r="BQ41" s="10" t="s">
         <v>174</v>
       </c>
       <c r="BR41" s="8"/>
@@ -13611,7 +13608,7 @@
       <c r="BV41" s="8"/>
       <c r="BW41" s="8"/>
       <c r="BX41" s="8"/>
-      <c r="BY41" s="9" t="s">
+      <c r="BY41" s="10" t="s">
         <v>192</v>
       </c>
       <c r="BZ41" s="8"/>
@@ -13623,7 +13620,7 @@
       <c r="CD41" s="8"/>
       <c r="CE41" s="8"/>
       <c r="CF41" s="8"/>
-      <c r="CG41" s="9" t="s">
+      <c r="CG41" s="10" t="s">
         <v>213</v>
       </c>
       <c r="CH41" s="8"/>
@@ -13635,7 +13632,7 @@
       <c r="CL41" s="8"/>
       <c r="CM41" s="8"/>
       <c r="CN41" s="8"/>
-      <c r="CO41" s="9" t="s">
+      <c r="CO41" s="10" t="s">
         <v>234</v>
       </c>
       <c r="CP41" s="8"/>
@@ -13647,7 +13644,7 @@
       <c r="CT41" s="8"/>
       <c r="CU41" s="8"/>
       <c r="CV41" s="8"/>
-      <c r="CW41" s="9" t="s">
+      <c r="CW41" s="10" t="s">
         <v>253</v>
       </c>
       <c r="CX41" s="8"/>
@@ -13659,44 +13656,44 @@
       <c r="DB41" s="8"/>
       <c r="DC41" s="8"/>
       <c r="DD41" s="8"/>
-      <c r="DE41" s="9" t="s">
+      <c r="DE41" s="10" t="s">
         <v>275</v>
       </c>
       <c r="DF41" s="8"/>
       <c r="DG41" s="8"/>
       <c r="DH41" s="8"/>
       <c r="DI41" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="DJ41" s="8"/>
       <c r="DK41" s="8"/>
       <c r="DL41" s="8"/>
-      <c r="DM41" s="9" t="s">
-        <v>296</v>
+      <c r="DM41" s="10" t="s">
+        <v>295</v>
       </c>
       <c r="DN41" s="8"/>
       <c r="DO41" s="8"/>
       <c r="DP41" s="8"/>
       <c r="DQ41" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="DR41" s="8"/>
       <c r="DS41" s="8"/>
       <c r="DT41" s="8"/>
-      <c r="DU41" s="9" t="s">
-        <v>320</v>
+      <c r="DU41" s="10" t="s">
+        <v>319</v>
       </c>
       <c r="DV41" s="8"/>
       <c r="DW41" s="8"/>
       <c r="DX41" s="8"/>
       <c r="DY41" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="DZ41" s="8"/>
       <c r="EA41" s="8"/>
       <c r="EB41" s="8"/>
-      <c r="EC41" s="9" t="s">
-        <v>336</v>
+      <c r="EC41" s="10" t="s">
+        <v>335</v>
       </c>
       <c r="ED41" s="8"/>
       <c r="EE41" s="8"/>
@@ -15126,25 +15123,25 @@
       <c r="DO51" s="6"/>
       <c r="DP51" s="6"/>
       <c r="DQ51" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="DR51" s="6"/>
       <c r="DS51" s="6"/>
       <c r="DT51" s="6"/>
       <c r="DU51" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="DV51" s="6"/>
       <c r="DW51" s="6"/>
       <c r="DX51" s="6"/>
       <c r="DY51" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="DZ51" s="6"/>
       <c r="EA51" s="6"/>
       <c r="EB51" s="6"/>
       <c r="EC51" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="ED51" s="6"/>
       <c r="EE51" s="6"/>
@@ -16430,7 +16427,7 @@
       <c r="W61" s="6"/>
       <c r="X61" s="6"/>
       <c r="Y61" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Z61" s="6"/>
       <c r="AA61" s="6"/>
@@ -16574,25 +16571,25 @@
       <c r="DO61" s="6"/>
       <c r="DP61" s="6"/>
       <c r="DQ61" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="DR61" s="6"/>
       <c r="DS61" s="6"/>
       <c r="DT61" s="6"/>
       <c r="DU61" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="DV61" s="6"/>
       <c r="DW61" s="6"/>
       <c r="DX61" s="6"/>
       <c r="DY61" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="DZ61" s="6"/>
       <c r="EA61" s="6"/>
       <c r="EB61" s="6"/>
       <c r="EC61" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="ED61" s="6"/>
       <c r="EE61" s="6"/>
@@ -18022,25 +18019,25 @@
       <c r="DO71" s="6"/>
       <c r="DP71" s="6"/>
       <c r="DQ71" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="DR71" s="6"/>
       <c r="DS71" s="6"/>
       <c r="DT71" s="6"/>
       <c r="DU71" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="DV71" s="6"/>
       <c r="DW71" s="6"/>
       <c r="DX71" s="6"/>
       <c r="DY71" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="DZ71" s="6"/>
       <c r="EA71" s="6"/>
       <c r="EB71" s="6"/>
       <c r="EC71" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="ED71" s="6"/>
       <c r="EE71" s="6"/>
@@ -19458,37 +19455,37 @@
       <c r="DG81" s="6"/>
       <c r="DH81" s="6"/>
       <c r="DI81" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="DJ81" s="6"/>
       <c r="DK81" s="6"/>
       <c r="DL81" s="6"/>
       <c r="DM81" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="DN81" s="6"/>
       <c r="DO81" s="6"/>
       <c r="DP81" s="6"/>
       <c r="DQ81" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="DR81" s="6"/>
       <c r="DS81" s="6"/>
       <c r="DT81" s="6"/>
       <c r="DU81" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="DV81" s="6"/>
       <c r="DW81" s="6"/>
       <c r="DX81" s="6"/>
       <c r="DY81" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="DZ81" s="6"/>
       <c r="EA81" s="6"/>
       <c r="EB81" s="6"/>
       <c r="EC81" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="ED81" s="6"/>
       <c r="EE81" s="6"/>
@@ -20906,37 +20903,37 @@
       <c r="DG91" s="6"/>
       <c r="DH91" s="6"/>
       <c r="DI91" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="DJ91" s="6"/>
       <c r="DK91" s="6"/>
       <c r="DL91" s="6"/>
       <c r="DM91" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="DN91" s="6"/>
       <c r="DO91" s="6"/>
       <c r="DP91" s="6"/>
       <c r="DQ91" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="DR91" s="6"/>
       <c r="DS91" s="6"/>
       <c r="DT91" s="6"/>
       <c r="DU91" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="DV91" s="6"/>
       <c r="DW91" s="6"/>
       <c r="DX91" s="6"/>
       <c r="DY91" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="DZ91" s="6"/>
       <c r="EA91" s="6"/>
       <c r="EB91" s="6"/>
       <c r="EC91" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="ED91" s="6"/>
       <c r="EE91" s="6"/>
@@ -22253,9 +22250,6 @@
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
       <c r="L105" s="4"/>
-      <c r="DM105" t="s">
-        <v>289</v>
-      </c>
     </row>
     <row r="106" spans="1:136" x14ac:dyDescent="0.3">
       <c r="A106" s="2"/>
@@ -22895,118 +22889,210 @@
     </row>
   </sheetData>
   <mergeCells count="340">
-    <mergeCell ref="DY51:EB60"/>
-    <mergeCell ref="EC51:EF60"/>
-    <mergeCell ref="DY71:EB80"/>
-    <mergeCell ref="EC71:EF80"/>
-    <mergeCell ref="DY81:EB90"/>
-    <mergeCell ref="EC81:EF90"/>
-    <mergeCell ref="DY91:EB100"/>
-    <mergeCell ref="EC91:EF100"/>
-    <mergeCell ref="DY61:EB70"/>
-    <mergeCell ref="EC61:EF70"/>
-    <mergeCell ref="DY1:EB10"/>
-    <mergeCell ref="EC1:EF10"/>
-    <mergeCell ref="DY11:EB20"/>
-    <mergeCell ref="EC11:EF20"/>
-    <mergeCell ref="DY21:EB30"/>
-    <mergeCell ref="EC21:EF30"/>
-    <mergeCell ref="DY31:EB40"/>
-    <mergeCell ref="EC31:EF40"/>
-    <mergeCell ref="DY41:EB50"/>
-    <mergeCell ref="EC41:EF50"/>
-    <mergeCell ref="DQ51:DT60"/>
-    <mergeCell ref="DU51:DX60"/>
-    <mergeCell ref="DQ61:DT70"/>
-    <mergeCell ref="DU61:DX70"/>
-    <mergeCell ref="DQ71:DT80"/>
-    <mergeCell ref="DU71:DX80"/>
-    <mergeCell ref="DQ81:DT90"/>
-    <mergeCell ref="DU81:DX90"/>
-    <mergeCell ref="DQ91:DT100"/>
-    <mergeCell ref="DU91:DX100"/>
-    <mergeCell ref="DQ1:DT10"/>
-    <mergeCell ref="DU1:DX10"/>
-    <mergeCell ref="DQ11:DT20"/>
-    <mergeCell ref="DU11:DX20"/>
-    <mergeCell ref="DQ21:DT30"/>
-    <mergeCell ref="DU21:DX30"/>
-    <mergeCell ref="DQ31:DT40"/>
-    <mergeCell ref="DU31:DX40"/>
-    <mergeCell ref="DQ41:DT50"/>
-    <mergeCell ref="DU41:DX50"/>
-    <mergeCell ref="DI51:DL60"/>
-    <mergeCell ref="DM51:DP60"/>
-    <mergeCell ref="DI61:DL70"/>
-    <mergeCell ref="DM61:DP70"/>
-    <mergeCell ref="DI71:DL80"/>
-    <mergeCell ref="DM71:DP80"/>
-    <mergeCell ref="DI81:DL90"/>
-    <mergeCell ref="DM81:DP90"/>
-    <mergeCell ref="DI91:DL100"/>
-    <mergeCell ref="DM91:DP100"/>
-    <mergeCell ref="DI1:DL10"/>
-    <mergeCell ref="DM1:DP10"/>
-    <mergeCell ref="DI11:DL20"/>
-    <mergeCell ref="DM11:DP20"/>
-    <mergeCell ref="DI21:DL30"/>
-    <mergeCell ref="DM21:DP30"/>
-    <mergeCell ref="DI31:DL40"/>
-    <mergeCell ref="DM31:DP40"/>
-    <mergeCell ref="DI41:DL50"/>
-    <mergeCell ref="DM41:DP50"/>
-    <mergeCell ref="CK51:CN60"/>
-    <mergeCell ref="CO51:CR60"/>
-    <mergeCell ref="CK61:CN70"/>
-    <mergeCell ref="CO61:CR70"/>
-    <mergeCell ref="CK71:CN80"/>
-    <mergeCell ref="CO71:CR80"/>
-    <mergeCell ref="CK81:CN90"/>
-    <mergeCell ref="CO81:CR90"/>
-    <mergeCell ref="CK91:CN100"/>
-    <mergeCell ref="CO91:CR100"/>
-    <mergeCell ref="CK1:CN10"/>
-    <mergeCell ref="CO1:CR10"/>
-    <mergeCell ref="CK11:CN20"/>
-    <mergeCell ref="CO11:CR20"/>
-    <mergeCell ref="CK21:CN30"/>
-    <mergeCell ref="CO21:CR30"/>
-    <mergeCell ref="CK31:CN40"/>
-    <mergeCell ref="CO31:CR40"/>
-    <mergeCell ref="CK41:CN50"/>
-    <mergeCell ref="CO41:CR50"/>
-    <mergeCell ref="CC51:CF60"/>
-    <mergeCell ref="CG51:CJ60"/>
-    <mergeCell ref="CC61:CF70"/>
-    <mergeCell ref="CG61:CJ70"/>
-    <mergeCell ref="CC71:CF80"/>
-    <mergeCell ref="CG71:CJ80"/>
-    <mergeCell ref="CC81:CF90"/>
-    <mergeCell ref="CG81:CJ90"/>
-    <mergeCell ref="CC91:CF100"/>
-    <mergeCell ref="CG91:CJ100"/>
-    <mergeCell ref="CC1:CF10"/>
-    <mergeCell ref="CG1:CJ10"/>
-    <mergeCell ref="CC11:CF20"/>
-    <mergeCell ref="CG11:CJ20"/>
-    <mergeCell ref="CC21:CF30"/>
-    <mergeCell ref="CG21:CJ30"/>
-    <mergeCell ref="CC31:CF40"/>
-    <mergeCell ref="CG31:CJ40"/>
-    <mergeCell ref="CC41:CF50"/>
-    <mergeCell ref="CG41:CJ50"/>
-    <mergeCell ref="AS91:AV100"/>
-    <mergeCell ref="AS61:AV70"/>
-    <mergeCell ref="AO71:AR80"/>
-    <mergeCell ref="AS71:AV80"/>
-    <mergeCell ref="AO81:AR90"/>
-    <mergeCell ref="AS81:AV90"/>
-    <mergeCell ref="AO31:AR40"/>
-    <mergeCell ref="AS31:AV40"/>
-    <mergeCell ref="AO41:AR50"/>
-    <mergeCell ref="AS41:AV50"/>
-    <mergeCell ref="AO51:AR60"/>
-    <mergeCell ref="AS51:AV60"/>
+    <mergeCell ref="DA51:DD60"/>
+    <mergeCell ref="DE51:DH60"/>
+    <mergeCell ref="DA61:DD70"/>
+    <mergeCell ref="DE61:DH70"/>
+    <mergeCell ref="DA71:DD80"/>
+    <mergeCell ref="DE71:DH80"/>
+    <mergeCell ref="DA81:DD90"/>
+    <mergeCell ref="DE81:DH90"/>
+    <mergeCell ref="DA91:DD100"/>
+    <mergeCell ref="DE91:DH100"/>
+    <mergeCell ref="DA1:DD10"/>
+    <mergeCell ref="DE1:DH10"/>
+    <mergeCell ref="DA11:DD20"/>
+    <mergeCell ref="DE11:DH20"/>
+    <mergeCell ref="DA21:DD30"/>
+    <mergeCell ref="DE21:DH30"/>
+    <mergeCell ref="DA31:DD40"/>
+    <mergeCell ref="DE31:DH40"/>
+    <mergeCell ref="DA41:DD50"/>
+    <mergeCell ref="DE41:DH50"/>
+    <mergeCell ref="CS51:CV60"/>
+    <mergeCell ref="CW51:CZ60"/>
+    <mergeCell ref="CS61:CV70"/>
+    <mergeCell ref="CW61:CZ70"/>
+    <mergeCell ref="CS71:CV80"/>
+    <mergeCell ref="CW71:CZ80"/>
+    <mergeCell ref="CS81:CV90"/>
+    <mergeCell ref="CW81:CZ90"/>
+    <mergeCell ref="CS91:CV100"/>
+    <mergeCell ref="CW91:CZ100"/>
+    <mergeCell ref="CS1:CV10"/>
+    <mergeCell ref="CW1:CZ10"/>
+    <mergeCell ref="CS11:CV20"/>
+    <mergeCell ref="CW11:CZ20"/>
+    <mergeCell ref="CS21:CV30"/>
+    <mergeCell ref="CW21:CZ30"/>
+    <mergeCell ref="CS31:CV40"/>
+    <mergeCell ref="CW31:CZ40"/>
+    <mergeCell ref="CS41:CV50"/>
+    <mergeCell ref="CW41:CZ50"/>
+    <mergeCell ref="BU51:BX60"/>
+    <mergeCell ref="BY51:CB60"/>
+    <mergeCell ref="BU61:BX70"/>
+    <mergeCell ref="BY61:CB70"/>
+    <mergeCell ref="BU71:BX80"/>
+    <mergeCell ref="BY71:CB80"/>
+    <mergeCell ref="BU81:BX90"/>
+    <mergeCell ref="BY81:CB90"/>
+    <mergeCell ref="BU91:BX100"/>
+    <mergeCell ref="BY91:CB100"/>
+    <mergeCell ref="BU1:BX10"/>
+    <mergeCell ref="BY1:CB10"/>
+    <mergeCell ref="BU11:BX20"/>
+    <mergeCell ref="BY11:CB20"/>
+    <mergeCell ref="BU21:BX30"/>
+    <mergeCell ref="BY21:CB30"/>
+    <mergeCell ref="BU31:BX40"/>
+    <mergeCell ref="BY31:CB40"/>
+    <mergeCell ref="BU41:BX50"/>
+    <mergeCell ref="BY41:CB50"/>
+    <mergeCell ref="BM51:BP60"/>
+    <mergeCell ref="BQ51:BT60"/>
+    <mergeCell ref="BM61:BP70"/>
+    <mergeCell ref="BQ61:BT70"/>
+    <mergeCell ref="BM71:BP80"/>
+    <mergeCell ref="BQ71:BT80"/>
+    <mergeCell ref="BM81:BP90"/>
+    <mergeCell ref="BQ81:BT90"/>
+    <mergeCell ref="BM91:BP100"/>
+    <mergeCell ref="BQ91:BT100"/>
+    <mergeCell ref="BM1:BP10"/>
+    <mergeCell ref="BQ1:BT10"/>
+    <mergeCell ref="BM11:BP20"/>
+    <mergeCell ref="BQ11:BT20"/>
+    <mergeCell ref="BM21:BP30"/>
+    <mergeCell ref="BQ21:BT30"/>
+    <mergeCell ref="BM31:BP40"/>
+    <mergeCell ref="BQ31:BT40"/>
+    <mergeCell ref="BM41:BP50"/>
+    <mergeCell ref="BQ41:BT50"/>
+    <mergeCell ref="BE51:BH60"/>
+    <mergeCell ref="BI51:BL60"/>
+    <mergeCell ref="BE61:BH70"/>
+    <mergeCell ref="BI61:BL70"/>
+    <mergeCell ref="BE71:BH80"/>
+    <mergeCell ref="BI71:BL80"/>
+    <mergeCell ref="BE81:BH90"/>
+    <mergeCell ref="BI81:BL90"/>
+    <mergeCell ref="BE91:BH100"/>
+    <mergeCell ref="BI91:BL100"/>
+    <mergeCell ref="BE1:BH10"/>
+    <mergeCell ref="BI1:BL10"/>
+    <mergeCell ref="BE11:BH20"/>
+    <mergeCell ref="BI11:BL20"/>
+    <mergeCell ref="BE21:BH30"/>
+    <mergeCell ref="BI21:BL30"/>
+    <mergeCell ref="BE31:BH40"/>
+    <mergeCell ref="BI31:BL40"/>
+    <mergeCell ref="BE41:BH50"/>
+    <mergeCell ref="BI41:BL50"/>
+    <mergeCell ref="Q91:T100"/>
+    <mergeCell ref="U91:X100"/>
+    <mergeCell ref="Y91:AB100"/>
+    <mergeCell ref="AC91:AF100"/>
+    <mergeCell ref="AW1:AZ10"/>
+    <mergeCell ref="BA1:BD10"/>
+    <mergeCell ref="AW11:AZ20"/>
+    <mergeCell ref="BA11:BD20"/>
+    <mergeCell ref="AW21:AZ30"/>
+    <mergeCell ref="BA21:BD30"/>
+    <mergeCell ref="AW31:AZ40"/>
+    <mergeCell ref="BA31:BD40"/>
+    <mergeCell ref="AW41:AZ50"/>
+    <mergeCell ref="BA41:BD50"/>
+    <mergeCell ref="AW51:AZ60"/>
+    <mergeCell ref="BA51:BD60"/>
+    <mergeCell ref="AW61:AZ70"/>
+    <mergeCell ref="BA61:BD70"/>
+    <mergeCell ref="AW71:AZ80"/>
+    <mergeCell ref="BA71:BD80"/>
+    <mergeCell ref="AW81:AZ90"/>
+    <mergeCell ref="BA81:BD90"/>
+    <mergeCell ref="AW91:AZ100"/>
+    <mergeCell ref="BA91:BD100"/>
+    <mergeCell ref="Q61:T70"/>
+    <mergeCell ref="U61:X70"/>
+    <mergeCell ref="Y61:AB70"/>
+    <mergeCell ref="AC61:AF70"/>
+    <mergeCell ref="Q71:T80"/>
+    <mergeCell ref="U71:X80"/>
+    <mergeCell ref="Y71:AB80"/>
+    <mergeCell ref="AC71:AF80"/>
+    <mergeCell ref="Q81:T90"/>
+    <mergeCell ref="U81:X90"/>
+    <mergeCell ref="Y81:AB90"/>
+    <mergeCell ref="AC81:AF90"/>
+    <mergeCell ref="Q31:T40"/>
+    <mergeCell ref="U31:X40"/>
+    <mergeCell ref="Y31:AB40"/>
+    <mergeCell ref="AC31:AF40"/>
+    <mergeCell ref="Q41:T50"/>
+    <mergeCell ref="U41:X50"/>
+    <mergeCell ref="Y41:AB50"/>
+    <mergeCell ref="AC41:AF50"/>
+    <mergeCell ref="Q51:T60"/>
+    <mergeCell ref="U51:X60"/>
+    <mergeCell ref="Y51:AB60"/>
+    <mergeCell ref="AC51:AF60"/>
+    <mergeCell ref="Q1:T10"/>
+    <mergeCell ref="U1:X10"/>
+    <mergeCell ref="Y1:AB10"/>
+    <mergeCell ref="AC1:AF10"/>
+    <mergeCell ref="Q11:T20"/>
+    <mergeCell ref="U11:X20"/>
+    <mergeCell ref="Y11:AB20"/>
+    <mergeCell ref="AC11:AF20"/>
+    <mergeCell ref="Q21:T30"/>
+    <mergeCell ref="U21:X30"/>
+    <mergeCell ref="Y21:AB30"/>
+    <mergeCell ref="AC21:AF30"/>
+    <mergeCell ref="I81:L90"/>
+    <mergeCell ref="M81:P90"/>
+    <mergeCell ref="I91:L100"/>
+    <mergeCell ref="M91:P100"/>
+    <mergeCell ref="I51:L60"/>
+    <mergeCell ref="M51:P60"/>
+    <mergeCell ref="I61:L70"/>
+    <mergeCell ref="M61:P70"/>
+    <mergeCell ref="I71:L80"/>
+    <mergeCell ref="M71:P80"/>
+    <mergeCell ref="A81:D90"/>
+    <mergeCell ref="E81:H90"/>
+    <mergeCell ref="A91:D100"/>
+    <mergeCell ref="E91:H100"/>
+    <mergeCell ref="A51:D60"/>
+    <mergeCell ref="E51:H60"/>
+    <mergeCell ref="A61:D70"/>
+    <mergeCell ref="E61:H70"/>
+    <mergeCell ref="A71:D80"/>
+    <mergeCell ref="E71:H80"/>
+    <mergeCell ref="AG41:AJ50"/>
+    <mergeCell ref="AK41:AN50"/>
+    <mergeCell ref="AG71:AJ80"/>
+    <mergeCell ref="AK71:AN80"/>
+    <mergeCell ref="A1:D10"/>
+    <mergeCell ref="E1:H10"/>
+    <mergeCell ref="A11:D20"/>
+    <mergeCell ref="E11:H20"/>
+    <mergeCell ref="A21:D30"/>
+    <mergeCell ref="E21:H30"/>
+    <mergeCell ref="M31:P40"/>
+    <mergeCell ref="I41:L50"/>
+    <mergeCell ref="M41:P50"/>
+    <mergeCell ref="A31:D40"/>
+    <mergeCell ref="E31:H40"/>
+    <mergeCell ref="A41:D50"/>
+    <mergeCell ref="E41:H50"/>
+    <mergeCell ref="I31:L40"/>
+    <mergeCell ref="I1:L10"/>
+    <mergeCell ref="M1:P10"/>
+    <mergeCell ref="I11:L20"/>
+    <mergeCell ref="M11:P20"/>
+    <mergeCell ref="I21:L30"/>
+    <mergeCell ref="M21:P30"/>
     <mergeCell ref="AO1:AR10"/>
     <mergeCell ref="AS1:AV10"/>
     <mergeCell ref="AO11:AR20"/>
@@ -23031,213 +23117,121 @@
     <mergeCell ref="AK21:AN30"/>
     <mergeCell ref="AG31:AJ40"/>
     <mergeCell ref="AK31:AN40"/>
-    <mergeCell ref="AG41:AJ50"/>
-    <mergeCell ref="AK41:AN50"/>
-    <mergeCell ref="AG71:AJ80"/>
-    <mergeCell ref="AK71:AN80"/>
-    <mergeCell ref="A1:D10"/>
-    <mergeCell ref="E1:H10"/>
-    <mergeCell ref="A11:D20"/>
-    <mergeCell ref="E11:H20"/>
-    <mergeCell ref="A21:D30"/>
-    <mergeCell ref="E21:H30"/>
-    <mergeCell ref="M31:P40"/>
-    <mergeCell ref="I41:L50"/>
-    <mergeCell ref="M41:P50"/>
-    <mergeCell ref="A31:D40"/>
-    <mergeCell ref="E31:H40"/>
-    <mergeCell ref="A41:D50"/>
-    <mergeCell ref="E41:H50"/>
-    <mergeCell ref="I31:L40"/>
-    <mergeCell ref="I1:L10"/>
-    <mergeCell ref="M1:P10"/>
-    <mergeCell ref="I11:L20"/>
-    <mergeCell ref="M11:P20"/>
-    <mergeCell ref="I21:L30"/>
-    <mergeCell ref="M21:P30"/>
-    <mergeCell ref="A81:D90"/>
-    <mergeCell ref="E81:H90"/>
-    <mergeCell ref="A91:D100"/>
-    <mergeCell ref="E91:H100"/>
-    <mergeCell ref="A51:D60"/>
-    <mergeCell ref="E51:H60"/>
-    <mergeCell ref="A61:D70"/>
-    <mergeCell ref="E61:H70"/>
-    <mergeCell ref="A71:D80"/>
-    <mergeCell ref="E71:H80"/>
-    <mergeCell ref="I81:L90"/>
-    <mergeCell ref="M81:P90"/>
-    <mergeCell ref="I91:L100"/>
-    <mergeCell ref="M91:P100"/>
-    <mergeCell ref="I51:L60"/>
-    <mergeCell ref="M51:P60"/>
-    <mergeCell ref="I61:L70"/>
-    <mergeCell ref="M61:P70"/>
-    <mergeCell ref="I71:L80"/>
-    <mergeCell ref="M71:P80"/>
-    <mergeCell ref="Q1:T10"/>
-    <mergeCell ref="U1:X10"/>
-    <mergeCell ref="Y1:AB10"/>
-    <mergeCell ref="AC1:AF10"/>
-    <mergeCell ref="Q11:T20"/>
-    <mergeCell ref="U11:X20"/>
-    <mergeCell ref="Y11:AB20"/>
-    <mergeCell ref="AC11:AF20"/>
-    <mergeCell ref="Q21:T30"/>
-    <mergeCell ref="U21:X30"/>
-    <mergeCell ref="Y21:AB30"/>
-    <mergeCell ref="AC21:AF30"/>
-    <mergeCell ref="Q31:T40"/>
-    <mergeCell ref="U31:X40"/>
-    <mergeCell ref="Y31:AB40"/>
-    <mergeCell ref="AC31:AF40"/>
-    <mergeCell ref="Q41:T50"/>
-    <mergeCell ref="U41:X50"/>
-    <mergeCell ref="Y41:AB50"/>
-    <mergeCell ref="AC41:AF50"/>
-    <mergeCell ref="Q51:T60"/>
-    <mergeCell ref="U51:X60"/>
-    <mergeCell ref="Y51:AB60"/>
-    <mergeCell ref="AC51:AF60"/>
-    <mergeCell ref="Q61:T70"/>
-    <mergeCell ref="U61:X70"/>
-    <mergeCell ref="Y61:AB70"/>
-    <mergeCell ref="AC61:AF70"/>
-    <mergeCell ref="Q71:T80"/>
-    <mergeCell ref="U71:X80"/>
-    <mergeCell ref="Y71:AB80"/>
-    <mergeCell ref="AC71:AF80"/>
-    <mergeCell ref="Q81:T90"/>
-    <mergeCell ref="U81:X90"/>
-    <mergeCell ref="Y81:AB90"/>
-    <mergeCell ref="AC81:AF90"/>
-    <mergeCell ref="Q91:T100"/>
-    <mergeCell ref="U91:X100"/>
-    <mergeCell ref="Y91:AB100"/>
-    <mergeCell ref="AC91:AF100"/>
-    <mergeCell ref="AW1:AZ10"/>
-    <mergeCell ref="BA1:BD10"/>
-    <mergeCell ref="AW11:AZ20"/>
-    <mergeCell ref="BA11:BD20"/>
-    <mergeCell ref="AW21:AZ30"/>
-    <mergeCell ref="BA21:BD30"/>
-    <mergeCell ref="AW31:AZ40"/>
-    <mergeCell ref="BA31:BD40"/>
-    <mergeCell ref="AW41:AZ50"/>
-    <mergeCell ref="BA41:BD50"/>
-    <mergeCell ref="AW51:AZ60"/>
-    <mergeCell ref="BA51:BD60"/>
-    <mergeCell ref="AW61:AZ70"/>
-    <mergeCell ref="BA61:BD70"/>
-    <mergeCell ref="AW71:AZ80"/>
-    <mergeCell ref="BA71:BD80"/>
-    <mergeCell ref="AW81:AZ90"/>
-    <mergeCell ref="BA81:BD90"/>
-    <mergeCell ref="AW91:AZ100"/>
-    <mergeCell ref="BA91:BD100"/>
-    <mergeCell ref="BE1:BH10"/>
-    <mergeCell ref="BI1:BL10"/>
-    <mergeCell ref="BE11:BH20"/>
-    <mergeCell ref="BI11:BL20"/>
-    <mergeCell ref="BE21:BH30"/>
-    <mergeCell ref="BI21:BL30"/>
-    <mergeCell ref="BE31:BH40"/>
-    <mergeCell ref="BI31:BL40"/>
-    <mergeCell ref="BE41:BH50"/>
-    <mergeCell ref="BI41:BL50"/>
-    <mergeCell ref="BE51:BH60"/>
-    <mergeCell ref="BI51:BL60"/>
-    <mergeCell ref="BE61:BH70"/>
-    <mergeCell ref="BI61:BL70"/>
-    <mergeCell ref="BE71:BH80"/>
-    <mergeCell ref="BI71:BL80"/>
-    <mergeCell ref="BE81:BH90"/>
-    <mergeCell ref="BI81:BL90"/>
-    <mergeCell ref="BE91:BH100"/>
-    <mergeCell ref="BI91:BL100"/>
-    <mergeCell ref="BM1:BP10"/>
-    <mergeCell ref="BQ1:BT10"/>
-    <mergeCell ref="BM11:BP20"/>
-    <mergeCell ref="BQ11:BT20"/>
-    <mergeCell ref="BM21:BP30"/>
-    <mergeCell ref="BQ21:BT30"/>
-    <mergeCell ref="BM31:BP40"/>
-    <mergeCell ref="BQ31:BT40"/>
-    <mergeCell ref="BM41:BP50"/>
-    <mergeCell ref="BQ41:BT50"/>
-    <mergeCell ref="BM51:BP60"/>
-    <mergeCell ref="BQ51:BT60"/>
-    <mergeCell ref="BM61:BP70"/>
-    <mergeCell ref="BQ61:BT70"/>
-    <mergeCell ref="BM71:BP80"/>
-    <mergeCell ref="BQ71:BT80"/>
-    <mergeCell ref="BM81:BP90"/>
-    <mergeCell ref="BQ81:BT90"/>
-    <mergeCell ref="BM91:BP100"/>
-    <mergeCell ref="BQ91:BT100"/>
-    <mergeCell ref="BU1:BX10"/>
-    <mergeCell ref="BY1:CB10"/>
-    <mergeCell ref="BU11:BX20"/>
-    <mergeCell ref="BY11:CB20"/>
-    <mergeCell ref="BU21:BX30"/>
-    <mergeCell ref="BY21:CB30"/>
-    <mergeCell ref="BU31:BX40"/>
-    <mergeCell ref="BY31:CB40"/>
-    <mergeCell ref="BU41:BX50"/>
-    <mergeCell ref="BY41:CB50"/>
-    <mergeCell ref="BU51:BX60"/>
-    <mergeCell ref="BY51:CB60"/>
-    <mergeCell ref="BU61:BX70"/>
-    <mergeCell ref="BY61:CB70"/>
-    <mergeCell ref="BU71:BX80"/>
-    <mergeCell ref="BY71:CB80"/>
-    <mergeCell ref="BU81:BX90"/>
-    <mergeCell ref="BY81:CB90"/>
-    <mergeCell ref="BU91:BX100"/>
-    <mergeCell ref="BY91:CB100"/>
-    <mergeCell ref="CS1:CV10"/>
-    <mergeCell ref="CW1:CZ10"/>
-    <mergeCell ref="CS11:CV20"/>
-    <mergeCell ref="CW11:CZ20"/>
-    <mergeCell ref="CS21:CV30"/>
-    <mergeCell ref="CW21:CZ30"/>
-    <mergeCell ref="CS31:CV40"/>
-    <mergeCell ref="CW31:CZ40"/>
-    <mergeCell ref="CS41:CV50"/>
-    <mergeCell ref="CW41:CZ50"/>
-    <mergeCell ref="CS51:CV60"/>
-    <mergeCell ref="CW51:CZ60"/>
-    <mergeCell ref="CS61:CV70"/>
-    <mergeCell ref="CW61:CZ70"/>
-    <mergeCell ref="CS71:CV80"/>
-    <mergeCell ref="CW71:CZ80"/>
-    <mergeCell ref="CS81:CV90"/>
-    <mergeCell ref="CW81:CZ90"/>
-    <mergeCell ref="CS91:CV100"/>
-    <mergeCell ref="CW91:CZ100"/>
-    <mergeCell ref="DA1:DD10"/>
-    <mergeCell ref="DE1:DH10"/>
-    <mergeCell ref="DA11:DD20"/>
-    <mergeCell ref="DE11:DH20"/>
-    <mergeCell ref="DA21:DD30"/>
-    <mergeCell ref="DE21:DH30"/>
-    <mergeCell ref="DA31:DD40"/>
-    <mergeCell ref="DE31:DH40"/>
-    <mergeCell ref="DA41:DD50"/>
-    <mergeCell ref="DE41:DH50"/>
-    <mergeCell ref="DA51:DD60"/>
-    <mergeCell ref="DE51:DH60"/>
-    <mergeCell ref="DA61:DD70"/>
-    <mergeCell ref="DE61:DH70"/>
-    <mergeCell ref="DA71:DD80"/>
-    <mergeCell ref="DE71:DH80"/>
-    <mergeCell ref="DA81:DD90"/>
-    <mergeCell ref="DE81:DH90"/>
-    <mergeCell ref="DA91:DD100"/>
-    <mergeCell ref="DE91:DH100"/>
+    <mergeCell ref="AS91:AV100"/>
+    <mergeCell ref="AS61:AV70"/>
+    <mergeCell ref="AO71:AR80"/>
+    <mergeCell ref="AS71:AV80"/>
+    <mergeCell ref="AO81:AR90"/>
+    <mergeCell ref="AS81:AV90"/>
+    <mergeCell ref="AO31:AR40"/>
+    <mergeCell ref="AS31:AV40"/>
+    <mergeCell ref="AO41:AR50"/>
+    <mergeCell ref="AS41:AV50"/>
+    <mergeCell ref="AO51:AR60"/>
+    <mergeCell ref="AS51:AV60"/>
+    <mergeCell ref="CC1:CF10"/>
+    <mergeCell ref="CG1:CJ10"/>
+    <mergeCell ref="CC11:CF20"/>
+    <mergeCell ref="CG11:CJ20"/>
+    <mergeCell ref="CC21:CF30"/>
+    <mergeCell ref="CG21:CJ30"/>
+    <mergeCell ref="CC31:CF40"/>
+    <mergeCell ref="CG31:CJ40"/>
+    <mergeCell ref="CC41:CF50"/>
+    <mergeCell ref="CG41:CJ50"/>
+    <mergeCell ref="CC51:CF60"/>
+    <mergeCell ref="CG51:CJ60"/>
+    <mergeCell ref="CC61:CF70"/>
+    <mergeCell ref="CG61:CJ70"/>
+    <mergeCell ref="CC71:CF80"/>
+    <mergeCell ref="CG71:CJ80"/>
+    <mergeCell ref="CC81:CF90"/>
+    <mergeCell ref="CG81:CJ90"/>
+    <mergeCell ref="CC91:CF100"/>
+    <mergeCell ref="CG91:CJ100"/>
+    <mergeCell ref="CK1:CN10"/>
+    <mergeCell ref="CO1:CR10"/>
+    <mergeCell ref="CK11:CN20"/>
+    <mergeCell ref="CO11:CR20"/>
+    <mergeCell ref="CK21:CN30"/>
+    <mergeCell ref="CO21:CR30"/>
+    <mergeCell ref="CK31:CN40"/>
+    <mergeCell ref="CO31:CR40"/>
+    <mergeCell ref="CK41:CN50"/>
+    <mergeCell ref="CO41:CR50"/>
+    <mergeCell ref="CK51:CN60"/>
+    <mergeCell ref="CO51:CR60"/>
+    <mergeCell ref="CK61:CN70"/>
+    <mergeCell ref="CO61:CR70"/>
+    <mergeCell ref="CK71:CN80"/>
+    <mergeCell ref="CO71:CR80"/>
+    <mergeCell ref="CK81:CN90"/>
+    <mergeCell ref="CO81:CR90"/>
+    <mergeCell ref="CK91:CN100"/>
+    <mergeCell ref="CO91:CR100"/>
+    <mergeCell ref="DI1:DL10"/>
+    <mergeCell ref="DM1:DP10"/>
+    <mergeCell ref="DI11:DL20"/>
+    <mergeCell ref="DM11:DP20"/>
+    <mergeCell ref="DI21:DL30"/>
+    <mergeCell ref="DM21:DP30"/>
+    <mergeCell ref="DI31:DL40"/>
+    <mergeCell ref="DM31:DP40"/>
+    <mergeCell ref="DI41:DL50"/>
+    <mergeCell ref="DM41:DP50"/>
+    <mergeCell ref="DI51:DL60"/>
+    <mergeCell ref="DM51:DP60"/>
+    <mergeCell ref="DI61:DL70"/>
+    <mergeCell ref="DM61:DP70"/>
+    <mergeCell ref="DI71:DL80"/>
+    <mergeCell ref="DM71:DP80"/>
+    <mergeCell ref="DI81:DL90"/>
+    <mergeCell ref="DM81:DP90"/>
+    <mergeCell ref="DI91:DL100"/>
+    <mergeCell ref="DM91:DP100"/>
+    <mergeCell ref="DQ1:DT10"/>
+    <mergeCell ref="DU1:DX10"/>
+    <mergeCell ref="DQ11:DT20"/>
+    <mergeCell ref="DU11:DX20"/>
+    <mergeCell ref="DQ21:DT30"/>
+    <mergeCell ref="DU21:DX30"/>
+    <mergeCell ref="DQ31:DT40"/>
+    <mergeCell ref="DU31:DX40"/>
+    <mergeCell ref="DQ41:DT50"/>
+    <mergeCell ref="DU41:DX50"/>
+    <mergeCell ref="DQ51:DT60"/>
+    <mergeCell ref="DU51:DX60"/>
+    <mergeCell ref="DQ61:DT70"/>
+    <mergeCell ref="DU61:DX70"/>
+    <mergeCell ref="DQ71:DT80"/>
+    <mergeCell ref="DU71:DX80"/>
+    <mergeCell ref="DQ81:DT90"/>
+    <mergeCell ref="DU81:DX90"/>
+    <mergeCell ref="DQ91:DT100"/>
+    <mergeCell ref="DU91:DX100"/>
+    <mergeCell ref="DY1:EB10"/>
+    <mergeCell ref="EC1:EF10"/>
+    <mergeCell ref="DY11:EB20"/>
+    <mergeCell ref="EC11:EF20"/>
+    <mergeCell ref="DY21:EB30"/>
+    <mergeCell ref="EC21:EF30"/>
+    <mergeCell ref="DY31:EB40"/>
+    <mergeCell ref="EC31:EF40"/>
+    <mergeCell ref="DY41:EB50"/>
+    <mergeCell ref="EC41:EF50"/>
+    <mergeCell ref="DY51:EB60"/>
+    <mergeCell ref="EC51:EF60"/>
+    <mergeCell ref="DY71:EB80"/>
+    <mergeCell ref="EC71:EF80"/>
+    <mergeCell ref="DY81:EB90"/>
+    <mergeCell ref="EC81:EF90"/>
+    <mergeCell ref="DY91:EB100"/>
+    <mergeCell ref="EC91:EF100"/>
+    <mergeCell ref="DY61:EB70"/>
+    <mergeCell ref="EC61:EF70"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.6692913385826772" right="0.6692913385826772" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/tanulókártyák/Tanulókártyák.xlsx
+++ b/tanulókártyák/Tanulókártyák.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atesz\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851F31B6-9251-447D-82FC-1E667113CFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC9964E-DA1F-4E0A-8397-F3EE43BA6D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="359">
   <si>
     <r>
       <rPr>
@@ -7300,6 +7300,345 @@
       <t xml:space="preserve"> - Olyan objektum, melynek állapota a létrehozása után nem változtatható meg. Minden „módosítás” valójában egy új objektum létrehozását jelenti. 
 Példa: String, Wrapper objects, java.time package (majdnem) minden eleme</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Singleton</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> egy tervezési minta, amely biztosítja, hogy egy osztályból csak egy példány létezzen az alkalmazásban.
+Ezt gyakran egy privát konstruktorral és egy statikus példánymezővel valósítják meg.
+Globális hozzáférési pontot biztosít az egyetlen példányhoz.
+Gyakran használják konfigurációkhoz vagy közös erőforrások kezeléséhez.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a Singleton?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Reflection API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> lehetővé teszi, hogy futásidőben vizsgáljuk és módosítsuk az osztályokat, metódusokat és mezőket.
+Segítségével dinamikusan hívhatunk meg metódusokat vagy érhetünk el privát attribútumokat is.
+A Java java.lang.reflect csomagjában található.
+Használata rugalmas, de lassabb és kevésbé biztonságos.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@Component</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> egy Spring annotáció, amely egy osztályt Spring Bean-né tesz.
+A Spring automatikusan felismeri és kezeli az ilyen osztályokat component scan során.
+Ezeket dependency injection-nel lehet más komponensekbe injektálni.
+Általános célú annotáció, amelyet szolgáltatások, repository-k és más bean-ek alapjául is használnak.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a Reflection API?</t>
+  </si>
+  <si>
+    <t>Mit csinál a @Component annotáció?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@SpringBootApplication</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Ez egy összetett annotáció Spring Boot-ban, amely három annotációt egyesít: @Configuration, @EnableAutoConfiguration, @ComponentScan.
+Ez indítja el a Spring Boot alkalmazás automatikus konfigurációját.
+Megadja a kiindulópontot az alkalmazás futtatásához.
+Általában a main osztályon található.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mit csinál a @SpringBootApplication annotáció?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Servlet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> egy Java objektum, amely HTTP kéréseket kezel webes alkalmazásokban.
+A szerver (pl. Tomcat) futtatja és kezeli az életciklusát.
+Kérésekre válaszokat generál, általában dinamikus weboldalakhoz vagy API-khoz.
+A jakarta.servlet (korábban javax.servlet) csomag része.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a Servlet?</t>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Web Container</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (servlet container) olyan környezet, amely futtatja a servlet-eket.
+Kezeli az életciklust, a kérések feldolgozását és a szálkezelést.
+Példák: Apache Tomcat, Jetty.
+Biztosítja a webalkalmazások futtatásához szükséges infrastruktúrát.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a Web Container?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Web Server</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> HTTP kéréseket fogad és válaszokat küld vissza.
+Statikus tartalmat (HTML, CSS, képek) is kiszolgálhat.
+Dinamikus tartalom esetén gyakran együttműködik egy alkalmazásszerverrel vagy servlet containerrel.
+Példa: Apache HTTP Server, Nginx.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi a Web Server?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Servlet lifecycle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+A servlet életciklusa három fő lépésből áll: inicializálás, kéréskezelés és megsemmisítés.
+Az init() metódus egyszer fut le létrehozáskor.
+A service() vagy doGet/doPost kezeli a kéréseket.
+A destroy() akkor hívódik meg, amikor a servletet eltávolítják.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mit tudsz a servlet lifecycle-ről?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thread</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (szál) egy program végrehajtási egysége.
+Egy folyamatban több szál is futhat párhuzamosan.
+Java-ban a Thread osztály vagy Runnable interfész segítségével hozható létre.
+A szálak lehetővé teszik a párhuzamos feldolgozást és jobb teljesítményt.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HTML (HyperText Markup Language)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+A HTML a weboldalak struktúrájának leírására szolgáló jelölőnyelv.
+Ezzel határozzuk meg, hogy egy oldal milyen elemekből áll, például címek, bekezdések, képek és linkek.
+A HTML nem programozási nyelv, mert nem tartalmaz logikát, csak struktúrát ír le.
+A böngészők értelmezik és jelenítik meg a HTML kódot vizuális weboldallá.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mi az HTML?</t>
+  </si>
+  <si>
+    <t>Mi a thread?</t>
   </si>
 </sst>
 </file>
@@ -7695,13 +8034,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:EF151"/>
+  <dimension ref="A1:EN151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="136" width="11" customWidth="1"/>
+    <col min="1" max="144" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -7906,8 +8245,20 @@
       <c r="ED1" s="8"/>
       <c r="EE1" s="8"/>
       <c r="EF1" s="8"/>
+      <c r="EG1" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="EH1" s="8"/>
+      <c r="EI1" s="8"/>
+      <c r="EJ1" s="8"/>
+      <c r="EK1" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="EL1" s="8"/>
+      <c r="EM1" s="8"/>
+      <c r="EN1" s="8"/>
     </row>
-    <row r="2" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -8044,8 +8395,16 @@
       <c r="ED2" s="8"/>
       <c r="EE2" s="8"/>
       <c r="EF2" s="8"/>
+      <c r="EG2" s="8"/>
+      <c r="EH2" s="8"/>
+      <c r="EI2" s="8"/>
+      <c r="EJ2" s="8"/>
+      <c r="EK2" s="8"/>
+      <c r="EL2" s="8"/>
+      <c r="EM2" s="8"/>
+      <c r="EN2" s="8"/>
     </row>
-    <row r="3" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -8182,8 +8541,16 @@
       <c r="ED3" s="8"/>
       <c r="EE3" s="8"/>
       <c r="EF3" s="8"/>
+      <c r="EG3" s="8"/>
+      <c r="EH3" s="8"/>
+      <c r="EI3" s="8"/>
+      <c r="EJ3" s="8"/>
+      <c r="EK3" s="8"/>
+      <c r="EL3" s="8"/>
+      <c r="EM3" s="8"/>
+      <c r="EN3" s="8"/>
     </row>
-    <row r="4" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -8320,8 +8687,16 @@
       <c r="ED4" s="8"/>
       <c r="EE4" s="8"/>
       <c r="EF4" s="8"/>
+      <c r="EG4" s="8"/>
+      <c r="EH4" s="8"/>
+      <c r="EI4" s="8"/>
+      <c r="EJ4" s="8"/>
+      <c r="EK4" s="8"/>
+      <c r="EL4" s="8"/>
+      <c r="EM4" s="8"/>
+      <c r="EN4" s="8"/>
     </row>
-    <row r="5" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -8458,8 +8833,16 @@
       <c r="ED5" s="8"/>
       <c r="EE5" s="8"/>
       <c r="EF5" s="8"/>
+      <c r="EG5" s="8"/>
+      <c r="EH5" s="8"/>
+      <c r="EI5" s="8"/>
+      <c r="EJ5" s="8"/>
+      <c r="EK5" s="8"/>
+      <c r="EL5" s="8"/>
+      <c r="EM5" s="8"/>
+      <c r="EN5" s="8"/>
     </row>
-    <row r="6" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -8596,8 +8979,16 @@
       <c r="ED6" s="8"/>
       <c r="EE6" s="8"/>
       <c r="EF6" s="8"/>
+      <c r="EG6" s="8"/>
+      <c r="EH6" s="8"/>
+      <c r="EI6" s="8"/>
+      <c r="EJ6" s="8"/>
+      <c r="EK6" s="8"/>
+      <c r="EL6" s="8"/>
+      <c r="EM6" s="8"/>
+      <c r="EN6" s="8"/>
     </row>
-    <row r="7" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -8734,8 +9125,16 @@
       <c r="ED7" s="8"/>
       <c r="EE7" s="8"/>
       <c r="EF7" s="8"/>
+      <c r="EG7" s="8"/>
+      <c r="EH7" s="8"/>
+      <c r="EI7" s="8"/>
+      <c r="EJ7" s="8"/>
+      <c r="EK7" s="8"/>
+      <c r="EL7" s="8"/>
+      <c r="EM7" s="8"/>
+      <c r="EN7" s="8"/>
     </row>
-    <row r="8" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -8872,8 +9271,16 @@
       <c r="ED8" s="8"/>
       <c r="EE8" s="8"/>
       <c r="EF8" s="8"/>
+      <c r="EG8" s="8"/>
+      <c r="EH8" s="8"/>
+      <c r="EI8" s="8"/>
+      <c r="EJ8" s="8"/>
+      <c r="EK8" s="8"/>
+      <c r="EL8" s="8"/>
+      <c r="EM8" s="8"/>
+      <c r="EN8" s="8"/>
     </row>
-    <row r="9" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -9010,8 +9417,16 @@
       <c r="ED9" s="8"/>
       <c r="EE9" s="8"/>
       <c r="EF9" s="8"/>
+      <c r="EG9" s="8"/>
+      <c r="EH9" s="8"/>
+      <c r="EI9" s="8"/>
+      <c r="EJ9" s="8"/>
+      <c r="EK9" s="8"/>
+      <c r="EL9" s="8"/>
+      <c r="EM9" s="8"/>
+      <c r="EN9" s="8"/>
     </row>
-    <row r="10" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -9148,8 +9563,16 @@
       <c r="ED10" s="8"/>
       <c r="EE10" s="8"/>
       <c r="EF10" s="8"/>
+      <c r="EG10" s="8"/>
+      <c r="EH10" s="8"/>
+      <c r="EI10" s="8"/>
+      <c r="EJ10" s="8"/>
+      <c r="EK10" s="8"/>
+      <c r="EL10" s="8"/>
+      <c r="EM10" s="8"/>
+      <c r="EN10" s="8"/>
     </row>
-    <row r="11" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>2</v>
       </c>
@@ -9354,8 +9777,20 @@
       <c r="ED11" s="8"/>
       <c r="EE11" s="8"/>
       <c r="EF11" s="8"/>
+      <c r="EG11" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="EH11" s="8"/>
+      <c r="EI11" s="8"/>
+      <c r="EJ11" s="8"/>
+      <c r="EK11" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="EL11" s="8"/>
+      <c r="EM11" s="8"/>
+      <c r="EN11" s="8"/>
     </row>
-    <row r="12" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -9492,8 +9927,16 @@
       <c r="ED12" s="8"/>
       <c r="EE12" s="8"/>
       <c r="EF12" s="8"/>
+      <c r="EG12" s="8"/>
+      <c r="EH12" s="8"/>
+      <c r="EI12" s="8"/>
+      <c r="EJ12" s="8"/>
+      <c r="EK12" s="8"/>
+      <c r="EL12" s="8"/>
+      <c r="EM12" s="8"/>
+      <c r="EN12" s="8"/>
     </row>
-    <row r="13" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -9630,8 +10073,16 @@
       <c r="ED13" s="8"/>
       <c r="EE13" s="8"/>
       <c r="EF13" s="8"/>
+      <c r="EG13" s="8"/>
+      <c r="EH13" s="8"/>
+      <c r="EI13" s="8"/>
+      <c r="EJ13" s="8"/>
+      <c r="EK13" s="8"/>
+      <c r="EL13" s="8"/>
+      <c r="EM13" s="8"/>
+      <c r="EN13" s="8"/>
     </row>
-    <row r="14" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -9768,8 +10219,16 @@
       <c r="ED14" s="8"/>
       <c r="EE14" s="8"/>
       <c r="EF14" s="8"/>
+      <c r="EG14" s="8"/>
+      <c r="EH14" s="8"/>
+      <c r="EI14" s="8"/>
+      <c r="EJ14" s="8"/>
+      <c r="EK14" s="8"/>
+      <c r="EL14" s="8"/>
+      <c r="EM14" s="8"/>
+      <c r="EN14" s="8"/>
     </row>
-    <row r="15" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -9906,8 +10365,16 @@
       <c r="ED15" s="8"/>
       <c r="EE15" s="8"/>
       <c r="EF15" s="8"/>
+      <c r="EG15" s="8"/>
+      <c r="EH15" s="8"/>
+      <c r="EI15" s="8"/>
+      <c r="EJ15" s="8"/>
+      <c r="EK15" s="8"/>
+      <c r="EL15" s="8"/>
+      <c r="EM15" s="8"/>
+      <c r="EN15" s="8"/>
     </row>
-    <row r="16" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -10044,8 +10511,16 @@
       <c r="ED16" s="8"/>
       <c r="EE16" s="8"/>
       <c r="EF16" s="8"/>
+      <c r="EG16" s="8"/>
+      <c r="EH16" s="8"/>
+      <c r="EI16" s="8"/>
+      <c r="EJ16" s="8"/>
+      <c r="EK16" s="8"/>
+      <c r="EL16" s="8"/>
+      <c r="EM16" s="8"/>
+      <c r="EN16" s="8"/>
     </row>
-    <row r="17" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -10182,8 +10657,16 @@
       <c r="ED17" s="8"/>
       <c r="EE17" s="8"/>
       <c r="EF17" s="8"/>
+      <c r="EG17" s="8"/>
+      <c r="EH17" s="8"/>
+      <c r="EI17" s="8"/>
+      <c r="EJ17" s="8"/>
+      <c r="EK17" s="8"/>
+      <c r="EL17" s="8"/>
+      <c r="EM17" s="8"/>
+      <c r="EN17" s="8"/>
     </row>
-    <row r="18" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -10320,8 +10803,16 @@
       <c r="ED18" s="8"/>
       <c r="EE18" s="8"/>
       <c r="EF18" s="8"/>
+      <c r="EG18" s="8"/>
+      <c r="EH18" s="8"/>
+      <c r="EI18" s="8"/>
+      <c r="EJ18" s="8"/>
+      <c r="EK18" s="8"/>
+      <c r="EL18" s="8"/>
+      <c r="EM18" s="8"/>
+      <c r="EN18" s="8"/>
     </row>
-    <row r="19" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -10458,8 +10949,16 @@
       <c r="ED19" s="8"/>
       <c r="EE19" s="8"/>
       <c r="EF19" s="8"/>
+      <c r="EG19" s="8"/>
+      <c r="EH19" s="8"/>
+      <c r="EI19" s="8"/>
+      <c r="EJ19" s="8"/>
+      <c r="EK19" s="8"/>
+      <c r="EL19" s="8"/>
+      <c r="EM19" s="8"/>
+      <c r="EN19" s="8"/>
     </row>
-    <row r="20" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -10596,8 +11095,16 @@
       <c r="ED20" s="8"/>
       <c r="EE20" s="8"/>
       <c r="EF20" s="8"/>
+      <c r="EG20" s="8"/>
+      <c r="EH20" s="8"/>
+      <c r="EI20" s="8"/>
+      <c r="EJ20" s="8"/>
+      <c r="EK20" s="8"/>
+      <c r="EL20" s="8"/>
+      <c r="EM20" s="8"/>
+      <c r="EN20" s="8"/>
     </row>
-    <row r="21" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>4</v>
       </c>
@@ -10802,8 +11309,20 @@
       <c r="ED21" s="8"/>
       <c r="EE21" s="8"/>
       <c r="EF21" s="8"/>
+      <c r="EG21" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="EH21" s="8"/>
+      <c r="EI21" s="8"/>
+      <c r="EJ21" s="8"/>
+      <c r="EK21" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="EL21" s="8"/>
+      <c r="EM21" s="8"/>
+      <c r="EN21" s="8"/>
     </row>
-    <row r="22" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -10940,8 +11459,16 @@
       <c r="ED22" s="8"/>
       <c r="EE22" s="8"/>
       <c r="EF22" s="8"/>
+      <c r="EG22" s="8"/>
+      <c r="EH22" s="8"/>
+      <c r="EI22" s="8"/>
+      <c r="EJ22" s="8"/>
+      <c r="EK22" s="8"/>
+      <c r="EL22" s="8"/>
+      <c r="EM22" s="8"/>
+      <c r="EN22" s="8"/>
     </row>
-    <row r="23" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -11078,8 +11605,16 @@
       <c r="ED23" s="8"/>
       <c r="EE23" s="8"/>
       <c r="EF23" s="8"/>
+      <c r="EG23" s="8"/>
+      <c r="EH23" s="8"/>
+      <c r="EI23" s="8"/>
+      <c r="EJ23" s="8"/>
+      <c r="EK23" s="8"/>
+      <c r="EL23" s="8"/>
+      <c r="EM23" s="8"/>
+      <c r="EN23" s="8"/>
     </row>
-    <row r="24" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -11216,8 +11751,16 @@
       <c r="ED24" s="8"/>
       <c r="EE24" s="8"/>
       <c r="EF24" s="8"/>
+      <c r="EG24" s="8"/>
+      <c r="EH24" s="8"/>
+      <c r="EI24" s="8"/>
+      <c r="EJ24" s="8"/>
+      <c r="EK24" s="8"/>
+      <c r="EL24" s="8"/>
+      <c r="EM24" s="8"/>
+      <c r="EN24" s="8"/>
     </row>
-    <row r="25" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -11354,8 +11897,16 @@
       <c r="ED25" s="8"/>
       <c r="EE25" s="8"/>
       <c r="EF25" s="8"/>
+      <c r="EG25" s="8"/>
+      <c r="EH25" s="8"/>
+      <c r="EI25" s="8"/>
+      <c r="EJ25" s="8"/>
+      <c r="EK25" s="8"/>
+      <c r="EL25" s="8"/>
+      <c r="EM25" s="8"/>
+      <c r="EN25" s="8"/>
     </row>
-    <row r="26" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -11492,8 +12043,16 @@
       <c r="ED26" s="8"/>
       <c r="EE26" s="8"/>
       <c r="EF26" s="8"/>
+      <c r="EG26" s="8"/>
+      <c r="EH26" s="8"/>
+      <c r="EI26" s="8"/>
+      <c r="EJ26" s="8"/>
+      <c r="EK26" s="8"/>
+      <c r="EL26" s="8"/>
+      <c r="EM26" s="8"/>
+      <c r="EN26" s="8"/>
     </row>
-    <row r="27" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -11630,8 +12189,16 @@
       <c r="ED27" s="8"/>
       <c r="EE27" s="8"/>
       <c r="EF27" s="8"/>
+      <c r="EG27" s="8"/>
+      <c r="EH27" s="8"/>
+      <c r="EI27" s="8"/>
+      <c r="EJ27" s="8"/>
+      <c r="EK27" s="8"/>
+      <c r="EL27" s="8"/>
+      <c r="EM27" s="8"/>
+      <c r="EN27" s="8"/>
     </row>
-    <row r="28" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -11768,8 +12335,16 @@
       <c r="ED28" s="8"/>
       <c r="EE28" s="8"/>
       <c r="EF28" s="8"/>
+      <c r="EG28" s="8"/>
+      <c r="EH28" s="8"/>
+      <c r="EI28" s="8"/>
+      <c r="EJ28" s="8"/>
+      <c r="EK28" s="8"/>
+      <c r="EL28" s="8"/>
+      <c r="EM28" s="8"/>
+      <c r="EN28" s="8"/>
     </row>
-    <row r="29" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -11906,8 +12481,16 @@
       <c r="ED29" s="8"/>
       <c r="EE29" s="8"/>
       <c r="EF29" s="8"/>
+      <c r="EG29" s="8"/>
+      <c r="EH29" s="8"/>
+      <c r="EI29" s="8"/>
+      <c r="EJ29" s="8"/>
+      <c r="EK29" s="8"/>
+      <c r="EL29" s="8"/>
+      <c r="EM29" s="8"/>
+      <c r="EN29" s="8"/>
     </row>
-    <row r="30" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -12044,8 +12627,16 @@
       <c r="ED30" s="8"/>
       <c r="EE30" s="8"/>
       <c r="EF30" s="8"/>
+      <c r="EG30" s="8"/>
+      <c r="EH30" s="8"/>
+      <c r="EI30" s="8"/>
+      <c r="EJ30" s="8"/>
+      <c r="EK30" s="8"/>
+      <c r="EL30" s="8"/>
+      <c r="EM30" s="8"/>
+      <c r="EN30" s="8"/>
     </row>
-    <row r="31" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>13</v>
       </c>
@@ -12250,8 +12841,20 @@
       <c r="ED31" s="8"/>
       <c r="EE31" s="8"/>
       <c r="EF31" s="8"/>
+      <c r="EG31" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="EH31" s="8"/>
+      <c r="EI31" s="8"/>
+      <c r="EJ31" s="8"/>
+      <c r="EK31" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="EL31" s="8"/>
+      <c r="EM31" s="8"/>
+      <c r="EN31" s="8"/>
     </row>
-    <row r="32" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -12388,8 +12991,16 @@
       <c r="ED32" s="8"/>
       <c r="EE32" s="8"/>
       <c r="EF32" s="8"/>
+      <c r="EG32" s="8"/>
+      <c r="EH32" s="8"/>
+      <c r="EI32" s="8"/>
+      <c r="EJ32" s="8"/>
+      <c r="EK32" s="8"/>
+      <c r="EL32" s="8"/>
+      <c r="EM32" s="8"/>
+      <c r="EN32" s="8"/>
     </row>
-    <row r="33" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -12526,8 +13137,16 @@
       <c r="ED33" s="8"/>
       <c r="EE33" s="8"/>
       <c r="EF33" s="8"/>
+      <c r="EG33" s="8"/>
+      <c r="EH33" s="8"/>
+      <c r="EI33" s="8"/>
+      <c r="EJ33" s="8"/>
+      <c r="EK33" s="8"/>
+      <c r="EL33" s="8"/>
+      <c r="EM33" s="8"/>
+      <c r="EN33" s="8"/>
     </row>
-    <row r="34" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -12664,8 +13283,16 @@
       <c r="ED34" s="8"/>
       <c r="EE34" s="8"/>
       <c r="EF34" s="8"/>
+      <c r="EG34" s="8"/>
+      <c r="EH34" s="8"/>
+      <c r="EI34" s="8"/>
+      <c r="EJ34" s="8"/>
+      <c r="EK34" s="8"/>
+      <c r="EL34" s="8"/>
+      <c r="EM34" s="8"/>
+      <c r="EN34" s="8"/>
     </row>
-    <row r="35" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -12802,8 +13429,16 @@
       <c r="ED35" s="8"/>
       <c r="EE35" s="8"/>
       <c r="EF35" s="8"/>
+      <c r="EG35" s="8"/>
+      <c r="EH35" s="8"/>
+      <c r="EI35" s="8"/>
+      <c r="EJ35" s="8"/>
+      <c r="EK35" s="8"/>
+      <c r="EL35" s="8"/>
+      <c r="EM35" s="8"/>
+      <c r="EN35" s="8"/>
     </row>
-    <row r="36" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -12940,8 +13575,16 @@
       <c r="ED36" s="8"/>
       <c r="EE36" s="8"/>
       <c r="EF36" s="8"/>
+      <c r="EG36" s="8"/>
+      <c r="EH36" s="8"/>
+      <c r="EI36" s="8"/>
+      <c r="EJ36" s="8"/>
+      <c r="EK36" s="8"/>
+      <c r="EL36" s="8"/>
+      <c r="EM36" s="8"/>
+      <c r="EN36" s="8"/>
     </row>
-    <row r="37" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -13078,8 +13721,16 @@
       <c r="ED37" s="8"/>
       <c r="EE37" s="8"/>
       <c r="EF37" s="8"/>
+      <c r="EG37" s="8"/>
+      <c r="EH37" s="8"/>
+      <c r="EI37" s="8"/>
+      <c r="EJ37" s="8"/>
+      <c r="EK37" s="8"/>
+      <c r="EL37" s="8"/>
+      <c r="EM37" s="8"/>
+      <c r="EN37" s="8"/>
     </row>
-    <row r="38" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -13216,8 +13867,16 @@
       <c r="ED38" s="8"/>
       <c r="EE38" s="8"/>
       <c r="EF38" s="8"/>
+      <c r="EG38" s="8"/>
+      <c r="EH38" s="8"/>
+      <c r="EI38" s="8"/>
+      <c r="EJ38" s="8"/>
+      <c r="EK38" s="8"/>
+      <c r="EL38" s="8"/>
+      <c r="EM38" s="8"/>
+      <c r="EN38" s="8"/>
     </row>
-    <row r="39" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -13354,8 +14013,16 @@
       <c r="ED39" s="8"/>
       <c r="EE39" s="8"/>
       <c r="EF39" s="8"/>
+      <c r="EG39" s="8"/>
+      <c r="EH39" s="8"/>
+      <c r="EI39" s="8"/>
+      <c r="EJ39" s="8"/>
+      <c r="EK39" s="8"/>
+      <c r="EL39" s="8"/>
+      <c r="EM39" s="8"/>
+      <c r="EN39" s="8"/>
     </row>
-    <row r="40" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -13492,8 +14159,16 @@
       <c r="ED40" s="8"/>
       <c r="EE40" s="8"/>
       <c r="EF40" s="8"/>
+      <c r="EG40" s="8"/>
+      <c r="EH40" s="8"/>
+      <c r="EI40" s="8"/>
+      <c r="EJ40" s="8"/>
+      <c r="EK40" s="8"/>
+      <c r="EL40" s="8"/>
+      <c r="EM40" s="8"/>
+      <c r="EN40" s="8"/>
     </row>
-    <row r="41" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>16</v>
       </c>
@@ -13698,8 +14373,20 @@
       <c r="ED41" s="8"/>
       <c r="EE41" s="8"/>
       <c r="EF41" s="8"/>
+      <c r="EG41" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="EH41" s="8"/>
+      <c r="EI41" s="8"/>
+      <c r="EJ41" s="8"/>
+      <c r="EK41" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="EL41" s="8"/>
+      <c r="EM41" s="8"/>
+      <c r="EN41" s="8"/>
     </row>
-    <row r="42" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -13836,8 +14523,16 @@
       <c r="ED42" s="8"/>
       <c r="EE42" s="8"/>
       <c r="EF42" s="8"/>
+      <c r="EG42" s="8"/>
+      <c r="EH42" s="8"/>
+      <c r="EI42" s="8"/>
+      <c r="EJ42" s="8"/>
+      <c r="EK42" s="8"/>
+      <c r="EL42" s="8"/>
+      <c r="EM42" s="8"/>
+      <c r="EN42" s="8"/>
     </row>
-    <row r="43" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -13974,8 +14669,16 @@
       <c r="ED43" s="8"/>
       <c r="EE43" s="8"/>
       <c r="EF43" s="8"/>
+      <c r="EG43" s="8"/>
+      <c r="EH43" s="8"/>
+      <c r="EI43" s="8"/>
+      <c r="EJ43" s="8"/>
+      <c r="EK43" s="8"/>
+      <c r="EL43" s="8"/>
+      <c r="EM43" s="8"/>
+      <c r="EN43" s="8"/>
     </row>
-    <row r="44" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -14112,8 +14815,16 @@
       <c r="ED44" s="8"/>
       <c r="EE44" s="8"/>
       <c r="EF44" s="8"/>
+      <c r="EG44" s="8"/>
+      <c r="EH44" s="8"/>
+      <c r="EI44" s="8"/>
+      <c r="EJ44" s="8"/>
+      <c r="EK44" s="8"/>
+      <c r="EL44" s="8"/>
+      <c r="EM44" s="8"/>
+      <c r="EN44" s="8"/>
     </row>
-    <row r="45" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -14250,8 +14961,16 @@
       <c r="ED45" s="8"/>
       <c r="EE45" s="8"/>
       <c r="EF45" s="8"/>
+      <c r="EG45" s="8"/>
+      <c r="EH45" s="8"/>
+      <c r="EI45" s="8"/>
+      <c r="EJ45" s="8"/>
+      <c r="EK45" s="8"/>
+      <c r="EL45" s="8"/>
+      <c r="EM45" s="8"/>
+      <c r="EN45" s="8"/>
     </row>
-    <row r="46" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -14388,8 +15107,16 @@
       <c r="ED46" s="8"/>
       <c r="EE46" s="8"/>
       <c r="EF46" s="8"/>
+      <c r="EG46" s="8"/>
+      <c r="EH46" s="8"/>
+      <c r="EI46" s="8"/>
+      <c r="EJ46" s="8"/>
+      <c r="EK46" s="8"/>
+      <c r="EL46" s="8"/>
+      <c r="EM46" s="8"/>
+      <c r="EN46" s="8"/>
     </row>
-    <row r="47" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -14526,8 +15253,16 @@
       <c r="ED47" s="8"/>
       <c r="EE47" s="8"/>
       <c r="EF47" s="8"/>
+      <c r="EG47" s="8"/>
+      <c r="EH47" s="8"/>
+      <c r="EI47" s="8"/>
+      <c r="EJ47" s="8"/>
+      <c r="EK47" s="8"/>
+      <c r="EL47" s="8"/>
+      <c r="EM47" s="8"/>
+      <c r="EN47" s="8"/>
     </row>
-    <row r="48" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -14664,8 +15399,16 @@
       <c r="ED48" s="8"/>
       <c r="EE48" s="8"/>
       <c r="EF48" s="8"/>
+      <c r="EG48" s="8"/>
+      <c r="EH48" s="8"/>
+      <c r="EI48" s="8"/>
+      <c r="EJ48" s="8"/>
+      <c r="EK48" s="8"/>
+      <c r="EL48" s="8"/>
+      <c r="EM48" s="8"/>
+      <c r="EN48" s="8"/>
     </row>
-    <row r="49" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -14802,8 +15545,16 @@
       <c r="ED49" s="8"/>
       <c r="EE49" s="8"/>
       <c r="EF49" s="8"/>
+      <c r="EG49" s="8"/>
+      <c r="EH49" s="8"/>
+      <c r="EI49" s="8"/>
+      <c r="EJ49" s="8"/>
+      <c r="EK49" s="8"/>
+      <c r="EL49" s="8"/>
+      <c r="EM49" s="8"/>
+      <c r="EN49" s="8"/>
     </row>
-    <row r="50" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -14940,8 +15691,16 @@
       <c r="ED50" s="8"/>
       <c r="EE50" s="8"/>
       <c r="EF50" s="8"/>
+      <c r="EG50" s="8"/>
+      <c r="EH50" s="8"/>
+      <c r="EI50" s="8"/>
+      <c r="EJ50" s="8"/>
+      <c r="EK50" s="8"/>
+      <c r="EL50" s="8"/>
+      <c r="EM50" s="8"/>
+      <c r="EN50" s="8"/>
     </row>
-    <row r="51" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>6</v>
       </c>
@@ -15146,8 +15905,20 @@
       <c r="ED51" s="6"/>
       <c r="EE51" s="6"/>
       <c r="EF51" s="6"/>
+      <c r="EG51" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="EH51" s="6"/>
+      <c r="EI51" s="6"/>
+      <c r="EJ51" s="6"/>
+      <c r="EK51" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="EL51" s="6"/>
+      <c r="EM51" s="6"/>
+      <c r="EN51" s="6"/>
     </row>
-    <row r="52" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -15284,8 +16055,16 @@
       <c r="ED52" s="6"/>
       <c r="EE52" s="6"/>
       <c r="EF52" s="6"/>
+      <c r="EG52" s="6"/>
+      <c r="EH52" s="6"/>
+      <c r="EI52" s="6"/>
+      <c r="EJ52" s="6"/>
+      <c r="EK52" s="6"/>
+      <c r="EL52" s="6"/>
+      <c r="EM52" s="6"/>
+      <c r="EN52" s="6"/>
     </row>
-    <row r="53" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -15422,8 +16201,16 @@
       <c r="ED53" s="6"/>
       <c r="EE53" s="6"/>
       <c r="EF53" s="6"/>
+      <c r="EG53" s="6"/>
+      <c r="EH53" s="6"/>
+      <c r="EI53" s="6"/>
+      <c r="EJ53" s="6"/>
+      <c r="EK53" s="6"/>
+      <c r="EL53" s="6"/>
+      <c r="EM53" s="6"/>
+      <c r="EN53" s="6"/>
     </row>
-    <row r="54" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -15560,8 +16347,16 @@
       <c r="ED54" s="6"/>
       <c r="EE54" s="6"/>
       <c r="EF54" s="6"/>
+      <c r="EG54" s="6"/>
+      <c r="EH54" s="6"/>
+      <c r="EI54" s="6"/>
+      <c r="EJ54" s="6"/>
+      <c r="EK54" s="6"/>
+      <c r="EL54" s="6"/>
+      <c r="EM54" s="6"/>
+      <c r="EN54" s="6"/>
     </row>
-    <row r="55" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -15698,8 +16493,16 @@
       <c r="ED55" s="6"/>
       <c r="EE55" s="6"/>
       <c r="EF55" s="6"/>
+      <c r="EG55" s="6"/>
+      <c r="EH55" s="6"/>
+      <c r="EI55" s="6"/>
+      <c r="EJ55" s="6"/>
+      <c r="EK55" s="6"/>
+      <c r="EL55" s="6"/>
+      <c r="EM55" s="6"/>
+      <c r="EN55" s="6"/>
     </row>
-    <row r="56" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -15836,8 +16639,16 @@
       <c r="ED56" s="6"/>
       <c r="EE56" s="6"/>
       <c r="EF56" s="6"/>
+      <c r="EG56" s="6"/>
+      <c r="EH56" s="6"/>
+      <c r="EI56" s="6"/>
+      <c r="EJ56" s="6"/>
+      <c r="EK56" s="6"/>
+      <c r="EL56" s="6"/>
+      <c r="EM56" s="6"/>
+      <c r="EN56" s="6"/>
     </row>
-    <row r="57" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -15974,8 +16785,16 @@
       <c r="ED57" s="6"/>
       <c r="EE57" s="6"/>
       <c r="EF57" s="6"/>
+      <c r="EG57" s="6"/>
+      <c r="EH57" s="6"/>
+      <c r="EI57" s="6"/>
+      <c r="EJ57" s="6"/>
+      <c r="EK57" s="6"/>
+      <c r="EL57" s="6"/>
+      <c r="EM57" s="6"/>
+      <c r="EN57" s="6"/>
     </row>
-    <row r="58" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -16112,8 +16931,16 @@
       <c r="ED58" s="6"/>
       <c r="EE58" s="6"/>
       <c r="EF58" s="6"/>
+      <c r="EG58" s="6"/>
+      <c r="EH58" s="6"/>
+      <c r="EI58" s="6"/>
+      <c r="EJ58" s="6"/>
+      <c r="EK58" s="6"/>
+      <c r="EL58" s="6"/>
+      <c r="EM58" s="6"/>
+      <c r="EN58" s="6"/>
     </row>
-    <row r="59" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -16250,8 +17077,16 @@
       <c r="ED59" s="6"/>
       <c r="EE59" s="6"/>
       <c r="EF59" s="6"/>
+      <c r="EG59" s="6"/>
+      <c r="EH59" s="6"/>
+      <c r="EI59" s="6"/>
+      <c r="EJ59" s="6"/>
+      <c r="EK59" s="6"/>
+      <c r="EL59" s="6"/>
+      <c r="EM59" s="6"/>
+      <c r="EN59" s="6"/>
     </row>
-    <row r="60" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -16388,8 +17223,16 @@
       <c r="ED60" s="6"/>
       <c r="EE60" s="6"/>
       <c r="EF60" s="6"/>
+      <c r="EG60" s="6"/>
+      <c r="EH60" s="6"/>
+      <c r="EI60" s="6"/>
+      <c r="EJ60" s="6"/>
+      <c r="EK60" s="6"/>
+      <c r="EL60" s="6"/>
+      <c r="EM60" s="6"/>
+      <c r="EN60" s="6"/>
     </row>
-    <row r="61" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>8</v>
       </c>
@@ -16594,8 +17437,20 @@
       <c r="ED61" s="6"/>
       <c r="EE61" s="6"/>
       <c r="EF61" s="6"/>
+      <c r="EG61" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="EH61" s="6"/>
+      <c r="EI61" s="6"/>
+      <c r="EJ61" s="6"/>
+      <c r="EK61" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="EL61" s="6"/>
+      <c r="EM61" s="6"/>
+      <c r="EN61" s="6"/>
     </row>
-    <row r="62" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -16732,8 +17587,16 @@
       <c r="ED62" s="6"/>
       <c r="EE62" s="6"/>
       <c r="EF62" s="6"/>
+      <c r="EG62" s="6"/>
+      <c r="EH62" s="6"/>
+      <c r="EI62" s="6"/>
+      <c r="EJ62" s="6"/>
+      <c r="EK62" s="6"/>
+      <c r="EL62" s="6"/>
+      <c r="EM62" s="6"/>
+      <c r="EN62" s="6"/>
     </row>
-    <row r="63" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -16870,8 +17733,16 @@
       <c r="ED63" s="6"/>
       <c r="EE63" s="6"/>
       <c r="EF63" s="6"/>
+      <c r="EG63" s="6"/>
+      <c r="EH63" s="6"/>
+      <c r="EI63" s="6"/>
+      <c r="EJ63" s="6"/>
+      <c r="EK63" s="6"/>
+      <c r="EL63" s="6"/>
+      <c r="EM63" s="6"/>
+      <c r="EN63" s="6"/>
     </row>
-    <row r="64" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -17008,8 +17879,16 @@
       <c r="ED64" s="6"/>
       <c r="EE64" s="6"/>
       <c r="EF64" s="6"/>
+      <c r="EG64" s="6"/>
+      <c r="EH64" s="6"/>
+      <c r="EI64" s="6"/>
+      <c r="EJ64" s="6"/>
+      <c r="EK64" s="6"/>
+      <c r="EL64" s="6"/>
+      <c r="EM64" s="6"/>
+      <c r="EN64" s="6"/>
     </row>
-    <row r="65" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -17146,8 +18025,16 @@
       <c r="ED65" s="6"/>
       <c r="EE65" s="6"/>
       <c r="EF65" s="6"/>
+      <c r="EG65" s="6"/>
+      <c r="EH65" s="6"/>
+      <c r="EI65" s="6"/>
+      <c r="EJ65" s="6"/>
+      <c r="EK65" s="6"/>
+      <c r="EL65" s="6"/>
+      <c r="EM65" s="6"/>
+      <c r="EN65" s="6"/>
     </row>
-    <row r="66" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -17284,8 +18171,16 @@
       <c r="ED66" s="6"/>
       <c r="EE66" s="6"/>
       <c r="EF66" s="6"/>
+      <c r="EG66" s="6"/>
+      <c r="EH66" s="6"/>
+      <c r="EI66" s="6"/>
+      <c r="EJ66" s="6"/>
+      <c r="EK66" s="6"/>
+      <c r="EL66" s="6"/>
+      <c r="EM66" s="6"/>
+      <c r="EN66" s="6"/>
     </row>
-    <row r="67" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -17422,8 +18317,16 @@
       <c r="ED67" s="6"/>
       <c r="EE67" s="6"/>
       <c r="EF67" s="6"/>
+      <c r="EG67" s="6"/>
+      <c r="EH67" s="6"/>
+      <c r="EI67" s="6"/>
+      <c r="EJ67" s="6"/>
+      <c r="EK67" s="6"/>
+      <c r="EL67" s="6"/>
+      <c r="EM67" s="6"/>
+      <c r="EN67" s="6"/>
     </row>
-    <row r="68" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -17560,8 +18463,16 @@
       <c r="ED68" s="6"/>
       <c r="EE68" s="6"/>
       <c r="EF68" s="6"/>
+      <c r="EG68" s="6"/>
+      <c r="EH68" s="6"/>
+      <c r="EI68" s="6"/>
+      <c r="EJ68" s="6"/>
+      <c r="EK68" s="6"/>
+      <c r="EL68" s="6"/>
+      <c r="EM68" s="6"/>
+      <c r="EN68" s="6"/>
     </row>
-    <row r="69" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -17698,8 +18609,16 @@
       <c r="ED69" s="6"/>
       <c r="EE69" s="6"/>
       <c r="EF69" s="6"/>
+      <c r="EG69" s="6"/>
+      <c r="EH69" s="6"/>
+      <c r="EI69" s="6"/>
+      <c r="EJ69" s="6"/>
+      <c r="EK69" s="6"/>
+      <c r="EL69" s="6"/>
+      <c r="EM69" s="6"/>
+      <c r="EN69" s="6"/>
     </row>
-    <row r="70" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -17836,8 +18755,16 @@
       <c r="ED70" s="6"/>
       <c r="EE70" s="6"/>
       <c r="EF70" s="6"/>
+      <c r="EG70" s="6"/>
+      <c r="EH70" s="6"/>
+      <c r="EI70" s="6"/>
+      <c r="EJ70" s="6"/>
+      <c r="EK70" s="6"/>
+      <c r="EL70" s="6"/>
+      <c r="EM70" s="6"/>
+      <c r="EN70" s="6"/>
     </row>
-    <row r="71" spans="1:136" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:144" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>11</v>
       </c>
@@ -18042,8 +18969,20 @@
       <c r="ED71" s="6"/>
       <c r="EE71" s="6"/>
       <c r="EF71" s="6"/>
+      <c r="EG71" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="EH71" s="6"/>
+      <c r="EI71" s="6"/>
+      <c r="EJ71" s="6"/>
+      <c r="EK71" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="EL71" s="6"/>
+      <c r="EM71" s="6"/>
+      <c r="EN71" s="6"/>
     </row>
-    <row r="72" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -18180,8 +19119,16 @@
       <c r="ED72" s="6"/>
       <c r="EE72" s="6"/>
       <c r="EF72" s="6"/>
+      <c r="EG72" s="6"/>
+      <c r="EH72" s="6"/>
+      <c r="EI72" s="6"/>
+      <c r="EJ72" s="6"/>
+      <c r="EK72" s="6"/>
+      <c r="EL72" s="6"/>
+      <c r="EM72" s="6"/>
+      <c r="EN72" s="6"/>
     </row>
-    <row r="73" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -18318,8 +19265,16 @@
       <c r="ED73" s="6"/>
       <c r="EE73" s="6"/>
       <c r="EF73" s="6"/>
+      <c r="EG73" s="6"/>
+      <c r="EH73" s="6"/>
+      <c r="EI73" s="6"/>
+      <c r="EJ73" s="6"/>
+      <c r="EK73" s="6"/>
+      <c r="EL73" s="6"/>
+      <c r="EM73" s="6"/>
+      <c r="EN73" s="6"/>
     </row>
-    <row r="74" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -18456,8 +19411,16 @@
       <c r="ED74" s="6"/>
       <c r="EE74" s="6"/>
       <c r="EF74" s="6"/>
+      <c r="EG74" s="6"/>
+      <c r="EH74" s="6"/>
+      <c r="EI74" s="6"/>
+      <c r="EJ74" s="6"/>
+      <c r="EK74" s="6"/>
+      <c r="EL74" s="6"/>
+      <c r="EM74" s="6"/>
+      <c r="EN74" s="6"/>
     </row>
-    <row r="75" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -18594,8 +19557,16 @@
       <c r="ED75" s="6"/>
       <c r="EE75" s="6"/>
       <c r="EF75" s="6"/>
+      <c r="EG75" s="6"/>
+      <c r="EH75" s="6"/>
+      <c r="EI75" s="6"/>
+      <c r="EJ75" s="6"/>
+      <c r="EK75" s="6"/>
+      <c r="EL75" s="6"/>
+      <c r="EM75" s="6"/>
+      <c r="EN75" s="6"/>
     </row>
-    <row r="76" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -18732,8 +19703,16 @@
       <c r="ED76" s="6"/>
       <c r="EE76" s="6"/>
       <c r="EF76" s="6"/>
+      <c r="EG76" s="6"/>
+      <c r="EH76" s="6"/>
+      <c r="EI76" s="6"/>
+      <c r="EJ76" s="6"/>
+      <c r="EK76" s="6"/>
+      <c r="EL76" s="6"/>
+      <c r="EM76" s="6"/>
+      <c r="EN76" s="6"/>
     </row>
-    <row r="77" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -18870,8 +19849,16 @@
       <c r="ED77" s="6"/>
       <c r="EE77" s="6"/>
       <c r="EF77" s="6"/>
+      <c r="EG77" s="6"/>
+      <c r="EH77" s="6"/>
+      <c r="EI77" s="6"/>
+      <c r="EJ77" s="6"/>
+      <c r="EK77" s="6"/>
+      <c r="EL77" s="6"/>
+      <c r="EM77" s="6"/>
+      <c r="EN77" s="6"/>
     </row>
-    <row r="78" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -19008,8 +19995,16 @@
       <c r="ED78" s="6"/>
       <c r="EE78" s="6"/>
       <c r="EF78" s="6"/>
+      <c r="EG78" s="6"/>
+      <c r="EH78" s="6"/>
+      <c r="EI78" s="6"/>
+      <c r="EJ78" s="6"/>
+      <c r="EK78" s="6"/>
+      <c r="EL78" s="6"/>
+      <c r="EM78" s="6"/>
+      <c r="EN78" s="6"/>
     </row>
-    <row r="79" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -19146,8 +20141,16 @@
       <c r="ED79" s="6"/>
       <c r="EE79" s="6"/>
       <c r="EF79" s="6"/>
+      <c r="EG79" s="6"/>
+      <c r="EH79" s="6"/>
+      <c r="EI79" s="6"/>
+      <c r="EJ79" s="6"/>
+      <c r="EK79" s="6"/>
+      <c r="EL79" s="6"/>
+      <c r="EM79" s="6"/>
+      <c r="EN79" s="6"/>
     </row>
-    <row r="80" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -19284,8 +20287,16 @@
       <c r="ED80" s="6"/>
       <c r="EE80" s="6"/>
       <c r="EF80" s="6"/>
+      <c r="EG80" s="6"/>
+      <c r="EH80" s="6"/>
+      <c r="EI80" s="6"/>
+      <c r="EJ80" s="6"/>
+      <c r="EK80" s="6"/>
+      <c r="EL80" s="6"/>
+      <c r="EM80" s="6"/>
+      <c r="EN80" s="6"/>
     </row>
-    <row r="81" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>15</v>
       </c>
@@ -19490,8 +20501,20 @@
       <c r="ED81" s="6"/>
       <c r="EE81" s="6"/>
       <c r="EF81" s="6"/>
+      <c r="EG81" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="EH81" s="6"/>
+      <c r="EI81" s="6"/>
+      <c r="EJ81" s="6"/>
+      <c r="EK81" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="EL81" s="6"/>
+      <c r="EM81" s="6"/>
+      <c r="EN81" s="6"/>
     </row>
-    <row r="82" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -19628,8 +20651,16 @@
       <c r="ED82" s="6"/>
       <c r="EE82" s="6"/>
       <c r="EF82" s="6"/>
+      <c r="EG82" s="6"/>
+      <c r="EH82" s="6"/>
+      <c r="EI82" s="6"/>
+      <c r="EJ82" s="6"/>
+      <c r="EK82" s="6"/>
+      <c r="EL82" s="6"/>
+      <c r="EM82" s="6"/>
+      <c r="EN82" s="6"/>
     </row>
-    <row r="83" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -19766,8 +20797,16 @@
       <c r="ED83" s="6"/>
       <c r="EE83" s="6"/>
       <c r="EF83" s="6"/>
+      <c r="EG83" s="6"/>
+      <c r="EH83" s="6"/>
+      <c r="EI83" s="6"/>
+      <c r="EJ83" s="6"/>
+      <c r="EK83" s="6"/>
+      <c r="EL83" s="6"/>
+      <c r="EM83" s="6"/>
+      <c r="EN83" s="6"/>
     </row>
-    <row r="84" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -19904,8 +20943,16 @@
       <c r="ED84" s="6"/>
       <c r="EE84" s="6"/>
       <c r="EF84" s="6"/>
+      <c r="EG84" s="6"/>
+      <c r="EH84" s="6"/>
+      <c r="EI84" s="6"/>
+      <c r="EJ84" s="6"/>
+      <c r="EK84" s="6"/>
+      <c r="EL84" s="6"/>
+      <c r="EM84" s="6"/>
+      <c r="EN84" s="6"/>
     </row>
-    <row r="85" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -20042,8 +21089,16 @@
       <c r="ED85" s="6"/>
       <c r="EE85" s="6"/>
       <c r="EF85" s="6"/>
+      <c r="EG85" s="6"/>
+      <c r="EH85" s="6"/>
+      <c r="EI85" s="6"/>
+      <c r="EJ85" s="6"/>
+      <c r="EK85" s="6"/>
+      <c r="EL85" s="6"/>
+      <c r="EM85" s="6"/>
+      <c r="EN85" s="6"/>
     </row>
-    <row r="86" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -20180,8 +21235,16 @@
       <c r="ED86" s="6"/>
       <c r="EE86" s="6"/>
       <c r="EF86" s="6"/>
+      <c r="EG86" s="6"/>
+      <c r="EH86" s="6"/>
+      <c r="EI86" s="6"/>
+      <c r="EJ86" s="6"/>
+      <c r="EK86" s="6"/>
+      <c r="EL86" s="6"/>
+      <c r="EM86" s="6"/>
+      <c r="EN86" s="6"/>
     </row>
-    <row r="87" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -20318,8 +21381,16 @@
       <c r="ED87" s="6"/>
       <c r="EE87" s="6"/>
       <c r="EF87" s="6"/>
+      <c r="EG87" s="6"/>
+      <c r="EH87" s="6"/>
+      <c r="EI87" s="6"/>
+      <c r="EJ87" s="6"/>
+      <c r="EK87" s="6"/>
+      <c r="EL87" s="6"/>
+      <c r="EM87" s="6"/>
+      <c r="EN87" s="6"/>
     </row>
-    <row r="88" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -20456,8 +21527,16 @@
       <c r="ED88" s="6"/>
       <c r="EE88" s="6"/>
       <c r="EF88" s="6"/>
+      <c r="EG88" s="6"/>
+      <c r="EH88" s="6"/>
+      <c r="EI88" s="6"/>
+      <c r="EJ88" s="6"/>
+      <c r="EK88" s="6"/>
+      <c r="EL88" s="6"/>
+      <c r="EM88" s="6"/>
+      <c r="EN88" s="6"/>
     </row>
-    <row r="89" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -20594,8 +21673,16 @@
       <c r="ED89" s="6"/>
       <c r="EE89" s="6"/>
       <c r="EF89" s="6"/>
+      <c r="EG89" s="6"/>
+      <c r="EH89" s="6"/>
+      <c r="EI89" s="6"/>
+      <c r="EJ89" s="6"/>
+      <c r="EK89" s="6"/>
+      <c r="EL89" s="6"/>
+      <c r="EM89" s="6"/>
+      <c r="EN89" s="6"/>
     </row>
-    <row r="90" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -20732,8 +21819,16 @@
       <c r="ED90" s="6"/>
       <c r="EE90" s="6"/>
       <c r="EF90" s="6"/>
+      <c r="EG90" s="6"/>
+      <c r="EH90" s="6"/>
+      <c r="EI90" s="6"/>
+      <c r="EJ90" s="6"/>
+      <c r="EK90" s="6"/>
+      <c r="EL90" s="6"/>
+      <c r="EM90" s="6"/>
+      <c r="EN90" s="6"/>
     </row>
-    <row r="91" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>19</v>
       </c>
@@ -20938,8 +22033,20 @@
       <c r="ED91" s="6"/>
       <c r="EE91" s="6"/>
       <c r="EF91" s="6"/>
+      <c r="EG91" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="EH91" s="6"/>
+      <c r="EI91" s="6"/>
+      <c r="EJ91" s="6"/>
+      <c r="EK91" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="EL91" s="6"/>
+      <c r="EM91" s="6"/>
+      <c r="EN91" s="6"/>
     </row>
-    <row r="92" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -21076,8 +22183,16 @@
       <c r="ED92" s="6"/>
       <c r="EE92" s="6"/>
       <c r="EF92" s="6"/>
+      <c r="EG92" s="6"/>
+      <c r="EH92" s="6"/>
+      <c r="EI92" s="6"/>
+      <c r="EJ92" s="6"/>
+      <c r="EK92" s="6"/>
+      <c r="EL92" s="6"/>
+      <c r="EM92" s="6"/>
+      <c r="EN92" s="6"/>
     </row>
-    <row r="93" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -21214,8 +22329,16 @@
       <c r="ED93" s="6"/>
       <c r="EE93" s="6"/>
       <c r="EF93" s="6"/>
+      <c r="EG93" s="6"/>
+      <c r="EH93" s="6"/>
+      <c r="EI93" s="6"/>
+      <c r="EJ93" s="6"/>
+      <c r="EK93" s="6"/>
+      <c r="EL93" s="6"/>
+      <c r="EM93" s="6"/>
+      <c r="EN93" s="6"/>
     </row>
-    <row r="94" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -21352,8 +22475,16 @@
       <c r="ED94" s="6"/>
       <c r="EE94" s="6"/>
       <c r="EF94" s="6"/>
+      <c r="EG94" s="6"/>
+      <c r="EH94" s="6"/>
+      <c r="EI94" s="6"/>
+      <c r="EJ94" s="6"/>
+      <c r="EK94" s="6"/>
+      <c r="EL94" s="6"/>
+      <c r="EM94" s="6"/>
+      <c r="EN94" s="6"/>
     </row>
-    <row r="95" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -21490,8 +22621,16 @@
       <c r="ED95" s="6"/>
       <c r="EE95" s="6"/>
       <c r="EF95" s="6"/>
+      <c r="EG95" s="6"/>
+      <c r="EH95" s="6"/>
+      <c r="EI95" s="6"/>
+      <c r="EJ95" s="6"/>
+      <c r="EK95" s="6"/>
+      <c r="EL95" s="6"/>
+      <c r="EM95" s="6"/>
+      <c r="EN95" s="6"/>
     </row>
-    <row r="96" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -21628,8 +22767,16 @@
       <c r="ED96" s="6"/>
       <c r="EE96" s="6"/>
       <c r="EF96" s="6"/>
+      <c r="EG96" s="6"/>
+      <c r="EH96" s="6"/>
+      <c r="EI96" s="6"/>
+      <c r="EJ96" s="6"/>
+      <c r="EK96" s="6"/>
+      <c r="EL96" s="6"/>
+      <c r="EM96" s="6"/>
+      <c r="EN96" s="6"/>
     </row>
-    <row r="97" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -21766,8 +22913,16 @@
       <c r="ED97" s="6"/>
       <c r="EE97" s="6"/>
       <c r="EF97" s="6"/>
+      <c r="EG97" s="6"/>
+      <c r="EH97" s="6"/>
+      <c r="EI97" s="6"/>
+      <c r="EJ97" s="6"/>
+      <c r="EK97" s="6"/>
+      <c r="EL97" s="6"/>
+      <c r="EM97" s="6"/>
+      <c r="EN97" s="6"/>
     </row>
-    <row r="98" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -21904,8 +23059,16 @@
       <c r="ED98" s="6"/>
       <c r="EE98" s="6"/>
       <c r="EF98" s="6"/>
+      <c r="EG98" s="6"/>
+      <c r="EH98" s="6"/>
+      <c r="EI98" s="6"/>
+      <c r="EJ98" s="6"/>
+      <c r="EK98" s="6"/>
+      <c r="EL98" s="6"/>
+      <c r="EM98" s="6"/>
+      <c r="EN98" s="6"/>
     </row>
-    <row r="99" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -22042,8 +23205,16 @@
       <c r="ED99" s="6"/>
       <c r="EE99" s="6"/>
       <c r="EF99" s="6"/>
+      <c r="EG99" s="6"/>
+      <c r="EH99" s="6"/>
+      <c r="EI99" s="6"/>
+      <c r="EJ99" s="6"/>
+      <c r="EK99" s="6"/>
+      <c r="EL99" s="6"/>
+      <c r="EM99" s="6"/>
+      <c r="EN99" s="6"/>
     </row>
-    <row r="100" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -22180,8 +23351,16 @@
       <c r="ED100" s="6"/>
       <c r="EE100" s="6"/>
       <c r="EF100" s="6"/>
+      <c r="EG100" s="6"/>
+      <c r="EH100" s="6"/>
+      <c r="EI100" s="6"/>
+      <c r="EJ100" s="6"/>
+      <c r="EK100" s="6"/>
+      <c r="EL100" s="6"/>
+      <c r="EM100" s="6"/>
+      <c r="EN100" s="6"/>
     </row>
-    <row r="101" spans="1:136" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:144" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -22195,7 +23374,7 @@
       <c r="K101" s="4"/>
       <c r="L101" s="4"/>
     </row>
-    <row r="102" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A102" s="2"/>
       <c r="B102" s="3"/>
       <c r="C102" s="4"/>
@@ -22209,7 +23388,7 @@
       <c r="K102" s="4"/>
       <c r="L102" s="4"/>
     </row>
-    <row r="103" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A103" s="2"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -22223,7 +23402,7 @@
       <c r="K103" s="4"/>
       <c r="L103" s="4"/>
     </row>
-    <row r="104" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A104" s="2"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -22237,7 +23416,7 @@
       <c r="K104" s="4"/>
       <c r="L104" s="4"/>
     </row>
-    <row r="105" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A105" s="2"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -22251,7 +23430,7 @@
       <c r="K105" s="4"/>
       <c r="L105" s="4"/>
     </row>
-    <row r="106" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A106" s="2"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -22265,7 +23444,7 @@
       <c r="K106" s="4"/>
       <c r="L106" s="4"/>
     </row>
-    <row r="107" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A107" s="2"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -22279,7 +23458,7 @@
       <c r="K107" s="4"/>
       <c r="L107" s="4"/>
     </row>
-    <row r="108" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A108" s="2"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -22293,7 +23472,7 @@
       <c r="K108" s="4"/>
       <c r="L108" s="4"/>
     </row>
-    <row r="109" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A109" s="2"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -22307,7 +23486,7 @@
       <c r="K109" s="4"/>
       <c r="L109" s="4"/>
     </row>
-    <row r="110" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A110" s="2"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -22321,7 +23500,7 @@
       <c r="K110" s="4"/>
       <c r="L110" s="4"/>
     </row>
-    <row r="111" spans="1:136" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:144" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -22335,7 +23514,7 @@
       <c r="K111" s="4"/>
       <c r="L111" s="4"/>
     </row>
-    <row r="112" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:144" x14ac:dyDescent="0.3">
       <c r="A112" s="2"/>
       <c r="B112" s="3"/>
       <c r="C112" s="4"/>
@@ -22888,7 +24067,27 @@
       <c r="E151" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="340">
+  <mergeCells count="360">
+    <mergeCell ref="EG51:EJ60"/>
+    <mergeCell ref="EK51:EN60"/>
+    <mergeCell ref="EG61:EJ70"/>
+    <mergeCell ref="EK61:EN70"/>
+    <mergeCell ref="EG71:EJ80"/>
+    <mergeCell ref="EK71:EN80"/>
+    <mergeCell ref="EG81:EJ90"/>
+    <mergeCell ref="EK81:EN90"/>
+    <mergeCell ref="EG91:EJ100"/>
+    <mergeCell ref="EK91:EN100"/>
+    <mergeCell ref="EG1:EJ10"/>
+    <mergeCell ref="EK1:EN10"/>
+    <mergeCell ref="EG11:EJ20"/>
+    <mergeCell ref="EK11:EN20"/>
+    <mergeCell ref="EG21:EJ30"/>
+    <mergeCell ref="EK21:EN30"/>
+    <mergeCell ref="EG31:EJ40"/>
+    <mergeCell ref="EK31:EN40"/>
+    <mergeCell ref="EG41:EJ50"/>
+    <mergeCell ref="EK41:EN50"/>
     <mergeCell ref="DA51:DD60"/>
     <mergeCell ref="DE51:DH60"/>
     <mergeCell ref="DA61:DD70"/>
@@ -23231,7 +24430,7 @@
     <mergeCell ref="EC61:EF70"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.6692913385826772" right="0.6692913385826772" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>